--- a/off-hours/Off_Hours_Unit_Economics.xlsx
+++ b/off-hours/Off_Hours_Unit_Economics.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="220">
   <si>
     <t xml:space="preserve">Off Hours: Unit Economics Model</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">1. Change only the blue numbers on the Inputs tab. Yellow cells are the assumptions that move the result most.</t>
   </si>
   <si>
+    <t xml:space="preserve">B2B: set the share of members paid by employers (teams, clinics, hospitals) on Inputs. Employer seats are cheaper but used less, which lowers massage and coffee costs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. Unit Economics shows one location at steady state: monthly P&amp;L, break-even members, and capacity checks.</t>
   </si>
   <si>
@@ -136,6 +139,39 @@
     <t xml:space="preserve">Assumption: boutique fitness memberships commonly lose 3 to 5% a month</t>
   </si>
   <si>
+    <t xml:space="preserve">B2B: teams and healthcare (employer-paid seats)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of members paid for by an employer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption. 0% = consumer only. Employers sign annual contracts for seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer seat price per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: volume discount off the $150 consumer price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer seat usage vs a self-paying member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption. Employer-paid perks are used less: a UK study found ~24% of corporate gym memberships never used (4global DataHub, 2018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer seat churn per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: annual contracts churn far less than individual members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2B sales cost (% of employer revenue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: commission for a salesperson, broker, or benefits platform fee</t>
+  </si>
+  <si>
     <t xml:space="preserve">Member usage</t>
   </si>
   <si>
@@ -358,10 +394,25 @@
     <t xml:space="preserve">Per member</t>
   </si>
   <si>
+    <t xml:space="preserve">Total members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-paying members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer-paid seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active-member equivalents (employer seats count at their usage rate)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Membership revenue</t>
+    <t xml:space="preserve">Self-paying memberships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer seat contracts</t>
   </si>
   <si>
     <t xml:space="preserve">Add-on revenue</t>
@@ -373,7 +424,10 @@
     <t xml:space="preserve">Variable costs (scale with members)</t>
   </si>
   <si>
-    <t xml:space="preserve">Card fees</t>
+    <t xml:space="preserve">Card fees (self-paying members and add-ons; employers pay by bank transfer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2B sales cost</t>
   </si>
   <si>
     <t xml:space="preserve">Massage therapist labor</t>
@@ -427,16 +481,28 @@
     <t xml:space="preserve">Break-even</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue per member (after card fees)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massage labor per member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other variable cost per member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribution per member</t>
+    <t xml:space="preserve">Massage labor per active member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other variable cost per active member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution per self-paying member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution per employer seat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended contribution per member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended revenue per member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended variable cost per member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended monthly churn</t>
   </si>
   <si>
     <t xml:space="preserve">Fixed costs (rent counted as fixed lease)</t>
@@ -466,7 +532,7 @@
     <t xml:space="preserve">Massage rooms OK?</t>
   </si>
   <si>
-    <t xml:space="preserve">Max members the massage rooms can serve</t>
+    <t xml:space="preserve">Max active-member equivalents the massage rooms can serve</t>
   </si>
   <si>
     <t xml:space="preserve">Part-time therapists needed</t>
@@ -490,7 +556,7 @@
     <t xml:space="preserve">First location, month by month</t>
   </si>
   <si>
-    <t xml:space="preserve">Month 0 = opening costs. Members start at the opening-day number, add new members monthly, lose churn, and cap at steady state.</t>
+    <t xml:space="preserve">Month 0 = opening costs. Members start at the opening-day number, add new members monthly (self-paying + employer seats, same mix as Inputs), lose blended churn, and cap at steady state.</t>
   </si>
   <si>
     <t xml:space="preserve">Month</t>
@@ -532,18 +598,24 @@
     <t xml:space="preserve">Uses the fixed-lease rent and all other inputs from the Inputs tab. Green = profitable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 1: Members (down) x Monthly price (across). Massage minutes as on Inputs.</t>
+    <t xml:space="preserve">Table 1: Members (down) x Self-paying price (across). B2B mix, seat price and massage minutes as on Inputs.</t>
   </si>
   <si>
     <t xml:space="preserve">Members \ Price</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 2: Included massage minutes per month (down) x Monthly price (across). Members as on Inputs.</t>
+    <t xml:space="preserve">Table 2: Included massage minutes per month (down) x Self-paying price (across). Members and B2B mix as on Inputs.</t>
   </si>
   <si>
     <t xml:space="preserve">Massage min \ Price</t>
   </si>
   <si>
+    <t xml:space="preserve">Table 3: Share of members paid by employers (down) x Employer seat price (across). Members, consumer price and massage minutes as on Inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2B share \ Seat price</t>
+  </si>
+  <si>
     <t xml:space="preserve">Company view: multi-location rollout (annual)</t>
   </si>
   <si>
@@ -608,6 +680,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fabrik below-market flexible leases and Hines backing (CoStar): https://www.costar.com/article/1868835210/this-hines-backed-startup-offers-flexible-space-to-more-than-office-workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate membership usage benchmark: ~24% of employer-provided gym memberships never used (4global DataHub, UK, 2018). https://ukactive.com/news/new-research-explores-value-of-employer-provided-gym-memberships/</t>
   </si>
   <si>
     <t xml:space="preserve">Everything not listed above is a planning assumption, labeled on the Inputs tab. Replace with real quotes as you get them.</t>
@@ -617,7 +692,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -626,6 +701,7 @@
     <numFmt numFmtId="169" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="@"/>
+    <numFmt numFmtId="172" formatCode="0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -776,7 +852,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -869,6 +945,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -893,6 +973,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -902,10 +986,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -930,6 +1010,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1205,7 +1289,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="130"/>
@@ -1255,43 +1339,43 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
+      <c r="A16" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1303,6 +1387,11 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1321,7 +1410,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1332,7 +1421,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -1350,13 +1439,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -1372,7 +1461,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
@@ -1382,13 +1471,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>150</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -1396,13 +1485,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>15</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1410,13 +1499,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>0.03</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
@@ -1424,13 +1513,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>450</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -1438,13 +1527,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>100</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -1452,13 +1541,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>40</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -1466,13 +1555,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="17" t="n">
         <v>0.04</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -1488,7 +1577,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -1498,13 +1587,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>6</v>
+        <v>38</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>0.4</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -1512,13 +1601,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="18" t="n">
-        <v>1.5</v>
+        <v>40</v>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>125</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -1526,13 +1615,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="18" t="n">
-        <v>2.5</v>
+        <v>42</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>0.65</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -1540,13 +1629,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>14</v>
+        <v>44</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>0.015</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -1554,55 +1643,45 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>0.1</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>47</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>49</v>
-      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="B22" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1612,11 +1691,11 @@
       <c r="A23" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="19" t="n">
-        <v>1.1</v>
+      <c r="B23" s="18" t="n">
+        <v>1.5</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -1626,43 +1705,53 @@
       <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="19" t="n">
-        <v>0.75</v>
+      <c r="B24" s="18" t="n">
+        <v>2.5</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
+      <c r="A25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="A26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>38</v>
+        <v>58</v>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>60</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -1670,13 +1759,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>0.15</v>
+        <v>60</v>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>0.75</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -1684,13 +1773,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="17" t="n">
-        <v>0.75</v>
+        <v>62</v>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>1.2</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -1698,13 +1787,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>80</v>
+        <v>63</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>1.1</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -1712,59 +1801,59 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>4</v>
+        <v>64</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>0.75</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="14" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>33</v>
-      </c>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
+      <c r="A33" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="A34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="15" t="n">
-        <v>3000</v>
+        <v>68</v>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>0.15</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -1772,13 +1861,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="20" t="n">
-        <v>55</v>
+        <v>70</v>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>0.75</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -1786,13 +1875,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="21" t="n">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>80</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -1800,13 +1889,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="14" t="n">
-        <v>0.18</v>
+        <v>74</v>
+      </c>
+      <c r="B38" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -1814,13 +1903,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>45</v>
+        <v>75</v>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>0.65</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -1836,7 +1925,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -1846,13 +1935,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" s="13" t="n">
-        <v>80000</v>
+        <v>77</v>
+      </c>
+      <c r="B42" s="15" t="n">
+        <v>3000</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -1860,13 +1949,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" s="19" t="n">
-        <v>22</v>
+        <v>78</v>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>55</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -1874,13 +1963,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" s="18" t="n">
-        <v>1.25</v>
+        <v>80</v>
+      </c>
+      <c r="B44" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -1888,13 +1977,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>0.18</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -1902,13 +1991,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" s="13" t="n">
-        <v>125</v>
+        <v>83</v>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>45</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -1924,7 +2013,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
@@ -1934,13 +2023,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B49" s="13" t="n">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -1948,13 +2037,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" s="13" t="n">
-        <v>3000</v>
+        <v>86</v>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>22</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -1962,13 +2051,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B51" s="13" t="n">
-        <v>1000</v>
+        <v>87</v>
+      </c>
+      <c r="B51" s="18" t="n">
+        <v>1.25</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -1976,13 +2065,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="13" t="n">
-        <v>800</v>
+        <v>88</v>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>30</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -1990,73 +2079,73 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B53" s="13" t="n">
-        <v>4000</v>
+        <v>125</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B54" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>33</v>
-      </c>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>33</v>
-      </c>
+      <c r="A55" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
+      <c r="A56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
+      <c r="A57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B58" s="11" t="n">
-        <v>120</v>
+        <v>94</v>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>1000</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -2064,13 +2153,13 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B59" s="13" t="n">
-        <v>40</v>
+        <v>800</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -2078,13 +2167,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B60" s="13" t="n">
-        <v>90000</v>
+        <v>4000</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -2092,105 +2181,193 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B61" s="13" t="n">
-        <v>70000</v>
+        <v>1000</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
+      <c r="A62" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>700</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
       <c r="F63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D64" s="3" t="s">
+      <c r="A64" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="B65" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B65" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" s="16" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
+      <c r="B66" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B66" s="13" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C66" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D66" s="13" t="n">
-        <v>800000</v>
-      </c>
-      <c r="E66" s="13" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="F66" s="13" t="n">
-        <v>2200000</v>
-      </c>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
+      <c r="B67" s="13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>105</v>
+      </c>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B68" s="13" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B73" s="13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C73" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D73" s="13" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E73" s="13" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2208,7 +2385,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
@@ -2218,14 +2395,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -2237,18 +2414,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">Inputs!$B$9</f>
@@ -2257,296 +2434,303 @@
       <c r="C5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="23" t="n">
+        <f aca="false">$B$5*(1-Inputs!$B$15)</f>
+        <v>270</v>
+      </c>
       <c r="C6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>109</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <f aca="false">$B$5*Inputs!$B$15</f>
+        <v>180</v>
+      </c>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B8" s="23" t="n">
-        <f aca="false">$B$5*Inputs!$B$6</f>
-        <v>67500</v>
-      </c>
-      <c r="C8" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B8/$B$5)</f>
-        <v>150</v>
-      </c>
+        <f aca="false">$B$6+$B$7*Inputs!$B$17</f>
+        <v>387</v>
+      </c>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="23" t="n">
-        <f aca="false">$B$5*Inputs!$B$7</f>
-        <v>6750</v>
-      </c>
-      <c r="C9" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B9/$B$5)</f>
-        <v>15</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="25" t="n">
-        <f aca="false">$B$8+$B$9</f>
-        <v>74250</v>
-      </c>
-      <c r="C10" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B10/$B$5)</f>
-        <v>165</v>
+      <c r="A10" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
+      <c r="A11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <f aca="false">$B$6*Inputs!$B$6</f>
+        <v>40500</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B11/$B$5)</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>109</v>
+      <c r="A12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <f aca="false">$B$7*Inputs!$B$16</f>
+        <v>22500</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B12/$B$5)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="23" t="n">
-        <f aca="false">$B$10*Inputs!$B$8</f>
-        <v>2227.5</v>
-      </c>
-      <c r="C13" s="24" t="n">
+        <v>129</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <f aca="false">$B$8*Inputs!$B$7</f>
+        <v>5805</v>
+      </c>
+      <c r="C13" s="25" t="n">
         <f aca="false">IF($B$5=0,0,B13/$B$5)</f>
-        <v>4.95</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="23" t="n">
-        <f aca="false">$B$5*Inputs!$B$20/60*Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)</f>
-        <v>19665</v>
-      </c>
-      <c r="C14" s="24" t="n">
+      <c r="A14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="26" t="n">
+        <f aca="false">$B$11+$B$12+$B$13</f>
+        <v>68805</v>
+      </c>
+      <c r="C14" s="25" t="n">
         <f aca="false">IF($B$5=0,0,B14/$B$5)</f>
-        <v>43.7</v>
+        <v>152.9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="23" t="n">
-        <f aca="false">$B$5*Inputs!$B$15*Inputs!$B$22*Inputs!$B$23</f>
-        <v>3564</v>
-      </c>
-      <c r="C15" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B15/$B$5)</f>
-        <v>7.92</v>
-      </c>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B16" s="23" t="n">
-        <f aca="false">$B$5*Inputs!$B$15*Inputs!$B$24</f>
-        <v>2025</v>
-      </c>
-      <c r="C16" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B16/$B$5)</f>
-        <v>4.5</v>
+      <c r="A16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="25" t="n">
-        <f aca="false">SUM($B$13:$B$16)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="C17" s="24" t="n">
+      <c r="A17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <f aca="false">($B$11+$B$13)*Inputs!$B$8</f>
+        <v>1389.15</v>
+      </c>
+      <c r="C17" s="25" t="n">
         <f aca="false">IF($B$5=0,0,B17/$B$5)</f>
-        <v>61.07</v>
+        <v>3.087</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="25" t="n">
-        <f aca="false">$B$10-$B$17</f>
-        <v>46768.5</v>
-      </c>
-      <c r="C18" s="24" t="n">
+      <c r="A18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <f aca="false">$B$12*Inputs!$B$19</f>
+        <v>2250</v>
+      </c>
+      <c r="C18" s="25" t="n">
         <f aca="false">IF($B$5=0,0,B18/$B$5)</f>
-        <v>103.93</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
+      <c r="A19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <f aca="false">$B$8*Inputs!$B$27/60*Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)</f>
+        <v>16911.9</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B19/$B$5)</f>
+        <v>37.582</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>109</v>
+      <c r="A20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <f aca="false">$B$8*Inputs!$B$22*Inputs!$B$29*Inputs!$B$30</f>
+        <v>3065.04</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B20/$B$5)</f>
+        <v>6.8112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,$B$10*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+        <v>136</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <f aca="false">$B$8*Inputs!$B$22*Inputs!$B$31</f>
+        <v>1741.5</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B21/$B$5)</f>
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="26" t="n">
+        <f aca="false">SUM($B$17:$B$21)</f>
+        <v>25357.59</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B22/$B$5)</f>
+        <v>56.3502</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="26" t="n">
+        <f aca="false">$B$14-$B$22</f>
+        <v>43447.41</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B23/$B$5)</f>
+        <v>96.5498</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,$B$14*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="C21" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B21/$B$5)</f>
+      <c r="C26" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B26/$B$5)</f>
         <v>30.5555555555556</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B22" s="23" t="n">
-        <f aca="false">Inputs!$B$42*(1+Inputs!$B$28)/12</f>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <f aca="false">Inputs!$B$49*(1+Inputs!$B$35)/12</f>
         <v>7666.66666666667</v>
       </c>
-      <c r="C22" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B22/$B$5)</f>
+      <c r="C27" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B27/$B$5)</f>
         <v>17.037037037037</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" s="23" t="n">
-        <f aca="false">Inputs!$B$18*Inputs!$B$19*Inputs!$B$44*Inputs!$B$43*(1+Inputs!$B$28)</f>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <f aca="false">Inputs!$B$25*Inputs!$B$26*Inputs!$B$51*Inputs!$B$50*(1+Inputs!$B$35)</f>
         <v>13282.5</v>
       </c>
-      <c r="C23" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B23/$B$5)</f>
+      <c r="C28" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B28/$B$5)</f>
         <v>29.5166666666667</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B24" s="23" t="n">
-        <f aca="false">Inputs!$B$45*Inputs!$B$46</f>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <f aca="false">Inputs!$B$52*Inputs!$B$53</f>
         <v>3750</v>
       </c>
-      <c r="C24" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B24/$B$5)</f>
+      <c r="C29" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B29/$B$5)</f>
         <v>8.33333333333333</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="23" t="n">
-        <f aca="false">Inputs!$B$49+Inputs!$B$50+Inputs!$B$51+Inputs!$B$52+Inputs!$B$53+Inputs!$B$54+Inputs!$B$55</f>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <f aca="false">Inputs!$B$56+Inputs!$B$57+Inputs!$B$58+Inputs!$B$59+Inputs!$B$60+Inputs!$B$61+Inputs!$B$62</f>
         <v>13000</v>
       </c>
-      <c r="C25" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B25/$B$5)</f>
+      <c r="C30" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B30/$B$5)</f>
         <v>28.8888888888889</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="25" t="n">
-        <f aca="false">SUM($B$21:$B$25)</f>
-        <v>51449.1666666667</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B26/$B$5)</f>
-        <v>114.331481481481</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B29" s="25" t="n">
-        <f aca="false">$B$18-$B$26</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="C29" s="24" t="n">
-        <f aca="false">IF($B$5=0,0,B29/$B$5)</f>
-        <v>-10.4014814814815</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B30" s="26" t="n">
-        <f aca="false">IF($B$10=0,0,$B$29/$B$10)</f>
-        <v>-0.0630392817059483</v>
-      </c>
-      <c r="C30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="25" t="n">
-        <f aca="false">$B$29*12</f>
-        <v>-56168</v>
-      </c>
-      <c r="C31" s="7"/>
+        <v>145</v>
+      </c>
+      <c r="B31" s="26" t="n">
+        <f aca="false">SUM($B$26:$B$30)</f>
+        <v>51449.1666666667</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B31/$B$5)</f>
+        <v>114.331481481481</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
@@ -2555,246 +2739,335 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" s="27" t="n">
-        <f aca="false">(Inputs!$B$6+Inputs!$B$7)*(1-Inputs!$B$8)</f>
-        <v>160.05</v>
-      </c>
-      <c r="C34" s="7"/>
+      <c r="A34" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="26" t="n">
+        <f aca="false">$B$23-$B$31</f>
+        <v>-8001.75666666666</v>
+      </c>
+      <c r="C34" s="25" t="n">
+        <f aca="false">IF($B$5=0,0,B34/$B$5)</f>
+        <v>-17.7816814814815</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>134</v>
+      <c r="A35" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="B35" s="27" t="n">
-        <f aca="false">Inputs!$B$20/60*Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)</f>
+        <f aca="false">IF($B$14=0,0,$B$34/$B$14)</f>
+        <v>-0.116296150958021</v>
+      </c>
+      <c r="C35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="26" t="n">
+        <f aca="false">$B$34*12</f>
+        <v>-96021.0799999999</v>
+      </c>
+      <c r="C36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="28" t="n">
+        <f aca="false">Inputs!$B$27/60*Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)</f>
         <v>43.7</v>
       </c>
-      <c r="C35" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B36" s="27" t="n">
-        <f aca="false">Inputs!$B$15*(Inputs!$B$22*Inputs!$B$23+Inputs!$B$24)</f>
+      <c r="C39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="28" t="n">
+        <f aca="false">Inputs!$B$22*(Inputs!$B$29*Inputs!$B$30+Inputs!$B$31)</f>
         <v>12.42</v>
       </c>
-      <c r="C36" s="7"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B37" s="28" t="n">
-        <f aca="false">$B$34-$B$35-$B$36</f>
+      <c r="C40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="28" t="n">
+        <f aca="false">(Inputs!$B$6+Inputs!$B$7)*(1-Inputs!$B$8)-$B$39-$B$40</f>
         <v>103.93</v>
       </c>
-      <c r="C37" s="7"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B38" s="23" t="n">
-        <f aca="false">$B$26-$B$21+Inputs!$B$35*Inputs!$B$36/12</f>
-        <v>51449.1666666667</v>
-      </c>
-      <c r="C38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" s="29" t="n">
-        <f aca="false">IF($B$37&lt;=0,"Never",ROUNDUP($B$38/$B$37,0))</f>
-        <v>496</v>
-      </c>
-      <c r="C39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="29" t="n">
-        <f aca="false">IF($B$37-(Inputs!$B$6+Inputs!$B$7)*Inputs!$B$38&lt;=0,"Never",ROUNDUP(($B$38-Inputs!$B$35*Inputs!$B$36/12)/($B$37-(Inputs!$B$6+Inputs!$B$7)*Inputs!$B$38),0))</f>
-        <v>508</v>
-      </c>
-      <c r="C40" s="7"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
       <c r="C41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>109</v>
-      </c>
+      <c r="A42" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B42" s="28" t="n">
+        <f aca="false">Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$B$39-$B$40)</f>
+        <v>85.4795</v>
+      </c>
+      <c r="C42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B43" s="30" t="n">
-        <f aca="false">$B$5*Inputs!$B$15/Inputs!$B$19*Inputs!$B$16/Inputs!$B$18*Inputs!$B$17</f>
-        <v>24.1071428571429</v>
+      <c r="A43" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="29" t="n">
+        <f aca="false">(1-Inputs!$B$15)*$B$41+Inputs!$B$15*$B$42</f>
+        <v>96.5498</v>
       </c>
       <c r="C43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="22" t="n">
-        <f aca="false">Inputs!$B$39</f>
-        <v>45</v>
+        <v>156</v>
+      </c>
+      <c r="B44" s="28" t="n">
+        <f aca="false">(1-Inputs!$B$15)*(Inputs!$B$6+Inputs!$B$7)+Inputs!$B$15*(Inputs!$B$16+Inputs!$B$17*Inputs!$B$7)</f>
+        <v>152.9</v>
       </c>
       <c r="C44" s="7"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B45" s="31" t="str">
-        <f aca="false">IF($B$43&lt;=$B$44,"OK","Over capacity")</f>
-        <v>OK</v>
+      <c r="A45" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="28" t="n">
+        <f aca="false">$B$44-$B$43</f>
+        <v>56.3502</v>
       </c>
       <c r="C45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" s="32" t="n">
-        <f aca="false">$B$5*Inputs!$B$20/60*Inputs!$B$21</f>
-        <v>337.5</v>
+        <v>158</v>
+      </c>
+      <c r="B46" s="30" t="n">
+        <f aca="false">(1-Inputs!$B$15)*Inputs!$B$12+Inputs!$B$15*Inputs!$B$18</f>
+        <v>0.03</v>
       </c>
       <c r="C46" s="7"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B47" s="32" t="n">
-        <f aca="false">Inputs!$B$31*Inputs!$B$18*Inputs!$B$19*Inputs!$B$32</f>
-        <v>1092</v>
+        <v>159</v>
+      </c>
+      <c r="B47" s="24" t="n">
+        <f aca="false">$B$31-$B$26+Inputs!$B$42*Inputs!$B$43/12</f>
+        <v>51449.1666666667</v>
       </c>
       <c r="C47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B48" s="31" t="str">
-        <f aca="false">IF($B$46&lt;=$B$47,"OK","Need more rooms")</f>
-        <v>OK</v>
+        <v>160</v>
+      </c>
+      <c r="B48" s="31" t="n">
+        <f aca="false">IF($B$43&lt;=0,"Never",ROUNDUP($B$47/$B$43,0))</f>
+        <v>533</v>
       </c>
       <c r="C48" s="7"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B49" s="32" t="n">
-        <f aca="false">IF(Inputs!$B$20*Inputs!$B$21=0,0,ROUNDDOWN($B$47/(Inputs!$B$20/60*Inputs!$B$21),0))</f>
-        <v>1456</v>
+      <c r="A49" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49" s="31" t="n">
+        <f aca="false">IF($B$43-$B$44*Inputs!$B$45&lt;=0,"Never",ROUNDUP(($B$47-Inputs!$B$42*Inputs!$B$43/12)/($B$43-$B$44*Inputs!$B$45),0))</f>
+        <v>547</v>
       </c>
       <c r="C49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B50" s="32" t="n">
-        <f aca="false">ROUNDUP($B$46/Inputs!$B$29/Inputs!$B$30,0)</f>
-        <v>6</v>
-      </c>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
       <c r="C50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
+      <c r="A51" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>109</v>
-      </c>
+      <c r="A52" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B52" s="32" t="n">
+        <f aca="false">$B$8*Inputs!$B$22/Inputs!$B$26*Inputs!$B$23/Inputs!$B$25*Inputs!$B$24</f>
+        <v>20.7321428571429</v>
+      </c>
+      <c r="C52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B53" s="23" t="n">
-        <f aca="false">Inputs!$B$35*MAX(0,Inputs!$B$58-Inputs!$B$59)</f>
-        <v>240000</v>
+        <v>83</v>
+      </c>
+      <c r="B53" s="22" t="n">
+        <f aca="false">Inputs!$B$46</f>
+        <v>45</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B54" s="33" t="n">
-        <f aca="false">Inputs!$B$60</f>
-        <v>90000</v>
+      <c r="A54" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B54" s="33" t="str">
+        <f aca="false">IF($B$52&lt;=$B$53,"OK","Over capacity")</f>
+        <v>OK</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" s="33" t="n">
-        <f aca="false">Inputs!$B$61</f>
-        <v>70000</v>
+        <v>165</v>
+      </c>
+      <c r="B55" s="23" t="n">
+        <f aca="false">$B$8*Inputs!$B$27/60*Inputs!$B$28</f>
+        <v>290.25</v>
       </c>
       <c r="C55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B56" s="25" t="n">
-        <f aca="false">SUM($B$53:$B$55)</f>
-        <v>400000</v>
+      <c r="A56" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B56" s="23" t="n">
+        <f aca="false">Inputs!$B$38*Inputs!$B$25*Inputs!$B$26*Inputs!$B$39</f>
+        <v>1092</v>
       </c>
       <c r="C56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B57" s="34" t="str">
-        <f aca="false">IF($B$31&lt;=0,"Never",$B$56/$B$31)</f>
+        <v>167</v>
+      </c>
+      <c r="B57" s="33" t="str">
+        <f aca="false">IF($B$55&lt;=$B$56,"OK","Need more rooms")</f>
+        <v>OK</v>
+      </c>
+      <c r="C57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="23" t="n">
+        <f aca="false">IF(Inputs!$B$27*Inputs!$B$28=0,0,ROUNDDOWN($B$56/(Inputs!$B$27/60*Inputs!$B$28),0))</f>
+        <v>1456</v>
+      </c>
+      <c r="C58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" s="23" t="n">
+        <f aca="false">ROUNDUP($B$55/Inputs!$B$36/Inputs!$B$37,0)</f>
+        <v>5</v>
+      </c>
+      <c r="C59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" s="24" t="n">
+        <f aca="false">Inputs!$B$42*MAX(0,Inputs!$B$65-Inputs!$B$66)</f>
+        <v>240000</v>
+      </c>
+      <c r="C62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B63" s="34" t="n">
+        <f aca="false">Inputs!$B$67</f>
+        <v>90000</v>
+      </c>
+      <c r="C63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B64" s="34" t="n">
+        <f aca="false">Inputs!$B$68</f>
+        <v>70000</v>
+      </c>
+      <c r="C64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B65" s="26" t="n">
+        <f aca="false">SUM($B$62:$B$64)</f>
+        <v>400000</v>
+      </c>
+      <c r="C65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B66" s="35" t="str">
+        <f aca="false">IF($B$36&lt;=0,"Never",$B$65/$B$36)</f>
         <v>Never</v>
       </c>
-      <c r="C57" s="7"/>
+      <c r="C66" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2821,7 +3094,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -2863,7 +3136,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -2945,7 +3218,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="B4" s="9" t="n">
         <v>0</v>
@@ -3061,1485 +3334,1485 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="32" t="n">
+        <v>119</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="23" t="n">
         <f aca="false">Inputs!$B$10</f>
         <v>100</v>
       </c>
-      <c r="D5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,C5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>136</v>
-      </c>
-      <c r="E5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,D5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>170.56</v>
-      </c>
-      <c r="F5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,E5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>203.7376</v>
-      </c>
-      <c r="G5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,F5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>235.588096</v>
-      </c>
-      <c r="H5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,G5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>266.16457216</v>
-      </c>
-      <c r="I5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,H5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>295.5179892736</v>
-      </c>
-      <c r="J5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,I5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>323.697269702656</v>
-      </c>
-      <c r="K5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,J5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>350.74937891455</v>
-      </c>
-      <c r="L5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,K5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>376.719403757968</v>
-      </c>
-      <c r="M5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,L5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>401.650627607649</v>
-      </c>
-      <c r="N5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,M5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>425.584602503343</v>
-      </c>
-      <c r="O5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,N5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
-        <v>448.561218403209</v>
-      </c>
-      <c r="P5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,O5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="D5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,C5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>137</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,D5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>172.89</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,E5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>207.7033</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,F5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>241.472201</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,G5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>274.22803497</v>
+      </c>
+      <c r="I5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,H5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>306.0011939209</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,I5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>336.821158103273</v>
+      </c>
+      <c r="K5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,J5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>366.716523360175</v>
+      </c>
+      <c r="L5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,K5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>395.715027659369</v>
+      </c>
+      <c r="M5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,L5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>423.843576829588</v>
+      </c>
+      <c r="N5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,M5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="Q5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,P5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="O5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,N5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="R5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,Q5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="P5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,O5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="S5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,R5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="Q5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,P5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="T5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,S5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="R5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,Q5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="U5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,T5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="S5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,R5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="V5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,U5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="T5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,S5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="W5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,V5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="U5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,T5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="X5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,W5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="V5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,U5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="Y5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,X5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="W5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,V5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="Z5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,Y5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="X5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,W5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AA5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,Z5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="Y5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,X5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AB5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AA5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="Z5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,Y5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AC5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AB5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AA5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,Z5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AD5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AC5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AB5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AA5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AE5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AD5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AC5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AB5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AF5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AE5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AD5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AC5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AG5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AF5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AE5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AD5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AH5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AG5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AF5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AE5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AI5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AH5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AG5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AF5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AJ5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AI5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AH5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AG5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AK5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AJ5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AI5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AH5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AL5" s="32" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AK5*(1-Inputs!$B$12)+Inputs!$B$11)</f>
+      <c r="AJ5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AI5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>450</v>
+      </c>
+      <c r="AK5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AJ5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
+        <v>450</v>
+      </c>
+      <c r="AL5" s="23" t="n">
+        <f aca="false">MIN(Inputs!$B$9,AK5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="23" t="n">
+        <v>126</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">C5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>16500</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <f aca="false">D5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>22440</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">E5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>28142.4</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <f aca="false">F5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>33616.704</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <f aca="false">G5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>38872.03584</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <f aca="false">H5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>43917.1544064</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <f aca="false">I5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>48760.468230144</v>
-      </c>
-      <c r="J6" s="23" t="n">
-        <f aca="false">J5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>53410.0495009382</v>
-      </c>
-      <c r="K6" s="23" t="n">
-        <f aca="false">K5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>57873.6475209007</v>
-      </c>
-      <c r="L6" s="23" t="n">
-        <f aca="false">L5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>62158.7016200647</v>
-      </c>
-      <c r="M6" s="23" t="n">
-        <f aca="false">M5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>66272.3535552621</v>
-      </c>
-      <c r="N6" s="23" t="n">
-        <f aca="false">N5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>70221.4594130516</v>
-      </c>
-      <c r="O6" s="23" t="n">
-        <f aca="false">O5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74012.6010365295</v>
-      </c>
-      <c r="P6" s="23" t="n">
-        <f aca="false">P5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="Q6" s="23" t="n">
-        <f aca="false">Q5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="R6" s="23" t="n">
-        <f aca="false">R5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="S6" s="23" t="n">
-        <f aca="false">S5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="T6" s="23" t="n">
-        <f aca="false">T5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="U6" s="23" t="n">
-        <f aca="false">U5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="V6" s="23" t="n">
-        <f aca="false">V5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="W6" s="23" t="n">
-        <f aca="false">W5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="X6" s="23" t="n">
-        <f aca="false">X5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="Y6" s="23" t="n">
-        <f aca="false">Y5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="Z6" s="23" t="n">
-        <f aca="false">Z5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AA6" s="23" t="n">
-        <f aca="false">AA5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AB6" s="23" t="n">
-        <f aca="false">AB5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AC6" s="23" t="n">
-        <f aca="false">AC5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AD6" s="23" t="n">
-        <f aca="false">AD5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AE6" s="23" t="n">
-        <f aca="false">AE5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AF6" s="23" t="n">
-        <f aca="false">AF5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AG6" s="23" t="n">
-        <f aca="false">AG5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AH6" s="23" t="n">
-        <f aca="false">AH5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AI6" s="23" t="n">
-        <f aca="false">AI5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AJ6" s="23" t="n">
-        <f aca="false">AJ5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AK6" s="23" t="n">
-        <f aca="false">AK5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
-      </c>
-      <c r="AL6" s="23" t="n">
-        <f aca="false">AL5*(Inputs!$B$6+Inputs!$B$7)</f>
-        <v>74250</v>
+      <c r="C6" s="24" t="n">
+        <f aca="false">C5*'Unit Economics'!$B$44</f>
+        <v>15290</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <f aca="false">D5*'Unit Economics'!$B$44</f>
+        <v>20947.3</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <f aca="false">E5*'Unit Economics'!$B$44</f>
+        <v>26434.881</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <f aca="false">F5*'Unit Economics'!$B$44</f>
+        <v>31757.83457</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <f aca="false">G5*'Unit Economics'!$B$44</f>
+        <v>36921.0995329</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <f aca="false">H5*'Unit Economics'!$B$44</f>
+        <v>41929.466546913</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <f aca="false">I5*'Unit Economics'!$B$44</f>
+        <v>46787.5825505056</v>
+      </c>
+      <c r="J6" s="24" t="n">
+        <f aca="false">J5*'Unit Economics'!$B$44</f>
+        <v>51499.9550739904</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <f aca="false">K5*'Unit Economics'!$B$44</f>
+        <v>56070.9564217707</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <f aca="false">L5*'Unit Economics'!$B$44</f>
+        <v>60504.8277291176</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <f aca="false">M5*'Unit Economics'!$B$44</f>
+        <v>64805.6828972441</v>
+      </c>
+      <c r="N6" s="24" t="n">
+        <f aca="false">N5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="O6" s="24" t="n">
+        <f aca="false">O5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="P6" s="24" t="n">
+        <f aca="false">P5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="Q6" s="24" t="n">
+        <f aca="false">Q5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="R6" s="24" t="n">
+        <f aca="false">R5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="S6" s="24" t="n">
+        <f aca="false">S5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="T6" s="24" t="n">
+        <f aca="false">T5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="U6" s="24" t="n">
+        <f aca="false">U5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="V6" s="24" t="n">
+        <f aca="false">V5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="W6" s="24" t="n">
+        <f aca="false">W5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="X6" s="24" t="n">
+        <f aca="false">X5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="Y6" s="24" t="n">
+        <f aca="false">Y5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="Z6" s="24" t="n">
+        <f aca="false">Z5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AA6" s="24" t="n">
+        <f aca="false">AA5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AB6" s="24" t="n">
+        <f aca="false">AB5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AC6" s="24" t="n">
+        <f aca="false">AC5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AD6" s="24" t="n">
+        <f aca="false">AD5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AE6" s="24" t="n">
+        <f aca="false">AE5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AF6" s="24" t="n">
+        <f aca="false">AF5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AG6" s="24" t="n">
+        <f aca="false">AG5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AH6" s="24" t="n">
+        <f aca="false">AH5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AI6" s="24" t="n">
+        <f aca="false">AI5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AJ6" s="24" t="n">
+        <f aca="false">AJ5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AK6" s="24" t="n">
+        <f aca="false">AK5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
+      </c>
+      <c r="AL6" s="24" t="n">
+        <f aca="false">AL5*'Unit Economics'!$B$44</f>
+        <v>68805</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="23" t="n">
+        <v>178</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">C6*Inputs!$B$8+C5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>6107</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <f aca="false">D6*Inputs!$B$8+D5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>8305.52</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <f aca="false">E6*Inputs!$B$8+E5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>10416.0992</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <f aca="false">F6*Inputs!$B$8+F5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>12442.255232</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <f aca="false">G6*Inputs!$B$8+G5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>14387.36502272</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <f aca="false">H6*Inputs!$B$8+H5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>16254.6704218112</v>
-      </c>
-      <c r="I7" s="23" t="n">
-        <f aca="false">I6*Inputs!$B$8+I5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>18047.2836049387</v>
-      </c>
-      <c r="J7" s="23" t="n">
-        <f aca="false">J6*Inputs!$B$8+J5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>19768.1922607412</v>
-      </c>
-      <c r="K7" s="23" t="n">
-        <f aca="false">K6*Inputs!$B$8+K5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>21420.2645703116</v>
-      </c>
-      <c r="L7" s="23" t="n">
-        <f aca="false">L6*Inputs!$B$8+L5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>23006.2539874991</v>
-      </c>
-      <c r="M7" s="23" t="n">
-        <f aca="false">M6*Inputs!$B$8+M5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>24528.8038279991</v>
-      </c>
-      <c r="N7" s="23" t="n">
-        <f aca="false">N6*Inputs!$B$8+N5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>25990.4516748792</v>
-      </c>
-      <c r="O7" s="23" t="n">
-        <f aca="false">O6*Inputs!$B$8+O5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27393.633607884</v>
-      </c>
-      <c r="P7" s="23" t="n">
-        <f aca="false">P6*Inputs!$B$8+P5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="Q7" s="23" t="n">
-        <f aca="false">Q6*Inputs!$B$8+Q5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="R7" s="23" t="n">
-        <f aca="false">R6*Inputs!$B$8+R5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="S7" s="23" t="n">
-        <f aca="false">S6*Inputs!$B$8+S5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="T7" s="23" t="n">
-        <f aca="false">T6*Inputs!$B$8+T5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="U7" s="23" t="n">
-        <f aca="false">U6*Inputs!$B$8+U5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="V7" s="23" t="n">
-        <f aca="false">V6*Inputs!$B$8+V5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="W7" s="23" t="n">
-        <f aca="false">W6*Inputs!$B$8+W5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="X7" s="23" t="n">
-        <f aca="false">X6*Inputs!$B$8+X5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="Y7" s="23" t="n">
-        <f aca="false">Y6*Inputs!$B$8+Y5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="Z7" s="23" t="n">
-        <f aca="false">Z6*Inputs!$B$8+Z5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AA7" s="23" t="n">
-        <f aca="false">AA6*Inputs!$B$8+AA5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AB7" s="23" t="n">
-        <f aca="false">AB6*Inputs!$B$8+AB5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AC7" s="23" t="n">
-        <f aca="false">AC6*Inputs!$B$8+AC5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AD7" s="23" t="n">
-        <f aca="false">AD6*Inputs!$B$8+AD5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AE7" s="23" t="n">
-        <f aca="false">AE6*Inputs!$B$8+AE5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AF7" s="23" t="n">
-        <f aca="false">AF6*Inputs!$B$8+AF5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AG7" s="23" t="n">
-        <f aca="false">AG6*Inputs!$B$8+AG5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AH7" s="23" t="n">
-        <f aca="false">AH6*Inputs!$B$8+AH5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AI7" s="23" t="n">
-        <f aca="false">AI6*Inputs!$B$8+AI5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AJ7" s="23" t="n">
-        <f aca="false">AJ6*Inputs!$B$8+AJ5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AK7" s="23" t="n">
-        <f aca="false">AK6*Inputs!$B$8+AK5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
-      </c>
-      <c r="AL7" s="23" t="n">
-        <f aca="false">AL6*Inputs!$B$8+AL5*('Unit Economics'!$B$35+'Unit Economics'!$B$36)</f>
-        <v>27481.5</v>
+      <c r="C7" s="24" t="n">
+        <f aca="false">C5*'Unit Economics'!$B$45</f>
+        <v>5635.02</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <f aca="false">D5*'Unit Economics'!$B$45</f>
+        <v>7719.9774</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">E5*'Unit Economics'!$B$45</f>
+        <v>9742.386078</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <f aca="false">F5*'Unit Economics'!$B$45</f>
+        <v>11704.12249566</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <f aca="false">G5*'Unit Economics'!$B$45</f>
+        <v>13607.0068207902</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <f aca="false">H5*'Unit Economics'!$B$45</f>
+        <v>15452.8046161665</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <f aca="false">I5*'Unit Economics'!$B$45</f>
+        <v>17243.2284776815</v>
+      </c>
+      <c r="J7" s="24" t="n">
+        <f aca="false">J5*'Unit Economics'!$B$45</f>
+        <v>18979.9396233511</v>
+      </c>
+      <c r="K7" s="24" t="n">
+        <f aca="false">K5*'Unit Economics'!$B$45</f>
+        <v>20664.5494346505</v>
+      </c>
+      <c r="L7" s="24" t="n">
+        <f aca="false">L5*'Unit Economics'!$B$45</f>
+        <v>22298.620951611</v>
+      </c>
+      <c r="M7" s="24" t="n">
+        <f aca="false">M5*'Unit Economics'!$B$45</f>
+        <v>23883.6703230627</v>
+      </c>
+      <c r="N7" s="24" t="n">
+        <f aca="false">N5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="O7" s="24" t="n">
+        <f aca="false">O5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="P7" s="24" t="n">
+        <f aca="false">P5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="Q7" s="24" t="n">
+        <f aca="false">Q5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="R7" s="24" t="n">
+        <f aca="false">R5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="S7" s="24" t="n">
+        <f aca="false">S5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="T7" s="24" t="n">
+        <f aca="false">T5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="U7" s="24" t="n">
+        <f aca="false">U5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="V7" s="24" t="n">
+        <f aca="false">V5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="W7" s="24" t="n">
+        <f aca="false">W5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="X7" s="24" t="n">
+        <f aca="false">X5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="Y7" s="24" t="n">
+        <f aca="false">Y5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="Z7" s="24" t="n">
+        <f aca="false">Z5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AA7" s="24" t="n">
+        <f aca="false">AA5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AB7" s="24" t="n">
+        <f aca="false">AB5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AC7" s="24" t="n">
+        <f aca="false">AC5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AD7" s="24" t="n">
+        <f aca="false">AD5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AE7" s="24" t="n">
+        <f aca="false">AE5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AF7" s="24" t="n">
+        <f aca="false">AF5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AG7" s="24" t="n">
+        <f aca="false">AG5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <f aca="false">AH5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AI7" s="24" t="n">
+        <f aca="false">AI5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AJ7" s="24" t="n">
+        <f aca="false">AJ5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AK7" s="24" t="n">
+        <f aca="false">AK5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
+      </c>
+      <c r="AL7" s="24" t="n">
+        <f aca="false">AL5*'Unit Economics'!$B$45</f>
+        <v>25357.59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>140</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,C6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="C8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,C6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="D8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,D6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="D8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,D6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="E8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,E6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="E8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,E6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="F8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,F6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="F8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,F6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="G8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,G6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="G8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,G6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="H8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,H6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="H8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,H6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="I8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,I6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="I8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,I6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="J8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,J6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="J8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,J6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="K8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,K6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="K8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,K6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="L8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,L6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="L8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,L6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="M8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,M6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="M8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,M6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="N8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,N6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="N8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,N6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="O8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,O6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="O8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,O6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="P8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,P6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="P8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,P6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="Q8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,Q6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="Q8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,Q6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="R8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,R6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="R8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,R6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="S8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,S6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="S8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,S6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="T8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,T6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="T8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,T6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="U8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,U6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="U8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,U6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="V8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,V6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="V8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,V6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="W8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,W6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="W8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,W6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="X8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,X6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="X8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,X6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="Y8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,Y6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="Y8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,Y6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="Z8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,Z6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="Z8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,Z6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AA8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AA6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AA8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AA6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AB8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AB6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AB8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AB6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AC8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AC6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AC8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AC6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AD8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AD6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AD8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AD6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AE8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AE6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AE8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AE6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AF8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AF6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AF8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AF6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AG8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AG6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AG8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AG6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AH8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AH6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AH8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AH6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AI8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AI6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AI8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AI6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AJ8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AJ6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AJ8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AJ6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AK8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AK6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AK8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AK6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AL8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$37=2,AL6*Inputs!$B$38,Inputs!$B$35*Inputs!$B$36/12)</f>
+      <c r="AL8" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$44=2,AL6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B9" s="23" t="n">
+        <v>179</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="C9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="D9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="D9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="E9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="F9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="F9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="G9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="G9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="H9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="H9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="I9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="I9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="J9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="J9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="K9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="K9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="L9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="L9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="M9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="M9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="N9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="N9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="O9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="O9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="P9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="P9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="Q9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="Q9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="R9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="R9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="S9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="S9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="T9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="T9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="U9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="U9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="V9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="V9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="W9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="W9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="X9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="X9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="Y9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="Y9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="Z9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="Z9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AA9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AA9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AB9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AB9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AC9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AC9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AD9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AD9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AE9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AE9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AF9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AF9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AG9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AG9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AH9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AH9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AI9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AI9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AJ9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AJ9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AK9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AK9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AL9" s="23" t="n">
-        <f aca="false">('Unit Economics'!$B$26-'Unit Economics'!$B$21)</f>
+      <c r="AL9" s="24" t="n">
+        <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="25" t="n">
+        <v>180</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <f aca="false">C6-C7-C8-C9</f>
-        <v>-41056.1666666667</v>
-      </c>
-      <c r="D10" s="25" t="n">
+        <v>-41794.1866666667</v>
+      </c>
+      <c r="D10" s="26" t="n">
         <f aca="false">D6-D7-D8-D9</f>
-        <v>-37314.6866666667</v>
-      </c>
-      <c r="E10" s="25" t="n">
+        <v>-38221.8440666667</v>
+      </c>
+      <c r="E10" s="26" t="n">
         <f aca="false">E6-E7-E8-E9</f>
-        <v>-33722.8658666667</v>
-      </c>
-      <c r="F10" s="25" t="n">
+        <v>-34756.6717446667</v>
+      </c>
+      <c r="F10" s="26" t="n">
         <f aca="false">F6-F7-F8-F9</f>
-        <v>-30274.7178986667</v>
-      </c>
-      <c r="G10" s="25" t="n">
+        <v>-31395.4545923267</v>
+      </c>
+      <c r="G10" s="26" t="n">
         <f aca="false">G6-G7-G8-G9</f>
-        <v>-26964.4958493867</v>
-      </c>
-      <c r="H10" s="25" t="n">
+        <v>-28135.0739545569</v>
+      </c>
+      <c r="H10" s="26" t="n">
         <f aca="false">H6-H7-H8-H9</f>
-        <v>-23786.6826820779</v>
-      </c>
-      <c r="I10" s="25" t="n">
+        <v>-24972.5047359202</v>
+      </c>
+      <c r="I10" s="26" t="n">
         <f aca="false">I6-I7-I8-I9</f>
-        <v>-20735.9820414614</v>
-      </c>
-      <c r="J10" s="25" t="n">
+        <v>-21904.8125938426</v>
+      </c>
+      <c r="J10" s="26" t="n">
         <f aca="false">J6-J7-J8-J9</f>
-        <v>-17807.3094264696</v>
-      </c>
-      <c r="K10" s="25" t="n">
+        <v>-18929.1512160273</v>
+      </c>
+      <c r="K10" s="26" t="n">
         <f aca="false">K6-K7-K8-K9</f>
-        <v>-14995.7837160775</v>
-      </c>
-      <c r="L10" s="25" t="n">
+        <v>-16042.7596795465</v>
+      </c>
+      <c r="L10" s="26" t="n">
         <f aca="false">L6-L7-L8-L9</f>
-        <v>-12296.7190341011</v>
-      </c>
-      <c r="M10" s="25" t="n">
+        <v>-13242.9598891601</v>
+      </c>
+      <c r="M10" s="26" t="n">
         <f aca="false">M6-M7-M8-M9</f>
-        <v>-9705.61693940371</v>
-      </c>
-      <c r="N10" s="25" t="n">
+        <v>-10527.1540924853</v>
+      </c>
+      <c r="N10" s="26" t="n">
         <f aca="false">N6-N7-N8-N9</f>
-        <v>-7218.15892849422</v>
-      </c>
-      <c r="O10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="O10" s="26" t="n">
         <f aca="false">O6-O7-O8-O9</f>
-        <v>-4830.19923802113</v>
-      </c>
-      <c r="P10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="P10" s="26" t="n">
         <f aca="false">P6-P7-P8-P9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="Q10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="Q10" s="26" t="n">
         <f aca="false">Q6-Q7-Q8-Q9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="R10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="R10" s="26" t="n">
         <f aca="false">R6-R7-R8-R9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="S10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="S10" s="26" t="n">
         <f aca="false">S6-S7-S8-S9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="T10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="T10" s="26" t="n">
         <f aca="false">T6-T7-T8-T9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="U10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="U10" s="26" t="n">
         <f aca="false">U6-U7-U8-U9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="V10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="V10" s="26" t="n">
         <f aca="false">V6-V7-V8-V9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="W10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="W10" s="26" t="n">
         <f aca="false">W6-W7-W8-W9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="X10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="X10" s="26" t="n">
         <f aca="false">X6-X7-X8-X9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="Y10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="Y10" s="26" t="n">
         <f aca="false">Y6-Y7-Y8-Y9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="Z10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="Z10" s="26" t="n">
         <f aca="false">Z6-Z7-Z8-Z9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AA10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AA10" s="26" t="n">
         <f aca="false">AA6-AA7-AA8-AA9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AB10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AB10" s="26" t="n">
         <f aca="false">AB6-AB7-AB8-AB9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AC10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AC10" s="26" t="n">
         <f aca="false">AC6-AC7-AC8-AC9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AD10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AD10" s="26" t="n">
         <f aca="false">AD6-AD7-AD8-AD9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AE10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AE10" s="26" t="n">
         <f aca="false">AE6-AE7-AE8-AE9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AF10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AF10" s="26" t="n">
         <f aca="false">AF6-AF7-AF8-AF9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AG10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AG10" s="26" t="n">
         <f aca="false">AG6-AG7-AG8-AG9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AH10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AH10" s="26" t="n">
         <f aca="false">AH6-AH7-AH8-AH9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AI10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AI10" s="26" t="n">
         <f aca="false">AI6-AI7-AI8-AI9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AJ10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AJ10" s="26" t="n">
         <f aca="false">AJ6-AJ7-AJ8-AJ9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AK10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AK10" s="26" t="n">
         <f aca="false">AK6-AK7-AK8-AK9</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AL10" s="25" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AL10" s="26" t="n">
         <f aca="false">AL6-AL7-AL8-AL9</f>
-        <v>-4680.66666666666</v>
+        <v>-8001.75666666668</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="23" t="n">
-        <f aca="false">'Unit Economics'!$B$56</f>
+        <v>181</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <f aca="false">'Unit Economics'!$B$65</f>
         <v>400000</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="23" t="n">
+      <c r="H11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="23" t="n">
+      <c r="M11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="23" t="n">
+      <c r="N11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="23" t="n">
+      <c r="O11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="23" t="n">
+      <c r="P11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="23" t="n">
+      <c r="Q11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="23" t="n">
+      <c r="R11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="23" t="n">
+      <c r="S11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="23" t="n">
+      <c r="T11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="23" t="n">
+      <c r="U11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="23" t="n">
+      <c r="V11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="23" t="n">
+      <c r="W11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="23" t="n">
+      <c r="X11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" s="23" t="n">
+      <c r="Y11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="23" t="n">
+      <c r="Z11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AA11" s="23" t="n">
+      <c r="AA11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" s="23" t="n">
+      <c r="AB11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="23" t="n">
+      <c r="AC11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="23" t="n">
+      <c r="AD11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" s="23" t="n">
+      <c r="AE11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" s="23" t="n">
+      <c r="AF11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AG11" s="23" t="n">
+      <c r="AG11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" s="23" t="n">
+      <c r="AH11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="23" t="n">
+      <c r="AI11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" s="23" t="n">
+      <c r="AJ11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AK11" s="23" t="n">
+      <c r="AK11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="AL11" s="23" t="n">
+      <c r="AL11" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B12" s="23" t="n">
+        <v>182</v>
+      </c>
+      <c r="B12" s="24" t="n">
         <f aca="false">B10-B11</f>
         <v>-400000</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="24" t="n">
         <f aca="false">C10-C11</f>
-        <v>-41056.1666666667</v>
-      </c>
-      <c r="D12" s="23" t="n">
+        <v>-41794.1866666667</v>
+      </c>
+      <c r="D12" s="24" t="n">
         <f aca="false">D10-D11</f>
-        <v>-37314.6866666667</v>
-      </c>
-      <c r="E12" s="23" t="n">
+        <v>-38221.8440666667</v>
+      </c>
+      <c r="E12" s="24" t="n">
         <f aca="false">E10-E11</f>
-        <v>-33722.8658666667</v>
-      </c>
-      <c r="F12" s="23" t="n">
+        <v>-34756.6717446667</v>
+      </c>
+      <c r="F12" s="24" t="n">
         <f aca="false">F10-F11</f>
-        <v>-30274.7178986667</v>
-      </c>
-      <c r="G12" s="23" t="n">
+        <v>-31395.4545923267</v>
+      </c>
+      <c r="G12" s="24" t="n">
         <f aca="false">G10-G11</f>
-        <v>-26964.4958493867</v>
-      </c>
-      <c r="H12" s="23" t="n">
+        <v>-28135.0739545569</v>
+      </c>
+      <c r="H12" s="24" t="n">
         <f aca="false">H10-H11</f>
-        <v>-23786.6826820779</v>
-      </c>
-      <c r="I12" s="23" t="n">
+        <v>-24972.5047359202</v>
+      </c>
+      <c r="I12" s="24" t="n">
         <f aca="false">I10-I11</f>
-        <v>-20735.9820414614</v>
-      </c>
-      <c r="J12" s="23" t="n">
+        <v>-21904.8125938426</v>
+      </c>
+      <c r="J12" s="24" t="n">
         <f aca="false">J10-J11</f>
-        <v>-17807.3094264696</v>
-      </c>
-      <c r="K12" s="23" t="n">
+        <v>-18929.1512160273</v>
+      </c>
+      <c r="K12" s="24" t="n">
         <f aca="false">K10-K11</f>
-        <v>-14995.7837160775</v>
-      </c>
-      <c r="L12" s="23" t="n">
+        <v>-16042.7596795465</v>
+      </c>
+      <c r="L12" s="24" t="n">
         <f aca="false">L10-L11</f>
-        <v>-12296.7190341011</v>
-      </c>
-      <c r="M12" s="23" t="n">
+        <v>-13242.9598891601</v>
+      </c>
+      <c r="M12" s="24" t="n">
         <f aca="false">M10-M11</f>
-        <v>-9705.61693940371</v>
-      </c>
-      <c r="N12" s="23" t="n">
+        <v>-10527.1540924853</v>
+      </c>
+      <c r="N12" s="24" t="n">
         <f aca="false">N10-N11</f>
-        <v>-7218.15892849422</v>
-      </c>
-      <c r="O12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="O12" s="24" t="n">
         <f aca="false">O10-O11</f>
-        <v>-4830.19923802113</v>
-      </c>
-      <c r="P12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="P12" s="24" t="n">
         <f aca="false">P10-P11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="Q12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="Q12" s="24" t="n">
         <f aca="false">Q10-Q11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="R12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="R12" s="24" t="n">
         <f aca="false">R10-R11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="S12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="S12" s="24" t="n">
         <f aca="false">S10-S11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="T12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="T12" s="24" t="n">
         <f aca="false">T10-T11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="U12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="U12" s="24" t="n">
         <f aca="false">U10-U11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="V12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="V12" s="24" t="n">
         <f aca="false">V10-V11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="W12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="W12" s="24" t="n">
         <f aca="false">W10-W11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="X12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="X12" s="24" t="n">
         <f aca="false">X10-X11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="Y12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="Y12" s="24" t="n">
         <f aca="false">Y10-Y11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="Z12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="Z12" s="24" t="n">
         <f aca="false">Z10-Z11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AA12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AA12" s="24" t="n">
         <f aca="false">AA10-AA11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AB12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AB12" s="24" t="n">
         <f aca="false">AB10-AB11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AC12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AC12" s="24" t="n">
         <f aca="false">AC10-AC11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AD12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AD12" s="24" t="n">
         <f aca="false">AD10-AD11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AE12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AE12" s="24" t="n">
         <f aca="false">AE10-AE11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AF12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AF12" s="24" t="n">
         <f aca="false">AF10-AF11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AG12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AG12" s="24" t="n">
         <f aca="false">AG10-AG11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AH12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AH12" s="24" t="n">
         <f aca="false">AH10-AH11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AI12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AI12" s="24" t="n">
         <f aca="false">AI10-AI11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AJ12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AJ12" s="24" t="n">
         <f aca="false">AJ10-AJ11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AK12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AK12" s="24" t="n">
         <f aca="false">AK10-AK11</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="AL12" s="23" t="n">
+        <v>-8001.75666666668</v>
+      </c>
+      <c r="AL12" s="24" t="n">
         <f aca="false">AL10-AL11</f>
-        <v>-4680.66666666666</v>
+        <v>-8001.75666666668</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="25" t="n">
+        <v>183</v>
+      </c>
+      <c r="B13" s="26" t="n">
         <f aca="false">B12</f>
         <v>-400000</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <f aca="false">B13+C12</f>
-        <v>-441056.166666667</v>
-      </c>
-      <c r="D13" s="25" t="n">
+        <v>-441794.186666667</v>
+      </c>
+      <c r="D13" s="26" t="n">
         <f aca="false">C13+D12</f>
-        <v>-478370.853333333</v>
-      </c>
-      <c r="E13" s="25" t="n">
+        <v>-480016.030733333</v>
+      </c>
+      <c r="E13" s="26" t="n">
         <f aca="false">D13+E12</f>
-        <v>-512093.7192</v>
-      </c>
-      <c r="F13" s="25" t="n">
+        <v>-514772.702478</v>
+      </c>
+      <c r="F13" s="26" t="n">
         <f aca="false">E13+F12</f>
-        <v>-542368.437098667</v>
-      </c>
-      <c r="G13" s="25" t="n">
+        <v>-546168.157070327</v>
+      </c>
+      <c r="G13" s="26" t="n">
         <f aca="false">F13+G12</f>
-        <v>-569332.932948053</v>
-      </c>
-      <c r="H13" s="25" t="n">
+        <v>-574303.231024884</v>
+      </c>
+      <c r="H13" s="26" t="n">
         <f aca="false">G13+H12</f>
-        <v>-593119.615630131</v>
-      </c>
-      <c r="I13" s="25" t="n">
+        <v>-599275.735760804</v>
+      </c>
+      <c r="I13" s="26" t="n">
         <f aca="false">H13+I12</f>
-        <v>-613855.597671593</v>
-      </c>
-      <c r="J13" s="25" t="n">
+        <v>-621180.548354646</v>
+      </c>
+      <c r="J13" s="26" t="n">
         <f aca="false">I13+J12</f>
-        <v>-631662.907098062</v>
-      </c>
-      <c r="K13" s="25" t="n">
+        <v>-640109.699570673</v>
+      </c>
+      <c r="K13" s="26" t="n">
         <f aca="false">J13+K12</f>
-        <v>-646658.69081414</v>
-      </c>
-      <c r="L13" s="25" t="n">
+        <v>-656152.45925022</v>
+      </c>
+      <c r="L13" s="26" t="n">
         <f aca="false">K13+L12</f>
-        <v>-658955.409848241</v>
-      </c>
-      <c r="M13" s="25" t="n">
+        <v>-669395.41913938</v>
+      </c>
+      <c r="M13" s="26" t="n">
         <f aca="false">L13+M12</f>
-        <v>-668661.026787645</v>
-      </c>
-      <c r="N13" s="25" t="n">
+        <v>-679922.573231865</v>
+      </c>
+      <c r="N13" s="26" t="n">
         <f aca="false">M13+N12</f>
-        <v>-675879.185716139</v>
-      </c>
-      <c r="O13" s="25" t="n">
+        <v>-687924.329898532</v>
+      </c>
+      <c r="O13" s="26" t="n">
         <f aca="false">N13+O12</f>
-        <v>-680709.38495416</v>
-      </c>
-      <c r="P13" s="25" t="n">
+        <v>-695926.086565199</v>
+      </c>
+      <c r="P13" s="26" t="n">
         <f aca="false">O13+P12</f>
-        <v>-685390.051620827</v>
-      </c>
-      <c r="Q13" s="25" t="n">
+        <v>-703927.843231865</v>
+      </c>
+      <c r="Q13" s="26" t="n">
         <f aca="false">P13+Q12</f>
-        <v>-690070.718287493</v>
-      </c>
-      <c r="R13" s="25" t="n">
+        <v>-711929.599898532</v>
+      </c>
+      <c r="R13" s="26" t="n">
         <f aca="false">Q13+R12</f>
-        <v>-694751.38495416</v>
-      </c>
-      <c r="S13" s="25" t="n">
+        <v>-719931.356565199</v>
+      </c>
+      <c r="S13" s="26" t="n">
         <f aca="false">R13+S12</f>
-        <v>-699432.051620827</v>
-      </c>
-      <c r="T13" s="25" t="n">
+        <v>-727933.113231866</v>
+      </c>
+      <c r="T13" s="26" t="n">
         <f aca="false">S13+T12</f>
-        <v>-704112.718287493</v>
-      </c>
-      <c r="U13" s="25" t="n">
+        <v>-735934.869898532</v>
+      </c>
+      <c r="U13" s="26" t="n">
         <f aca="false">T13+U12</f>
-        <v>-708793.38495416</v>
-      </c>
-      <c r="V13" s="25" t="n">
+        <v>-743936.626565199</v>
+      </c>
+      <c r="V13" s="26" t="n">
         <f aca="false">U13+V12</f>
-        <v>-713474.051620826</v>
-      </c>
-      <c r="W13" s="25" t="n">
+        <v>-751938.383231866</v>
+      </c>
+      <c r="W13" s="26" t="n">
         <f aca="false">V13+W12</f>
-        <v>-718154.718287493</v>
-      </c>
-      <c r="X13" s="25" t="n">
+        <v>-759940.139898532</v>
+      </c>
+      <c r="X13" s="26" t="n">
         <f aca="false">W13+X12</f>
-        <v>-722835.38495416</v>
-      </c>
-      <c r="Y13" s="25" t="n">
+        <v>-767941.896565199</v>
+      </c>
+      <c r="Y13" s="26" t="n">
         <f aca="false">X13+Y12</f>
-        <v>-727516.051620826</v>
-      </c>
-      <c r="Z13" s="25" t="n">
+        <v>-775943.653231866</v>
+      </c>
+      <c r="Z13" s="26" t="n">
         <f aca="false">Y13+Z12</f>
-        <v>-732196.718287493</v>
-      </c>
-      <c r="AA13" s="25" t="n">
+        <v>-783945.409898533</v>
+      </c>
+      <c r="AA13" s="26" t="n">
         <f aca="false">Z13+AA12</f>
-        <v>-736877.38495416</v>
-      </c>
-      <c r="AB13" s="25" t="n">
+        <v>-791947.166565199</v>
+      </c>
+      <c r="AB13" s="26" t="n">
         <f aca="false">AA13+AB12</f>
-        <v>-741558.051620826</v>
-      </c>
-      <c r="AC13" s="25" t="n">
+        <v>-799948.923231866</v>
+      </c>
+      <c r="AC13" s="26" t="n">
         <f aca="false">AB13+AC12</f>
-        <v>-746238.718287493</v>
-      </c>
-      <c r="AD13" s="25" t="n">
+        <v>-807950.679898533</v>
+      </c>
+      <c r="AD13" s="26" t="n">
         <f aca="false">AC13+AD12</f>
-        <v>-750919.384954159</v>
-      </c>
-      <c r="AE13" s="25" t="n">
+        <v>-815952.436565199</v>
+      </c>
+      <c r="AE13" s="26" t="n">
         <f aca="false">AD13+AE12</f>
-        <v>-755600.051620826</v>
-      </c>
-      <c r="AF13" s="25" t="n">
+        <v>-823954.193231866</v>
+      </c>
+      <c r="AF13" s="26" t="n">
         <f aca="false">AE13+AF12</f>
-        <v>-760280.718287493</v>
-      </c>
-      <c r="AG13" s="25" t="n">
+        <v>-831955.949898533</v>
+      </c>
+      <c r="AG13" s="26" t="n">
         <f aca="false">AF13+AG12</f>
-        <v>-764961.384954159</v>
-      </c>
-      <c r="AH13" s="25" t="n">
+        <v>-839957.7065652</v>
+      </c>
+      <c r="AH13" s="26" t="n">
         <f aca="false">AG13+AH12</f>
-        <v>-769642.051620826</v>
-      </c>
-      <c r="AI13" s="25" t="n">
+        <v>-847959.463231866</v>
+      </c>
+      <c r="AI13" s="26" t="n">
         <f aca="false">AH13+AI12</f>
-        <v>-774322.718287493</v>
-      </c>
-      <c r="AJ13" s="25" t="n">
+        <v>-855961.219898533</v>
+      </c>
+      <c r="AJ13" s="26" t="n">
         <f aca="false">AI13+AJ12</f>
-        <v>-779003.384954159</v>
-      </c>
-      <c r="AK13" s="25" t="n">
+        <v>-863962.9765652</v>
+      </c>
+      <c r="AK13" s="26" t="n">
         <f aca="false">AJ13+AK12</f>
-        <v>-783684.051620826</v>
-      </c>
-      <c r="AL13" s="25" t="n">
+        <v>-871964.733231866</v>
+      </c>
+      <c r="AL13" s="26" t="n">
         <f aca="false">AK13+AL12</f>
-        <v>-788364.718287492</v>
+        <v>-879966.489898533</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35" t="str">
+        <v>184</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36" t="str">
         <f aca="false">IF(AND(C13&gt;=0,B13&lt;0),C4,"")</f>
         <v/>
       </c>
-      <c r="D14" s="35" t="str">
+      <c r="D14" s="36" t="str">
         <f aca="false">IF(AND(D13&gt;=0,C13&lt;0),D4,"")</f>
         <v/>
       </c>
-      <c r="E14" s="35" t="str">
+      <c r="E14" s="36" t="str">
         <f aca="false">IF(AND(E13&gt;=0,D13&lt;0),E4,"")</f>
         <v/>
       </c>
-      <c r="F14" s="35" t="str">
+      <c r="F14" s="36" t="str">
         <f aca="false">IF(AND(F13&gt;=0,E13&lt;0),F4,"")</f>
         <v/>
       </c>
-      <c r="G14" s="35" t="str">
+      <c r="G14" s="36" t="str">
         <f aca="false">IF(AND(G13&gt;=0,F13&lt;0),G4,"")</f>
         <v/>
       </c>
-      <c r="H14" s="35" t="str">
+      <c r="H14" s="36" t="str">
         <f aca="false">IF(AND(H13&gt;=0,G13&lt;0),H4,"")</f>
         <v/>
       </c>
-      <c r="I14" s="35" t="str">
+      <c r="I14" s="36" t="str">
         <f aca="false">IF(AND(I13&gt;=0,H13&lt;0),I4,"")</f>
         <v/>
       </c>
-      <c r="J14" s="35" t="str">
+      <c r="J14" s="36" t="str">
         <f aca="false">IF(AND(J13&gt;=0,I13&lt;0),J4,"")</f>
         <v/>
       </c>
-      <c r="K14" s="35" t="str">
+      <c r="K14" s="36" t="str">
         <f aca="false">IF(AND(K13&gt;=0,J13&lt;0),K4,"")</f>
         <v/>
       </c>
-      <c r="L14" s="35" t="str">
+      <c r="L14" s="36" t="str">
         <f aca="false">IF(AND(L13&gt;=0,K13&lt;0),L4,"")</f>
         <v/>
       </c>
-      <c r="M14" s="35" t="str">
+      <c r="M14" s="36" t="str">
         <f aca="false">IF(AND(M13&gt;=0,L13&lt;0),M4,"")</f>
         <v/>
       </c>
-      <c r="N14" s="35" t="str">
+      <c r="N14" s="36" t="str">
         <f aca="false">IF(AND(N13&gt;=0,M13&lt;0),N4,"")</f>
         <v/>
       </c>
-      <c r="O14" s="35" t="str">
+      <c r="O14" s="36" t="str">
         <f aca="false">IF(AND(O13&gt;=0,N13&lt;0),O4,"")</f>
         <v/>
       </c>
-      <c r="P14" s="35" t="str">
+      <c r="P14" s="36" t="str">
         <f aca="false">IF(AND(P13&gt;=0,O13&lt;0),P4,"")</f>
         <v/>
       </c>
-      <c r="Q14" s="35" t="str">
+      <c r="Q14" s="36" t="str">
         <f aca="false">IF(AND(Q13&gt;=0,P13&lt;0),Q4,"")</f>
         <v/>
       </c>
-      <c r="R14" s="35" t="str">
+      <c r="R14" s="36" t="str">
         <f aca="false">IF(AND(R13&gt;=0,Q13&lt;0),R4,"")</f>
         <v/>
       </c>
-      <c r="S14" s="35" t="str">
+      <c r="S14" s="36" t="str">
         <f aca="false">IF(AND(S13&gt;=0,R13&lt;0),S4,"")</f>
         <v/>
       </c>
-      <c r="T14" s="35" t="str">
+      <c r="T14" s="36" t="str">
         <f aca="false">IF(AND(T13&gt;=0,S13&lt;0),T4,"")</f>
         <v/>
       </c>
-      <c r="U14" s="35" t="str">
+      <c r="U14" s="36" t="str">
         <f aca="false">IF(AND(U13&gt;=0,T13&lt;0),U4,"")</f>
         <v/>
       </c>
-      <c r="V14" s="35" t="str">
+      <c r="V14" s="36" t="str">
         <f aca="false">IF(AND(V13&gt;=0,U13&lt;0),V4,"")</f>
         <v/>
       </c>
-      <c r="W14" s="35" t="str">
+      <c r="W14" s="36" t="str">
         <f aca="false">IF(AND(W13&gt;=0,V13&lt;0),W4,"")</f>
         <v/>
       </c>
-      <c r="X14" s="35" t="str">
+      <c r="X14" s="36" t="str">
         <f aca="false">IF(AND(X13&gt;=0,W13&lt;0),X4,"")</f>
         <v/>
       </c>
-      <c r="Y14" s="35" t="str">
+      <c r="Y14" s="36" t="str">
         <f aca="false">IF(AND(Y13&gt;=0,X13&lt;0),Y4,"")</f>
         <v/>
       </c>
-      <c r="Z14" s="35" t="str">
+      <c r="Z14" s="36" t="str">
         <f aca="false">IF(AND(Z13&gt;=0,Y13&lt;0),Z4,"")</f>
         <v/>
       </c>
-      <c r="AA14" s="35" t="str">
+      <c r="AA14" s="36" t="str">
         <f aca="false">IF(AND(AA13&gt;=0,Z13&lt;0),AA4,"")</f>
         <v/>
       </c>
-      <c r="AB14" s="35" t="str">
+      <c r="AB14" s="36" t="str">
         <f aca="false">IF(AND(AB13&gt;=0,AA13&lt;0),AB4,"")</f>
         <v/>
       </c>
-      <c r="AC14" s="35" t="str">
+      <c r="AC14" s="36" t="str">
         <f aca="false">IF(AND(AC13&gt;=0,AB13&lt;0),AC4,"")</f>
         <v/>
       </c>
-      <c r="AD14" s="35" t="str">
+      <c r="AD14" s="36" t="str">
         <f aca="false">IF(AND(AD13&gt;=0,AC13&lt;0),AD4,"")</f>
         <v/>
       </c>
-      <c r="AE14" s="35" t="str">
+      <c r="AE14" s="36" t="str">
         <f aca="false">IF(AND(AE13&gt;=0,AD13&lt;0),AE4,"")</f>
         <v/>
       </c>
-      <c r="AF14" s="35" t="str">
+      <c r="AF14" s="36" t="str">
         <f aca="false">IF(AND(AF13&gt;=0,AE13&lt;0),AF4,"")</f>
         <v/>
       </c>
-      <c r="AG14" s="35" t="str">
+      <c r="AG14" s="36" t="str">
         <f aca="false">IF(AND(AG13&gt;=0,AF13&lt;0),AG4,"")</f>
         <v/>
       </c>
-      <c r="AH14" s="35" t="str">
+      <c r="AH14" s="36" t="str">
         <f aca="false">IF(AND(AH13&gt;=0,AG13&lt;0),AH4,"")</f>
         <v/>
       </c>
-      <c r="AI14" s="35" t="str">
+      <c r="AI14" s="36" t="str">
         <f aca="false">IF(AND(AI13&gt;=0,AH13&lt;0),AI4,"")</f>
         <v/>
       </c>
-      <c r="AJ14" s="35" t="str">
+      <c r="AJ14" s="36" t="str">
         <f aca="false">IF(AND(AJ13&gt;=0,AI13&lt;0),AJ4,"")</f>
         <v/>
       </c>
-      <c r="AK14" s="35" t="str">
+      <c r="AK14" s="36" t="str">
         <f aca="false">IF(AND(AK13&gt;=0,AJ13&lt;0),AK4,"")</f>
         <v/>
       </c>
-      <c r="AL14" s="35" t="str">
+      <c r="AL14" s="36" t="str">
         <f aca="false">IF(AND(AL13&gt;=0,AK13&lt;0),AL4,"")</f>
         <v/>
       </c>
@@ -4586,7 +4859,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="B16" s="3" t="str">
         <f aca="false">IF(COUNT(C14:AL14)=0,"Beyond 36 months",MIN(C14:AL14))</f>
@@ -4631,11 +4904,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="25" t="n">
+        <v>186</v>
+      </c>
+      <c r="B17" s="26" t="n">
         <f aca="false">MIN(B13:AL13)</f>
-        <v>-788364.718287492</v>
+        <v>-879966.489898533</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -4676,11 +4949,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="25" t="n">
+        <v>187</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <f aca="false">AL13</f>
-        <v>-788364.718287492</v>
+        <v>-879966.489898533</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -4735,7 +5008,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -4744,7 +5017,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4754,7 +5027,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -4772,7 +5045,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -4782,247 +5055,247 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="36" t="n">
+        <v>191</v>
+      </c>
+      <c r="B5" s="37" t="n">
         <v>130</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="37" t="n">
         <v>150</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="37" t="n">
         <v>175</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="37" t="n">
         <v>195</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="37" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="n">
+      <c r="A6" s="38" t="n">
         <v>250</v>
       </c>
-      <c r="B6" s="23" t="n">
-        <f aca="false">$A6*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-30316.6666666667</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">$A6*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-25466.6666666667</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <f aca="false">$A6*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-19404.1666666667</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">$A6*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-14554.1666666667</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <f aca="false">$A6*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-7279.16666666666</v>
+      <c r="B6" s="24" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-30221.7166666667</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-27311.7166666667</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-23674.2166666667</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-20764.2166666667</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-16399.2166666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="38" t="n">
         <v>300</v>
       </c>
-      <c r="B7" s="23" t="n">
-        <f aca="false">$A7*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-26090.1666666667</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">$A7*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-20270.1666666667</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <f aca="false">$A7*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-12995.1666666667</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <f aca="false">$A7*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-7175.16666666667</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <f aca="false">$A7*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>1554.83333333334</v>
+      <c r="B7" s="24" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-25976.2266666667</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-22484.2266666667</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-18119.2266666667</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-14627.2266666667</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-9389.22666666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="38" t="n">
         <v>350</v>
       </c>
-      <c r="B8" s="23" t="n">
-        <f aca="false">$A8*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-21863.6666666667</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">$A8*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-15073.6666666667</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <f aca="false">$A8*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-6586.16666666666</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <f aca="false">$A8*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>203.833333333328</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <f aca="false">$A8*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>10388.8333333333</v>
+      <c r="B8" s="24" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-21730.7366666667</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-17656.7366666667</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-12564.2366666667</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-8490.23666666667</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-2379.23666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="38" t="n">
         <v>400</v>
       </c>
-      <c r="B9" s="23" t="n">
-        <f aca="false">$A9*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-17637.1666666667</v>
-      </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">$A9*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-9877.16666666666</v>
-      </c>
-      <c r="D9" s="23" t="n">
-        <f aca="false">$A9*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-177.166666666664</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">$A9*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>7582.83333333333</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <f aca="false">$A9*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>19222.8333333333</v>
+      <c r="B9" s="24" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-17485.2466666667</v>
+      </c>
+      <c r="C9" s="24" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-12829.2466666667</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-7009.24666666667</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-2353.24666666667</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>4630.75333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="38" t="n">
         <v>450</v>
       </c>
-      <c r="B10" s="23" t="n">
-        <f aca="false">$A10*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-13410.6666666667</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <f aca="false">$A10*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="D10" s="23" t="n">
-        <f aca="false">$A10*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>6231.83333333334</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <f aca="false">$A10*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>14961.8333333333</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <f aca="false">$A10*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>28056.8333333333</v>
+      <c r="B10" s="24" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-13239.7566666667</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-8001.75666666667</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-1454.25666666666</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>3783.74333333333</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>11640.7433333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="38" t="n">
         <v>500</v>
       </c>
-      <c r="B11" s="23" t="n">
-        <f aca="false">$A11*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-9184.16666666666</v>
-      </c>
-      <c r="C11" s="23" t="n">
-        <f aca="false">$A11*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>515.833333333329</v>
-      </c>
-      <c r="D11" s="23" t="n">
-        <f aca="false">$A11*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>12640.8333333333</v>
-      </c>
-      <c r="E11" s="23" t="n">
-        <f aca="false">$A11*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>22340.8333333333</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <f aca="false">$A11*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>36890.8333333333</v>
+      <c r="B11" s="24" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-8994.26666666666</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-3174.26666666667</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>4100.73333333334</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>9920.73333333333</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>18650.7333333333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="38" t="n">
         <v>550</v>
       </c>
-      <c r="B12" s="23" t="n">
-        <f aca="false">$A12*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-4957.66666666666</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <f aca="false">$A12*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>5712.33333333333</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <f aca="false">$A12*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>19049.8333333333</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <f aca="false">$A12*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>29719.8333333333</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <f aca="false">$A12*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>45724.8333333333</v>
+      <c r="B12" s="24" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-4748.77666666666</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>1653.22333333333</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>9655.72333333334</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>16057.7233333333</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>25660.7233333333</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="38" t="n">
         <v>600</v>
       </c>
-      <c r="B13" s="23" t="n">
-        <f aca="false">$A13*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-731.166666666657</v>
-      </c>
-      <c r="C13" s="23" t="n">
-        <f aca="false">$A13*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>10908.8333333333</v>
-      </c>
-      <c r="D13" s="23" t="n">
-        <f aca="false">$A13*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>25458.8333333333</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <f aca="false">$A13*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>37098.8333333333</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <f aca="false">$A13*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>54558.8333333333</v>
+      <c r="B13" s="24" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-503.286666666652</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>6480.71333333333</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>15210.7133333333</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>22194.7133333333</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>32670.7133333333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="38" t="n">
         <v>700</v>
       </c>
-      <c r="B14" s="23" t="n">
-        <f aca="false">$A14*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>7721.83333333334</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <f aca="false">$A14*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>21301.8333333333</v>
-      </c>
-      <c r="D14" s="23" t="n">
-        <f aca="false">$A14*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>38276.8333333333</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <f aca="false">$A14*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>51856.8333333333</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <f aca="false">$A14*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>72226.8333333333</v>
+      <c r="B14" s="24" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>7987.69333333335</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>16135.6933333333</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>26320.6933333333</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>34468.6933333333</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>46690.6933333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5043,7 +5316,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -5053,147 +5326,318 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="B18" s="36" t="n">
+        <v>193</v>
+      </c>
+      <c r="B18" s="37" t="n">
         <v>130</v>
       </c>
-      <c r="C18" s="36" t="n">
+      <c r="C18" s="37" t="n">
         <v>150</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="37" t="n">
         <v>175</v>
       </c>
-      <c r="E18" s="36" t="n">
+      <c r="E18" s="37" t="n">
         <v>195</v>
       </c>
-      <c r="F18" s="36" t="n">
+      <c r="F18" s="37" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="B19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>6254.33333333334</v>
-      </c>
-      <c r="C19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>14984.3333333333</v>
-      </c>
-      <c r="D19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>25896.8333333333</v>
-      </c>
-      <c r="E19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>34626.8333333333</v>
-      </c>
-      <c r="F19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>47721.8333333333</v>
+      <c r="B19" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>3672.14333333334</v>
+      </c>
+      <c r="C19" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>8910.14333333333</v>
+      </c>
+      <c r="D19" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>15457.6433333333</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>20695.6433333333</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>28552.6433333333</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="38" t="n">
+      <c r="A20" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="B20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-3578.16666666666</v>
-      </c>
-      <c r="C20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>5151.83333333333</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>16064.3333333333</v>
-      </c>
-      <c r="E20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>24794.3333333333</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>37889.3333333333</v>
+      <c r="B20" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-4783.80666666666</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>454.193333333336</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>7001.69333333333</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>12239.6933333333</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>20096.6933333333</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="38" t="n">
+      <c r="A21" s="39" t="n">
         <v>45</v>
       </c>
-      <c r="B21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-8494.41666666666</v>
-      </c>
-      <c r="C21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>235.583333333321</v>
-      </c>
-      <c r="D21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>11148.0833333333</v>
-      </c>
-      <c r="E21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>19878.0833333333</v>
-      </c>
-      <c r="F21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>32973.0833333333</v>
+      <c r="B21" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-9011.78166666667</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-3773.78166666668</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>2773.71833333333</v>
+      </c>
+      <c r="E21" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>8011.71833333334</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>15868.7183333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="39" t="n">
         <v>60</v>
       </c>
-      <c r="B22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-13410.6666666667</v>
-      </c>
-      <c r="C22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
+      <c r="B22" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-13239.7566666667</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-8001.75666666667</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-1454.25666666666</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>3783.74333333333</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>11640.7433333333</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="39" t="n">
+        <v>90</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-21695.7066666667</v>
+      </c>
+      <c r="C23" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-16457.7066666667</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-9910.20666666667</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-4672.20666666667</v>
+      </c>
+      <c r="F23" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>3184.79333333333</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B27" s="37" t="n">
+        <v>100</v>
+      </c>
+      <c r="C27" s="37" t="n">
+        <v>115</v>
+      </c>
+      <c r="D27" s="37" t="n">
+        <v>125</v>
+      </c>
+      <c r="E27" s="37" t="n">
+        <v>140</v>
+      </c>
+      <c r="F27" s="37" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4680.66666666666</v>
       </c>
-      <c r="D22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>6231.83333333334</v>
-      </c>
-      <c r="E22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>14961.8333333333</v>
-      </c>
-      <c r="F22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>28056.8333333333</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="n">
-        <v>90</v>
-      </c>
-      <c r="B23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-23243.1666666667</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-14513.1666666667</v>
-      </c>
-      <c r="D23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>-3600.66666666667</v>
-      </c>
-      <c r="E23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>5129.33333333332</v>
-      </c>
-      <c r="F23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$21/Inputs!$B$29*Inputs!$B$27*(1+Inputs!$B$28)/60)-'Unit Economics'!$B$36)-'Unit Economics'!$B$38</f>
-        <v>18224.3333333333</v>
+      <c r="C28" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-4680.66666666666</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-4680.66666666666</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-4680.66666666666</v>
+      </c>
+      <c r="F28" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-4680.66666666666</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-8366.21166666666</v>
+      </c>
+      <c r="C29" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-7151.21166666666</v>
+      </c>
+      <c r="D29" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-6341.21166666666</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-5126.21166666666</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-4316.21166666666</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-12051.7566666667</v>
+      </c>
+      <c r="C30" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-9621.75666666667</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-8001.75666666667</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-5571.75666666667</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-3951.75666666667</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B31" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-15737.3016666667</v>
+      </c>
+      <c r="C31" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-12092.3016666667</v>
+      </c>
+      <c r="D31" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-9662.30166666666</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-6017.30166666667</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-3587.30166666666</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B32" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-19422.8466666667</v>
+      </c>
+      <c r="C32" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-14562.8466666667</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-11322.8466666667</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-6462.84666666666</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>-3222.84666666666</v>
       </c>
     </row>
   </sheetData>
@@ -5210,6 +5654,14 @@
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:F32">
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5237,7 +5689,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5247,7 +5699,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5266,294 +5718,294 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8"/>
       <c r="B4" s="8" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="B5" s="22" t="n">
-        <f aca="false">Inputs!B65</f>
+        <f aca="false">Inputs!B72</f>
         <v>1</v>
       </c>
       <c r="C5" s="22" t="n">
-        <f aca="false">Inputs!C65</f>
+        <f aca="false">Inputs!C72</f>
         <v>1</v>
       </c>
       <c r="D5" s="22" t="n">
-        <f aca="false">Inputs!D65</f>
+        <f aca="false">Inputs!D72</f>
         <v>2</v>
       </c>
       <c r="E5" s="22" t="n">
-        <f aca="false">Inputs!E65</f>
+        <f aca="false">Inputs!E72</f>
         <v>4</v>
       </c>
       <c r="F5" s="22" t="n">
-        <f aca="false">Inputs!F65</f>
+        <f aca="false">Inputs!F72</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="32" t="n">
+        <v>199</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C6" s="32" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">B5</f>
         <v>1</v>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">C5</f>
         <v>1</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="23" t="n">
         <f aca="false">D5</f>
         <v>2</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">E5</f>
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="32" t="n">
+        <v>200</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">B7+B6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">C7+C6</f>
         <v>1</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">D7+D6</f>
         <v>2</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">E7+E6</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="32" t="n">
+        <v>201</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>1</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="23" t="n">
         <f aca="false">C5+C6+C7</f>
         <v>2</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">D5+D6+D7</f>
         <v>4</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">E5+E6+E7</f>
         <v>8</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">F5+F6+F7</f>
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="23" t="n">
+        <v>126</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C6:N6)+B6*SUM('36-Month Ramp'!O6:Z6)+B7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>542184.974086761</v>
-      </c>
-      <c r="C9" s="23" t="n">
+        <v>521754.586322441</v>
+      </c>
+      <c r="C9" s="24" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C6:N6)+C6*SUM('36-Month Ramp'!O6:Z6)+C7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>1432947.57512329</v>
-      </c>
-      <c r="D9" s="23" t="n">
+        <v>1347414.58632244</v>
+      </c>
+      <c r="D9" s="24" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C6:N6)+D6*SUM('36-Month Ramp'!O6:Z6)+D7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>2866132.54921005</v>
-      </c>
-      <c r="E9" s="23" t="n">
+        <v>2694829.17264488</v>
+      </c>
+      <c r="E9" s="24" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C6:N6)+E6*SUM('36-Month Ramp'!O6:Z6)+E7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>5732265.0984201</v>
-      </c>
-      <c r="F9" s="23" t="n">
+        <v>5389658.34528977</v>
+      </c>
+      <c r="F9" s="24" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C6:N6)+F6*SUM('36-Month Ramp'!O6:Z6)+F7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>10380160.2486667</v>
+        <v>9735807.51793465</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="23" t="n">
+        <v>202</v>
+      </c>
+      <c r="B10" s="24" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C10:N10)+B6*SUM('36-Month Ramp'!O10:Z10)+B7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-275879.185716139</v>
-      </c>
-      <c r="C10" s="23" t="n">
+        <v>-287924.329898532</v>
+      </c>
+      <c r="C10" s="24" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C10:N10)+C6*SUM('36-Month Ramp'!O10:Z10)+C7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-332196.718287493</v>
-      </c>
-      <c r="D10" s="23" t="n">
+        <v>-383945.409898532</v>
+      </c>
+      <c r="D10" s="24" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C10:N10)+D6*SUM('36-Month Ramp'!O10:Z10)+D7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-664243.904003632</v>
-      </c>
-      <c r="E10" s="23" t="n">
+        <v>-767890.819797064</v>
+      </c>
+      <c r="E10" s="24" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C10:N10)+E6*SUM('36-Month Ramp'!O10:Z10)+E7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-1328487.80800726</v>
-      </c>
-      <c r="F10" s="23" t="n">
+        <v>-1535781.63959413</v>
+      </c>
+      <c r="F10" s="24" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C10:N10)+F6*SUM('36-Month Ramp'!O10:Z10)+F7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-2105217.24458225</v>
+        <v>-2495714.61939119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" s="23" t="n">
-        <f aca="false">-Inputs!B66</f>
+        <v>203</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <f aca="false">-Inputs!B73</f>
         <v>-150000</v>
       </c>
-      <c r="C11" s="23" t="n">
-        <f aca="false">-Inputs!C66</f>
+      <c r="C11" s="24" t="n">
+        <f aca="false">-Inputs!C73</f>
         <v>-400000</v>
       </c>
-      <c r="D11" s="23" t="n">
-        <f aca="false">-Inputs!D66</f>
+      <c r="D11" s="24" t="n">
+        <f aca="false">-Inputs!D73</f>
         <v>-800000</v>
       </c>
-      <c r="E11" s="23" t="n">
-        <f aca="false">-Inputs!E66</f>
+      <c r="E11" s="24" t="n">
+        <f aca="false">-Inputs!E73</f>
         <v>-1400000</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <f aca="false">-Inputs!F66</f>
+      <c r="F11" s="24" t="n">
+        <f aca="false">-Inputs!F73</f>
         <v>-2200000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B12" s="25" t="n">
+        <v>204</v>
+      </c>
+      <c r="B12" s="26" t="n">
         <f aca="false">B10+B11</f>
-        <v>-425879.185716139</v>
-      </c>
-      <c r="C12" s="25" t="n">
+        <v>-437924.329898532</v>
+      </c>
+      <c r="C12" s="26" t="n">
         <f aca="false">C10+C11</f>
-        <v>-732196.718287493</v>
-      </c>
-      <c r="D12" s="25" t="n">
+        <v>-783945.409898532</v>
+      </c>
+      <c r="D12" s="26" t="n">
         <f aca="false">D10+D11</f>
-        <v>-1464243.90400363</v>
-      </c>
-      <c r="E12" s="25" t="n">
+        <v>-1567890.81979706</v>
+      </c>
+      <c r="E12" s="26" t="n">
         <f aca="false">E10+E11</f>
-        <v>-2728487.80800726</v>
-      </c>
-      <c r="F12" s="25" t="n">
+        <v>-2935781.63959413</v>
+      </c>
+      <c r="F12" s="26" t="n">
         <f aca="false">F10+F11</f>
-        <v>-4305217.24458225</v>
+        <v>-4695714.61939119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B13" s="23" t="n">
-        <f aca="false">-B5*'Unit Economics'!$B$56</f>
+        <v>205</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <f aca="false">-B5*'Unit Economics'!$B$65</f>
         <v>-400000</v>
       </c>
-      <c r="C13" s="23" t="n">
-        <f aca="false">-C5*'Unit Economics'!$B$56</f>
+      <c r="C13" s="24" t="n">
+        <f aca="false">-C5*'Unit Economics'!$B$65</f>
         <v>-400000</v>
       </c>
-      <c r="D13" s="23" t="n">
-        <f aca="false">-D5*'Unit Economics'!$B$56</f>
+      <c r="D13" s="24" t="n">
+        <f aca="false">-D5*'Unit Economics'!$B$65</f>
         <v>-800000</v>
       </c>
-      <c r="E13" s="23" t="n">
-        <f aca="false">-E5*'Unit Economics'!$B$56</f>
+      <c r="E13" s="24" t="n">
+        <f aca="false">-E5*'Unit Economics'!$B$65</f>
         <v>-1600000</v>
       </c>
-      <c r="F13" s="23" t="n">
-        <f aca="false">-F5*'Unit Economics'!$B$56</f>
+      <c r="F13" s="24" t="n">
+        <f aca="false">-F5*'Unit Economics'!$B$65</f>
         <v>-2400000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B14" s="23" t="n">
+        <v>206</v>
+      </c>
+      <c r="B14" s="24" t="n">
         <f aca="false">B12+B13</f>
-        <v>-825879.185716139</v>
-      </c>
-      <c r="C14" s="23" t="n">
+        <v>-837924.329898532</v>
+      </c>
+      <c r="C14" s="24" t="n">
         <f aca="false">C12+C13</f>
-        <v>-1132196.71828749</v>
-      </c>
-      <c r="D14" s="23" t="n">
+        <v>-1183945.40989853</v>
+      </c>
+      <c r="D14" s="24" t="n">
         <f aca="false">D12+D13</f>
-        <v>-2264243.90400363</v>
-      </c>
-      <c r="E14" s="23" t="n">
+        <v>-2367890.81979706</v>
+      </c>
+      <c r="E14" s="24" t="n">
         <f aca="false">E12+E13</f>
-        <v>-4328487.80800726</v>
-      </c>
-      <c r="F14" s="23" t="n">
+        <v>-4535781.63959413</v>
+      </c>
+      <c r="F14" s="24" t="n">
         <f aca="false">F12+F13</f>
-        <v>-6705217.24458225</v>
+        <v>-7095714.61939119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15" s="25" t="n">
+        <v>183</v>
+      </c>
+      <c r="B15" s="26" t="n">
         <f aca="false">B14</f>
-        <v>-825879.185716139</v>
-      </c>
-      <c r="C15" s="25" t="n">
+        <v>-837924.329898532</v>
+      </c>
+      <c r="C15" s="26" t="n">
         <f aca="false">B15+C14</f>
-        <v>-1958075.90400363</v>
-      </c>
-      <c r="D15" s="25" t="n">
+        <v>-2021869.73979706</v>
+      </c>
+      <c r="D15" s="26" t="n">
         <f aca="false">C15+D14</f>
-        <v>-4222319.80800726</v>
-      </c>
-      <c r="E15" s="25" t="n">
+        <v>-4389760.55959413</v>
+      </c>
+      <c r="E15" s="26" t="n">
         <f aca="false">D15+E14</f>
-        <v>-8550807.61601453</v>
-      </c>
-      <c r="F15" s="25" t="n">
+        <v>-8925542.19918826</v>
+      </c>
+      <c r="F15" s="26" t="n">
         <f aca="false">E15+F14</f>
-        <v>-15256024.8605968</v>
+        <v>-16021256.8185795</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5566,11 +6018,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B17" s="39" t="n">
+        <v>207</v>
+      </c>
+      <c r="B17" s="41" t="n">
         <f aca="false">-MIN(0,MIN(B15:F15))</f>
-        <v>15256024.8605968</v>
+        <v>16021256.8185795</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -5579,7 +6031,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -5603,7 +6055,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="150"/>
@@ -5611,7 +6063,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5619,50 +6071,55 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>194</v>
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/off-hours/Off_Hours_Unit_Economics.xlsx
+++ b/off-hours/Off_Hours_Unit_Economics.xlsx
@@ -14,7 +14,8 @@
     <sheet name="36-Month Ramp" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Sensitivity" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Rollout" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Sources &amp; Notes" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Funding Plan" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Sources &amp; Notes" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="261">
   <si>
     <t xml:space="preserve">Off Hours: Unit Economics Model</t>
   </si>
@@ -52,6 +53,9 @@
     <t xml:space="preserve">4. Sensitivity shows monthly profit across price, member count, and included massage minutes.</t>
   </si>
   <si>
+    <t xml:space="preserve">6. Funding Plan shows how much cash Location 1 needs and one way to stack your $50K, prepayments, an SBA loan and investors.</t>
+  </si>
+  <si>
     <t xml:space="preserve">5. Rollout shows the company view (many locations + HQ costs) and how much capital you would need to raise.</t>
   </si>
   <si>
@@ -655,6 +659,120 @@
     <t xml:space="preserve">Add a 20-30% buffer on top of this when deciding how much to raise.</t>
   </si>
   <si>
+    <t xml:space="preserve">Funding plan for Location 1 (sources and uses)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses pull from the model. Change the blue cells under Sources. Investors/angels is the plug: whatever is left to raise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses: what the money pays for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating losses until the location covers itself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest cumulative cash on the 36-Month Ramp, minus opening costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency (% of the above)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: buildouts almost always run over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total cash needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources: where the money comes from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your own cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding members who prepay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months each founding member prepays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: e.g. 3 months up front to lock founding status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founding member prepayments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash before opening. It is revenue pulled forward, so it lowers what you raise but you collect less later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companies that prepay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your target: 10 companies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seats per company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months each company prepays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: quarterly in advance; some will pay annually</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer prepayments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA 7(a) loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption. Requires a personal guarantee and at least 10% equity injection for a startup (SOP 50 10 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investors / angels / friends and family (left to raise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typically raised on a SAFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity (you + investors) as % of total cash needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA lenders want at least 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meets the 10% SBA minimum?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA loan interest rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: prime plus a spread; get a lender quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan term (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual loan payments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt coverage (steady-state profit / loan payments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenders usually want 1.25x or more</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sources and notes</t>
   </si>
   <si>
@@ -683,6 +801,12 @@
   </si>
   <si>
     <t xml:space="preserve">Corporate membership usage benchmark: ~24% of employer-provided gym memberships never used (4global DataHub, UK, 2018). https://ukactive.com/news/new-research-explores-value-of-employer-provided-gym-memberships/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBA 7(a) 10% equity injection for startups under SOP 50 10 8 (secondary summary; confirm with a lender): https://beancount.io/blog/2026/07/29/sba-sop-50-10-8-collateral-equity-injection-rules-guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA chair-massage exemption from establishment licensure, 269 CMR 6.03(8): https://www.law.cornell.edu/regulations/massachusetts/269-CMR-6-03</t>
   </si>
   <si>
     <t xml:space="preserve">Everything not listed above is a planning assumption, labeled on the Inputs tab. Replace with real quotes as you get them.</t>
@@ -692,7 +816,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -702,6 +826,7 @@
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="@"/>
     <numFmt numFmtId="172" formatCode="0%"/>
+    <numFmt numFmtId="173" formatCode="0.00\x"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -852,7 +977,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -873,11 +998,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1018,6 +1139,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1289,7 +1418,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="130"/>
@@ -1344,43 +1473,43 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="A18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1392,6 +1521,11 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1421,953 +1555,953 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+        <v>19</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="C3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="A5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="C7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="C8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B9" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="B10" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="B11" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="C11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="B12" s="16" t="n">
         <v>0.04</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="C12" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="B15" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="C15" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="B16" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="C16" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="B17" s="16" t="n">
         <v>0.65</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="C17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B18" s="13" t="n">
         <v>0.015</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="C18" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="B19" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="C19" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="A21" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="B22" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="B23" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="C23" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="B24" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="C24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="B25" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="C25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="B26" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="C26" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="B27" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="C27" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="B28" s="16" t="n">
         <v>0.75</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="C28" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="B29" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="C29" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="19" t="n">
+        <v>64</v>
+      </c>
+      <c r="B30" s="18" t="n">
         <v>1.1</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="C30" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="B31" s="18" t="n">
         <v>0.75</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="C31" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="A33" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="B34" s="19" t="n">
         <v>38</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="C34" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="B35" s="13" t="n">
         <v>0.15</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="C35" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="B36" s="16" t="n">
         <v>0.75</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="C36" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="B37" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="C37" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="B38" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
+      <c r="C38" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="B39" s="13" t="n">
         <v>0.65</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
+      <c r="C39" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
+      <c r="A41" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="B42" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
+      <c r="C42" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" s="20" t="n">
+        <v>79</v>
+      </c>
+      <c r="B43" s="19" t="n">
         <v>55</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
+      <c r="C43" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" s="21" t="n">
+        <v>81</v>
+      </c>
+      <c r="B44" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="C44" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="B45" s="13" t="n">
         <v>0.18</v>
       </c>
-      <c r="C45" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
+      <c r="C45" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B46" s="16" t="n">
+        <v>84</v>
+      </c>
+      <c r="B46" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
+      <c r="C46" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
+      <c r="A48" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B49" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B49" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="C49" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
+      <c r="C49" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B50" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="B50" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
+      <c r="C50" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B51" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="B51" s="17" t="n">
         <v>1.25</v>
       </c>
-      <c r="C51" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
+      <c r="C51" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B52" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="B52" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C52" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="C52" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B53" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B53" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
+      <c r="C53" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
+      <c r="A55" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="B56" s="12" t="n">
         <v>2500</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
+      <c r="C56" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B57" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="B57" s="12" t="n">
         <v>3000</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
+      <c r="C57" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B58" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="B58" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
+      <c r="C58" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B59" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="B59" s="12" t="n">
         <v>800</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
+      <c r="C59" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B60" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="B60" s="12" t="n">
         <v>4000</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
+      <c r="C60" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B61" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B61" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
+      <c r="C61" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B62" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="B62" s="12" t="n">
         <v>700</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
+      <c r="C62" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
+      <c r="A64" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="B65" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="C65" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
+      <c r="C65" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B66" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="B66" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
+      <c r="C66" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="B67" s="12" t="n">
         <v>90000</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
+      <c r="C67" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B68" s="13" t="n">
+        <v>107</v>
+      </c>
+      <c r="B68" s="12" t="n">
         <v>70000</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
+      <c r="C68" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
+      <c r="A70" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B72" s="16" t="n">
+      <c r="A72" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B72" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="16" t="n">
+      <c r="C72" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E72" s="16" t="n">
+      <c r="E72" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="16" t="n">
+      <c r="F72" s="15" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B73" s="13" t="n">
+      <c r="A73" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="C73" s="13" t="n">
+      <c r="C73" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="12" t="n">
         <v>800000</v>
       </c>
-      <c r="E73" s="13" t="n">
+      <c r="E73" s="12" t="n">
         <v>1400000</v>
       </c>
-      <c r="F73" s="13" t="n">
+      <c r="F73" s="12" t="n">
         <v>2200000</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
+      <c r="A74" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2395,679 +2529,679 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+        <v>118</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="A2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="22" t="n">
+        <v>123</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <f aca="false">Inputs!$B$9</f>
         <v>450</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B6" s="23" t="n">
+        <v>124</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">$B$5*(1-Inputs!$B$15)</f>
         <v>270</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="23" t="n">
+        <v>125</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <f aca="false">$B$5*Inputs!$B$15</f>
         <v>180</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>126</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <f aca="false">$B$6+$B$7*Inputs!$B$17</f>
         <v>387</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="24" t="n">
+        <v>128</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <f aca="false">$B$6*Inputs!$B$6</f>
         <v>40500</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B11/$B$5)</f>
         <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B12" s="24" t="n">
+        <v>129</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <f aca="false">$B$7*Inputs!$B$16</f>
         <v>22500</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B12/$B$5)</f>
         <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="B13" s="23" t="n">
         <f aca="false">$B$8*Inputs!$B$7</f>
         <v>5805</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B13/$B$5)</f>
         <v>12.9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="26" t="n">
+        <v>131</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <f aca="false">$B$11+$B$12+$B$13</f>
         <v>68805</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B14/$B$5)</f>
         <v>152.9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="A16" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="24" t="n">
+        <v>133</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">($B$11+$B$13)*Inputs!$B$8</f>
         <v>1389.15</v>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B17/$B$5)</f>
         <v>3.087</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="24" t="n">
+        <v>134</v>
+      </c>
+      <c r="B18" s="23" t="n">
         <f aca="false">$B$12*Inputs!$B$19</f>
         <v>2250</v>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B18/$B$5)</f>
         <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="24" t="n">
+        <v>135</v>
+      </c>
+      <c r="B19" s="23" t="n">
         <f aca="false">$B$8*Inputs!$B$27/60*Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)</f>
         <v>16911.9</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B19/$B$5)</f>
         <v>37.582</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="24" t="n">
+        <v>136</v>
+      </c>
+      <c r="B20" s="23" t="n">
         <f aca="false">$B$8*Inputs!$B$22*Inputs!$B$29*Inputs!$B$30</f>
         <v>3065.04</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B20/$B$5)</f>
         <v>6.8112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="24" t="n">
+        <v>137</v>
+      </c>
+      <c r="B21" s="23" t="n">
         <f aca="false">$B$8*Inputs!$B$22*Inputs!$B$31</f>
         <v>1741.5</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B21/$B$5)</f>
         <v>3.87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <f aca="false">SUM($B$17:$B$21)</f>
         <v>25357.59</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B22/$B$5)</f>
         <v>56.3502</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="26" t="n">
+        <v>139</v>
+      </c>
+      <c r="B23" s="25" t="n">
         <f aca="false">$B$14-$B$22</f>
         <v>43447.41</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B23/$B$5)</f>
         <v>96.5498</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="A25" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="24" t="n">
+        <v>141</v>
+      </c>
+      <c r="B26" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,$B$14*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B26/$B$5)</f>
         <v>30.5555555555556</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B27" s="24" t="n">
+        <v>142</v>
+      </c>
+      <c r="B27" s="23" t="n">
         <f aca="false">Inputs!$B$49*(1+Inputs!$B$35)/12</f>
         <v>7666.66666666667</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B27/$B$5)</f>
         <v>17.037037037037</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B28" s="24" t="n">
+        <v>143</v>
+      </c>
+      <c r="B28" s="23" t="n">
         <f aca="false">Inputs!$B$25*Inputs!$B$26*Inputs!$B$51*Inputs!$B$50*(1+Inputs!$B$35)</f>
         <v>13282.5</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B28/$B$5)</f>
         <v>29.5166666666667</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="24" t="n">
+        <v>144</v>
+      </c>
+      <c r="B29" s="23" t="n">
         <f aca="false">Inputs!$B$52*Inputs!$B$53</f>
         <v>3750</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B29/$B$5)</f>
         <v>8.33333333333333</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B30" s="24" t="n">
+        <v>145</v>
+      </c>
+      <c r="B30" s="23" t="n">
         <f aca="false">Inputs!$B$56+Inputs!$B$57+Inputs!$B$58+Inputs!$B$59+Inputs!$B$60+Inputs!$B$61+Inputs!$B$62</f>
         <v>13000</v>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B30/$B$5)</f>
         <v>28.8888888888889</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B31" s="26" t="n">
+        <v>146</v>
+      </c>
+      <c r="B31" s="25" t="n">
         <f aca="false">SUM($B$26:$B$30)</f>
         <v>51449.1666666667</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B31/$B$5)</f>
         <v>114.331481481481</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="8" t="s">
+      <c r="A33" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B34" s="26" t="n">
+        <v>148</v>
+      </c>
+      <c r="B34" s="25" t="n">
         <f aca="false">$B$23-$B$31</f>
         <v>-8001.75666666666</v>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="24" t="n">
         <f aca="false">IF($B$5=0,0,B34/$B$5)</f>
         <v>-17.7816814814815</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B35" s="27" t="n">
+        <v>149</v>
+      </c>
+      <c r="B35" s="26" t="n">
         <f aca="false">IF($B$14=0,0,$B$34/$B$14)</f>
         <v>-0.116296150958021</v>
       </c>
-      <c r="C35" s="7"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="B36" s="25" t="n">
         <f aca="false">$B$34*12</f>
         <v>-96021.0799999999</v>
       </c>
-      <c r="C36" s="7"/>
+      <c r="C36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" s="8" t="s">
+      <c r="A38" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B39" s="28" t="n">
+        <v>152</v>
+      </c>
+      <c r="B39" s="27" t="n">
         <f aca="false">Inputs!$B$27/60*Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)</f>
         <v>43.7</v>
       </c>
-      <c r="C39" s="7"/>
+      <c r="C39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B40" s="28" t="n">
+        <v>153</v>
+      </c>
+      <c r="B40" s="27" t="n">
         <f aca="false">Inputs!$B$22*(Inputs!$B$29*Inputs!$B$30+Inputs!$B$31)</f>
         <v>12.42</v>
       </c>
-      <c r="C40" s="7"/>
+      <c r="C40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="28" t="n">
+        <v>154</v>
+      </c>
+      <c r="B41" s="27" t="n">
         <f aca="false">(Inputs!$B$6+Inputs!$B$7)*(1-Inputs!$B$8)-$B$39-$B$40</f>
         <v>103.93</v>
       </c>
-      <c r="C41" s="7"/>
+      <c r="C41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B42" s="28" t="n">
+        <v>155</v>
+      </c>
+      <c r="B42" s="27" t="n">
         <f aca="false">Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$B$39-$B$40)</f>
         <v>85.4795</v>
       </c>
-      <c r="C42" s="7"/>
+      <c r="C42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B43" s="29" t="n">
+        <v>156</v>
+      </c>
+      <c r="B43" s="28" t="n">
         <f aca="false">(1-Inputs!$B$15)*$B$41+Inputs!$B$15*$B$42</f>
         <v>96.5498</v>
       </c>
-      <c r="C43" s="7"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B44" s="28" t="n">
+        <v>157</v>
+      </c>
+      <c r="B44" s="27" t="n">
         <f aca="false">(1-Inputs!$B$15)*(Inputs!$B$6+Inputs!$B$7)+Inputs!$B$15*(Inputs!$B$16+Inputs!$B$17*Inputs!$B$7)</f>
         <v>152.9</v>
       </c>
-      <c r="C44" s="7"/>
+      <c r="C44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B45" s="28" t="n">
+        <v>158</v>
+      </c>
+      <c r="B45" s="27" t="n">
         <f aca="false">$B$44-$B$43</f>
         <v>56.3502</v>
       </c>
-      <c r="C45" s="7"/>
+      <c r="C45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B46" s="30" t="n">
+        <v>159</v>
+      </c>
+      <c r="B46" s="29" t="n">
         <f aca="false">(1-Inputs!$B$15)*Inputs!$B$12+Inputs!$B$15*Inputs!$B$18</f>
         <v>0.03</v>
       </c>
-      <c r="C46" s="7"/>
+      <c r="C46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B47" s="24" t="n">
+        <v>160</v>
+      </c>
+      <c r="B47" s="23" t="n">
         <f aca="false">$B$31-$B$26+Inputs!$B$42*Inputs!$B$43/12</f>
         <v>51449.1666666667</v>
       </c>
-      <c r="C47" s="7"/>
+      <c r="C47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B48" s="31" t="n">
+        <v>161</v>
+      </c>
+      <c r="B48" s="30" t="n">
         <f aca="false">IF($B$43&lt;=0,"Never",ROUNDUP($B$47/$B$43,0))</f>
         <v>533</v>
       </c>
-      <c r="C48" s="7"/>
+      <c r="C48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B49" s="31" t="n">
+        <v>162</v>
+      </c>
+      <c r="B49" s="30" t="n">
         <f aca="false">IF($B$43-$B$44*Inputs!$B$45&lt;=0,"Never",ROUNDUP(($B$47-Inputs!$B$42*Inputs!$B$43/12)/($B$43-$B$44*Inputs!$B$45),0))</f>
         <v>547</v>
       </c>
-      <c r="C49" s="7"/>
+      <c r="C49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" s="8" t="s">
+      <c r="A51" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B52" s="32" t="n">
+        <v>164</v>
+      </c>
+      <c r="B52" s="31" t="n">
         <f aca="false">$B$8*Inputs!$B$22/Inputs!$B$26*Inputs!$B$23/Inputs!$B$25*Inputs!$B$24</f>
         <v>20.7321428571429</v>
       </c>
-      <c r="C52" s="7"/>
+      <c r="C52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="22" t="n">
+        <v>84</v>
+      </c>
+      <c r="B53" s="21" t="n">
         <f aca="false">Inputs!$B$46</f>
         <v>45</v>
       </c>
-      <c r="C53" s="7"/>
+      <c r="C53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B54" s="33" t="str">
+        <v>165</v>
+      </c>
+      <c r="B54" s="32" t="str">
         <f aca="false">IF($B$52&lt;=$B$53,"OK","Over capacity")</f>
         <v>OK</v>
       </c>
-      <c r="C54" s="7"/>
+      <c r="C54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B55" s="23" t="n">
+        <v>166</v>
+      </c>
+      <c r="B55" s="22" t="n">
         <f aca="false">$B$8*Inputs!$B$27/60*Inputs!$B$28</f>
         <v>290.25</v>
       </c>
-      <c r="C55" s="7"/>
+      <c r="C55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B56" s="23" t="n">
+        <v>167</v>
+      </c>
+      <c r="B56" s="22" t="n">
         <f aca="false">Inputs!$B$38*Inputs!$B$25*Inputs!$B$26*Inputs!$B$39</f>
         <v>1092</v>
       </c>
-      <c r="C56" s="7"/>
+      <c r="C56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B57" s="33" t="str">
+        <v>168</v>
+      </c>
+      <c r="B57" s="32" t="str">
         <f aca="false">IF($B$55&lt;=$B$56,"OK","Need more rooms")</f>
         <v>OK</v>
       </c>
-      <c r="C57" s="7"/>
+      <c r="C57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B58" s="23" t="n">
+        <v>169</v>
+      </c>
+      <c r="B58" s="22" t="n">
         <f aca="false">IF(Inputs!$B$27*Inputs!$B$28=0,0,ROUNDDOWN($B$56/(Inputs!$B$27/60*Inputs!$B$28),0))</f>
         <v>1456</v>
       </c>
-      <c r="C58" s="7"/>
+      <c r="C58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B59" s="23" t="n">
+        <v>170</v>
+      </c>
+      <c r="B59" s="22" t="n">
         <f aca="false">ROUNDUP($B$55/Inputs!$B$36/Inputs!$B$37,0)</f>
         <v>5</v>
       </c>
-      <c r="C59" s="7"/>
+      <c r="C59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="8" t="s">
+      <c r="A61" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>121</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B62" s="24" t="n">
+        <v>172</v>
+      </c>
+      <c r="B62" s="23" t="n">
         <f aca="false">Inputs!$B$42*MAX(0,Inputs!$B$65-Inputs!$B$66)</f>
         <v>240000</v>
       </c>
-      <c r="C62" s="7"/>
+      <c r="C62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B63" s="34" t="n">
+        <v>105</v>
+      </c>
+      <c r="B63" s="33" t="n">
         <f aca="false">Inputs!$B$67</f>
         <v>90000</v>
       </c>
-      <c r="C63" s="7"/>
+      <c r="C63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B64" s="34" t="n">
+        <v>173</v>
+      </c>
+      <c r="B64" s="33" t="n">
         <f aca="false">Inputs!$B$68</f>
         <v>70000</v>
       </c>
-      <c r="C64" s="7"/>
+      <c r="C64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B65" s="26" t="n">
+        <v>174</v>
+      </c>
+      <c r="B65" s="25" t="n">
         <f aca="false">SUM($B$62:$B$64)</f>
         <v>400000</v>
       </c>
-      <c r="C65" s="7"/>
+      <c r="C65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B66" s="35" t="str">
+        <v>175</v>
+      </c>
+      <c r="B66" s="34" t="str">
         <f aca="false">IF($B$36&lt;=0,"Never",$B$65/$B$36)</f>
         <v>Never</v>
       </c>
-      <c r="C66" s="7"/>
+      <c r="C66" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3094,1903 +3228,1903 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
+        <v>176</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
-      <c r="AE2" s="7"/>
-      <c r="AF2" s="7"/>
-      <c r="AG2" s="7"/>
-      <c r="AH2" s="7"/>
-      <c r="AI2" s="7"/>
-      <c r="AJ2" s="7"/>
-      <c r="AK2" s="7"/>
-      <c r="AL2" s="7"/>
+      <c r="A2" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="7"/>
-      <c r="AI3" s="7"/>
-      <c r="AJ3" s="7"/>
-      <c r="AK3" s="7"/>
-      <c r="AL3" s="7"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6"/>
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="B4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="X4" s="9" t="n">
+      <c r="X4" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="Y4" s="9" t="n">
+      <c r="Y4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="Z4" s="9" t="n">
+      <c r="Z4" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="AA4" s="9" t="n">
+      <c r="AA4" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="AB4" s="9" t="n">
+      <c r="AB4" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="AC4" s="9" t="n">
+      <c r="AC4" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="AD4" s="9" t="n">
+      <c r="AD4" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="AE4" s="9" t="n">
+      <c r="AE4" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="AF4" s="9" t="n">
+      <c r="AF4" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="AG4" s="9" t="n">
+      <c r="AG4" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="AH4" s="9" t="n">
+      <c r="AH4" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="AI4" s="9" t="n">
+      <c r="AI4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="AJ4" s="9" t="n">
+      <c r="AJ4" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="AK4" s="9" t="n">
+      <c r="AK4" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="AL4" s="9" t="n">
+      <c r="AL4" s="8" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="23" t="n">
+        <v>120</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="22" t="n">
         <f aca="false">Inputs!$B$10</f>
         <v>100</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,C5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>137</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,D5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>172.89</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,E5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>207.7033</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,F5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>241.472201</v>
       </c>
-      <c r="H5" s="23" t="n">
+      <c r="H5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,G5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>274.22803497</v>
       </c>
-      <c r="I5" s="23" t="n">
+      <c r="I5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,H5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>306.0011939209</v>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,I5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>336.821158103273</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,J5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>366.716523360175</v>
       </c>
-      <c r="L5" s="23" t="n">
+      <c r="L5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,K5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>395.715027659369</v>
       </c>
-      <c r="M5" s="23" t="n">
+      <c r="M5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,L5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>423.843576829588</v>
       </c>
-      <c r="N5" s="23" t="n">
+      <c r="N5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,M5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="O5" s="23" t="n">
+      <c r="O5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,N5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="P5" s="23" t="n">
+      <c r="P5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,O5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="Q5" s="23" t="n">
+      <c r="Q5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,P5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="R5" s="23" t="n">
+      <c r="R5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,Q5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="S5" s="23" t="n">
+      <c r="S5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,R5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="T5" s="23" t="n">
+      <c r="T5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,S5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="U5" s="23" t="n">
+      <c r="U5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,T5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="V5" s="23" t="n">
+      <c r="V5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,U5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="W5" s="23" t="n">
+      <c r="W5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,V5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="X5" s="23" t="n">
+      <c r="X5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,W5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="Y5" s="23" t="n">
+      <c r="Y5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,X5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="Z5" s="23" t="n">
+      <c r="Z5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,Y5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AA5" s="23" t="n">
+      <c r="AA5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,Z5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AB5" s="23" t="n">
+      <c r="AB5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AA5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AC5" s="23" t="n">
+      <c r="AC5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AB5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AD5" s="23" t="n">
+      <c r="AD5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AC5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AE5" s="23" t="n">
+      <c r="AE5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AD5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AF5" s="23" t="n">
+      <c r="AF5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AE5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AG5" s="23" t="n">
+      <c r="AG5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AF5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AH5" s="23" t="n">
+      <c r="AH5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AG5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AI5" s="23" t="n">
+      <c r="AI5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AH5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AJ5" s="23" t="n">
+      <c r="AJ5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AI5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AK5" s="23" t="n">
+      <c r="AK5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AJ5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
-      <c r="AL5" s="23" t="n">
+      <c r="AL5" s="22" t="n">
         <f aca="false">MIN(Inputs!$B$9,AK5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
         <v>450</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="24" t="n">
+        <v>127</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">C5*'Unit Economics'!$B$44</f>
         <v>15290</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">D5*'Unit Economics'!$B$44</f>
         <v>20947.3</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="23" t="n">
         <f aca="false">E5*'Unit Economics'!$B$44</f>
         <v>26434.881</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">F5*'Unit Economics'!$B$44</f>
         <v>31757.83457</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="23" t="n">
         <f aca="false">G5*'Unit Economics'!$B$44</f>
         <v>36921.0995329</v>
       </c>
-      <c r="H6" s="24" t="n">
+      <c r="H6" s="23" t="n">
         <f aca="false">H5*'Unit Economics'!$B$44</f>
         <v>41929.466546913</v>
       </c>
-      <c r="I6" s="24" t="n">
+      <c r="I6" s="23" t="n">
         <f aca="false">I5*'Unit Economics'!$B$44</f>
         <v>46787.5825505056</v>
       </c>
-      <c r="J6" s="24" t="n">
+      <c r="J6" s="23" t="n">
         <f aca="false">J5*'Unit Economics'!$B$44</f>
         <v>51499.9550739904</v>
       </c>
-      <c r="K6" s="24" t="n">
+      <c r="K6" s="23" t="n">
         <f aca="false">K5*'Unit Economics'!$B$44</f>
         <v>56070.9564217707</v>
       </c>
-      <c r="L6" s="24" t="n">
+      <c r="L6" s="23" t="n">
         <f aca="false">L5*'Unit Economics'!$B$44</f>
         <v>60504.8277291176</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="23" t="n">
         <f aca="false">M5*'Unit Economics'!$B$44</f>
         <v>64805.6828972441</v>
       </c>
-      <c r="N6" s="24" t="n">
+      <c r="N6" s="23" t="n">
         <f aca="false">N5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="O6" s="24" t="n">
+      <c r="O6" s="23" t="n">
         <f aca="false">O5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="P6" s="24" t="n">
+      <c r="P6" s="23" t="n">
         <f aca="false">P5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="Q6" s="24" t="n">
+      <c r="Q6" s="23" t="n">
         <f aca="false">Q5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="R6" s="24" t="n">
+      <c r="R6" s="23" t="n">
         <f aca="false">R5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="S6" s="24" t="n">
+      <c r="S6" s="23" t="n">
         <f aca="false">S5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="T6" s="24" t="n">
+      <c r="T6" s="23" t="n">
         <f aca="false">T5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="U6" s="24" t="n">
+      <c r="U6" s="23" t="n">
         <f aca="false">U5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="V6" s="24" t="n">
+      <c r="V6" s="23" t="n">
         <f aca="false">V5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="W6" s="24" t="n">
+      <c r="W6" s="23" t="n">
         <f aca="false">W5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="X6" s="24" t="n">
+      <c r="X6" s="23" t="n">
         <f aca="false">X5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="Y6" s="24" t="n">
+      <c r="Y6" s="23" t="n">
         <f aca="false">Y5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="Z6" s="24" t="n">
+      <c r="Z6" s="23" t="n">
         <f aca="false">Z5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AA6" s="24" t="n">
+      <c r="AA6" s="23" t="n">
         <f aca="false">AA5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AB6" s="24" t="n">
+      <c r="AB6" s="23" t="n">
         <f aca="false">AB5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AC6" s="24" t="n">
+      <c r="AC6" s="23" t="n">
         <f aca="false">AC5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AD6" s="24" t="n">
+      <c r="AD6" s="23" t="n">
         <f aca="false">AD5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AE6" s="24" t="n">
+      <c r="AE6" s="23" t="n">
         <f aca="false">AE5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AF6" s="24" t="n">
+      <c r="AF6" s="23" t="n">
         <f aca="false">AF5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AG6" s="24" t="n">
+      <c r="AG6" s="23" t="n">
         <f aca="false">AG5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AH6" s="24" t="n">
+      <c r="AH6" s="23" t="n">
         <f aca="false">AH5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AI6" s="24" t="n">
+      <c r="AI6" s="23" t="n">
         <f aca="false">AI5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AJ6" s="24" t="n">
+      <c r="AJ6" s="23" t="n">
         <f aca="false">AJ5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AK6" s="24" t="n">
+      <c r="AK6" s="23" t="n">
         <f aca="false">AK5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
-      <c r="AL6" s="24" t="n">
+      <c r="AL6" s="23" t="n">
         <f aca="false">AL5*'Unit Economics'!$B$44</f>
         <v>68805</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="24" t="n">
+        <v>179</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">C5*'Unit Economics'!$B$45</f>
         <v>5635.02</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">D5*'Unit Economics'!$B$45</f>
         <v>7719.9774</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">E5*'Unit Economics'!$B$45</f>
         <v>9742.386078</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">F5*'Unit Economics'!$B$45</f>
         <v>11704.12249566</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="23" t="n">
         <f aca="false">G5*'Unit Economics'!$B$45</f>
         <v>13607.0068207902</v>
       </c>
-      <c r="H7" s="24" t="n">
+      <c r="H7" s="23" t="n">
         <f aca="false">H5*'Unit Economics'!$B$45</f>
         <v>15452.8046161665</v>
       </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="23" t="n">
         <f aca="false">I5*'Unit Economics'!$B$45</f>
         <v>17243.2284776815</v>
       </c>
-      <c r="J7" s="24" t="n">
+      <c r="J7" s="23" t="n">
         <f aca="false">J5*'Unit Economics'!$B$45</f>
         <v>18979.9396233511</v>
       </c>
-      <c r="K7" s="24" t="n">
+      <c r="K7" s="23" t="n">
         <f aca="false">K5*'Unit Economics'!$B$45</f>
         <v>20664.5494346505</v>
       </c>
-      <c r="L7" s="24" t="n">
+      <c r="L7" s="23" t="n">
         <f aca="false">L5*'Unit Economics'!$B$45</f>
         <v>22298.620951611</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="23" t="n">
         <f aca="false">M5*'Unit Economics'!$B$45</f>
         <v>23883.6703230627</v>
       </c>
-      <c r="N7" s="24" t="n">
+      <c r="N7" s="23" t="n">
         <f aca="false">N5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="O7" s="24" t="n">
+      <c r="O7" s="23" t="n">
         <f aca="false">O5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="P7" s="24" t="n">
+      <c r="P7" s="23" t="n">
         <f aca="false">P5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="Q7" s="24" t="n">
+      <c r="Q7" s="23" t="n">
         <f aca="false">Q5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="R7" s="24" t="n">
+      <c r="R7" s="23" t="n">
         <f aca="false">R5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="S7" s="24" t="n">
+      <c r="S7" s="23" t="n">
         <f aca="false">S5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="T7" s="24" t="n">
+      <c r="T7" s="23" t="n">
         <f aca="false">T5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="U7" s="24" t="n">
+      <c r="U7" s="23" t="n">
         <f aca="false">U5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="V7" s="24" t="n">
+      <c r="V7" s="23" t="n">
         <f aca="false">V5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="W7" s="24" t="n">
+      <c r="W7" s="23" t="n">
         <f aca="false">W5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="X7" s="24" t="n">
+      <c r="X7" s="23" t="n">
         <f aca="false">X5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="Y7" s="24" t="n">
+      <c r="Y7" s="23" t="n">
         <f aca="false">Y5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="Z7" s="24" t="n">
+      <c r="Z7" s="23" t="n">
         <f aca="false">Z5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AA7" s="24" t="n">
+      <c r="AA7" s="23" t="n">
         <f aca="false">AA5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AB7" s="24" t="n">
+      <c r="AB7" s="23" t="n">
         <f aca="false">AB5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AC7" s="24" t="n">
+      <c r="AC7" s="23" t="n">
         <f aca="false">AC5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AD7" s="24" t="n">
+      <c r="AD7" s="23" t="n">
         <f aca="false">AD5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AE7" s="24" t="n">
+      <c r="AE7" s="23" t="n">
         <f aca="false">AE5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AF7" s="24" t="n">
+      <c r="AF7" s="23" t="n">
         <f aca="false">AF5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AG7" s="24" t="n">
+      <c r="AG7" s="23" t="n">
         <f aca="false">AG5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AH7" s="24" t="n">
+      <c r="AH7" s="23" t="n">
         <f aca="false">AH5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AI7" s="24" t="n">
+      <c r="AI7" s="23" t="n">
         <f aca="false">AI5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AJ7" s="24" t="n">
+      <c r="AJ7" s="23" t="n">
         <f aca="false">AJ5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AK7" s="24" t="n">
+      <c r="AK7" s="23" t="n">
         <f aca="false">AK5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
-      <c r="AL7" s="24" t="n">
+      <c r="AL7" s="23" t="n">
         <f aca="false">AL5*'Unit Economics'!$B$45</f>
         <v>25357.59</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B8" s="24" t="n">
+        <v>141</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,C6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,D6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,E6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,F6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,G6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="H8" s="24" t="n">
+      <c r="H8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,H6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="I8" s="24" t="n">
+      <c r="I8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,I6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="J8" s="24" t="n">
+      <c r="J8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,J6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="K8" s="24" t="n">
+      <c r="K8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,K6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="L8" s="24" t="n">
+      <c r="L8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,L6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="M8" s="24" t="n">
+      <c r="M8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,M6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="N8" s="24" t="n">
+      <c r="N8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,N6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="O8" s="24" t="n">
+      <c r="O8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,O6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="P8" s="24" t="n">
+      <c r="P8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,P6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="Q8" s="24" t="n">
+      <c r="Q8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,Q6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="R8" s="24" t="n">
+      <c r="R8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,R6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="S8" s="24" t="n">
+      <c r="S8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,S6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="T8" s="24" t="n">
+      <c r="T8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,T6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="U8" s="24" t="n">
+      <c r="U8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,U6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="V8" s="24" t="n">
+      <c r="V8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,V6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="W8" s="24" t="n">
+      <c r="W8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,W6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="X8" s="24" t="n">
+      <c r="X8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,X6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="Y8" s="24" t="n">
+      <c r="Y8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,Y6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="Z8" s="24" t="n">
+      <c r="Z8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,Z6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AA8" s="24" t="n">
+      <c r="AA8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AA6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AB8" s="24" t="n">
+      <c r="AB8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AB6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AC8" s="24" t="n">
+      <c r="AC8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AC6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AD8" s="24" t="n">
+      <c r="AD8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AD6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AE8" s="24" t="n">
+      <c r="AE8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AE6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AF8" s="24" t="n">
+      <c r="AF8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AF6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AG8" s="24" t="n">
+      <c r="AG8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AG6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AH8" s="24" t="n">
+      <c r="AH8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AH6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AI8" s="24" t="n">
+      <c r="AI8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AI6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AJ8" s="24" t="n">
+      <c r="AJ8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AJ6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AK8" s="24" t="n">
+      <c r="AK8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AK6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
-      <c r="AL8" s="24" t="n">
+      <c r="AL8" s="23" t="n">
         <f aca="false">IF(Inputs!$B$44=2,AL6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
         <v>13750</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="B9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="H9" s="24" t="n">
+      <c r="H9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="I9" s="24" t="n">
+      <c r="I9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="J9" s="24" t="n">
+      <c r="J9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="K9" s="24" t="n">
+      <c r="K9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="L9" s="24" t="n">
+      <c r="L9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="M9" s="24" t="n">
+      <c r="M9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="N9" s="24" t="n">
+      <c r="N9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="O9" s="24" t="n">
+      <c r="O9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="P9" s="24" t="n">
+      <c r="P9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="Q9" s="24" t="n">
+      <c r="Q9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="R9" s="24" t="n">
+      <c r="R9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="S9" s="24" t="n">
+      <c r="S9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="T9" s="24" t="n">
+      <c r="T9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="U9" s="24" t="n">
+      <c r="U9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="V9" s="24" t="n">
+      <c r="V9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="W9" s="24" t="n">
+      <c r="W9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="X9" s="24" t="n">
+      <c r="X9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="Y9" s="24" t="n">
+      <c r="Y9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="Z9" s="24" t="n">
+      <c r="Z9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AA9" s="24" t="n">
+      <c r="AA9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AB9" s="24" t="n">
+      <c r="AB9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AC9" s="24" t="n">
+      <c r="AC9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AD9" s="24" t="n">
+      <c r="AD9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AE9" s="24" t="n">
+      <c r="AE9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AF9" s="24" t="n">
+      <c r="AF9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AG9" s="24" t="n">
+      <c r="AG9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AH9" s="24" t="n">
+      <c r="AH9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AI9" s="24" t="n">
+      <c r="AI9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AJ9" s="24" t="n">
+      <c r="AJ9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AK9" s="24" t="n">
+      <c r="AK9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
-      <c r="AL9" s="24" t="n">
+      <c r="AL9" s="23" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>37699.1666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="26" t="n">
+        <v>181</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="25" t="n">
         <f aca="false">C6-C7-C8-C9</f>
         <v>-41794.1866666667</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="25" t="n">
         <f aca="false">D6-D7-D8-D9</f>
         <v>-38221.8440666667</v>
       </c>
-      <c r="E10" s="26" t="n">
+      <c r="E10" s="25" t="n">
         <f aca="false">E6-E7-E8-E9</f>
         <v>-34756.6717446667</v>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="25" t="n">
         <f aca="false">F6-F7-F8-F9</f>
         <v>-31395.4545923267</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="25" t="n">
         <f aca="false">G6-G7-G8-G9</f>
         <v>-28135.0739545569</v>
       </c>
-      <c r="H10" s="26" t="n">
+      <c r="H10" s="25" t="n">
         <f aca="false">H6-H7-H8-H9</f>
         <v>-24972.5047359202</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="25" t="n">
         <f aca="false">I6-I7-I8-I9</f>
         <v>-21904.8125938426</v>
       </c>
-      <c r="J10" s="26" t="n">
+      <c r="J10" s="25" t="n">
         <f aca="false">J6-J7-J8-J9</f>
         <v>-18929.1512160273</v>
       </c>
-      <c r="K10" s="26" t="n">
+      <c r="K10" s="25" t="n">
         <f aca="false">K6-K7-K8-K9</f>
         <v>-16042.7596795465</v>
       </c>
-      <c r="L10" s="26" t="n">
+      <c r="L10" s="25" t="n">
         <f aca="false">L6-L7-L8-L9</f>
         <v>-13242.9598891601</v>
       </c>
-      <c r="M10" s="26" t="n">
+      <c r="M10" s="25" t="n">
         <f aca="false">M6-M7-M8-M9</f>
         <v>-10527.1540924853</v>
       </c>
-      <c r="N10" s="26" t="n">
+      <c r="N10" s="25" t="n">
         <f aca="false">N6-N7-N8-N9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="O10" s="26" t="n">
+      <c r="O10" s="25" t="n">
         <f aca="false">O6-O7-O8-O9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="P10" s="26" t="n">
+      <c r="P10" s="25" t="n">
         <f aca="false">P6-P7-P8-P9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="Q10" s="26" t="n">
+      <c r="Q10" s="25" t="n">
         <f aca="false">Q6-Q7-Q8-Q9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="R10" s="26" t="n">
+      <c r="R10" s="25" t="n">
         <f aca="false">R6-R7-R8-R9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="S10" s="26" t="n">
+      <c r="S10" s="25" t="n">
         <f aca="false">S6-S7-S8-S9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="T10" s="26" t="n">
+      <c r="T10" s="25" t="n">
         <f aca="false">T6-T7-T8-T9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="U10" s="26" t="n">
+      <c r="U10" s="25" t="n">
         <f aca="false">U6-U7-U8-U9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="V10" s="26" t="n">
+      <c r="V10" s="25" t="n">
         <f aca="false">V6-V7-V8-V9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="W10" s="26" t="n">
+      <c r="W10" s="25" t="n">
         <f aca="false">W6-W7-W8-W9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="X10" s="26" t="n">
+      <c r="X10" s="25" t="n">
         <f aca="false">X6-X7-X8-X9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="Y10" s="26" t="n">
+      <c r="Y10" s="25" t="n">
         <f aca="false">Y6-Y7-Y8-Y9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="Z10" s="26" t="n">
+      <c r="Z10" s="25" t="n">
         <f aca="false">Z6-Z7-Z8-Z9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AA10" s="26" t="n">
+      <c r="AA10" s="25" t="n">
         <f aca="false">AA6-AA7-AA8-AA9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AB10" s="26" t="n">
+      <c r="AB10" s="25" t="n">
         <f aca="false">AB6-AB7-AB8-AB9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AC10" s="26" t="n">
+      <c r="AC10" s="25" t="n">
         <f aca="false">AC6-AC7-AC8-AC9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AD10" s="26" t="n">
+      <c r="AD10" s="25" t="n">
         <f aca="false">AD6-AD7-AD8-AD9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AE10" s="26" t="n">
+      <c r="AE10" s="25" t="n">
         <f aca="false">AE6-AE7-AE8-AE9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AF10" s="26" t="n">
+      <c r="AF10" s="25" t="n">
         <f aca="false">AF6-AF7-AF8-AF9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AG10" s="26" t="n">
+      <c r="AG10" s="25" t="n">
         <f aca="false">AG6-AG7-AG8-AG9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AH10" s="26" t="n">
+      <c r="AH10" s="25" t="n">
         <f aca="false">AH6-AH7-AH8-AH9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AI10" s="26" t="n">
+      <c r="AI10" s="25" t="n">
         <f aca="false">AI6-AI7-AI8-AI9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AJ10" s="26" t="n">
+      <c r="AJ10" s="25" t="n">
         <f aca="false">AJ6-AJ7-AJ8-AJ9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AK10" s="26" t="n">
+      <c r="AK10" s="25" t="n">
         <f aca="false">AK6-AK7-AK8-AK9</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AL10" s="26" t="n">
+      <c r="AL10" s="25" t="n">
         <f aca="false">AL6-AL7-AL8-AL9</f>
         <v>-8001.75666666668</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="24" t="n">
+        <v>182</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <f aca="false">'Unit Economics'!$B$65</f>
         <v>400000</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="24" t="n">
+      <c r="H11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="24" t="n">
+      <c r="I11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="24" t="n">
+      <c r="J11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="24" t="n">
+      <c r="K11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="24" t="n">
+      <c r="L11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="24" t="n">
+      <c r="M11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="24" t="n">
+      <c r="N11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="24" t="n">
+      <c r="O11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="24" t="n">
+      <c r="P11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="24" t="n">
+      <c r="Q11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="24" t="n">
+      <c r="R11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="24" t="n">
+      <c r="S11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="24" t="n">
+      <c r="T11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="24" t="n">
+      <c r="U11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="24" t="n">
+      <c r="V11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="24" t="n">
+      <c r="W11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="24" t="n">
+      <c r="X11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" s="24" t="n">
+      <c r="Y11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="24" t="n">
+      <c r="Z11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AA11" s="24" t="n">
+      <c r="AA11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" s="24" t="n">
+      <c r="AB11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="24" t="n">
+      <c r="AC11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="24" t="n">
+      <c r="AD11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" s="24" t="n">
+      <c r="AE11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" s="24" t="n">
+      <c r="AF11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AG11" s="24" t="n">
+      <c r="AG11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" s="24" t="n">
+      <c r="AH11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="24" t="n">
+      <c r="AI11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" s="24" t="n">
+      <c r="AJ11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AK11" s="24" t="n">
+      <c r="AK11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AL11" s="24" t="n">
+      <c r="AL11" s="23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="24" t="n">
+        <v>183</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <f aca="false">B10-B11</f>
         <v>-400000</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="23" t="n">
         <f aca="false">C10-C11</f>
         <v>-41794.1866666667</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">D10-D11</f>
         <v>-38221.8440666667</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="23" t="n">
         <f aca="false">E10-E11</f>
         <v>-34756.6717446667</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="23" t="n">
         <f aca="false">F10-F11</f>
         <v>-31395.4545923267</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="23" t="n">
         <f aca="false">G10-G11</f>
         <v>-28135.0739545569</v>
       </c>
-      <c r="H12" s="24" t="n">
+      <c r="H12" s="23" t="n">
         <f aca="false">H10-H11</f>
         <v>-24972.5047359202</v>
       </c>
-      <c r="I12" s="24" t="n">
+      <c r="I12" s="23" t="n">
         <f aca="false">I10-I11</f>
         <v>-21904.8125938426</v>
       </c>
-      <c r="J12" s="24" t="n">
+      <c r="J12" s="23" t="n">
         <f aca="false">J10-J11</f>
         <v>-18929.1512160273</v>
       </c>
-      <c r="K12" s="24" t="n">
+      <c r="K12" s="23" t="n">
         <f aca="false">K10-K11</f>
         <v>-16042.7596795465</v>
       </c>
-      <c r="L12" s="24" t="n">
+      <c r="L12" s="23" t="n">
         <f aca="false">L10-L11</f>
         <v>-13242.9598891601</v>
       </c>
-      <c r="M12" s="24" t="n">
+      <c r="M12" s="23" t="n">
         <f aca="false">M10-M11</f>
         <v>-10527.1540924853</v>
       </c>
-      <c r="N12" s="24" t="n">
+      <c r="N12" s="23" t="n">
         <f aca="false">N10-N11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="O12" s="24" t="n">
+      <c r="O12" s="23" t="n">
         <f aca="false">O10-O11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="P12" s="24" t="n">
+      <c r="P12" s="23" t="n">
         <f aca="false">P10-P11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="Q12" s="24" t="n">
+      <c r="Q12" s="23" t="n">
         <f aca="false">Q10-Q11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="R12" s="24" t="n">
+      <c r="R12" s="23" t="n">
         <f aca="false">R10-R11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="S12" s="24" t="n">
+      <c r="S12" s="23" t="n">
         <f aca="false">S10-S11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="T12" s="24" t="n">
+      <c r="T12" s="23" t="n">
         <f aca="false">T10-T11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="U12" s="24" t="n">
+      <c r="U12" s="23" t="n">
         <f aca="false">U10-U11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="V12" s="24" t="n">
+      <c r="V12" s="23" t="n">
         <f aca="false">V10-V11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="W12" s="24" t="n">
+      <c r="W12" s="23" t="n">
         <f aca="false">W10-W11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="X12" s="24" t="n">
+      <c r="X12" s="23" t="n">
         <f aca="false">X10-X11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="Y12" s="24" t="n">
+      <c r="Y12" s="23" t="n">
         <f aca="false">Y10-Y11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="Z12" s="24" t="n">
+      <c r="Z12" s="23" t="n">
         <f aca="false">Z10-Z11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AA12" s="24" t="n">
+      <c r="AA12" s="23" t="n">
         <f aca="false">AA10-AA11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AB12" s="24" t="n">
+      <c r="AB12" s="23" t="n">
         <f aca="false">AB10-AB11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AC12" s="24" t="n">
+      <c r="AC12" s="23" t="n">
         <f aca="false">AC10-AC11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AD12" s="24" t="n">
+      <c r="AD12" s="23" t="n">
         <f aca="false">AD10-AD11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AE12" s="24" t="n">
+      <c r="AE12" s="23" t="n">
         <f aca="false">AE10-AE11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AF12" s="24" t="n">
+      <c r="AF12" s="23" t="n">
         <f aca="false">AF10-AF11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AG12" s="24" t="n">
+      <c r="AG12" s="23" t="n">
         <f aca="false">AG10-AG11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AH12" s="24" t="n">
+      <c r="AH12" s="23" t="n">
         <f aca="false">AH10-AH11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AI12" s="24" t="n">
+      <c r="AI12" s="23" t="n">
         <f aca="false">AI10-AI11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AJ12" s="24" t="n">
+      <c r="AJ12" s="23" t="n">
         <f aca="false">AJ10-AJ11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AK12" s="24" t="n">
+      <c r="AK12" s="23" t="n">
         <f aca="false">AK10-AK11</f>
         <v>-8001.75666666668</v>
       </c>
-      <c r="AL12" s="24" t="n">
+      <c r="AL12" s="23" t="n">
         <f aca="false">AL10-AL11</f>
         <v>-8001.75666666668</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="26" t="n">
+        <v>184</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <f aca="false">B12</f>
         <v>-400000</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="25" t="n">
         <f aca="false">B13+C12</f>
         <v>-441794.186666667</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="25" t="n">
         <f aca="false">C13+D12</f>
         <v>-480016.030733333</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">D13+E12</f>
         <v>-514772.702478</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="25" t="n">
         <f aca="false">E13+F12</f>
         <v>-546168.157070327</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="25" t="n">
         <f aca="false">F13+G12</f>
         <v>-574303.231024884</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="25" t="n">
         <f aca="false">G13+H12</f>
         <v>-599275.735760804</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="25" t="n">
         <f aca="false">H13+I12</f>
         <v>-621180.548354646</v>
       </c>
-      <c r="J13" s="26" t="n">
+      <c r="J13" s="25" t="n">
         <f aca="false">I13+J12</f>
         <v>-640109.699570673</v>
       </c>
-      <c r="K13" s="26" t="n">
+      <c r="K13" s="25" t="n">
         <f aca="false">J13+K12</f>
         <v>-656152.45925022</v>
       </c>
-      <c r="L13" s="26" t="n">
+      <c r="L13" s="25" t="n">
         <f aca="false">K13+L12</f>
         <v>-669395.41913938</v>
       </c>
-      <c r="M13" s="26" t="n">
+      <c r="M13" s="25" t="n">
         <f aca="false">L13+M12</f>
         <v>-679922.573231865</v>
       </c>
-      <c r="N13" s="26" t="n">
+      <c r="N13" s="25" t="n">
         <f aca="false">M13+N12</f>
         <v>-687924.329898532</v>
       </c>
-      <c r="O13" s="26" t="n">
+      <c r="O13" s="25" t="n">
         <f aca="false">N13+O12</f>
         <v>-695926.086565199</v>
       </c>
-      <c r="P13" s="26" t="n">
+      <c r="P13" s="25" t="n">
         <f aca="false">O13+P12</f>
         <v>-703927.843231865</v>
       </c>
-      <c r="Q13" s="26" t="n">
+      <c r="Q13" s="25" t="n">
         <f aca="false">P13+Q12</f>
         <v>-711929.599898532</v>
       </c>
-      <c r="R13" s="26" t="n">
+      <c r="R13" s="25" t="n">
         <f aca="false">Q13+R12</f>
         <v>-719931.356565199</v>
       </c>
-      <c r="S13" s="26" t="n">
+      <c r="S13" s="25" t="n">
         <f aca="false">R13+S12</f>
         <v>-727933.113231866</v>
       </c>
-      <c r="T13" s="26" t="n">
+      <c r="T13" s="25" t="n">
         <f aca="false">S13+T12</f>
         <v>-735934.869898532</v>
       </c>
-      <c r="U13" s="26" t="n">
+      <c r="U13" s="25" t="n">
         <f aca="false">T13+U12</f>
         <v>-743936.626565199</v>
       </c>
-      <c r="V13" s="26" t="n">
+      <c r="V13" s="25" t="n">
         <f aca="false">U13+V12</f>
         <v>-751938.383231866</v>
       </c>
-      <c r="W13" s="26" t="n">
+      <c r="W13" s="25" t="n">
         <f aca="false">V13+W12</f>
         <v>-759940.139898532</v>
       </c>
-      <c r="X13" s="26" t="n">
+      <c r="X13" s="25" t="n">
         <f aca="false">W13+X12</f>
         <v>-767941.896565199</v>
       </c>
-      <c r="Y13" s="26" t="n">
+      <c r="Y13" s="25" t="n">
         <f aca="false">X13+Y12</f>
         <v>-775943.653231866</v>
       </c>
-      <c r="Z13" s="26" t="n">
+      <c r="Z13" s="25" t="n">
         <f aca="false">Y13+Z12</f>
         <v>-783945.409898533</v>
       </c>
-      <c r="AA13" s="26" t="n">
+      <c r="AA13" s="25" t="n">
         <f aca="false">Z13+AA12</f>
         <v>-791947.166565199</v>
       </c>
-      <c r="AB13" s="26" t="n">
+      <c r="AB13" s="25" t="n">
         <f aca="false">AA13+AB12</f>
         <v>-799948.923231866</v>
       </c>
-      <c r="AC13" s="26" t="n">
+      <c r="AC13" s="25" t="n">
         <f aca="false">AB13+AC12</f>
         <v>-807950.679898533</v>
       </c>
-      <c r="AD13" s="26" t="n">
+      <c r="AD13" s="25" t="n">
         <f aca="false">AC13+AD12</f>
         <v>-815952.436565199</v>
       </c>
-      <c r="AE13" s="26" t="n">
+      <c r="AE13" s="25" t="n">
         <f aca="false">AD13+AE12</f>
         <v>-823954.193231866</v>
       </c>
-      <c r="AF13" s="26" t="n">
+      <c r="AF13" s="25" t="n">
         <f aca="false">AE13+AF12</f>
         <v>-831955.949898533</v>
       </c>
-      <c r="AG13" s="26" t="n">
+      <c r="AG13" s="25" t="n">
         <f aca="false">AF13+AG12</f>
         <v>-839957.7065652</v>
       </c>
-      <c r="AH13" s="26" t="n">
+      <c r="AH13" s="25" t="n">
         <f aca="false">AG13+AH12</f>
         <v>-847959.463231866</v>
       </c>
-      <c r="AI13" s="26" t="n">
+      <c r="AI13" s="25" t="n">
         <f aca="false">AH13+AI12</f>
         <v>-855961.219898533</v>
       </c>
-      <c r="AJ13" s="26" t="n">
+      <c r="AJ13" s="25" t="n">
         <f aca="false">AI13+AJ12</f>
         <v>-863962.9765652</v>
       </c>
-      <c r="AK13" s="26" t="n">
+      <c r="AK13" s="25" t="n">
         <f aca="false">AJ13+AK12</f>
         <v>-871964.733231866</v>
       </c>
-      <c r="AL13" s="26" t="n">
+      <c r="AL13" s="25" t="n">
         <f aca="false">AK13+AL12</f>
         <v>-879966.489898533</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36" t="str">
+        <v>185</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35" t="str">
         <f aca="false">IF(AND(C13&gt;=0,B13&lt;0),C4,"")</f>
         <v/>
       </c>
-      <c r="D14" s="36" t="str">
+      <c r="D14" s="35" t="str">
         <f aca="false">IF(AND(D13&gt;=0,C13&lt;0),D4,"")</f>
         <v/>
       </c>
-      <c r="E14" s="36" t="str">
+      <c r="E14" s="35" t="str">
         <f aca="false">IF(AND(E13&gt;=0,D13&lt;0),E4,"")</f>
         <v/>
       </c>
-      <c r="F14" s="36" t="str">
+      <c r="F14" s="35" t="str">
         <f aca="false">IF(AND(F13&gt;=0,E13&lt;0),F4,"")</f>
         <v/>
       </c>
-      <c r="G14" s="36" t="str">
+      <c r="G14" s="35" t="str">
         <f aca="false">IF(AND(G13&gt;=0,F13&lt;0),G4,"")</f>
         <v/>
       </c>
-      <c r="H14" s="36" t="str">
+      <c r="H14" s="35" t="str">
         <f aca="false">IF(AND(H13&gt;=0,G13&lt;0),H4,"")</f>
         <v/>
       </c>
-      <c r="I14" s="36" t="str">
+      <c r="I14" s="35" t="str">
         <f aca="false">IF(AND(I13&gt;=0,H13&lt;0),I4,"")</f>
         <v/>
       </c>
-      <c r="J14" s="36" t="str">
+      <c r="J14" s="35" t="str">
         <f aca="false">IF(AND(J13&gt;=0,I13&lt;0),J4,"")</f>
         <v/>
       </c>
-      <c r="K14" s="36" t="str">
+      <c r="K14" s="35" t="str">
         <f aca="false">IF(AND(K13&gt;=0,J13&lt;0),K4,"")</f>
         <v/>
       </c>
-      <c r="L14" s="36" t="str">
+      <c r="L14" s="35" t="str">
         <f aca="false">IF(AND(L13&gt;=0,K13&lt;0),L4,"")</f>
         <v/>
       </c>
-      <c r="M14" s="36" t="str">
+      <c r="M14" s="35" t="str">
         <f aca="false">IF(AND(M13&gt;=0,L13&lt;0),M4,"")</f>
         <v/>
       </c>
-      <c r="N14" s="36" t="str">
+      <c r="N14" s="35" t="str">
         <f aca="false">IF(AND(N13&gt;=0,M13&lt;0),N4,"")</f>
         <v/>
       </c>
-      <c r="O14" s="36" t="str">
+      <c r="O14" s="35" t="str">
         <f aca="false">IF(AND(O13&gt;=0,N13&lt;0),O4,"")</f>
         <v/>
       </c>
-      <c r="P14" s="36" t="str">
+      <c r="P14" s="35" t="str">
         <f aca="false">IF(AND(P13&gt;=0,O13&lt;0),P4,"")</f>
         <v/>
       </c>
-      <c r="Q14" s="36" t="str">
+      <c r="Q14" s="35" t="str">
         <f aca="false">IF(AND(Q13&gt;=0,P13&lt;0),Q4,"")</f>
         <v/>
       </c>
-      <c r="R14" s="36" t="str">
+      <c r="R14" s="35" t="str">
         <f aca="false">IF(AND(R13&gt;=0,Q13&lt;0),R4,"")</f>
         <v/>
       </c>
-      <c r="S14" s="36" t="str">
+      <c r="S14" s="35" t="str">
         <f aca="false">IF(AND(S13&gt;=0,R13&lt;0),S4,"")</f>
         <v/>
       </c>
-      <c r="T14" s="36" t="str">
+      <c r="T14" s="35" t="str">
         <f aca="false">IF(AND(T13&gt;=0,S13&lt;0),T4,"")</f>
         <v/>
       </c>
-      <c r="U14" s="36" t="str">
+      <c r="U14" s="35" t="str">
         <f aca="false">IF(AND(U13&gt;=0,T13&lt;0),U4,"")</f>
         <v/>
       </c>
-      <c r="V14" s="36" t="str">
+      <c r="V14" s="35" t="str">
         <f aca="false">IF(AND(V13&gt;=0,U13&lt;0),V4,"")</f>
         <v/>
       </c>
-      <c r="W14" s="36" t="str">
+      <c r="W14" s="35" t="str">
         <f aca="false">IF(AND(W13&gt;=0,V13&lt;0),W4,"")</f>
         <v/>
       </c>
-      <c r="X14" s="36" t="str">
+      <c r="X14" s="35" t="str">
         <f aca="false">IF(AND(X13&gt;=0,W13&lt;0),X4,"")</f>
         <v/>
       </c>
-      <c r="Y14" s="36" t="str">
+      <c r="Y14" s="35" t="str">
         <f aca="false">IF(AND(Y13&gt;=0,X13&lt;0),Y4,"")</f>
         <v/>
       </c>
-      <c r="Z14" s="36" t="str">
+      <c r="Z14" s="35" t="str">
         <f aca="false">IF(AND(Z13&gt;=0,Y13&lt;0),Z4,"")</f>
         <v/>
       </c>
-      <c r="AA14" s="36" t="str">
+      <c r="AA14" s="35" t="str">
         <f aca="false">IF(AND(AA13&gt;=0,Z13&lt;0),AA4,"")</f>
         <v/>
       </c>
-      <c r="AB14" s="36" t="str">
+      <c r="AB14" s="35" t="str">
         <f aca="false">IF(AND(AB13&gt;=0,AA13&lt;0),AB4,"")</f>
         <v/>
       </c>
-      <c r="AC14" s="36" t="str">
+      <c r="AC14" s="35" t="str">
         <f aca="false">IF(AND(AC13&gt;=0,AB13&lt;0),AC4,"")</f>
         <v/>
       </c>
-      <c r="AD14" s="36" t="str">
+      <c r="AD14" s="35" t="str">
         <f aca="false">IF(AND(AD13&gt;=0,AC13&lt;0),AD4,"")</f>
         <v/>
       </c>
-      <c r="AE14" s="36" t="str">
+      <c r="AE14" s="35" t="str">
         <f aca="false">IF(AND(AE13&gt;=0,AD13&lt;0),AE4,"")</f>
         <v/>
       </c>
-      <c r="AF14" s="36" t="str">
+      <c r="AF14" s="35" t="str">
         <f aca="false">IF(AND(AF13&gt;=0,AE13&lt;0),AF4,"")</f>
         <v/>
       </c>
-      <c r="AG14" s="36" t="str">
+      <c r="AG14" s="35" t="str">
         <f aca="false">IF(AND(AG13&gt;=0,AF13&lt;0),AG4,"")</f>
         <v/>
       </c>
-      <c r="AH14" s="36" t="str">
+      <c r="AH14" s="35" t="str">
         <f aca="false">IF(AND(AH13&gt;=0,AG13&lt;0),AH4,"")</f>
         <v/>
       </c>
-      <c r="AI14" s="36" t="str">
+      <c r="AI14" s="35" t="str">
         <f aca="false">IF(AND(AI13&gt;=0,AH13&lt;0),AI4,"")</f>
         <v/>
       </c>
-      <c r="AJ14" s="36" t="str">
+      <c r="AJ14" s="35" t="str">
         <f aca="false">IF(AND(AJ13&gt;=0,AI13&lt;0),AJ4,"")</f>
         <v/>
       </c>
-      <c r="AK14" s="36" t="str">
+      <c r="AK14" s="35" t="str">
         <f aca="false">IF(AND(AK13&gt;=0,AJ13&lt;0),AK4,"")</f>
         <v/>
       </c>
-      <c r="AL14" s="36" t="str">
+      <c r="AL14" s="35" t="str">
         <f aca="false">IF(AND(AL13&gt;=0,AK13&lt;0),AL4,"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7"/>
-      <c r="AE15" s="7"/>
-      <c r="AF15" s="7"/>
-      <c r="AG15" s="7"/>
-      <c r="AH15" s="7"/>
-      <c r="AI15" s="7"/>
-      <c r="AJ15" s="7"/>
-      <c r="AK15" s="7"/>
-      <c r="AL15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
+      <c r="AG15" s="6"/>
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="6"/>
+      <c r="AJ15" s="6"/>
+      <c r="AK15" s="6"/>
+      <c r="AL15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" s="3" t="str">
         <f aca="false">IF(COUNT(C14:AL14)=0,"Beyond 36 months",MIN(C14:AL14))</f>
         <v>Beyond 36 months</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
-      <c r="AE16" s="7"/>
-      <c r="AF16" s="7"/>
-      <c r="AG16" s="7"/>
-      <c r="AH16" s="7"/>
-      <c r="AI16" s="7"/>
-      <c r="AJ16" s="7"/>
-      <c r="AK16" s="7"/>
-      <c r="AL16" s="7"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6"/>
+      <c r="AG16" s="6"/>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="6"/>
+      <c r="AJ16" s="6"/>
+      <c r="AK16" s="6"/>
+      <c r="AL16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" s="26" t="n">
+        <v>187</v>
+      </c>
+      <c r="B17" s="25" t="n">
         <f aca="false">MIN(B13:AL13)</f>
         <v>-879966.489898533</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
-      <c r="AE17" s="7"/>
-      <c r="AF17" s="7"/>
-      <c r="AG17" s="7"/>
-      <c r="AH17" s="7"/>
-      <c r="AI17" s="7"/>
-      <c r="AJ17" s="7"/>
-      <c r="AK17" s="7"/>
-      <c r="AL17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="6"/>
+      <c r="AJ17" s="6"/>
+      <c r="AK17" s="6"/>
+      <c r="AL17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="26" t="n">
+        <v>188</v>
+      </c>
+      <c r="B18" s="25" t="n">
         <f aca="false">AL13</f>
         <v>-879966.489898533</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
-      <c r="AE18" s="7"/>
-      <c r="AF18" s="7"/>
-      <c r="AG18" s="7"/>
-      <c r="AH18" s="7"/>
-      <c r="AI18" s="7"/>
-      <c r="AJ18" s="7"/>
-      <c r="AK18" s="7"/>
-      <c r="AL18" s="7"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="6"/>
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="6"/>
+      <c r="AL18" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5017,625 +5151,625 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+        <v>189</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="A2" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+        <v>191</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="37" t="n">
+      <c r="A5" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="36" t="n">
         <v>130</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="36" t="n">
         <v>195</v>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="36" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="37" t="n">
         <v>250</v>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="23" t="n">
         <f aca="false">$A6*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-30221.7166666667</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">$A6*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-27311.7166666667</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">$A6*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-23674.2166666667</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="23" t="n">
         <f aca="false">$A6*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-20764.2166666667</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">$A6*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-16399.2166666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="37" t="n">
         <v>300</v>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="23" t="n">
         <f aca="false">$A7*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-25976.2266666667</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">$A7*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-22484.2266666667</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">$A7*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-18119.2266666667</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">$A7*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-14627.2266666667</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">$A7*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-9389.22666666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="37" t="n">
         <v>350</v>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="23" t="n">
         <f aca="false">$A8*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-21730.7366666667</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="23" t="n">
         <f aca="false">$A8*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-17656.7366666667</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">$A8*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-12564.2366666667</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">$A8*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-8490.23666666667</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">$A8*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-2379.23666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="37" t="n">
         <v>400</v>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="23" t="n">
         <f aca="false">$A9*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-17485.2466666667</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="23" t="n">
         <f aca="false">$A9*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-12829.2466666667</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">$A9*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-7009.24666666667</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="23" t="n">
         <f aca="false">$A9*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-2353.24666666667</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="23" t="n">
         <f aca="false">$A9*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>4630.75333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="37" t="n">
         <v>450</v>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="23" t="n">
         <f aca="false">$A10*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-13239.7566666667</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="23" t="n">
         <f aca="false">$A10*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-8001.75666666667</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">$A10*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-1454.25666666666</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="23" t="n">
         <f aca="false">$A10*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>3783.74333333333</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="23" t="n">
         <f aca="false">$A10*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>11640.7433333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="37" t="n">
         <v>500</v>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="23" t="n">
         <f aca="false">$A11*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-8994.26666666666</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="23" t="n">
         <f aca="false">$A11*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-3174.26666666667</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">$A11*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>4100.73333333334</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="23" t="n">
         <f aca="false">$A11*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>9920.73333333333</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="23" t="n">
         <f aca="false">$A11*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>18650.7333333333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="37" t="n">
         <v>550</v>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="23" t="n">
         <f aca="false">$A12*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-4748.77666666666</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="23" t="n">
         <f aca="false">$A12*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>1653.22333333333</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">$A12*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>9655.72333333334</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="23" t="n">
         <f aca="false">$A12*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>16057.7233333333</v>
       </c>
-      <c r="F12" s="24" t="n">
+      <c r="F12" s="23" t="n">
         <f aca="false">$A12*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>25660.7233333333</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="37" t="n">
         <v>600</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="23" t="n">
         <f aca="false">$A13*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>-503.286666666652</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="23" t="n">
         <f aca="false">$A13*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>6480.71333333333</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="23" t="n">
         <f aca="false">$A13*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>15210.7133333333</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="23" t="n">
         <f aca="false">$A13*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>22194.7133333333</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="23" t="n">
         <f aca="false">$A13*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>32670.7133333333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="37" t="n">
         <v>700</v>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="23" t="n">
         <f aca="false">$A14*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>7987.69333333335</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="23" t="n">
         <f aca="false">$A14*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>16135.6933333333</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="23" t="n">
         <f aca="false">$A14*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>26320.6933333333</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="23" t="n">
         <f aca="false">$A14*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>34468.6933333333</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="23" t="n">
         <f aca="false">$A14*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
         <v>46690.6933333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+        <v>193</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="37" t="n">
+      <c r="A18" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="36" t="n">
         <v>130</v>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="36" t="n">
         <v>175</v>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="36" t="n">
         <v>195</v>
       </c>
-      <c r="F18" s="37" t="n">
+      <c r="F18" s="36" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="n">
+      <c r="A19" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>3672.14333333334</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>8910.14333333333</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>15457.6433333333</v>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>20695.6433333333</v>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>28552.6433333333</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="39" t="n">
+      <c r="A20" s="38" t="n">
         <v>30</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4783.80666666666</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>454.193333333336</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>7001.69333333333</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>12239.6933333333</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>20096.6933333333</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39" t="n">
+      <c r="A21" s="38" t="n">
         <v>45</v>
       </c>
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-9011.78166666667</v>
       </c>
-      <c r="C21" s="24" t="n">
+      <c r="C21" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-3773.78166666668</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>2773.71833333333</v>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>8011.71833333334</v>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="F21" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>15868.7183333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="39" t="n">
+      <c r="A22" s="38" t="n">
         <v>60</v>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-13239.7566666667</v>
       </c>
-      <c r="C22" s="24" t="n">
+      <c r="C22" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-8001.75666666667</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-1454.25666666666</v>
       </c>
-      <c r="E22" s="24" t="n">
+      <c r="E22" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>3783.74333333333</v>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>11640.7433333333</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="39" t="n">
+      <c r="A23" s="38" t="n">
         <v>90</v>
       </c>
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-21695.7066666667</v>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-16457.7066666667</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-9910.20666666667</v>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4672.20666666667</v>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>3184.79333333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B27" s="37" t="n">
+      <c r="A27" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="36" t="n">
         <v>115</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="36" t="n">
         <v>125</v>
       </c>
-      <c r="E27" s="37" t="n">
+      <c r="E27" s="36" t="n">
         <v>140</v>
       </c>
-      <c r="F27" s="37" t="n">
+      <c r="F27" s="36" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40" t="n">
+      <c r="A28" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="B28" s="24" t="n">
+      <c r="B28" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4680.66666666666</v>
       </c>
-      <c r="C28" s="24" t="n">
+      <c r="C28" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4680.66666666666</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4680.66666666666</v>
       </c>
-      <c r="E28" s="24" t="n">
+      <c r="E28" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4680.66666666666</v>
       </c>
-      <c r="F28" s="24" t="n">
+      <c r="F28" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4680.66666666666</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40" t="n">
+      <c r="A29" s="39" t="n">
         <v>0.2</v>
       </c>
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-8366.21166666666</v>
       </c>
-      <c r="C29" s="24" t="n">
+      <c r="C29" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-7151.21166666666</v>
       </c>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-6341.21166666666</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-5126.21166666666</v>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-4316.21166666666</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40" t="n">
+      <c r="A30" s="39" t="n">
         <v>0.4</v>
       </c>
-      <c r="B30" s="24" t="n">
+      <c r="B30" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-12051.7566666667</v>
       </c>
-      <c r="C30" s="24" t="n">
+      <c r="C30" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-9621.75666666667</v>
       </c>
-      <c r="D30" s="24" t="n">
+      <c r="D30" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-8001.75666666667</v>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E30" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-5571.75666666667</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-3951.75666666667</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="40" t="n">
+      <c r="A31" s="39" t="n">
         <v>0.6</v>
       </c>
-      <c r="B31" s="24" t="n">
+      <c r="B31" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-15737.3016666667</v>
       </c>
-      <c r="C31" s="24" t="n">
+      <c r="C31" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-12092.3016666667</v>
       </c>
-      <c r="D31" s="24" t="n">
+      <c r="D31" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-9662.30166666666</v>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-6017.30166666667</v>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-3587.30166666666</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="40" t="n">
+      <c r="A32" s="39" t="n">
         <v>0.8</v>
       </c>
-      <c r="B32" s="24" t="n">
+      <c r="B32" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-19422.8466666667</v>
       </c>
-      <c r="C32" s="24" t="n">
+      <c r="C32" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-14562.8466666667</v>
       </c>
-      <c r="D32" s="24" t="n">
+      <c r="D32" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-11322.8466666667</v>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E32" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-6462.84666666666</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="23" t="n">
         <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
         <v>-3222.84666666666</v>
       </c>
@@ -5689,355 +5823,355 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+        <v>197</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="A2" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>113</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="22" t="n">
+        <v>199</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <f aca="false">Inputs!B72</f>
         <v>1</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="21" t="n">
         <f aca="false">Inputs!C72</f>
         <v>1</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="21" t="n">
         <f aca="false">Inputs!D72</f>
         <v>2</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="21" t="n">
         <f aca="false">Inputs!E72</f>
         <v>4</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="21" t="n">
         <f aca="false">Inputs!F72</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B6" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="22" t="n">
         <f aca="false">B5</f>
         <v>1</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="22" t="n">
         <f aca="false">C5</f>
         <v>1</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="22" t="n">
         <f aca="false">D5</f>
         <v>2</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="22" t="n">
         <f aca="false">E5</f>
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="23" t="n">
+        <v>201</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="22" t="n">
         <f aca="false">B7+B6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="22" t="n">
         <f aca="false">C7+C6</f>
         <v>1</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="22" t="n">
         <f aca="false">D7+D6</f>
         <v>2</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="22" t="n">
         <f aca="false">E7+E6</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>202</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>1</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="22" t="n">
         <f aca="false">C5+C6+C7</f>
         <v>2</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="22" t="n">
         <f aca="false">D5+D6+D7</f>
         <v>4</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="22" t="n">
         <f aca="false">E5+E6+E7</f>
         <v>8</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="22" t="n">
         <f aca="false">F5+F6+F7</f>
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="24" t="n">
+        <v>127</v>
+      </c>
+      <c r="B9" s="23" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C6:N6)+B6*SUM('36-Month Ramp'!O6:Z6)+B7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>521754.586322441</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="23" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C6:N6)+C6*SUM('36-Month Ramp'!O6:Z6)+C7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>1347414.58632244</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C6:N6)+D6*SUM('36-Month Ramp'!O6:Z6)+D7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>2694829.17264488</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="23" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C6:N6)+E6*SUM('36-Month Ramp'!O6:Z6)+E7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>5389658.34528977</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="23" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C6:N6)+F6*SUM('36-Month Ramp'!O6:Z6)+F7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>9735807.51793465</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B10" s="24" t="n">
+        <v>203</v>
+      </c>
+      <c r="B10" s="23" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C10:N10)+B6*SUM('36-Month Ramp'!O10:Z10)+B7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>-287924.329898532</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="23" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C10:N10)+C6*SUM('36-Month Ramp'!O10:Z10)+C7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>-383945.409898532</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C10:N10)+D6*SUM('36-Month Ramp'!O10:Z10)+D7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>-767890.819797064</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="23" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C10:N10)+E6*SUM('36-Month Ramp'!O10:Z10)+E7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>-1535781.63959413</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="23" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C10:N10)+F6*SUM('36-Month Ramp'!O10:Z10)+F7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>-2495714.61939119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="24" t="n">
+        <v>204</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <f aca="false">-Inputs!B73</f>
         <v>-150000</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="23" t="n">
         <f aca="false">-Inputs!C73</f>
         <v>-400000</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">-Inputs!D73</f>
         <v>-800000</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="23" t="n">
         <f aca="false">-Inputs!E73</f>
         <v>-1400000</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="23" t="n">
         <f aca="false">-Inputs!F73</f>
         <v>-2200000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="26" t="n">
+        <v>205</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <f aca="false">B10+B11</f>
         <v>-437924.329898532</v>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="25" t="n">
         <f aca="false">C10+C11</f>
         <v>-783945.409898532</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">D10+D11</f>
         <v>-1567890.81979706</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="25" t="n">
         <f aca="false">E10+E11</f>
         <v>-2935781.63959413</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="25" t="n">
         <f aca="false">F10+F11</f>
         <v>-4695714.61939119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="24" t="n">
+        <v>206</v>
+      </c>
+      <c r="B13" s="23" t="n">
         <f aca="false">-B5*'Unit Economics'!$B$65</f>
         <v>-400000</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="23" t="n">
         <f aca="false">-C5*'Unit Economics'!$B$65</f>
         <v>-400000</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="23" t="n">
         <f aca="false">-D5*'Unit Economics'!$B$65</f>
         <v>-800000</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="23" t="n">
         <f aca="false">-E5*'Unit Economics'!$B$65</f>
         <v>-1600000</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="23" t="n">
         <f aca="false">-F5*'Unit Economics'!$B$65</f>
         <v>-2400000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14" s="24" t="n">
+        <v>207</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <f aca="false">B12+B13</f>
         <v>-837924.329898532</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="23" t="n">
         <f aca="false">C12+C13</f>
         <v>-1183945.40989853</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="23" t="n">
         <f aca="false">D12+D13</f>
         <v>-2367890.81979706</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="23" t="n">
         <f aca="false">E12+E13</f>
         <v>-4535781.63959413</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="23" t="n">
         <f aca="false">F12+F13</f>
         <v>-7095714.61939119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="B15" s="26" t="n">
+        <v>184</v>
+      </c>
+      <c r="B15" s="25" t="n">
         <f aca="false">B14</f>
         <v>-837924.329898532</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="25" t="n">
         <f aca="false">B15+C14</f>
         <v>-2021869.73979706</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="25" t="n">
         <f aca="false">C15+D14</f>
         <v>-4389760.55959413</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="25" t="n">
         <f aca="false">D15+E14</f>
         <v>-8925542.19918826</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="25" t="n">
         <f aca="false">E15+F14</f>
         <v>-16021256.8185795</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="41" t="n">
+        <v>208</v>
+      </c>
+      <c r="B17" s="40" t="n">
         <f aca="false">-MIN(0,MIN(B15:F15))</f>
         <v>16021256.8185795</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6055,7 +6189,341 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="33" t="n">
+        <f aca="false">'Unit Economics'!$B$62</f>
+        <v>240000</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="33" t="n">
+        <f aca="false">'Unit Economics'!$B$63</f>
+        <v>90000</v>
+      </c>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="33" t="n">
+        <f aca="false">'Unit Economics'!$B$64</f>
+        <v>70000</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <f aca="false">MAX(0,-'36-Month Ramp'!$B$17-'Unit Economics'!$B$65)</f>
+        <v>479966.489898533</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="23" t="n">
+        <f aca="false">SUM($B$5:$B$8)*$B$9</f>
+        <v>175993.297979707</v>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="25" t="n">
+        <f aca="false">SUM($B$5:$B$8)+$B$10</f>
+        <v>1055959.78787824</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="23" t="n">
+        <f aca="false">$B$15*$B$16*Inputs!$B$6</f>
+        <v>45000</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="23" t="n">
+        <f aca="false">$B$18*$B$19*$B$20*Inputs!$B$16</f>
+        <v>37500</v>
+      </c>
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B23" s="25" t="n">
+        <f aca="false">MAX(0,$B$11-$B$14-$B$17-$B$21-$B$22)</f>
+        <v>673459.78787824</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B24" s="25" t="n">
+        <f aca="false">$B$14+$B$17+$B$21+$B$22+$B$23</f>
+        <v>1055959.78787824</v>
+      </c>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="29" t="n">
+        <f aca="false">IF($B$11=0,0,($B$14+$B$23)/$B$11)</f>
+        <v>0.685120585256283</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B28" s="32" t="str">
+        <f aca="false">IF($B$27&gt;=0.1,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B29" s="16" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B31" s="23" t="n">
+        <f aca="false">IF($B$22=0,0,-PMT($B$29,$B$30,$B$22))</f>
+        <v>41564.3301565634</v>
+      </c>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B32" s="42" t="n">
+        <f aca="false">IF($B$31=0,"No loan",'Unit Economics'!$B$36/$B$31)</f>
+        <v>-2.31017989796324</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="150"/>
@@ -6063,7 +6531,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6071,55 +6539,65 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>210</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>219</v>
+      <c r="A13" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/off-hours/Off_Hours_Unit_Economics.xlsx
+++ b/off-hours/Off_Hours_Unit_Economics.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="274">
   <si>
     <t xml:space="preserve">Off Hours: Unit Economics Model</t>
   </si>
@@ -107,10 +107,34 @@
     <t xml:space="preserve">From you: $150/month</t>
   </si>
   <si>
-    <t xml:space="preserve">Add-on revenue per member per month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumption: extra or longer massages, guest passes, retail tea. Not on the site yet</t>
+    <t xml:space="preserve">Extra 15-minute chair massage: list price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: list price for non-included massages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member discount on extra massages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From you: members get 10% off additional massages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra massages bought per active member per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: about one extra massage every two months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other add-on revenue per active member (guest passes, retail tea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add-on revenue per active member (calculated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula: other add-ons + extra massages at the member price</t>
   </si>
   <si>
     <t xml:space="preserve">Card processing fees (% of revenue)</t>
@@ -122,21 +146,18 @@
     <t xml:space="preserve">Steady-state members per location</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption. The single most important number in the model</t>
+    <t xml:space="preserve">Assumption: e.g. 330 consumers + 220 employer seats (~22 companies x 10). The single most important number in the model</t>
   </si>
   <si>
     <t xml:space="preserve">Members on opening day</t>
   </si>
   <si>
-    <t xml:space="preserve">From the site: first 100 on the list get founding status</t>
+    <t xml:space="preserve">Assumption: 100 of your 250+ waitlist sign-ups join, plus 50 employer seats (e.g. 5 of your 10 companies x 10 seats)</t>
   </si>
   <si>
     <t xml:space="preserve">New members joining per month (during ramp)</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monthly member churn</t>
   </si>
   <si>
@@ -155,7 +176,7 @@
     <t xml:space="preserve">Employer seat price per month</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption: volume discount off the $150 consumer price</t>
+    <t xml:space="preserve">Assumption: modest discount for annual contracts. Below ~$135 a seat earns less than a consumer member</t>
   </si>
   <si>
     <t xml:space="preserve">Employer seat usage vs a self-paying member</t>
@@ -209,7 +230,7 @@
     <t xml:space="preserve">Massage minutes included per member per month</t>
   </si>
   <si>
-    <t xml:space="preserve">From the site: four 15-minute massages</t>
+    <t xml:space="preserve">From you: two 15-minute chair massages a month</t>
   </si>
   <si>
     <t xml:space="preserve">Share of included massage minutes actually used</t>
@@ -254,10 +275,19 @@
     <t xml:space="preserve">Assumption: part-time, about 20 hours a week</t>
   </si>
   <si>
-    <t xml:space="preserve">Massage rooms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target room occupancy</t>
+    <t xml:space="preserve">Massage chair stations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: semi-private chair massage spaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor cost of extra massages per active member (calculated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula: extra massages x 15 minutes, paid at therapist cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target chair station occupancy</t>
   </si>
   <si>
     <t xml:space="preserve">Space</t>
@@ -266,6 +296,9 @@
     <t xml:space="preserve">Square feet</t>
   </si>
   <si>
+    <t xml:space="preserve">Assumption: upper-floor space near Downtown Crossing / Park Street</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rent per sq ft per year (all-in)</t>
   </si>
   <si>
@@ -281,6 +314,9 @@
     <t xml:space="preserve">Landlord revenue share (% of revenue, if structure = 2)</t>
   </si>
   <si>
+    <t xml:space="preserve">Assumption: target to negotiate. Downtown office vacancy was 25.3% in Q2 2026 (Downtown Boston Alliance)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lounge seats</t>
   </si>
   <si>
@@ -341,7 +377,7 @@
     <t xml:space="preserve">Landlord tenant improvement allowance per sq ft</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption. Negotiable; larger in landlord partnerships</t>
+    <t xml:space="preserve">Assumption: landlord funds most of the buildout as part of a revenue-share deal</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture, fixtures, equipment</t>
@@ -434,7 +470,7 @@
     <t xml:space="preserve">B2B sales cost</t>
   </si>
   <si>
-    <t xml:space="preserve">Massage therapist labor</t>
+    <t xml:space="preserve">Massage therapist labor (included + extra massages)</t>
   </si>
   <si>
     <t xml:space="preserve">Coffee and tea</t>
@@ -485,7 +521,7 @@
     <t xml:space="preserve">Break-even</t>
   </si>
   <si>
-    <t xml:space="preserve">Massage labor per active member</t>
+    <t xml:space="preserve">Massage labor per active member (incl. extra massages)</t>
   </si>
   <si>
     <t xml:space="preserve">Other variable cost per active member</t>
@@ -527,16 +563,16 @@
     <t xml:space="preserve">Lounge OK?</t>
   </si>
   <si>
-    <t xml:space="preserve">Massage hours booked per month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massage room hours available per month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massage rooms OK?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max active-member equivalents the massage rooms can serve</t>
+    <t xml:space="preserve">Massage hours booked per month (incl. extra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chair station hours available per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chair stations OK?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max active-member equivalents the chair stations can serve</t>
   </si>
   <si>
     <t xml:space="preserve">Part-time therapists needed</t>
@@ -698,6 +734,9 @@
     <t xml:space="preserve">Founding members who prepay</t>
   </si>
   <si>
+    <t xml:space="preserve">From you: no founding prepayments</t>
+  </si>
+  <si>
     <t xml:space="preserve">Months each founding member prepays</t>
   </si>
   <si>
@@ -722,7 +761,7 @@
     <t xml:space="preserve">Months each company prepays</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption: quarterly in advance; some will pay annually</t>
+    <t xml:space="preserve">Set to 0: interest is not a contract. Upside if companies pay quarterly in advance</t>
   </si>
   <si>
     <t xml:space="preserve">Employer prepayments</t>
@@ -776,7 +815,7 @@
     <t xml:space="preserve">Sources and notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Membership price and benefits: visitoffhours.com (from your screen recording) and your instruction that the price is $150/month.</t>
+    <t xml:space="preserve">Membership price and benefits: from you. $150/month, two 15-minute chair massages included, 10% member discount on extra massages. Location: Downtown Crossing / Park Street, revenue-share deal.</t>
   </si>
   <si>
     <t xml:space="preserve">Massage therapist pay: Boston-Cambridge-Newton median $36.13/hr, BLS May 2025 via WageDex. https://wagedex.com/jobs/massage-therapists/metro/boston-cambridge-newton-ma-nh</t>
@@ -820,9 +859,9 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\);\-"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;\(#,##0.0\);\-"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="@"/>
     <numFmt numFmtId="172" formatCode="0%"/>
@@ -977,7 +1016,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1038,7 +1077,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1046,7 +1089,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1054,7 +1097,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1062,11 +1109,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1074,7 +1121,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1086,7 +1133,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1094,15 +1145,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1114,7 +1157,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1126,7 +1169,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1544,7 +1587,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1622,7 +1665,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>27</v>
@@ -1636,7 +1679,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="13" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>29</v>
@@ -1650,7 +1693,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="14" t="n">
-        <v>450</v>
+        <v>0.5</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>31</v>
@@ -1663,8 +1706,8 @@
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="15" t="n">
-        <v>100</v>
+      <c r="B10" s="12" t="n">
+        <v>5</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>33</v>
@@ -1677,8 +1720,9 @@
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>40</v>
+      <c r="B11" s="15" t="n">
+        <f aca="false">Inputs!$B$10+Inputs!$B$9*Inputs!$B$7*(1-Inputs!$B$8)</f>
+        <v>23</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>35</v>
@@ -1691,8 +1735,8 @@
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>0.04</v>
+      <c r="B12" s="13" t="n">
+        <v>0.03</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>37</v>
@@ -1702,32 +1746,42 @@
       <c r="F12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>550</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>41</v>
+      </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B15" s="16" t="n">
-        <v>0.4</v>
+        <v>40</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -1735,87 +1789,87 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>125</v>
+        <v>43</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>0.04</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>44</v>
-      </c>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="13" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>46</v>
-      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>6</v>
+        <v>52</v>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>0.015</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -1823,42 +1877,32 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>1.5</v>
+        <v>54</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0.1</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>54</v>
-      </c>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C25" s="11" t="s">
+      <c r="A25" s="8" t="s">
         <v>56</v>
       </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -1867,8 +1911,8 @@
       <c r="A26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="15" t="n">
-        <v>30</v>
+      <c r="B26" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>58</v>
@@ -1881,11 +1925,11 @@
       <c r="A27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>60</v>
+      <c r="B27" s="18" t="n">
+        <v>1.5</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -1893,13 +1937,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="B28" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>62</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -1907,13 +1951,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="B29" s="17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -1923,11 +1967,11 @@
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="18" t="n">
-        <v>1.1</v>
+      <c r="B30" s="19" t="n">
+        <v>30</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -1935,45 +1979,55 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="18" t="n">
-        <v>0.75</v>
+        <v>66</v>
+      </c>
+      <c r="B31" s="16" t="n">
+        <v>30</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
+      <c r="A32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>69</v>
+      </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>38</v>
+        <v>71</v>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>1.1</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -1981,55 +2035,45 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="13" t="n">
-        <v>0.15</v>
+        <v>72</v>
+      </c>
+      <c r="B35" s="20" t="n">
+        <v>0.75</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>72</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>74</v>
-      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="C38" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="B38" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -2040,42 +2084,52 @@
         <v>76</v>
       </c>
       <c r="B39" s="13" t="n">
-        <v>0.65</v>
+        <v>0.15</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+      <c r="A40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
+      <c r="A41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>81</v>
+      </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="14" t="n">
-        <v>3000</v>
+        <v>82</v>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -2083,13 +2137,14 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="19" t="n">
-        <v>55</v>
+        <v>84</v>
+      </c>
+      <c r="B43" s="15" t="n">
+        <f aca="false">Inputs!$B$9*15/60/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)</f>
+        <v>7.28333333333333</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -2097,73 +2152,73 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="20" t="n">
-        <v>1</v>
+        <v>86</v>
+      </c>
+      <c r="B44" s="13" t="n">
+        <v>0.65</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="13" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A46" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
+      <c r="A47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>89</v>
+      </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
+      <c r="A48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>91</v>
+      </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B49" s="12" t="n">
-        <v>80000</v>
+        <v>92</v>
+      </c>
+      <c r="B49" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -2171,13 +2226,13 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B50" s="18" t="n">
-        <v>22</v>
+        <v>94</v>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>0.15</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -2185,73 +2240,73 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B51" s="17" t="n">
-        <v>1.25</v>
+        <v>96</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>45</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B52" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B53" s="12" t="n">
-        <v>125</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A53" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
+      <c r="A54" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
+      <c r="A55" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B56" s="12" t="n">
-        <v>2500</v>
+        <v>100</v>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -2259,13 +2314,13 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57" s="12" t="n">
-        <v>3000</v>
+        <v>101</v>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>30</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -2273,55 +2328,45 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B58" s="12" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B59" s="12" t="n">
-        <v>800</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B60" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A60" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B61" s="12" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -2329,45 +2374,55 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B62" s="12" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
+      <c r="A63" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
+      <c r="A64" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" s="10" t="n">
-        <v>120</v>
+        <v>109</v>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>4000</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -2375,13 +2430,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B66" s="12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -2389,119 +2444,179 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B67" s="12" t="n">
-        <v>90000</v>
+        <v>700</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B68" s="12" t="n">
-        <v>70000</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
+      <c r="A69" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
+      <c r="A70" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>114</v>
+      </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>114</v>
-      </c>
+      <c r="A71" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B72" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F72" s="15" t="n">
-        <v>6</v>
-      </c>
+      <c r="A72" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
-        <v>116</v>
+      <c r="A73" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="B73" s="12" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C73" s="12" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D73" s="12" t="n">
-        <v>800000</v>
-      </c>
-      <c r="E73" s="12" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>2200000</v>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="11" t="s">
-        <v>117</v>
-      </c>
+      <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C78" s="12" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D78" s="12" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2529,14 +2644,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2548,52 +2663,52 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="21" t="n">
-        <f aca="false">Inputs!$B$9</f>
-        <v>450</v>
+        <v>135</v>
+      </c>
+      <c r="B5" s="23" t="n">
+        <f aca="false">Inputs!$B$13</f>
+        <v>550</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="22" t="n">
-        <f aca="false">$B$5*(1-Inputs!$B$15)</f>
-        <v>270</v>
+        <v>136</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <f aca="false">$B$5*(1-Inputs!$B$19)</f>
+        <v>330</v>
       </c>
       <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="22" t="n">
-        <f aca="false">$B$5*Inputs!$B$15</f>
-        <v>180</v>
+        <v>137</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <f aca="false">$B$5*Inputs!$B$19</f>
+        <v>220</v>
       </c>
       <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="22" t="n">
-        <f aca="false">$B$6+$B$7*Inputs!$B$17</f>
-        <v>387</v>
+        <v>138</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <f aca="false">$B$6+$B$7*Inputs!$B$21</f>
+        <v>473</v>
       </c>
       <c r="C8" s="6"/>
     </row>
@@ -2604,65 +2719,65 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="23" t="n">
+        <v>140</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <f aca="false">$B$6*Inputs!$B$6</f>
-        <v>40500</v>
-      </c>
-      <c r="C11" s="24" t="n">
+        <v>49500</v>
+      </c>
+      <c r="C11" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B11/$B$5)</f>
         <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B12" s="23" t="n">
-        <f aca="false">$B$7*Inputs!$B$16</f>
-        <v>22500</v>
-      </c>
-      <c r="C12" s="24" t="n">
+        <v>141</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <f aca="false">$B$7*Inputs!$B$20</f>
+        <v>30800</v>
+      </c>
+      <c r="C12" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B12/$B$5)</f>
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B13" s="23" t="n">
-        <f aca="false">$B$8*Inputs!$B$7</f>
-        <v>5805</v>
-      </c>
-      <c r="C13" s="24" t="n">
+        <v>142</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <f aca="false">$B$8*Inputs!$B$11</f>
+        <v>10879</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B13/$B$5)</f>
-        <v>12.9</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="25" t="n">
+        <v>143</v>
+      </c>
+      <c r="B14" s="27" t="n">
         <f aca="false">$B$11+$B$12+$B$13</f>
-        <v>68805</v>
-      </c>
-      <c r="C14" s="24" t="n">
+        <v>91179</v>
+      </c>
+      <c r="C14" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B14/$B$5)</f>
-        <v>152.9</v>
+        <v>165.78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2672,104 +2787,104 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="23" t="n">
-        <f aca="false">($B$11+$B$13)*Inputs!$B$8</f>
-        <v>1389.15</v>
-      </c>
-      <c r="C17" s="24" t="n">
+        <v>145</v>
+      </c>
+      <c r="B17" s="25" t="n">
+        <f aca="false">($B$11+$B$13)*Inputs!$B$12</f>
+        <v>1811.37</v>
+      </c>
+      <c r="C17" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B17/$B$5)</f>
-        <v>3.087</v>
+        <v>3.2934</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="23" t="n">
-        <f aca="false">$B$12*Inputs!$B$19</f>
-        <v>2250</v>
-      </c>
-      <c r="C18" s="24" t="n">
+        <v>146</v>
+      </c>
+      <c r="B18" s="25" t="n">
+        <f aca="false">$B$12*Inputs!$B$23</f>
+        <v>3080</v>
+      </c>
+      <c r="C18" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B18/$B$5)</f>
-        <v>5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B19" s="23" t="n">
-        <f aca="false">$B$8*Inputs!$B$27/60*Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)</f>
-        <v>16911.9</v>
-      </c>
-      <c r="C19" s="24" t="n">
+        <v>147</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <f aca="false">$B$8*(Inputs!$B$31/60*Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)+Inputs!$B$43)</f>
+        <v>13780.0666666667</v>
+      </c>
+      <c r="C19" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B19/$B$5)</f>
-        <v>37.582</v>
+        <v>25.0546666666667</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B20" s="23" t="n">
-        <f aca="false">$B$8*Inputs!$B$22*Inputs!$B$29*Inputs!$B$30</f>
-        <v>3065.04</v>
-      </c>
-      <c r="C20" s="24" t="n">
+        <v>148</v>
+      </c>
+      <c r="B20" s="25" t="n">
+        <f aca="false">$B$8*Inputs!$B$26*Inputs!$B$33*Inputs!$B$34</f>
+        <v>3746.16</v>
+      </c>
+      <c r="C20" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B20/$B$5)</f>
         <v>6.8112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="23" t="n">
-        <f aca="false">$B$8*Inputs!$B$22*Inputs!$B$31</f>
-        <v>1741.5</v>
-      </c>
-      <c r="C21" s="24" t="n">
+        <v>149</v>
+      </c>
+      <c r="B21" s="25" t="n">
+        <f aca="false">$B$8*Inputs!$B$26*Inputs!$B$35</f>
+        <v>2128.5</v>
+      </c>
+      <c r="C21" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B21/$B$5)</f>
         <v>3.87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="B22" s="27" t="n">
         <f aca="false">SUM($B$17:$B$21)</f>
-        <v>25357.59</v>
-      </c>
-      <c r="C22" s="24" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="C22" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B22/$B$5)</f>
-        <v>56.3502</v>
+        <v>44.6292666666667</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B23" s="25" t="n">
+        <v>151</v>
+      </c>
+      <c r="B23" s="27" t="n">
         <f aca="false">$B$14-$B$22</f>
-        <v>43447.41</v>
-      </c>
-      <c r="C23" s="24" t="n">
+        <v>66632.9033333333</v>
+      </c>
+      <c r="C23" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B23/$B$5)</f>
-        <v>96.5498</v>
+        <v>121.150733333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2779,91 +2894,91 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,$B$14*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="C26" s="24" t="n">
+        <v>153</v>
+      </c>
+      <c r="B26" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,$B$14*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="C26" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B26/$B$5)</f>
-        <v>30.5555555555556</v>
+        <v>24.867</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B27" s="23" t="n">
-        <f aca="false">Inputs!$B$49*(1+Inputs!$B$35)/12</f>
+        <v>154</v>
+      </c>
+      <c r="B27" s="25" t="n">
+        <f aca="false">Inputs!$B$54*(1+Inputs!$B$39)/12</f>
         <v>7666.66666666667</v>
       </c>
-      <c r="C27" s="24" t="n">
+      <c r="C27" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B27/$B$5)</f>
-        <v>17.037037037037</v>
+        <v>13.9393939393939</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="23" t="n">
-        <f aca="false">Inputs!$B$25*Inputs!$B$26*Inputs!$B$51*Inputs!$B$50*(1+Inputs!$B$35)</f>
-        <v>13282.5</v>
-      </c>
-      <c r="C28" s="24" t="n">
+        <v>155</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <f aca="false">Inputs!$B$29*Inputs!$B$30*Inputs!$B$56*Inputs!$B$55*(1+Inputs!$B$39)</f>
+        <v>10626</v>
+      </c>
+      <c r="C28" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B28/$B$5)</f>
-        <v>29.5166666666667</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="23" t="n">
-        <f aca="false">Inputs!$B$52*Inputs!$B$53</f>
+        <v>156</v>
+      </c>
+      <c r="B29" s="25" t="n">
+        <f aca="false">Inputs!$B$57*Inputs!$B$58</f>
         <v>3750</v>
       </c>
-      <c r="C29" s="24" t="n">
+      <c r="C29" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B29/$B$5)</f>
-        <v>8.33333333333333</v>
+        <v>6.81818181818182</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="23" t="n">
-        <f aca="false">Inputs!$B$56+Inputs!$B$57+Inputs!$B$58+Inputs!$B$59+Inputs!$B$60+Inputs!$B$61+Inputs!$B$62</f>
+        <v>157</v>
+      </c>
+      <c r="B30" s="25" t="n">
+        <f aca="false">Inputs!$B$61+Inputs!$B$62+Inputs!$B$63+Inputs!$B$64+Inputs!$B$65+Inputs!$B$66+Inputs!$B$67</f>
         <v>13000</v>
       </c>
-      <c r="C30" s="24" t="n">
+      <c r="C30" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B30/$B$5)</f>
-        <v>28.8888888888889</v>
+        <v>23.6363636363636</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B31" s="25" t="n">
+        <v>158</v>
+      </c>
+      <c r="B31" s="27" t="n">
         <f aca="false">SUM($B$26:$B$30)</f>
-        <v>51449.1666666667</v>
-      </c>
-      <c r="C31" s="24" t="n">
+        <v>48719.5166666667</v>
+      </c>
+      <c r="C31" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B31/$B$5)</f>
-        <v>114.331481481481</v>
+        <v>88.5809393939394</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2873,45 +2988,45 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B34" s="25" t="n">
+        <v>160</v>
+      </c>
+      <c r="B34" s="27" t="n">
         <f aca="false">$B$23-$B$31</f>
-        <v>-8001.75666666666</v>
-      </c>
-      <c r="C34" s="24" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="C34" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B34/$B$5)</f>
-        <v>-17.7816814814815</v>
+        <v>32.5697939393939</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B35" s="26" t="n">
+        <v>161</v>
+      </c>
+      <c r="B35" s="28" t="n">
         <f aca="false">IF($B$14=0,0,$B$34/$B$14)</f>
-        <v>-0.116296150958021</v>
+        <v>0.19646395186026</v>
       </c>
       <c r="C35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="25" t="n">
+        <v>162</v>
+      </c>
+      <c r="B36" s="27" t="n">
         <f aca="false">$B$34*12</f>
-        <v>-96021.0799999999</v>
+        <v>214960.64</v>
       </c>
       <c r="C36" s="6"/>
     </row>
@@ -2922,122 +3037,122 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="27" t="n">
-        <f aca="false">Inputs!$B$27/60*Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)</f>
-        <v>43.7</v>
+        <v>164</v>
+      </c>
+      <c r="B39" s="15" t="n">
+        <f aca="false">Inputs!$B$31/60*Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)+Inputs!$B$43</f>
+        <v>29.1333333333333</v>
       </c>
       <c r="C39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B40" s="27" t="n">
-        <f aca="false">Inputs!$B$22*(Inputs!$B$29*Inputs!$B$30+Inputs!$B$31)</f>
+        <v>165</v>
+      </c>
+      <c r="B40" s="15" t="n">
+        <f aca="false">Inputs!$B$26*(Inputs!$B$33*Inputs!$B$34+Inputs!$B$35)</f>
         <v>12.42</v>
       </c>
       <c r="C40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="27" t="n">
-        <f aca="false">(Inputs!$B$6+Inputs!$B$7)*(1-Inputs!$B$8)-$B$39-$B$40</f>
-        <v>103.93</v>
+        <v>166</v>
+      </c>
+      <c r="B41" s="15" t="n">
+        <f aca="false">(Inputs!$B$6+Inputs!$B$11)*(1-Inputs!$B$12)-$B$39-$B$40</f>
+        <v>126.256666666667</v>
       </c>
       <c r="C41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B42" s="27" t="n">
-        <f aca="false">Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$B$39-$B$40)</f>
-        <v>85.4795</v>
+        <v>167</v>
+      </c>
+      <c r="B42" s="15" t="n">
+        <f aca="false">Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$B$39-$B$40)</f>
+        <v>113.491833333333</v>
       </c>
       <c r="C42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B43" s="28" t="n">
-        <f aca="false">(1-Inputs!$B$15)*$B$41+Inputs!$B$15*$B$42</f>
-        <v>96.5498</v>
+        <v>168</v>
+      </c>
+      <c r="B43" s="29" t="n">
+        <f aca="false">(1-Inputs!$B$19)*$B$41+Inputs!$B$19*$B$42</f>
+        <v>121.150733333333</v>
       </c>
       <c r="C43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B44" s="27" t="n">
-        <f aca="false">(1-Inputs!$B$15)*(Inputs!$B$6+Inputs!$B$7)+Inputs!$B$15*(Inputs!$B$16+Inputs!$B$17*Inputs!$B$7)</f>
-        <v>152.9</v>
+        <v>169</v>
+      </c>
+      <c r="B44" s="15" t="n">
+        <f aca="false">(1-Inputs!$B$19)*(Inputs!$B$6+Inputs!$B$11)+Inputs!$B$19*(Inputs!$B$20+Inputs!$B$21*Inputs!$B$11)</f>
+        <v>165.78</v>
       </c>
       <c r="C44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B45" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="B45" s="15" t="n">
         <f aca="false">$B$44-$B$43</f>
-        <v>56.3502</v>
+        <v>44.6292666666667</v>
       </c>
       <c r="C45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B46" s="29" t="n">
-        <f aca="false">(1-Inputs!$B$15)*Inputs!$B$12+Inputs!$B$15*Inputs!$B$18</f>
+        <v>171</v>
+      </c>
+      <c r="B46" s="30" t="n">
+        <f aca="false">(1-Inputs!$B$19)*Inputs!$B$16+Inputs!$B$19*Inputs!$B$22</f>
         <v>0.03</v>
       </c>
       <c r="C46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B47" s="23" t="n">
-        <f aca="false">$B$31-$B$26+Inputs!$B$42*Inputs!$B$43/12</f>
-        <v>51449.1666666667</v>
+        <v>172</v>
+      </c>
+      <c r="B47" s="25" t="n">
+        <f aca="false">$B$31-$B$26+Inputs!$B$47*Inputs!$B$48/12</f>
+        <v>46042.6666666667</v>
       </c>
       <c r="C47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B48" s="30" t="n">
+        <v>173</v>
+      </c>
+      <c r="B48" s="31" t="n">
         <f aca="false">IF($B$43&lt;=0,"Never",ROUNDUP($B$47/$B$43,0))</f>
-        <v>533</v>
+        <v>381</v>
       </c>
       <c r="C48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B49" s="30" t="n">
-        <f aca="false">IF($B$43-$B$44*Inputs!$B$45&lt;=0,"Never",ROUNDUP(($B$47-Inputs!$B$42*Inputs!$B$43/12)/($B$43-$B$44*Inputs!$B$45),0))</f>
-        <v>547</v>
+        <v>174</v>
+      </c>
+      <c r="B49" s="31" t="n">
+        <f aca="false">IF($B$43-$B$44*Inputs!$B$50&lt;=0,"Never",ROUNDUP(($B$47-Inputs!$B$47*Inputs!$B$48/12)/($B$43-$B$44*Inputs!$B$50),0))</f>
+        <v>364</v>
       </c>
       <c r="C49" s="6"/>
     </row>
@@ -3048,40 +3163,40 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B52" s="31" t="n">
-        <f aca="false">$B$8*Inputs!$B$22/Inputs!$B$26*Inputs!$B$23/Inputs!$B$25*Inputs!$B$24</f>
-        <v>20.7321428571429</v>
+        <v>176</v>
+      </c>
+      <c r="B52" s="32" t="n">
+        <f aca="false">$B$8*Inputs!$B$26/Inputs!$B$30*Inputs!$B$27/Inputs!$B$29*Inputs!$B$28</f>
+        <v>25.3392857142857</v>
       </c>
       <c r="C52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B53" s="21" t="n">
-        <f aca="false">Inputs!$B$46</f>
+        <v>96</v>
+      </c>
+      <c r="B53" s="23" t="n">
+        <f aca="false">Inputs!$B$51</f>
         <v>45</v>
       </c>
       <c r="C53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B54" s="32" t="str">
+        <v>177</v>
+      </c>
+      <c r="B54" s="33" t="str">
         <f aca="false">IF($B$52&lt;=$B$53,"OK","Over capacity")</f>
         <v>OK</v>
       </c>
@@ -3089,51 +3204,51 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B55" s="22" t="n">
-        <f aca="false">$B$8*Inputs!$B$27/60*Inputs!$B$28</f>
-        <v>290.25</v>
+        <v>178</v>
+      </c>
+      <c r="B55" s="24" t="n">
+        <f aca="false">$B$8*(Inputs!$B$31/60*Inputs!$B$32+Inputs!$B$9*15/60)</f>
+        <v>236.5</v>
       </c>
       <c r="C55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B56" s="22" t="n">
-        <f aca="false">Inputs!$B$38*Inputs!$B$25*Inputs!$B$26*Inputs!$B$39</f>
-        <v>1092</v>
+        <v>179</v>
+      </c>
+      <c r="B56" s="24" t="n">
+        <f aca="false">Inputs!$B$42*Inputs!$B$29*Inputs!$B$30*Inputs!$B$44</f>
+        <v>819</v>
       </c>
       <c r="C56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B57" s="32" t="str">
-        <f aca="false">IF($B$55&lt;=$B$56,"OK","Need more rooms")</f>
+        <v>180</v>
+      </c>
+      <c r="B57" s="33" t="str">
+        <f aca="false">IF($B$55&lt;=$B$56,"OK","Need more stations")</f>
         <v>OK</v>
       </c>
       <c r="C57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B58" s="22" t="n">
-        <f aca="false">IF(Inputs!$B$27*Inputs!$B$28=0,0,ROUNDDOWN($B$56/(Inputs!$B$27/60*Inputs!$B$28),0))</f>
-        <v>1456</v>
+        <v>181</v>
+      </c>
+      <c r="B58" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$31*Inputs!$B$32+Inputs!$B$9*15=0,0,ROUNDDOWN($B$56/(Inputs!$B$31/60*Inputs!$B$32+Inputs!$B$9*15/60),0))</f>
+        <v>1638</v>
       </c>
       <c r="C58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B59" s="22" t="n">
-        <f aca="false">ROUNDUP($B$55/Inputs!$B$36/Inputs!$B$37,0)</f>
-        <v>5</v>
+        <v>182</v>
+      </c>
+      <c r="B59" s="24" t="n">
+        <f aca="false">ROUNDUP($B$55/Inputs!$B$40/Inputs!$B$41,0)</f>
+        <v>4</v>
       </c>
       <c r="C59" s="6"/>
     </row>
@@ -3144,62 +3259,62 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B62" s="23" t="n">
-        <f aca="false">Inputs!$B$42*MAX(0,Inputs!$B$65-Inputs!$B$66)</f>
-        <v>240000</v>
+        <v>184</v>
+      </c>
+      <c r="B62" s="25" t="n">
+        <f aca="false">Inputs!$B$47*MAX(0,Inputs!$B$70-Inputs!$B$71)</f>
+        <v>72000</v>
       </c>
       <c r="C62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="33" t="n">
-        <f aca="false">Inputs!$B$67</f>
+        <v>117</v>
+      </c>
+      <c r="B63" s="34" t="n">
+        <f aca="false">Inputs!$B$72</f>
         <v>90000</v>
       </c>
       <c r="C63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B64" s="33" t="n">
-        <f aca="false">Inputs!$B$68</f>
+        <v>185</v>
+      </c>
+      <c r="B64" s="34" t="n">
+        <f aca="false">Inputs!$B$73</f>
         <v>70000</v>
       </c>
       <c r="C64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B65" s="25" t="n">
+        <v>186</v>
+      </c>
+      <c r="B65" s="27" t="n">
         <f aca="false">SUM($B$62:$B$64)</f>
-        <v>400000</v>
+        <v>232000</v>
       </c>
       <c r="C65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B66" s="34" t="str">
+        <v>187</v>
+      </c>
+      <c r="B66" s="35" t="n">
         <f aca="false">IF($B$36&lt;=0,"Never",$B$65/$B$36)</f>
-        <v>Never</v>
+        <v>1.07926734866439</v>
       </c>
       <c r="C66" s="6"/>
     </row>
@@ -3228,7 +3343,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3270,7 +3385,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3352,7 +3467,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>0</v>
@@ -3468,1485 +3583,1485 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="22" t="n">
+        <v>132</v>
+      </c>
+      <c r="B5" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="22" t="n">
-        <f aca="false">Inputs!$B$10</f>
-        <v>100</v>
-      </c>
-      <c r="D5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,C5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>137</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,D5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>172.89</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,E5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>207.7033</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,F5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>241.472201</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,G5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>274.22803497</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,H5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>306.0011939209</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,I5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>336.821158103273</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,J5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>366.716523360175</v>
-      </c>
-      <c r="L5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,K5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>395.715027659369</v>
-      </c>
-      <c r="M5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,L5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>423.843576829588</v>
-      </c>
-      <c r="N5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,M5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="O5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,N5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="P5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,O5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="Q5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,P5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="R5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,Q5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="S5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,R5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="T5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,S5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="U5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,T5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="V5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,U5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="W5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,V5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="X5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,W5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="Y5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,X5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="Z5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,Y5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AA5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,Z5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AB5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AA5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AC5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AB5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AD5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AC5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AE5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AD5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AF5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AE5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AG5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AF5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AH5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AG5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AI5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AH5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AJ5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AI5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AK5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AJ5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
-      </c>
-      <c r="AL5" s="22" t="n">
-        <f aca="false">MIN(Inputs!$B$9,AK5*(1-'Unit Economics'!$B$46)+Inputs!$B$11)</f>
-        <v>450</v>
+      <c r="C5" s="24" t="n">
+        <f aca="false">Inputs!$B$14</f>
+        <v>150</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,C5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>185.5</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,D5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>219.935</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,E5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>253.33695</v>
+      </c>
+      <c r="G5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,F5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>285.7368415</v>
+      </c>
+      <c r="H5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,G5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>317.164736255</v>
+      </c>
+      <c r="I5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,H5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>347.64979416735</v>
+      </c>
+      <c r="J5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,I5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>377.220300342329</v>
+      </c>
+      <c r="K5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,J5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>405.90369133206</v>
+      </c>
+      <c r="L5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,K5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>433.726580592098</v>
+      </c>
+      <c r="M5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,L5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>460.714783174335</v>
+      </c>
+      <c r="N5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,M5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>486.893339679105</v>
+      </c>
+      <c r="O5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,N5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>512.286539488732</v>
+      </c>
+      <c r="P5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,O5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>536.91794330407</v>
+      </c>
+      <c r="Q5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,P5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="R5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,Q5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="S5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,R5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="T5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,S5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="U5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,T5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="V5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,U5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="W5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,V5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="X5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,W5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="Y5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,X5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="Z5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,Y5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AA5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,Z5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AB5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AA5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AC5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AB5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AD5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AC5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AE5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AD5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AF5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AE5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AG5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AF5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AH5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AG5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AI5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AH5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AJ5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AI5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AK5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AJ5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
+      </c>
+      <c r="AL5" s="24" t="n">
+        <f aca="false">MIN(Inputs!$B$13,AK5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <v>550</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="23" t="n">
+        <v>139</v>
+      </c>
+      <c r="B6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">C5*'Unit Economics'!$B$44</f>
-        <v>15290</v>
-      </c>
-      <c r="D6" s="23" t="n">
+        <v>24867</v>
+      </c>
+      <c r="D6" s="25" t="n">
         <f aca="false">D5*'Unit Economics'!$B$44</f>
-        <v>20947.3</v>
-      </c>
-      <c r="E6" s="23" t="n">
+        <v>30752.19</v>
+      </c>
+      <c r="E6" s="25" t="n">
         <f aca="false">E5*'Unit Economics'!$B$44</f>
-        <v>26434.881</v>
-      </c>
-      <c r="F6" s="23" t="n">
+        <v>36460.8243</v>
+      </c>
+      <c r="F6" s="25" t="n">
         <f aca="false">F5*'Unit Economics'!$B$44</f>
-        <v>31757.83457</v>
-      </c>
-      <c r="G6" s="23" t="n">
+        <v>41998.199571</v>
+      </c>
+      <c r="G6" s="25" t="n">
         <f aca="false">G5*'Unit Economics'!$B$44</f>
-        <v>36921.0995329</v>
-      </c>
-      <c r="H6" s="23" t="n">
+        <v>47369.45358387</v>
+      </c>
+      <c r="H6" s="25" t="n">
         <f aca="false">H5*'Unit Economics'!$B$44</f>
-        <v>41929.466546913</v>
-      </c>
-      <c r="I6" s="23" t="n">
+        <v>52579.5699763539</v>
+      </c>
+      <c r="I6" s="25" t="n">
         <f aca="false">I5*'Unit Economics'!$B$44</f>
-        <v>46787.5825505056</v>
-      </c>
-      <c r="J6" s="23" t="n">
+        <v>57633.3828770633</v>
+      </c>
+      <c r="J6" s="25" t="n">
         <f aca="false">J5*'Unit Economics'!$B$44</f>
-        <v>51499.9550739904</v>
-      </c>
-      <c r="K6" s="23" t="n">
+        <v>62535.5813907514</v>
+      </c>
+      <c r="K6" s="25" t="n">
         <f aca="false">K5*'Unit Economics'!$B$44</f>
-        <v>56070.9564217707</v>
-      </c>
-      <c r="L6" s="23" t="n">
+        <v>67290.7139490288</v>
+      </c>
+      <c r="L6" s="25" t="n">
         <f aca="false">L5*'Unit Economics'!$B$44</f>
-        <v>60504.8277291176</v>
-      </c>
-      <c r="M6" s="23" t="n">
+        <v>71903.192530558</v>
+      </c>
+      <c r="M6" s="25" t="n">
         <f aca="false">M5*'Unit Economics'!$B$44</f>
-        <v>64805.6828972441</v>
-      </c>
-      <c r="N6" s="23" t="n">
+        <v>76377.2967546412</v>
+      </c>
+      <c r="N6" s="25" t="n">
         <f aca="false">N5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="O6" s="23" t="n">
+        <v>80717.177852002</v>
+      </c>
+      <c r="O6" s="25" t="n">
         <f aca="false">O5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="P6" s="23" t="n">
+        <v>84926.8625164419</v>
+      </c>
+      <c r="P6" s="25" t="n">
         <f aca="false">P5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="Q6" s="23" t="n">
+        <v>89010.2566409487</v>
+      </c>
+      <c r="Q6" s="25" t="n">
         <f aca="false">Q5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="R6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="R6" s="25" t="n">
         <f aca="false">R5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="S6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="S6" s="25" t="n">
         <f aca="false">S5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="T6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="T6" s="25" t="n">
         <f aca="false">T5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="U6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="U6" s="25" t="n">
         <f aca="false">U5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="V6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="V6" s="25" t="n">
         <f aca="false">V5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="W6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="W6" s="25" t="n">
         <f aca="false">W5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="X6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="X6" s="25" t="n">
         <f aca="false">X5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="Y6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="Y6" s="25" t="n">
         <f aca="false">Y5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="Z6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="Z6" s="25" t="n">
         <f aca="false">Z5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AA6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AA6" s="25" t="n">
         <f aca="false">AA5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AB6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AB6" s="25" t="n">
         <f aca="false">AB5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AC6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AC6" s="25" t="n">
         <f aca="false">AC5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AD6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AD6" s="25" t="n">
         <f aca="false">AD5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AE6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AE6" s="25" t="n">
         <f aca="false">AE5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AF6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AF6" s="25" t="n">
         <f aca="false">AF5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AG6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AG6" s="25" t="n">
         <f aca="false">AG5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AH6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AH6" s="25" t="n">
         <f aca="false">AH5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AI6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AI6" s="25" t="n">
         <f aca="false">AI5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AJ6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AJ6" s="25" t="n">
         <f aca="false">AJ5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AK6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AK6" s="25" t="n">
         <f aca="false">AK5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
-      </c>
-      <c r="AL6" s="23" t="n">
+        <v>91179</v>
+      </c>
+      <c r="AL6" s="25" t="n">
         <f aca="false">AL5*'Unit Economics'!$B$44</f>
-        <v>68805</v>
+        <v>91179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="23" t="n">
+        <v>191</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="25" t="n">
         <f aca="false">C5*'Unit Economics'!$B$45</f>
-        <v>5635.02</v>
-      </c>
-      <c r="D7" s="23" t="n">
+        <v>6694.39</v>
+      </c>
+      <c r="D7" s="25" t="n">
         <f aca="false">D5*'Unit Economics'!$B$45</f>
-        <v>7719.9774</v>
-      </c>
-      <c r="E7" s="23" t="n">
+        <v>8278.72896666667</v>
+      </c>
+      <c r="E7" s="25" t="n">
         <f aca="false">E5*'Unit Economics'!$B$45</f>
-        <v>9742.386078</v>
-      </c>
-      <c r="F7" s="23" t="n">
+        <v>9815.53776433333</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <f aca="false">F5*'Unit Economics'!$B$45</f>
-        <v>11704.12249566</v>
-      </c>
-      <c r="G7" s="23" t="n">
+        <v>11306.24229807</v>
+      </c>
+      <c r="G7" s="25" t="n">
         <f aca="false">G5*'Unit Economics'!$B$45</f>
-        <v>13607.0068207902</v>
-      </c>
-      <c r="H7" s="23" t="n">
+        <v>12752.2256957946</v>
+      </c>
+      <c r="H7" s="25" t="n">
         <f aca="false">H5*'Unit Economics'!$B$45</f>
-        <v>15452.8046161665</v>
-      </c>
-      <c r="I7" s="23" t="n">
+        <v>14154.8295915874</v>
+      </c>
+      <c r="I7" s="25" t="n">
         <f aca="false">I5*'Unit Economics'!$B$45</f>
-        <v>17243.2284776815</v>
-      </c>
-      <c r="J7" s="23" t="n">
+        <v>15515.3553705064</v>
+      </c>
+      <c r="J7" s="25" t="n">
         <f aca="false">J5*'Unit Economics'!$B$45</f>
-        <v>18979.9396233511</v>
-      </c>
-      <c r="K7" s="23" t="n">
+        <v>16835.0653760579</v>
+      </c>
+      <c r="K7" s="25" t="n">
         <f aca="false">K5*'Unit Economics'!$B$45</f>
-        <v>20664.5494346505</v>
-      </c>
-      <c r="L7" s="23" t="n">
+        <v>18115.1840814428</v>
+      </c>
+      <c r="L7" s="25" t="n">
         <f aca="false">L5*'Unit Economics'!$B$45</f>
-        <v>22298.620951611</v>
-      </c>
-      <c r="M7" s="23" t="n">
+        <v>19356.8992256662</v>
+      </c>
+      <c r="M7" s="25" t="n">
         <f aca="false">M5*'Unit Economics'!$B$45</f>
-        <v>23883.6703230627</v>
-      </c>
-      <c r="N7" s="23" t="n">
+        <v>20561.3629155629</v>
+      </c>
+      <c r="N7" s="25" t="n">
         <f aca="false">N5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="O7" s="23" t="n">
+        <v>21729.6926947627</v>
+      </c>
+      <c r="O7" s="25" t="n">
         <f aca="false">O5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="P7" s="23" t="n">
+        <v>22862.9725805865</v>
+      </c>
+      <c r="P7" s="25" t="n">
         <f aca="false">P5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="Q7" s="23" t="n">
+        <v>23962.2540698355</v>
+      </c>
+      <c r="Q7" s="25" t="n">
         <f aca="false">Q5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="R7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="R7" s="25" t="n">
         <f aca="false">R5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="S7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="S7" s="25" t="n">
         <f aca="false">S5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="T7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="T7" s="25" t="n">
         <f aca="false">T5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="U7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="U7" s="25" t="n">
         <f aca="false">U5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="V7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="V7" s="25" t="n">
         <f aca="false">V5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="W7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="W7" s="25" t="n">
         <f aca="false">W5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="X7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="X7" s="25" t="n">
         <f aca="false">X5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="Y7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="Y7" s="25" t="n">
         <f aca="false">Y5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="Z7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="Z7" s="25" t="n">
         <f aca="false">Z5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AA7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AA7" s="25" t="n">
         <f aca="false">AA5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AB7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AB7" s="25" t="n">
         <f aca="false">AB5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AC7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AC7" s="25" t="n">
         <f aca="false">AC5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AD7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AD7" s="25" t="n">
         <f aca="false">AD5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AE7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AE7" s="25" t="n">
         <f aca="false">AE5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AF7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AF7" s="25" t="n">
         <f aca="false">AF5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AG7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AG7" s="25" t="n">
         <f aca="false">AG5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AH7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AH7" s="25" t="n">
         <f aca="false">AH5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AI7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AI7" s="25" t="n">
         <f aca="false">AI5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AJ7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AJ7" s="25" t="n">
         <f aca="false">AJ5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AK7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AK7" s="25" t="n">
         <f aca="false">AK5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
-      </c>
-      <c r="AL7" s="23" t="n">
+        <v>24546.0966666667</v>
+      </c>
+      <c r="AL7" s="25" t="n">
         <f aca="false">AL5*'Unit Economics'!$B$45</f>
-        <v>25357.59</v>
+        <v>24546.0966666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>153</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,C6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,D6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,E6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,F6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,G6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,H6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,I6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="J8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,J6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="K8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,K6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="L8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,L6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="M8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,M6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="N8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,N6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="O8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,O6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="P8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,P6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="Q8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,Q6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="R8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,R6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="S8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,S6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="T8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,T6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="U8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,U6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="V8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,V6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="W8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,W6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="X8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,X6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="Y8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,Y6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="Z8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,Z6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AA8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AA6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AB8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AB6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AC8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AC6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AD8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AD6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AE8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AE6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AF8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AF6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AG8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AG6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AH8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AH6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AI8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AI6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AJ8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AJ6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AK8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AK6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
-      </c>
-      <c r="AL8" s="23" t="n">
-        <f aca="false">IF(Inputs!$B$44=2,AL6*Inputs!$B$45,Inputs!$B$42*Inputs!$B$43/12)</f>
-        <v>13750</v>
+      <c r="C8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,C6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>3730.05</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,D6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>4612.8285</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,E6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>5469.123645</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,F6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>6299.72993565</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,G6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>7105.4180375805</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,H6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>7886.93549645308</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,I6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>8645.00743155949</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,J6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>9380.33720861271</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,K6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>10093.6070923543</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,L6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>10785.4788795837</v>
+      </c>
+      <c r="M8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,M6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>11456.5945131962</v>
+      </c>
+      <c r="N8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,N6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>12107.5766778003</v>
+      </c>
+      <c r="O8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,O6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>12739.0293774663</v>
+      </c>
+      <c r="P8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,P6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13351.5384961423</v>
+      </c>
+      <c r="Q8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,Q6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="R8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,R6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="S8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,S6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="T8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,T6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="U8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,U6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="V8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,V6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="W8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,W6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="X8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,X6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="Y8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,Y6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="Z8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,Z6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AA8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AA6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AB8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AB6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AC8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AC6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AD8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AD6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AE8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AE6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AF8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AF6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AG8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AG6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AH8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AH6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AI8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AI6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AJ8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AJ6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AK8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AK6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
+      </c>
+      <c r="AL8" s="25" t="n">
+        <f aca="false">IF(Inputs!$B$49=2,AL6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <v>13676.85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="23" t="n">
+        <v>192</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="D9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="D9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="E9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="E9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="F9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="G9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="G9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="H9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="H9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="I9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="I9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="J9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="J9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="K9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="K9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="L9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="L9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="M9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="M9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="N9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="N9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="O9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="O9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="P9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="P9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="Q9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="Q9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="R9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="R9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="S9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="S9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="T9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="T9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="U9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="U9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="V9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="V9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="W9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="W9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="X9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="X9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="Y9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="Y9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="Z9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="Z9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AA9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AA9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AB9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AB9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AC9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AC9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AD9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AD9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AE9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AE9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AF9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AF9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AG9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AG9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AH9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AH9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AI9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AI9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AJ9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AJ9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AK9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AK9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
-      </c>
-      <c r="AL9" s="23" t="n">
+        <v>35042.6666666667</v>
+      </c>
+      <c r="AL9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>37699.1666666667</v>
+        <v>35042.6666666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="25" t="n">
+        <v>193</v>
+      </c>
+      <c r="B10" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="27" t="n">
         <f aca="false">C6-C7-C8-C9</f>
-        <v>-41794.1866666667</v>
-      </c>
-      <c r="D10" s="25" t="n">
+        <v>-20600.1066666667</v>
+      </c>
+      <c r="D10" s="27" t="n">
         <f aca="false">D6-D7-D8-D9</f>
-        <v>-38221.8440666667</v>
-      </c>
-      <c r="E10" s="25" t="n">
+        <v>-17182.0341333333</v>
+      </c>
+      <c r="E10" s="27" t="n">
         <f aca="false">E6-E7-E8-E9</f>
-        <v>-34756.6717446667</v>
-      </c>
-      <c r="F10" s="25" t="n">
+        <v>-13866.503776</v>
+      </c>
+      <c r="F10" s="27" t="n">
         <f aca="false">F6-F7-F8-F9</f>
-        <v>-31395.4545923267</v>
-      </c>
-      <c r="G10" s="25" t="n">
+        <v>-10650.4393293867</v>
+      </c>
+      <c r="G10" s="27" t="n">
         <f aca="false">G6-G7-G8-G9</f>
-        <v>-28135.0739545569</v>
-      </c>
-      <c r="H10" s="25" t="n">
+        <v>-7530.85681617174</v>
+      </c>
+      <c r="H10" s="27" t="n">
         <f aca="false">H6-H7-H8-H9</f>
-        <v>-24972.5047359202</v>
-      </c>
-      <c r="I10" s="25" t="n">
+        <v>-4504.86177835326</v>
+      </c>
+      <c r="I10" s="27" t="n">
         <f aca="false">I6-I7-I8-I9</f>
-        <v>-21904.8125938426</v>
-      </c>
-      <c r="J10" s="25" t="n">
+        <v>-1569.64659166933</v>
+      </c>
+      <c r="J10" s="27" t="n">
         <f aca="false">J6-J7-J8-J9</f>
-        <v>-18929.1512160273</v>
-      </c>
-      <c r="K10" s="25" t="n">
+        <v>1277.51213941409</v>
+      </c>
+      <c r="K10" s="27" t="n">
         <f aca="false">K6-K7-K8-K9</f>
-        <v>-16042.7596795465</v>
-      </c>
-      <c r="L10" s="25" t="n">
+        <v>4039.256108565</v>
+      </c>
+      <c r="L10" s="27" t="n">
         <f aca="false">L6-L7-L8-L9</f>
-        <v>-13242.9598891601</v>
-      </c>
-      <c r="M10" s="25" t="n">
+        <v>6718.14775864138</v>
+      </c>
+      <c r="M10" s="27" t="n">
         <f aca="false">M6-M7-M8-M9</f>
-        <v>-10527.1540924853</v>
-      </c>
-      <c r="N10" s="25" t="n">
+        <v>9316.67265921547</v>
+      </c>
+      <c r="N10" s="27" t="n">
         <f aca="false">N6-N7-N8-N9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="O10" s="25" t="n">
+        <v>11837.2418127723</v>
+      </c>
+      <c r="O10" s="27" t="n">
         <f aca="false">O6-O7-O8-O9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="P10" s="25" t="n">
+        <v>14282.1938917225</v>
+      </c>
+      <c r="P10" s="27" t="n">
         <f aca="false">P6-P7-P8-P9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="Q10" s="25" t="n">
+        <v>16653.7974083042</v>
+      </c>
+      <c r="Q10" s="27" t="n">
         <f aca="false">Q6-Q7-Q8-Q9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="R10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="R10" s="27" t="n">
         <f aca="false">R6-R7-R8-R9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="S10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="S10" s="27" t="n">
         <f aca="false">S6-S7-S8-S9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="T10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="T10" s="27" t="n">
         <f aca="false">T6-T7-T8-T9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="U10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="U10" s="27" t="n">
         <f aca="false">U6-U7-U8-U9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="V10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="V10" s="27" t="n">
         <f aca="false">V6-V7-V8-V9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="W10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="W10" s="27" t="n">
         <f aca="false">W6-W7-W8-W9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="X10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="X10" s="27" t="n">
         <f aca="false">X6-X7-X8-X9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="Y10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="Y10" s="27" t="n">
         <f aca="false">Y6-Y7-Y8-Y9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="Z10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="Z10" s="27" t="n">
         <f aca="false">Z6-Z7-Z8-Z9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AA10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AA10" s="27" t="n">
         <f aca="false">AA6-AA7-AA8-AA9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AB10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AB10" s="27" t="n">
         <f aca="false">AB6-AB7-AB8-AB9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AC10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AC10" s="27" t="n">
         <f aca="false">AC6-AC7-AC8-AC9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AD10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AD10" s="27" t="n">
         <f aca="false">AD6-AD7-AD8-AD9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AE10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AE10" s="27" t="n">
         <f aca="false">AE6-AE7-AE8-AE9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AF10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AF10" s="27" t="n">
         <f aca="false">AF6-AF7-AF8-AF9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AG10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AG10" s="27" t="n">
         <f aca="false">AG6-AG7-AG8-AG9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AH10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AH10" s="27" t="n">
         <f aca="false">AH6-AH7-AH8-AH9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AI10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AI10" s="27" t="n">
         <f aca="false">AI6-AI7-AI8-AI9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AJ10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AJ10" s="27" t="n">
         <f aca="false">AJ6-AJ7-AJ8-AJ9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AK10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AK10" s="27" t="n">
         <f aca="false">AK6-AK7-AK8-AK9</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AL10" s="25" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AL10" s="27" t="n">
         <f aca="false">AL6-AL7-AL8-AL9</f>
-        <v>-8001.75666666668</v>
+        <v>17913.3866666667</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="23" t="n">
+        <v>194</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <f aca="false">'Unit Economics'!$B$65</f>
-        <v>400000</v>
-      </c>
-      <c r="C11" s="23" t="n">
+        <v>232000</v>
+      </c>
+      <c r="C11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="23" t="n">
+      <c r="H11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="23" t="n">
+      <c r="M11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="23" t="n">
+      <c r="N11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="23" t="n">
+      <c r="O11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="23" t="n">
+      <c r="P11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="23" t="n">
+      <c r="Q11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="23" t="n">
+      <c r="R11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="23" t="n">
+      <c r="S11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="23" t="n">
+      <c r="T11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="23" t="n">
+      <c r="U11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="23" t="n">
+      <c r="V11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="23" t="n">
+      <c r="W11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="23" t="n">
+      <c r="X11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" s="23" t="n">
+      <c r="Y11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="23" t="n">
+      <c r="Z11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AA11" s="23" t="n">
+      <c r="AA11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" s="23" t="n">
+      <c r="AB11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="23" t="n">
+      <c r="AC11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="23" t="n">
+      <c r="AD11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" s="23" t="n">
+      <c r="AE11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" s="23" t="n">
+      <c r="AF11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AG11" s="23" t="n">
+      <c r="AG11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" s="23" t="n">
+      <c r="AH11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="23" t="n">
+      <c r="AI11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" s="23" t="n">
+      <c r="AJ11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AK11" s="23" t="n">
+      <c r="AK11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="AL11" s="23" t="n">
+      <c r="AL11" s="25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="23" t="n">
+        <v>195</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <f aca="false">B10-B11</f>
-        <v>-400000</v>
-      </c>
-      <c r="C12" s="23" t="n">
+        <v>-232000</v>
+      </c>
+      <c r="C12" s="25" t="n">
         <f aca="false">C10-C11</f>
-        <v>-41794.1866666667</v>
-      </c>
-      <c r="D12" s="23" t="n">
+        <v>-20600.1066666667</v>
+      </c>
+      <c r="D12" s="25" t="n">
         <f aca="false">D10-D11</f>
-        <v>-38221.8440666667</v>
-      </c>
-      <c r="E12" s="23" t="n">
+        <v>-17182.0341333333</v>
+      </c>
+      <c r="E12" s="25" t="n">
         <f aca="false">E10-E11</f>
-        <v>-34756.6717446667</v>
-      </c>
-      <c r="F12" s="23" t="n">
+        <v>-13866.503776</v>
+      </c>
+      <c r="F12" s="25" t="n">
         <f aca="false">F10-F11</f>
-        <v>-31395.4545923267</v>
-      </c>
-      <c r="G12" s="23" t="n">
+        <v>-10650.4393293867</v>
+      </c>
+      <c r="G12" s="25" t="n">
         <f aca="false">G10-G11</f>
-        <v>-28135.0739545569</v>
-      </c>
-      <c r="H12" s="23" t="n">
+        <v>-7530.85681617174</v>
+      </c>
+      <c r="H12" s="25" t="n">
         <f aca="false">H10-H11</f>
-        <v>-24972.5047359202</v>
-      </c>
-      <c r="I12" s="23" t="n">
+        <v>-4504.86177835326</v>
+      </c>
+      <c r="I12" s="25" t="n">
         <f aca="false">I10-I11</f>
-        <v>-21904.8125938426</v>
-      </c>
-      <c r="J12" s="23" t="n">
+        <v>-1569.64659166933</v>
+      </c>
+      <c r="J12" s="25" t="n">
         <f aca="false">J10-J11</f>
-        <v>-18929.1512160273</v>
-      </c>
-      <c r="K12" s="23" t="n">
+        <v>1277.51213941409</v>
+      </c>
+      <c r="K12" s="25" t="n">
         <f aca="false">K10-K11</f>
-        <v>-16042.7596795465</v>
-      </c>
-      <c r="L12" s="23" t="n">
+        <v>4039.256108565</v>
+      </c>
+      <c r="L12" s="25" t="n">
         <f aca="false">L10-L11</f>
-        <v>-13242.9598891601</v>
-      </c>
-      <c r="M12" s="23" t="n">
+        <v>6718.14775864138</v>
+      </c>
+      <c r="M12" s="25" t="n">
         <f aca="false">M10-M11</f>
-        <v>-10527.1540924853</v>
-      </c>
-      <c r="N12" s="23" t="n">
+        <v>9316.67265921547</v>
+      </c>
+      <c r="N12" s="25" t="n">
         <f aca="false">N10-N11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="O12" s="23" t="n">
+        <v>11837.2418127723</v>
+      </c>
+      <c r="O12" s="25" t="n">
         <f aca="false">O10-O11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="P12" s="23" t="n">
+        <v>14282.1938917225</v>
+      </c>
+      <c r="P12" s="25" t="n">
         <f aca="false">P10-P11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="Q12" s="23" t="n">
+        <v>16653.7974083042</v>
+      </c>
+      <c r="Q12" s="25" t="n">
         <f aca="false">Q10-Q11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="R12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="R12" s="25" t="n">
         <f aca="false">R10-R11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="S12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="S12" s="25" t="n">
         <f aca="false">S10-S11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="T12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="T12" s="25" t="n">
         <f aca="false">T10-T11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="U12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="U12" s="25" t="n">
         <f aca="false">U10-U11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="V12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="V12" s="25" t="n">
         <f aca="false">V10-V11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="W12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="W12" s="25" t="n">
         <f aca="false">W10-W11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="X12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="X12" s="25" t="n">
         <f aca="false">X10-X11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="Y12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="Y12" s="25" t="n">
         <f aca="false">Y10-Y11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="Z12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="Z12" s="25" t="n">
         <f aca="false">Z10-Z11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AA12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AA12" s="25" t="n">
         <f aca="false">AA10-AA11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AB12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AB12" s="25" t="n">
         <f aca="false">AB10-AB11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AC12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AC12" s="25" t="n">
         <f aca="false">AC10-AC11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AD12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AD12" s="25" t="n">
         <f aca="false">AD10-AD11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AE12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AE12" s="25" t="n">
         <f aca="false">AE10-AE11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AF12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AF12" s="25" t="n">
         <f aca="false">AF10-AF11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AG12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AG12" s="25" t="n">
         <f aca="false">AG10-AG11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AH12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AH12" s="25" t="n">
         <f aca="false">AH10-AH11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AI12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AI12" s="25" t="n">
         <f aca="false">AI10-AI11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AJ12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AJ12" s="25" t="n">
         <f aca="false">AJ10-AJ11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AK12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AK12" s="25" t="n">
         <f aca="false">AK10-AK11</f>
-        <v>-8001.75666666668</v>
-      </c>
-      <c r="AL12" s="23" t="n">
+        <v>17913.3866666667</v>
+      </c>
+      <c r="AL12" s="25" t="n">
         <f aca="false">AL10-AL11</f>
-        <v>-8001.75666666668</v>
+        <v>17913.3866666667</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="25" t="n">
+        <v>196</v>
+      </c>
+      <c r="B13" s="27" t="n">
         <f aca="false">B12</f>
-        <v>-400000</v>
-      </c>
-      <c r="C13" s="25" t="n">
+        <v>-232000</v>
+      </c>
+      <c r="C13" s="27" t="n">
         <f aca="false">B13+C12</f>
-        <v>-441794.186666667</v>
-      </c>
-      <c r="D13" s="25" t="n">
+        <v>-252600.106666667</v>
+      </c>
+      <c r="D13" s="27" t="n">
         <f aca="false">C13+D12</f>
-        <v>-480016.030733333</v>
-      </c>
-      <c r="E13" s="25" t="n">
+        <v>-269782.1408</v>
+      </c>
+      <c r="E13" s="27" t="n">
         <f aca="false">D13+E12</f>
-        <v>-514772.702478</v>
-      </c>
-      <c r="F13" s="25" t="n">
+        <v>-283648.644576</v>
+      </c>
+      <c r="F13" s="27" t="n">
         <f aca="false">E13+F12</f>
-        <v>-546168.157070327</v>
-      </c>
-      <c r="G13" s="25" t="n">
+        <v>-294299.083905387</v>
+      </c>
+      <c r="G13" s="27" t="n">
         <f aca="false">F13+G12</f>
-        <v>-574303.231024884</v>
-      </c>
-      <c r="H13" s="25" t="n">
+        <v>-301829.940721558</v>
+      </c>
+      <c r="H13" s="27" t="n">
         <f aca="false">G13+H12</f>
-        <v>-599275.735760804</v>
-      </c>
-      <c r="I13" s="25" t="n">
+        <v>-306334.802499912</v>
+      </c>
+      <c r="I13" s="27" t="n">
         <f aca="false">H13+I12</f>
-        <v>-621180.548354646</v>
-      </c>
-      <c r="J13" s="25" t="n">
+        <v>-307904.449091581</v>
+      </c>
+      <c r="J13" s="27" t="n">
         <f aca="false">I13+J12</f>
-        <v>-640109.699570673</v>
-      </c>
-      <c r="K13" s="25" t="n">
+        <v>-306626.936952167</v>
+      </c>
+      <c r="K13" s="27" t="n">
         <f aca="false">J13+K12</f>
-        <v>-656152.45925022</v>
-      </c>
-      <c r="L13" s="25" t="n">
+        <v>-302587.680843602</v>
+      </c>
+      <c r="L13" s="27" t="n">
         <f aca="false">K13+L12</f>
-        <v>-669395.41913938</v>
-      </c>
-      <c r="M13" s="25" t="n">
+        <v>-295869.533084961</v>
+      </c>
+      <c r="M13" s="27" t="n">
         <f aca="false">L13+M12</f>
-        <v>-679922.573231865</v>
-      </c>
-      <c r="N13" s="25" t="n">
+        <v>-286552.860425745</v>
+      </c>
+      <c r="N13" s="27" t="n">
         <f aca="false">M13+N12</f>
-        <v>-687924.329898532</v>
-      </c>
-      <c r="O13" s="25" t="n">
+        <v>-274715.618612973</v>
+      </c>
+      <c r="O13" s="27" t="n">
         <f aca="false">N13+O12</f>
-        <v>-695926.086565199</v>
-      </c>
-      <c r="P13" s="25" t="n">
+        <v>-260433.42472125</v>
+      </c>
+      <c r="P13" s="27" t="n">
         <f aca="false">O13+P12</f>
-        <v>-703927.843231865</v>
-      </c>
-      <c r="Q13" s="25" t="n">
+        <v>-243779.627312946</v>
+      </c>
+      <c r="Q13" s="27" t="n">
         <f aca="false">P13+Q12</f>
-        <v>-711929.599898532</v>
-      </c>
-      <c r="R13" s="25" t="n">
+        <v>-225866.240646279</v>
+      </c>
+      <c r="R13" s="27" t="n">
         <f aca="false">Q13+R12</f>
-        <v>-719931.356565199</v>
-      </c>
-      <c r="S13" s="25" t="n">
+        <v>-207952.853979613</v>
+      </c>
+      <c r="S13" s="27" t="n">
         <f aca="false">R13+S12</f>
-        <v>-727933.113231866</v>
-      </c>
-      <c r="T13" s="25" t="n">
+        <v>-190039.467312946</v>
+      </c>
+      <c r="T13" s="27" t="n">
         <f aca="false">S13+T12</f>
-        <v>-735934.869898532</v>
-      </c>
-      <c r="U13" s="25" t="n">
+        <v>-172126.080646279</v>
+      </c>
+      <c r="U13" s="27" t="n">
         <f aca="false">T13+U12</f>
-        <v>-743936.626565199</v>
-      </c>
-      <c r="V13" s="25" t="n">
+        <v>-154212.693979613</v>
+      </c>
+      <c r="V13" s="27" t="n">
         <f aca="false">U13+V12</f>
-        <v>-751938.383231866</v>
-      </c>
-      <c r="W13" s="25" t="n">
+        <v>-136299.307312946</v>
+      </c>
+      <c r="W13" s="27" t="n">
         <f aca="false">V13+W12</f>
-        <v>-759940.139898532</v>
-      </c>
-      <c r="X13" s="25" t="n">
+        <v>-118385.920646279</v>
+      </c>
+      <c r="X13" s="27" t="n">
         <f aca="false">W13+X12</f>
-        <v>-767941.896565199</v>
-      </c>
-      <c r="Y13" s="25" t="n">
+        <v>-100472.533979613</v>
+      </c>
+      <c r="Y13" s="27" t="n">
         <f aca="false">X13+Y12</f>
-        <v>-775943.653231866</v>
-      </c>
-      <c r="Z13" s="25" t="n">
+        <v>-82559.1473129462</v>
+      </c>
+      <c r="Z13" s="27" t="n">
         <f aca="false">Y13+Z12</f>
-        <v>-783945.409898533</v>
-      </c>
-      <c r="AA13" s="25" t="n">
+        <v>-64645.7606462795</v>
+      </c>
+      <c r="AA13" s="27" t="n">
         <f aca="false">Z13+AA12</f>
-        <v>-791947.166565199</v>
-      </c>
-      <c r="AB13" s="25" t="n">
+        <v>-46732.3739796128</v>
+      </c>
+      <c r="AB13" s="27" t="n">
         <f aca="false">AA13+AB12</f>
-        <v>-799948.923231866</v>
-      </c>
-      <c r="AC13" s="25" t="n">
+        <v>-28818.9873129462</v>
+      </c>
+      <c r="AC13" s="27" t="n">
         <f aca="false">AB13+AC12</f>
-        <v>-807950.679898533</v>
-      </c>
-      <c r="AD13" s="25" t="n">
+        <v>-10905.6006462795</v>
+      </c>
+      <c r="AD13" s="27" t="n">
         <f aca="false">AC13+AD12</f>
-        <v>-815952.436565199</v>
-      </c>
-      <c r="AE13" s="25" t="n">
+        <v>7007.78602038718</v>
+      </c>
+      <c r="AE13" s="27" t="n">
         <f aca="false">AD13+AE12</f>
-        <v>-823954.193231866</v>
-      </c>
-      <c r="AF13" s="25" t="n">
+        <v>24921.1726870538</v>
+      </c>
+      <c r="AF13" s="27" t="n">
         <f aca="false">AE13+AF12</f>
-        <v>-831955.949898533</v>
-      </c>
-      <c r="AG13" s="25" t="n">
+        <v>42834.5593537205</v>
+      </c>
+      <c r="AG13" s="27" t="n">
         <f aca="false">AF13+AG12</f>
-        <v>-839957.7065652</v>
-      </c>
-      <c r="AH13" s="25" t="n">
+        <v>60747.9460203872</v>
+      </c>
+      <c r="AH13" s="27" t="n">
         <f aca="false">AG13+AH12</f>
-        <v>-847959.463231866</v>
-      </c>
-      <c r="AI13" s="25" t="n">
+        <v>78661.3326870538</v>
+      </c>
+      <c r="AI13" s="27" t="n">
         <f aca="false">AH13+AI12</f>
-        <v>-855961.219898533</v>
-      </c>
-      <c r="AJ13" s="25" t="n">
+        <v>96574.7193537205</v>
+      </c>
+      <c r="AJ13" s="27" t="n">
         <f aca="false">AI13+AJ12</f>
-        <v>-863962.9765652</v>
-      </c>
-      <c r="AK13" s="25" t="n">
+        <v>114488.106020387</v>
+      </c>
+      <c r="AK13" s="27" t="n">
         <f aca="false">AJ13+AK12</f>
-        <v>-871964.733231866</v>
-      </c>
-      <c r="AL13" s="25" t="n">
+        <v>132401.492687054</v>
+      </c>
+      <c r="AL13" s="27" t="n">
         <f aca="false">AK13+AL12</f>
-        <v>-879966.489898533</v>
+        <v>150314.87935372</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35" t="str">
+        <v>197</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36" t="str">
         <f aca="false">IF(AND(C13&gt;=0,B13&lt;0),C4,"")</f>
         <v/>
       </c>
-      <c r="D14" s="35" t="str">
+      <c r="D14" s="36" t="str">
         <f aca="false">IF(AND(D13&gt;=0,C13&lt;0),D4,"")</f>
         <v/>
       </c>
-      <c r="E14" s="35" t="str">
+      <c r="E14" s="36" t="str">
         <f aca="false">IF(AND(E13&gt;=0,D13&lt;0),E4,"")</f>
         <v/>
       </c>
-      <c r="F14" s="35" t="str">
+      <c r="F14" s="36" t="str">
         <f aca="false">IF(AND(F13&gt;=0,E13&lt;0),F4,"")</f>
         <v/>
       </c>
-      <c r="G14" s="35" t="str">
+      <c r="G14" s="36" t="str">
         <f aca="false">IF(AND(G13&gt;=0,F13&lt;0),G4,"")</f>
         <v/>
       </c>
-      <c r="H14" s="35" t="str">
+      <c r="H14" s="36" t="str">
         <f aca="false">IF(AND(H13&gt;=0,G13&lt;0),H4,"")</f>
         <v/>
       </c>
-      <c r="I14" s="35" t="str">
+      <c r="I14" s="36" t="str">
         <f aca="false">IF(AND(I13&gt;=0,H13&lt;0),I4,"")</f>
         <v/>
       </c>
-      <c r="J14" s="35" t="str">
+      <c r="J14" s="36" t="str">
         <f aca="false">IF(AND(J13&gt;=0,I13&lt;0),J4,"")</f>
         <v/>
       </c>
-      <c r="K14" s="35" t="str">
+      <c r="K14" s="36" t="str">
         <f aca="false">IF(AND(K13&gt;=0,J13&lt;0),K4,"")</f>
         <v/>
       </c>
-      <c r="L14" s="35" t="str">
+      <c r="L14" s="36" t="str">
         <f aca="false">IF(AND(L13&gt;=0,K13&lt;0),L4,"")</f>
         <v/>
       </c>
-      <c r="M14" s="35" t="str">
+      <c r="M14" s="36" t="str">
         <f aca="false">IF(AND(M13&gt;=0,L13&lt;0),M4,"")</f>
         <v/>
       </c>
-      <c r="N14" s="35" t="str">
+      <c r="N14" s="36" t="str">
         <f aca="false">IF(AND(N13&gt;=0,M13&lt;0),N4,"")</f>
         <v/>
       </c>
-      <c r="O14" s="35" t="str">
+      <c r="O14" s="36" t="str">
         <f aca="false">IF(AND(O13&gt;=0,N13&lt;0),O4,"")</f>
         <v/>
       </c>
-      <c r="P14" s="35" t="str">
+      <c r="P14" s="36" t="str">
         <f aca="false">IF(AND(P13&gt;=0,O13&lt;0),P4,"")</f>
         <v/>
       </c>
-      <c r="Q14" s="35" t="str">
+      <c r="Q14" s="36" t="str">
         <f aca="false">IF(AND(Q13&gt;=0,P13&lt;0),Q4,"")</f>
         <v/>
       </c>
-      <c r="R14" s="35" t="str">
+      <c r="R14" s="36" t="str">
         <f aca="false">IF(AND(R13&gt;=0,Q13&lt;0),R4,"")</f>
         <v/>
       </c>
-      <c r="S14" s="35" t="str">
+      <c r="S14" s="36" t="str">
         <f aca="false">IF(AND(S13&gt;=0,R13&lt;0),S4,"")</f>
         <v/>
       </c>
-      <c r="T14" s="35" t="str">
+      <c r="T14" s="36" t="str">
         <f aca="false">IF(AND(T13&gt;=0,S13&lt;0),T4,"")</f>
         <v/>
       </c>
-      <c r="U14" s="35" t="str">
+      <c r="U14" s="36" t="str">
         <f aca="false">IF(AND(U13&gt;=0,T13&lt;0),U4,"")</f>
         <v/>
       </c>
-      <c r="V14" s="35" t="str">
+      <c r="V14" s="36" t="str">
         <f aca="false">IF(AND(V13&gt;=0,U13&lt;0),V4,"")</f>
         <v/>
       </c>
-      <c r="W14" s="35" t="str">
+      <c r="W14" s="36" t="str">
         <f aca="false">IF(AND(W13&gt;=0,V13&lt;0),W4,"")</f>
         <v/>
       </c>
-      <c r="X14" s="35" t="str">
+      <c r="X14" s="36" t="str">
         <f aca="false">IF(AND(X13&gt;=0,W13&lt;0),X4,"")</f>
         <v/>
       </c>
-      <c r="Y14" s="35" t="str">
+      <c r="Y14" s="36" t="str">
         <f aca="false">IF(AND(Y13&gt;=0,X13&lt;0),Y4,"")</f>
         <v/>
       </c>
-      <c r="Z14" s="35" t="str">
+      <c r="Z14" s="36" t="str">
         <f aca="false">IF(AND(Z13&gt;=0,Y13&lt;0),Z4,"")</f>
         <v/>
       </c>
-      <c r="AA14" s="35" t="str">
+      <c r="AA14" s="36" t="str">
         <f aca="false">IF(AND(AA13&gt;=0,Z13&lt;0),AA4,"")</f>
         <v/>
       </c>
-      <c r="AB14" s="35" t="str">
+      <c r="AB14" s="36" t="str">
         <f aca="false">IF(AND(AB13&gt;=0,AA13&lt;0),AB4,"")</f>
         <v/>
       </c>
-      <c r="AC14" s="35" t="str">
+      <c r="AC14" s="36" t="str">
         <f aca="false">IF(AND(AC13&gt;=0,AB13&lt;0),AC4,"")</f>
         <v/>
       </c>
-      <c r="AD14" s="35" t="str">
+      <c r="AD14" s="36" t="n">
         <f aca="false">IF(AND(AD13&gt;=0,AC13&lt;0),AD4,"")</f>
-        <v/>
-      </c>
-      <c r="AE14" s="35" t="str">
+        <v>28</v>
+      </c>
+      <c r="AE14" s="36" t="str">
         <f aca="false">IF(AND(AE13&gt;=0,AD13&lt;0),AE4,"")</f>
         <v/>
       </c>
-      <c r="AF14" s="35" t="str">
+      <c r="AF14" s="36" t="str">
         <f aca="false">IF(AND(AF13&gt;=0,AE13&lt;0),AF4,"")</f>
         <v/>
       </c>
-      <c r="AG14" s="35" t="str">
+      <c r="AG14" s="36" t="str">
         <f aca="false">IF(AND(AG13&gt;=0,AF13&lt;0),AG4,"")</f>
         <v/>
       </c>
-      <c r="AH14" s="35" t="str">
+      <c r="AH14" s="36" t="str">
         <f aca="false">IF(AND(AH13&gt;=0,AG13&lt;0),AH4,"")</f>
         <v/>
       </c>
-      <c r="AI14" s="35" t="str">
+      <c r="AI14" s="36" t="str">
         <f aca="false">IF(AND(AI13&gt;=0,AH13&lt;0),AI4,"")</f>
         <v/>
       </c>
-      <c r="AJ14" s="35" t="str">
+      <c r="AJ14" s="36" t="str">
         <f aca="false">IF(AND(AJ13&gt;=0,AI13&lt;0),AJ4,"")</f>
         <v/>
       </c>
-      <c r="AK14" s="35" t="str">
+      <c r="AK14" s="36" t="str">
         <f aca="false">IF(AND(AK13&gt;=0,AJ13&lt;0),AK4,"")</f>
         <v/>
       </c>
-      <c r="AL14" s="35" t="str">
+      <c r="AL14" s="36" t="str">
         <f aca="false">IF(AND(AL13&gt;=0,AK13&lt;0),AL4,"")</f>
         <v/>
       </c>
@@ -4993,11 +5108,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="3" t="str">
+        <v>198</v>
+      </c>
+      <c r="B16" s="3" t="n">
         <f aca="false">IF(COUNT(C14:AL14)=0,"Beyond 36 months",MIN(C14:AL14))</f>
-        <v>Beyond 36 months</v>
+        <v>28</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -5038,11 +5153,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" s="25" t="n">
+        <v>199</v>
+      </c>
+      <c r="B17" s="27" t="n">
         <f aca="false">MIN(B13:AL13)</f>
-        <v>-879966.489898533</v>
+        <v>-307904.449091581</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -5083,11 +5198,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B18" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="B18" s="27" t="n">
         <f aca="false">AL13</f>
-        <v>-879966.489898533</v>
+        <v>150314.87935372</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -5151,7 +5266,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -5161,7 +5276,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5179,7 +5294,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -5189,247 +5304,247 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" s="36" t="n">
+        <v>204</v>
+      </c>
+      <c r="B5" s="37" t="n">
         <v>130</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="37" t="n">
         <v>150</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="37" t="n">
         <v>175</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="37" t="n">
         <v>195</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="37" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="n">
+      <c r="A6" s="38" t="n">
         <v>250</v>
       </c>
-      <c r="B6" s="23" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-30221.7166666667</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-27311.7166666667</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-23674.2166666667</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-20764.2166666667</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-16399.2166666667</v>
+      <c r="B6" s="25" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-18664.9833333333</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-15754.9833333333</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-12117.4833333333</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-9207.48333333333</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <f aca="false">$A6*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-4842.48333333334</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="n">
+      <c r="A7" s="38" t="n">
         <v>300</v>
       </c>
-      <c r="B7" s="23" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-25976.2266666667</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-22484.2266666667</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-18119.2266666667</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-14627.2266666667</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-9389.22666666667</v>
+      <c r="B7" s="25" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-13189.4466666667</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-9697.44666666667</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-5332.44666666668</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-1840.44666666666</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <f aca="false">$A7*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>3397.55333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="n">
+      <c r="A8" s="38" t="n">
         <v>350</v>
       </c>
-      <c r="B8" s="23" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-21730.7366666667</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-17656.7366666667</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-12564.2366666667</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-8490.23666666667</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-2379.23666666667</v>
+      <c r="B8" s="25" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-7713.91</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-3639.91</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>1452.58999999999</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>5526.59</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <f aca="false">$A8*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>11637.59</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="n">
+      <c r="A9" s="38" t="n">
         <v>400</v>
       </c>
-      <c r="B9" s="23" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-17485.2466666667</v>
-      </c>
-      <c r="C9" s="23" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-12829.2466666667</v>
-      </c>
-      <c r="D9" s="23" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-7009.24666666667</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-2353.24666666667</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>4630.75333333333</v>
+      <c r="B9" s="25" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>-2238.37333333333</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>2417.62666666666</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>8237.62666666666</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>12893.6266666667</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <f aca="false">$A9*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>19877.6266666667</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="n">
+      <c r="A10" s="38" t="n">
         <v>450</v>
       </c>
-      <c r="B10" s="23" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-13239.7566666667</v>
-      </c>
-      <c r="C10" s="23" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-8001.75666666667</v>
-      </c>
-      <c r="D10" s="23" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-1454.25666666666</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>3783.74333333333</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>11640.7433333333</v>
+      <c r="B10" s="25" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>3237.16333333334</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>8475.16333333333</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>15022.6633333333</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>20260.6633333333</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <f aca="false">$A10*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>28117.6633333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="n">
+      <c r="A11" s="38" t="n">
         <v>500</v>
       </c>
-      <c r="B11" s="23" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-8994.26666666666</v>
-      </c>
-      <c r="C11" s="23" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-3174.26666666667</v>
-      </c>
-      <c r="D11" s="23" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>4100.73333333334</v>
-      </c>
-      <c r="E11" s="23" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>9920.73333333333</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>18650.7333333333</v>
+      <c r="B11" s="25" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>8712.7</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>14532.7</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>21807.7</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>27627.7</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <f aca="false">$A11*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>36357.7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="n">
+      <c r="A12" s="38" t="n">
         <v>550</v>
       </c>
-      <c r="B12" s="23" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-4748.77666666666</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>1653.22333333333</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>9655.72333333334</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>16057.7233333333</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>25660.7233333333</v>
+      <c r="B12" s="25" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>14188.2366666667</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>20590.2366666667</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>28592.7366666667</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>34994.7366666667</v>
+      </c>
+      <c r="F12" s="25" t="n">
+        <f aca="false">$A12*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>44597.7366666667</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="38" t="n">
         <v>600</v>
       </c>
-      <c r="B13" s="23" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-503.286666666652</v>
-      </c>
-      <c r="C13" s="23" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>6480.71333333333</v>
-      </c>
-      <c r="D13" s="23" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>15210.7133333333</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>22194.7133333333</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>32670.7133333333</v>
+      <c r="B13" s="25" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>19663.7733333333</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>26647.7733333333</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>35377.7733333333</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>42361.7733333333</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <f aca="false">$A13*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>52837.7733333333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="38" t="n">
         <v>700</v>
       </c>
-      <c r="B14" s="23" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$15)*((B$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>7987.69333333335</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$15)*((C$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>16135.6933333333</v>
-      </c>
-      <c r="D14" s="23" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$15)*((D$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>26320.6933333333</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$15)*((E$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>34468.6933333333</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$15)*((F$5+Inputs!$B$7)*(1-Inputs!$B$8)-Inputs!$B$27*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>46690.6933333333</v>
+      <c r="B14" s="25" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>30614.8466666667</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>38762.8466666667</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>48947.8466666667</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>57095.8466666667</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <f aca="false">$A14*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
+        <v>69317.8466666667</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5450,7 +5565,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -5460,147 +5575,147 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B18" s="36" t="n">
+        <v>206</v>
+      </c>
+      <c r="B18" s="37" t="n">
         <v>130</v>
       </c>
-      <c r="C18" s="36" t="n">
+      <c r="C18" s="37" t="n">
         <v>150</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="37" t="n">
         <v>175</v>
       </c>
-      <c r="E18" s="36" t="n">
+      <c r="E18" s="37" t="n">
         <v>195</v>
       </c>
-      <c r="F18" s="36" t="n">
+      <c r="F18" s="37" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="B19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>3672.14333333334</v>
-      </c>
-      <c r="C19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>8910.14333333333</v>
-      </c>
-      <c r="D19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>15457.6433333333</v>
-      </c>
-      <c r="E19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>20695.6433333333</v>
-      </c>
-      <c r="F19" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A19*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>28552.6433333333</v>
+      <c r="B19" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>24523.2866666667</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>30925.2866666667</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>38927.7866666667</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>45329.7866666667</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>54932.7866666667</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="38" t="n">
+      <c r="A20" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="B20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4783.80666666666</v>
-      </c>
-      <c r="C20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>454.193333333336</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>7001.69333333333</v>
-      </c>
-      <c r="E20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>12239.6933333333</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A20*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>20096.6933333333</v>
+      <c r="B20" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>14188.2366666667</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>20590.2366666667</v>
+      </c>
+      <c r="D20" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>28592.7366666667</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>34994.7366666667</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>44597.7366666667</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="38" t="n">
+      <c r="A21" s="39" t="n">
         <v>45</v>
       </c>
-      <c r="B21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-9011.78166666667</v>
-      </c>
-      <c r="C21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-3773.78166666668</v>
-      </c>
-      <c r="D21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>2773.71833333333</v>
-      </c>
-      <c r="E21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>8011.71833333334</v>
-      </c>
-      <c r="F21" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A21*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>15868.7183333333</v>
+      <c r="B21" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>9020.71166666666</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>15422.7116666667</v>
+      </c>
+      <c r="D21" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>23425.2116666667</v>
+      </c>
+      <c r="E21" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>29827.2116666667</v>
+      </c>
+      <c r="F21" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>39430.2116666667</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="39" t="n">
         <v>60</v>
       </c>
-      <c r="B22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-13239.7566666667</v>
-      </c>
-      <c r="C22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-8001.75666666667</v>
-      </c>
-      <c r="D22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-1454.25666666666</v>
-      </c>
-      <c r="E22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>3783.74333333333</v>
-      </c>
-      <c r="F22" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A22*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>11640.7433333333</v>
+      <c r="B22" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>3853.18666666666</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>10255.1866666667</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>18257.6866666667</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>24659.6866666667</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>34262.6866666667</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="39" t="n">
         <v>90</v>
       </c>
-      <c r="B23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((B$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-21695.7066666667</v>
-      </c>
-      <c r="C23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((C$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-16457.7066666667</v>
-      </c>
-      <c r="D23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((D$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-9910.20666666667</v>
-      </c>
-      <c r="E23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((E$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4672.20666666667</v>
-      </c>
-      <c r="F23" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-Inputs!$B$15)*((F$18+Inputs!$B$7)*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)+Inputs!$B$15*(Inputs!$B$16*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-$A23*(Inputs!$B$28/Inputs!$B$36*Inputs!$B$34*(1+Inputs!$B$35)/60)-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>3184.79333333333</v>
+      <c r="B23" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>-6481.86333333334</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>-79.8633333333346</v>
+      </c>
+      <c r="D23" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>7922.63666666667</v>
+      </c>
+      <c r="E23" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>14324.6366666667</v>
+      </c>
+      <c r="F23" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
+        <v>23927.6366666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5621,7 +5736,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -5631,147 +5746,147 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="36" t="n">
+        <v>208</v>
+      </c>
+      <c r="B27" s="37" t="n">
         <v>100</v>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="37" t="n">
         <v>115</v>
       </c>
-      <c r="D27" s="36" t="n">
+      <c r="D27" s="37" t="n">
         <v>125</v>
       </c>
-      <c r="E27" s="36" t="n">
+      <c r="E27" s="37" t="n">
         <v>140</v>
       </c>
-      <c r="F27" s="36" t="n">
+      <c r="F27" s="37" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="39" t="n">
+      <c r="A28" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="B28" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="C28" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="D28" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="E28" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4680.66666666666</v>
-      </c>
-      <c r="F28" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A28)*'Unit Economics'!$B$41+$A28*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4680.66666666666</v>
+      <c r="B28" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>23398.5</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>23398.5</v>
+      </c>
+      <c r="D28" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>23398.5</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>23398.5</v>
+      </c>
+      <c r="F28" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>23398.5</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39" t="n">
+      <c r="A29" s="40" t="n">
         <v>0.2</v>
       </c>
-      <c r="B29" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-8366.21166666666</v>
-      </c>
-      <c r="C29" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-7151.21166666666</v>
-      </c>
-      <c r="D29" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-6341.21166666666</v>
-      </c>
-      <c r="E29" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-5126.21166666666</v>
-      </c>
-      <c r="F29" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A29)*'Unit Economics'!$B$41+$A29*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-4316.21166666666</v>
+      <c r="B29" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>18034.3683333333</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>19519.3683333333</v>
+      </c>
+      <c r="D29" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>20509.3683333333</v>
+      </c>
+      <c r="E29" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>21994.3683333333</v>
+      </c>
+      <c r="F29" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>22984.3683333333</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="39" t="n">
+      <c r="A30" s="40" t="n">
         <v>0.4</v>
       </c>
-      <c r="B30" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-12051.7566666667</v>
-      </c>
-      <c r="C30" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-9621.75666666667</v>
-      </c>
-      <c r="D30" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-8001.75666666667</v>
-      </c>
-      <c r="E30" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-5571.75666666667</v>
-      </c>
-      <c r="F30" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A30)*'Unit Economics'!$B$41+$A30*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-3951.75666666667</v>
+      <c r="B30" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>12670.2366666667</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>15640.2366666667</v>
+      </c>
+      <c r="D30" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>17620.2366666667</v>
+      </c>
+      <c r="E30" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>20590.2366666667</v>
+      </c>
+      <c r="F30" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>22570.2366666667</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="39" t="n">
+      <c r="A31" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="B31" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-15737.3016666667</v>
-      </c>
-      <c r="C31" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-12092.3016666667</v>
-      </c>
-      <c r="D31" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-9662.30166666666</v>
-      </c>
-      <c r="E31" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-6017.30166666667</v>
-      </c>
-      <c r="F31" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A31)*'Unit Economics'!$B$41+$A31*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-3587.30166666666</v>
+      <c r="B31" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>7306.105</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>11761.105</v>
+      </c>
+      <c r="D31" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>14731.105</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>19186.105</v>
+      </c>
+      <c r="F31" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>22156.105</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="39" t="n">
+      <c r="A32" s="40" t="n">
         <v>0.8</v>
       </c>
-      <c r="B32" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(B$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-19422.8466666667</v>
-      </c>
-      <c r="C32" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(C$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-14562.8466666667</v>
-      </c>
-      <c r="D32" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(D$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-11322.8466666667</v>
-      </c>
-      <c r="E32" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(E$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-6462.84666666666</v>
-      </c>
-      <c r="F32" s="23" t="n">
-        <f aca="false">Inputs!$B$9*((1-$A32)*'Unit Economics'!$B$41+$A32*(F$27*(1-Inputs!$B$19)+Inputs!$B$17*(Inputs!$B$7*(1-Inputs!$B$8)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>-3222.84666666666</v>
+      <c r="B32" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>1941.97333333333</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>7881.97333333334</v>
+      </c>
+      <c r="D32" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>11841.9733333333</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>17781.9733333333</v>
+      </c>
+      <c r="F32" s="25" t="n">
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
+        <v>21741.9733333333</v>
       </c>
     </row>
   </sheetData>
@@ -5823,7 +5938,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -5833,7 +5948,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5852,294 +5967,294 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="21" t="n">
-        <f aca="false">Inputs!B72</f>
+        <v>211</v>
+      </c>
+      <c r="B5" s="23" t="n">
+        <f aca="false">Inputs!B77</f>
         <v>1</v>
       </c>
-      <c r="C5" s="21" t="n">
-        <f aca="false">Inputs!C72</f>
+      <c r="C5" s="23" t="n">
+        <f aca="false">Inputs!C77</f>
         <v>1</v>
       </c>
-      <c r="D5" s="21" t="n">
-        <f aca="false">Inputs!D72</f>
+      <c r="D5" s="23" t="n">
+        <f aca="false">Inputs!D77</f>
         <v>2</v>
       </c>
-      <c r="E5" s="21" t="n">
-        <f aca="false">Inputs!E72</f>
+      <c r="E5" s="23" t="n">
+        <f aca="false">Inputs!E77</f>
         <v>4</v>
       </c>
-      <c r="F5" s="21" t="n">
-        <f aca="false">Inputs!F72</f>
+      <c r="F5" s="23" t="n">
+        <f aca="false">Inputs!F77</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B6" s="22" t="n">
+        <v>212</v>
+      </c>
+      <c r="B6" s="24" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="24" t="n">
         <f aca="false">B5</f>
         <v>1</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="24" t="n">
         <f aca="false">C5</f>
         <v>1</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="24" t="n">
         <f aca="false">D5</f>
         <v>2</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="24" t="n">
         <f aca="false">E5</f>
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="22" t="n">
+        <v>213</v>
+      </c>
+      <c r="B7" s="24" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="24" t="n">
         <f aca="false">B7+B6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">C7+C6</f>
         <v>1</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="24" t="n">
         <f aca="false">D7+D6</f>
         <v>2</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="24" t="n">
         <f aca="false">E7+E6</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="22" t="n">
+        <v>214</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>1</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="24" t="n">
         <f aca="false">C5+C6+C7</f>
         <v>2</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="24" t="n">
         <f aca="false">D5+D6+D7</f>
         <v>4</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">E5+E6+E7</f>
         <v>8</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="24" t="n">
         <f aca="false">F5+F6+F7</f>
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="23" t="n">
+        <v>139</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C6:N6)+B6*SUM('36-Month Ramp'!O6:Z6)+B7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>521754.586322441</v>
-      </c>
-      <c r="C9" s="23" t="n">
+        <v>650484.582785269</v>
+      </c>
+      <c r="C9" s="25" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C6:N6)+C6*SUM('36-Month Ramp'!O6:Z6)+C7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>1347414.58632244</v>
-      </c>
-      <c r="D9" s="23" t="n">
+        <v>1736211.70194266</v>
+      </c>
+      <c r="D9" s="25" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C6:N6)+D6*SUM('36-Month Ramp'!O6:Z6)+D7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>2694829.17264488</v>
-      </c>
-      <c r="E9" s="23" t="n">
+        <v>3480844.28472793</v>
+      </c>
+      <c r="E9" s="25" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C6:N6)+E6*SUM('36-Month Ramp'!O6:Z6)+E7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>5389658.34528977</v>
-      </c>
-      <c r="F9" s="23" t="n">
+        <v>6961688.56945586</v>
+      </c>
+      <c r="F9" s="25" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C6:N6)+F6*SUM('36-Month Ramp'!O6:Z6)+F7*SUM('36-Month Ramp'!AA6:AL6)</f>
-        <v>9735807.51793465</v>
+        <v>12622407.9733412</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="23" t="n">
+        <v>215</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C10:N10)+B6*SUM('36-Month Ramp'!O10:Z10)+B7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-287924.329898532</v>
-      </c>
-      <c r="C10" s="23" t="n">
+        <v>-42715.6186129727</v>
+      </c>
+      <c r="C10" s="25" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C10:N10)+C6*SUM('36-Month Ramp'!O10:Z10)+C7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-383945.409898532</v>
-      </c>
-      <c r="D10" s="23" t="n">
+        <v>167354.239353721</v>
+      </c>
+      <c r="D10" s="25" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C10:N10)+D6*SUM('36-Month Ramp'!O10:Z10)+D7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-767890.819797064</v>
-      </c>
-      <c r="E10" s="23" t="n">
+        <v>339599.260740748</v>
+      </c>
+      <c r="E10" s="25" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C10:N10)+E6*SUM('36-Month Ramp'!O10:Z10)+E7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-1535781.63959413</v>
-      </c>
-      <c r="F10" s="23" t="n">
+        <v>679198.521481496</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C10:N10)+F6*SUM('36-Month Ramp'!O10:Z10)+F7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-2495714.61939119</v>
+        <v>1443828.28018894</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="23" t="n">
-        <f aca="false">-Inputs!B73</f>
+        <v>216</v>
+      </c>
+      <c r="B11" s="25" t="n">
+        <f aca="false">-Inputs!B78</f>
         <v>-150000</v>
       </c>
-      <c r="C11" s="23" t="n">
-        <f aca="false">-Inputs!C73</f>
+      <c r="C11" s="25" t="n">
+        <f aca="false">-Inputs!C78</f>
         <v>-400000</v>
       </c>
-      <c r="D11" s="23" t="n">
-        <f aca="false">-Inputs!D73</f>
+      <c r="D11" s="25" t="n">
+        <f aca="false">-Inputs!D78</f>
         <v>-800000</v>
       </c>
-      <c r="E11" s="23" t="n">
-        <f aca="false">-Inputs!E73</f>
+      <c r="E11" s="25" t="n">
+        <f aca="false">-Inputs!E78</f>
         <v>-1400000</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <f aca="false">-Inputs!F73</f>
+      <c r="F11" s="25" t="n">
+        <f aca="false">-Inputs!F78</f>
         <v>-2200000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="25" t="n">
+        <v>217</v>
+      </c>
+      <c r="B12" s="27" t="n">
         <f aca="false">B10+B11</f>
-        <v>-437924.329898532</v>
-      </c>
-      <c r="C12" s="25" t="n">
+        <v>-192715.618612973</v>
+      </c>
+      <c r="C12" s="27" t="n">
         <f aca="false">C10+C11</f>
-        <v>-783945.409898532</v>
-      </c>
-      <c r="D12" s="25" t="n">
+        <v>-232645.760646279</v>
+      </c>
+      <c r="D12" s="27" t="n">
         <f aca="false">D10+D11</f>
-        <v>-1567890.81979706</v>
-      </c>
-      <c r="E12" s="25" t="n">
+        <v>-460400.739259252</v>
+      </c>
+      <c r="E12" s="27" t="n">
         <f aca="false">E10+E11</f>
-        <v>-2935781.63959413</v>
-      </c>
-      <c r="F12" s="25" t="n">
+        <v>-720801.478518504</v>
+      </c>
+      <c r="F12" s="27" t="n">
         <f aca="false">F10+F11</f>
-        <v>-4695714.61939119</v>
+        <v>-756171.719811063</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="23" t="n">
+        <v>218</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <f aca="false">-B5*'Unit Economics'!$B$65</f>
-        <v>-400000</v>
-      </c>
-      <c r="C13" s="23" t="n">
+        <v>-232000</v>
+      </c>
+      <c r="C13" s="25" t="n">
         <f aca="false">-C5*'Unit Economics'!$B$65</f>
-        <v>-400000</v>
-      </c>
-      <c r="D13" s="23" t="n">
+        <v>-232000</v>
+      </c>
+      <c r="D13" s="25" t="n">
         <f aca="false">-D5*'Unit Economics'!$B$65</f>
-        <v>-800000</v>
-      </c>
-      <c r="E13" s="23" t="n">
+        <v>-464000</v>
+      </c>
+      <c r="E13" s="25" t="n">
         <f aca="false">-E5*'Unit Economics'!$B$65</f>
-        <v>-1600000</v>
-      </c>
-      <c r="F13" s="23" t="n">
+        <v>-928000</v>
+      </c>
+      <c r="F13" s="25" t="n">
         <f aca="false">-F5*'Unit Economics'!$B$65</f>
-        <v>-2400000</v>
+        <v>-1392000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="23" t="n">
+        <v>219</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <f aca="false">B12+B13</f>
-        <v>-837924.329898532</v>
-      </c>
-      <c r="C14" s="23" t="n">
+        <v>-424715.618612973</v>
+      </c>
+      <c r="C14" s="25" t="n">
         <f aca="false">C12+C13</f>
-        <v>-1183945.40989853</v>
-      </c>
-      <c r="D14" s="23" t="n">
+        <v>-464645.760646279</v>
+      </c>
+      <c r="D14" s="25" t="n">
         <f aca="false">D12+D13</f>
-        <v>-2367890.81979706</v>
-      </c>
-      <c r="E14" s="23" t="n">
+        <v>-924400.739259252</v>
+      </c>
+      <c r="E14" s="25" t="n">
         <f aca="false">E12+E13</f>
-        <v>-4535781.63959413</v>
-      </c>
-      <c r="F14" s="23" t="n">
+        <v>-1648801.4785185</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <f aca="false">F12+F13</f>
-        <v>-7095714.61939119</v>
+        <v>-2148171.71981106</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" s="25" t="n">
+        <v>196</v>
+      </c>
+      <c r="B15" s="27" t="n">
         <f aca="false">B14</f>
-        <v>-837924.329898532</v>
-      </c>
-      <c r="C15" s="25" t="n">
+        <v>-424715.618612973</v>
+      </c>
+      <c r="C15" s="27" t="n">
         <f aca="false">B15+C14</f>
-        <v>-2021869.73979706</v>
-      </c>
-      <c r="D15" s="25" t="n">
+        <v>-889361.379259252</v>
+      </c>
+      <c r="D15" s="27" t="n">
         <f aca="false">C15+D14</f>
-        <v>-4389760.55959413</v>
-      </c>
-      <c r="E15" s="25" t="n">
+        <v>-1813762.1185185</v>
+      </c>
+      <c r="E15" s="27" t="n">
         <f aca="false">D15+E14</f>
-        <v>-8925542.19918826</v>
-      </c>
-      <c r="F15" s="25" t="n">
+        <v>-3462563.59703701</v>
+      </c>
+      <c r="F15" s="27" t="n">
         <f aca="false">E15+F14</f>
-        <v>-16021256.8185795</v>
+        <v>-5610735.31684807</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6152,11 +6267,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B17" s="40" t="n">
+        <v>220</v>
+      </c>
+      <c r="B17" s="41" t="n">
         <f aca="false">-MIN(0,MIN(B15:F15))</f>
-        <v>16021256.8185795</v>
+        <v>5610735.31684807</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -6165,7 +6280,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -6199,14 +6314,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -6218,26 +6333,26 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
+        <v>224</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="33" t="n">
+        <v>184</v>
+      </c>
+      <c r="B5" s="34" t="n">
         <f aca="false">'Unit Economics'!$B$62</f>
-        <v>240000</v>
+        <v>72000</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="33" t="n">
+        <v>117</v>
+      </c>
+      <c r="B6" s="34" t="n">
         <f aca="false">'Unit Economics'!$B$63</f>
         <v>90000</v>
       </c>
@@ -6245,9 +6360,9 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="33" t="n">
+        <v>185</v>
+      </c>
+      <c r="B7" s="34" t="n">
         <f aca="false">'Unit Economics'!$B$64</f>
         <v>70000</v>
       </c>
@@ -6255,44 +6370,44 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B8" s="23" t="n">
+        <v>225</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <f aca="false">MAX(0,-'36-Month Ramp'!$B$17-'Unit Economics'!$B$65)</f>
-        <v>479966.489898533</v>
+        <v>75904.4490915811</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B9" s="16" t="n">
+        <v>227</v>
+      </c>
+      <c r="B9" s="17" t="n">
         <v>0.2</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="23" t="n">
+        <v>229</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <f aca="false">SUM($B$5:$B$8)*$B$9</f>
-        <v>175993.297979707</v>
+        <v>61580.8898183162</v>
       </c>
       <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="25" t="n">
+        <v>230</v>
+      </c>
+      <c r="B11" s="27" t="n">
         <f aca="false">SUM($B$5:$B$8)+$B$10</f>
-        <v>1055959.78787824</v>
+        <v>369485.338909897</v>
       </c>
       <c r="C11" s="6"/>
     </row>
@@ -6303,129 +6418,129 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
+        <v>231</v>
+      </c>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>50000</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>100</v>
+        <v>234</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>35</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B16" s="14" t="n">
+        <v>236</v>
+      </c>
+      <c r="B16" s="16" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B17" s="23" t="n">
+        <v>238</v>
+      </c>
+      <c r="B17" s="25" t="n">
         <f aca="false">$B$15*$B$16*Inputs!$B$6</f>
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="B18" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" s="14" t="n">
+        <v>242</v>
+      </c>
+      <c r="B19" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B20" s="14" t="n">
-        <v>3</v>
+        <v>243</v>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B21" s="23" t="n">
-        <f aca="false">$B$18*$B$19*$B$20*Inputs!$B$16</f>
-        <v>37500</v>
+        <v>245</v>
+      </c>
+      <c r="B21" s="25" t="n">
+        <f aca="false">$B$18*$B$19*$B$20*Inputs!$B$20</f>
+        <v>0</v>
       </c>
       <c r="C21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B22" s="10" t="n">
         <v>250000</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B23" s="25" t="n">
+        <v>248</v>
+      </c>
+      <c r="B23" s="27" t="n">
         <f aca="false">MAX(0,$B$11-$B$14-$B$17-$B$21-$B$22)</f>
-        <v>673459.78787824</v>
+        <v>69485.3389098973</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B24" s="25" t="n">
+        <v>250</v>
+      </c>
+      <c r="B24" s="27" t="n">
         <f aca="false">$B$14+$B$17+$B$21+$B$22+$B$23</f>
-        <v>1055959.78787824</v>
+        <v>369485.338909897</v>
       </c>
       <c r="C24" s="6"/>
     </row>
@@ -6436,28 +6551,28 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
+        <v>251</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B27" s="29" t="n">
+        <v>252</v>
+      </c>
+      <c r="B27" s="30" t="n">
         <f aca="false">IF($B$11=0,0,($B$14+$B$23)/$B$11)</f>
-        <v>0.685120585256283</v>
+        <v>0.323383166602545</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B28" s="32" t="str">
+        <v>254</v>
+      </c>
+      <c r="B28" s="33" t="str">
         <f aca="false">IF($B$27&gt;=0.1,"Yes","No")</f>
         <v>Yes</v>
       </c>
@@ -6465,31 +6580,31 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B29" s="16" t="n">
+        <v>255</v>
+      </c>
+      <c r="B29" s="17" t="n">
         <v>0.105</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B30" s="14" t="n">
+        <v>257</v>
+      </c>
+      <c r="B30" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B31" s="23" t="n">
+        <v>258</v>
+      </c>
+      <c r="B31" s="25" t="n">
         <f aca="false">IF($B$22=0,0,-PMT($B$29,$B$30,$B$22))</f>
         <v>41564.3301565634</v>
       </c>
@@ -6497,14 +6612,14 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B32" s="42" t="n">
+        <v>259</v>
+      </c>
+      <c r="B32" s="43" t="n">
         <f aca="false">IF($B$31=0,"No loan",'Unit Economics'!$B$36/$B$31)</f>
-        <v>-2.31017989796324</v>
+        <v>5.171757590951</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -6531,7 +6646,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6539,57 +6654,57 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6597,7 +6712,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/off-hours/Off_Hours_Unit_Economics.xlsx
+++ b/off-hours/Off_Hours_Unit_Economics.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="291">
   <si>
     <t xml:space="preserve">Off Hours: Unit Economics Model</t>
   </si>
@@ -317,13 +317,46 @@
     <t xml:space="preserve">Assumption: target to negotiate. Downtown office vacancy was 25.3% in Q2 2026 (Downtown Boston Alliance)</t>
   </si>
   <si>
+    <t xml:space="preserve">Minimum monthly rent under revenue share (floor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: landlords usually ask for the greater of a base rent or the % of revenue (~$30/sq ft/yr here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot months at reduced rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From you: lower rent while you prove the concept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot rent per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: to negotiate. Pilot is in the same space so you only build out once</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lounge seats</t>
   </si>
   <si>
     <t xml:space="preserve">Front of house and programming</t>
   </si>
   <si>
-    <t xml:space="preserve">General manager salary (per year)</t>
+    <t xml:space="preserve">Part-time general manager (per year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From you: part-time GM. Assumption: ~25 hrs/week at ~$35/hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your salary (per year, before taxes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From you: about $8K/month after taxes. Treated as a company cost, not a location cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months of your salary paid before opening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: lease signing to opening day</t>
   </si>
   <si>
     <t xml:space="preserve">Host / front desk hourly pay</t>
@@ -416,7 +449,7 @@
     <t xml:space="preserve">HQ overhead (team, tech, recruiting, legal)</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumptions. HQ grows as you hire ops, a regional manager per ~5 locations, and finance</t>
+    <t xml:space="preserve">Assumptions. Year 1 HQ includes your salary. HQ grows as you hire ops, a regional manager per ~5 locations, and finance</t>
   </si>
   <si>
     <t xml:space="preserve">One location at steady state (monthly)</t>
@@ -488,123 +521,138 @@
     <t xml:space="preserve">Fixed costs (same whether you have 200 or 500 members)</t>
   </si>
   <si>
+    <t xml:space="preserve">Rent (after the pilot period)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-time general manager (incl. taxes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hosts / front desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ritual facilitators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other operating costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total fixed costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location profit before HQ costs ("4-wall EBITDA")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-wall margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual 4-wall EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your salary (incl. payroll taxes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit after paying you (one-location company)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual profit after paying you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massage labor per active member (incl. extra massages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other variable cost per active member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution per self-paying member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution per employer seat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended contribution per member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended revenue per member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended variable cost per member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blended monthly churn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed costs (rent counted as fixed lease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even members (fixed lease)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even members incl. your salary (revenue-share rent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even members (revenue-share rent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity checks (can the space handle these members?)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lounge: people at the busiest hour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lounge OK?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massage hours booked per month (incl. extra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chair station hours available per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chair stations OK?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max active-member equivalents the chair stations can serve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-time therapists needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening investment and payback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildout (net of landlord allowance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-opening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total cash to open one location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple payback at steady state (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First location, month by month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month 0 = opening costs and your pre-opening salary. Rent uses the pilot rate for the pilot months. Members start at the opening-day number, add new members monthly (self-paying + employer seats, same mix as Inputs), lose blended churn, and cap at steady state.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable costs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rent</t>
   </si>
   <si>
-    <t xml:space="preserve">General manager (incl. taxes and benefits)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hosts / front desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ritual facilitators</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other operating costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total fixed costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location profit before HQ costs ("4-wall EBITDA")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-wall margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual 4-wall EBITDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Break-even</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massage labor per active member (incl. extra massages)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other variable cost per active member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribution per self-paying member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribution per employer seat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blended contribution per member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blended revenue per member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blended variable cost per member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blended monthly churn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed costs (rent counted as fixed lease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Break-even members (fixed lease)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Break-even members (revenue-share rent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capacity checks (can the space handle these members?)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lounge: people at the busiest hour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lounge OK?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massage hours booked per month (incl. extra)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chair station hours available per month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chair stations OK?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max active-member equivalents the chair stations can serve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part-time therapists needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opening investment and payback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildout (net of landlord allowance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-opening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total cash to open one location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple payback at steady state (years)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First location, month by month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month 0 = opening costs. Members start at the opening-day number, add new members monthly (self-paying + employer seats, same mix as Inputs), lose blended churn, and cap at steady state.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variable costs</t>
-  </si>
-  <si>
     <t xml:space="preserve">Other fixed costs</t>
   </si>
   <si>
@@ -614,7 +662,7 @@
     <t xml:space="preserve">Opening costs</t>
   </si>
   <si>
-    <t xml:space="preserve">Net cash flow</t>
+    <t xml:space="preserve">Net cash flow (after your salary)</t>
   </si>
   <si>
     <t xml:space="preserve">Cumulative cash</t>
@@ -623,7 +671,10 @@
     <t xml:space="preserve">Payback month flag</t>
   </si>
   <si>
-    <t xml:space="preserve">Payback month (cash back from opening costs)</t>
+    <t xml:space="preserve">Your salary (incl. taxes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payback month (cash back from opening costs and your salary)</t>
   </si>
   <si>
     <t xml:space="preserve">Lowest cash point (most cash at risk)</t>
@@ -704,10 +755,10 @@
     <t xml:space="preserve">Uses: what the money pays for</t>
   </si>
   <si>
-    <t xml:space="preserve">Operating losses until the location covers itself</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest cumulative cash on the 36-Month Ramp, minus opening costs</t>
+    <t xml:space="preserve">Your salary and operating losses until the location covers itself</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest cumulative cash on the 36-Month Ramp, minus opening costs. Includes your salary before and after opening</t>
   </si>
   <si>
     <t xml:space="preserve">Contingency (% of the above)</t>
@@ -770,7 +821,7 @@
     <t xml:space="preserve">SBA 7(a) loan</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumption. Requires a personal guarantee and at least 10% equity injection for a startup (SOP 50 10 8)</t>
+    <t xml:space="preserve">Set to 0: SBA requires an unlimited personal guarantee from every 20%+ owner (13 CFR 120.160), which you ruled out</t>
   </si>
   <si>
     <t xml:space="preserve">Investors / angels / friends and family (left to raise)</t>
@@ -1587,7 +1638,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -2242,40 +2293,50 @@
       <c r="A51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B51" s="19" t="n">
-        <v>45</v>
+      <c r="B51" s="10" t="n">
+        <v>6000</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
+      <c r="A52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>99</v>
+      </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
+      <c r="A53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B54" s="12" t="n">
-        <v>80000</v>
+        <v>102</v>
+      </c>
+      <c r="B54" s="19" t="n">
+        <v>45</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>33</v>
@@ -2285,42 +2346,32 @@
       <c r="F54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B55" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B56" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="A56" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B57" s="19" t="n">
-        <v>30</v>
+        <v>104</v>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>45000</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -2328,42 +2379,52 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B58" s="12" t="n">
-        <v>125</v>
+        <v>106</v>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>120000</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>33</v>
+        <v>107</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
+      <c r="A59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
+      <c r="A60" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B61" s="12" t="n">
-        <v>2500</v>
+        <v>111</v>
+      </c>
+      <c r="B61" s="18" t="n">
+        <v>1</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>33</v>
@@ -2374,13 +2435,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B62" s="12" t="n">
-        <v>3000</v>
+        <v>112</v>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>30</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -2388,10 +2449,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B63" s="12" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>33</v>
@@ -2401,39 +2462,29 @@
       <c r="F63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B64" s="12" t="n">
-        <v>800</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B65" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="A65" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B66" s="12" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>33</v>
@@ -2444,10 +2495,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B67" s="12" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>33</v>
@@ -2457,32 +2508,42 @@
       <c r="F67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
+      <c r="A68" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
+      <c r="A69" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" s="10" t="n">
         <v>120</v>
       </c>
+      <c r="B70" s="12" t="n">
+        <v>4000</v>
+      </c>
       <c r="C70" s="11" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -2490,13 +2551,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B71" s="10" t="n">
-        <v>90</v>
+        <v>121</v>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>1000</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -2504,119 +2565,179 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B72" s="12" t="n">
-        <v>90000</v>
+        <v>700</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B73" s="12" t="n">
-        <v>70000</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
+      <c r="A74" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B75" s="10" t="n">
         <v>120</v>
       </c>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
+      <c r="C75" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F76" s="3" t="s">
+      <c r="A76" s="2" t="s">
         <v>126</v>
       </c>
+      <c r="B76" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B77" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" s="19" t="n">
-        <v>6</v>
-      </c>
+      <c r="A77" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="s">
-        <v>128</v>
+      <c r="A78" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="B78" s="12" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C78" s="12" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D78" s="12" t="n">
-        <v>800000</v>
-      </c>
-      <c r="E78" s="12" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>2200000</v>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="11" t="s">
-        <v>129</v>
-      </c>
+      <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B82" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" s="19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C83" s="12" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D83" s="12" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2634,7 +2755,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
@@ -2644,14 +2765,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2663,18 +2784,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Inputs!$B$13</f>
@@ -2684,7 +2805,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">$B$5*(1-Inputs!$B$19)</f>
@@ -2694,7 +2815,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">$B$5*Inputs!$B$19</f>
@@ -2704,7 +2825,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">$B$6+$B$7*Inputs!$B$21</f>
@@ -2719,18 +2840,18 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">$B$6*Inputs!$B$6</f>
@@ -2743,7 +2864,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B12" s="25" t="n">
         <f aca="false">$B$7*Inputs!$B$20</f>
@@ -2756,7 +2877,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B13" s="25" t="n">
         <f aca="false">$B$8*Inputs!$B$11</f>
@@ -2769,7 +2890,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">$B$11+$B$12+$B$13</f>
@@ -2787,18 +2908,18 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>133</v>
-      </c>
       <c r="C16" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">($B$11+$B$13)*Inputs!$B$12</f>
@@ -2811,7 +2932,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">$B$12*Inputs!$B$23</f>
@@ -2824,7 +2945,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">$B$8*(Inputs!$B$31/60*Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)+Inputs!$B$43)</f>
@@ -2837,7 +2958,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">$B$8*Inputs!$B$26*Inputs!$B$33*Inputs!$B$34</f>
@@ -2850,7 +2971,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B21" s="25" t="n">
         <f aca="false">$B$8*Inputs!$B$26*Inputs!$B$35</f>
@@ -2863,7 +2984,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B22" s="27" t="n">
         <f aca="false">SUM($B$17:$B$21)</f>
@@ -2876,7 +2997,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B23" s="27" t="n">
         <f aca="false">$B$14-$B$22</f>
@@ -2894,21 +3015,21 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B26" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,$B$14*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(Inputs!$B$49=2,MAX(Inputs!$B$51,$B$14*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12)</f>
         <v>13676.85</v>
       </c>
       <c r="C26" s="26" t="n">
@@ -2918,23 +3039,23 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B27" s="25" t="n">
-        <f aca="false">Inputs!$B$54*(1+Inputs!$B$39)/12</f>
-        <v>7666.66666666667</v>
+        <f aca="false">Inputs!$B$57*(1+Inputs!$B$39)/12</f>
+        <v>4312.5</v>
       </c>
       <c r="C27" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B27/$B$5)</f>
-        <v>13.9393939393939</v>
+        <v>7.84090909090909</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B28" s="25" t="n">
-        <f aca="false">Inputs!$B$29*Inputs!$B$30*Inputs!$B$56*Inputs!$B$55*(1+Inputs!$B$39)</f>
+        <f aca="false">Inputs!$B$29*Inputs!$B$30*Inputs!$B$61*Inputs!$B$60*(1+Inputs!$B$39)</f>
         <v>10626</v>
       </c>
       <c r="C28" s="26" t="n">
@@ -2944,10 +3065,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B29" s="25" t="n">
-        <f aca="false">Inputs!$B$57*Inputs!$B$58</f>
+        <f aca="false">Inputs!$B$62*Inputs!$B$63</f>
         <v>3750</v>
       </c>
       <c r="C29" s="26" t="n">
@@ -2957,10 +3078,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B30" s="25" t="n">
-        <f aca="false">Inputs!$B$61+Inputs!$B$62+Inputs!$B$63+Inputs!$B$64+Inputs!$B$65+Inputs!$B$66+Inputs!$B$67</f>
+        <f aca="false">Inputs!$B$66+Inputs!$B$67+Inputs!$B$68+Inputs!$B$69+Inputs!$B$70+Inputs!$B$71+Inputs!$B$72</f>
         <v>13000</v>
       </c>
       <c r="C30" s="26" t="n">
@@ -2970,15 +3091,15 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">SUM($B$26:$B$30)</f>
-        <v>48719.5166666667</v>
+        <v>45365.35</v>
       </c>
       <c r="C31" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B31/$B$5)</f>
-        <v>88.5809393939394</v>
+        <v>82.4824545454545</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2988,335 +3109,375 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B34" s="27" t="n">
         <f aca="false">$B$23-$B$31</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="C34" s="26" t="n">
         <f aca="false">IF($B$5=0,0,B34/$B$5)</f>
-        <v>32.5697939393939</v>
+        <v>38.6682787878788</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B35" s="28" t="n">
         <f aca="false">IF($B$14=0,0,$B$34/$B$14)</f>
-        <v>0.19646395186026</v>
+        <v>0.233250565736994</v>
       </c>
       <c r="C35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B36" s="27" t="n">
         <f aca="false">$B$34*12</f>
-        <v>214960.64</v>
+        <v>255210.64</v>
       </c>
       <c r="C36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
+      <c r="A37" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="25" t="n">
+        <f aca="false">Inputs!$B$58*(1+Inputs!$B$39)/12</f>
+        <v>11500</v>
+      </c>
       <c r="C37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>134</v>
-      </c>
+      <c r="A38" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B38" s="27" t="n">
+        <f aca="false">$B$34-$B$37</f>
+        <v>9767.55333333334</v>
+      </c>
+      <c r="C38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B39" s="15" t="n">
+      <c r="A39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="27" t="n">
+        <f aca="false">$B$38*12</f>
+        <v>117210.64</v>
+      </c>
+      <c r="C39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="15" t="n">
         <f aca="false">Inputs!$B$31/60*Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)+Inputs!$B$43</f>
         <v>29.1333333333333</v>
       </c>
-      <c r="C39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B40" s="15" t="n">
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B43" s="15" t="n">
         <f aca="false">Inputs!$B$26*(Inputs!$B$33*Inputs!$B$34+Inputs!$B$35)</f>
         <v>12.42</v>
       </c>
-      <c r="C40" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B41" s="15" t="n">
-        <f aca="false">(Inputs!$B$6+Inputs!$B$11)*(1-Inputs!$B$12)-$B$39-$B$40</f>
-        <v>126.256666666667</v>
-      </c>
-      <c r="C41" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" s="15" t="n">
-        <f aca="false">Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$B$39-$B$40)</f>
-        <v>113.491833333333</v>
-      </c>
-      <c r="C42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B43" s="29" t="n">
-        <f aca="false">(1-Inputs!$B$19)*$B$41+Inputs!$B$19*$B$42</f>
-        <v>121.150733333333</v>
-      </c>
       <c r="C43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B44" s="15" t="n">
+        <f aca="false">(Inputs!$B$6+Inputs!$B$11)*(1-Inputs!$B$12)-$B$42-$B$43</f>
+        <v>126.256666666667</v>
+      </c>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" s="15" t="n">
+        <f aca="false">Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$B$42-$B$43)</f>
+        <v>113.491833333333</v>
+      </c>
+      <c r="C45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B46" s="29" t="n">
+        <f aca="false">(1-Inputs!$B$19)*$B$44+Inputs!$B$19*$B$45</f>
+        <v>121.150733333333</v>
+      </c>
+      <c r="C46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B47" s="15" t="n">
         <f aca="false">(1-Inputs!$B$19)*(Inputs!$B$6+Inputs!$B$11)+Inputs!$B$19*(Inputs!$B$20+Inputs!$B$21*Inputs!$B$11)</f>
         <v>165.78</v>
       </c>
-      <c r="C44" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B45" s="15" t="n">
-        <f aca="false">$B$44-$B$43</f>
+      <c r="C47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="15" t="n">
+        <f aca="false">$B$47-$B$46</f>
         <v>44.6292666666667</v>
       </c>
-      <c r="C45" s="6"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B46" s="30" t="n">
+      <c r="C48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="30" t="n">
         <f aca="false">(1-Inputs!$B$19)*Inputs!$B$16+Inputs!$B$19*Inputs!$B$22</f>
         <v>0.03</v>
       </c>
-      <c r="C46" s="6"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="25" t="n">
+      <c r="C49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="25" t="n">
         <f aca="false">$B$31-$B$26+Inputs!$B$47*Inputs!$B$48/12</f>
-        <v>46042.6666666667</v>
-      </c>
-      <c r="C47" s="6"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B48" s="31" t="n">
-        <f aca="false">IF($B$43&lt;=0,"Never",ROUNDUP($B$47/$B$43,0))</f>
-        <v>381</v>
-      </c>
-      <c r="C48" s="6"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B49" s="31" t="n">
-        <f aca="false">IF($B$43-$B$44*Inputs!$B$50&lt;=0,"Never",ROUNDUP(($B$47-Inputs!$B$47*Inputs!$B$48/12)/($B$43-$B$44*Inputs!$B$50),0))</f>
-        <v>364</v>
-      </c>
-      <c r="C49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
+        <v>42688.5</v>
+      </c>
       <c r="C50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>134</v>
-      </c>
+      <c r="A51" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="31" t="n">
+        <f aca="false">IF($B$46&lt;=0,"Never",ROUNDUP($B$50/$B$46,0))</f>
+        <v>353</v>
+      </c>
+      <c r="C51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B52" s="32" t="n">
+      <c r="A52" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B52" s="31" t="n">
+        <f aca="false">IF($B$46-$B$47*Inputs!$B$50&lt;=0,"Never",ROUNDUP(($B$50-Inputs!$B$47*Inputs!$B$48/12+$B$37)/($B$46-$B$47*Inputs!$B$50),0))</f>
+        <v>449</v>
+      </c>
+      <c r="C52" s="6"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B53" s="31" t="n">
+        <f aca="false">IF($B$46-$B$47*Inputs!$B$50&lt;=0,"Never",ROUNDUP(($B$50-Inputs!$B$47*Inputs!$B$48/12)/($B$46-$B$47*Inputs!$B$50),0))</f>
+        <v>330</v>
+      </c>
+      <c r="C53" s="6"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B56" s="32" t="n">
         <f aca="false">$B$8*Inputs!$B$26/Inputs!$B$30*Inputs!$B$27/Inputs!$B$29*Inputs!$B$28</f>
         <v>25.3392857142857</v>
       </c>
-      <c r="C52" s="6"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="23" t="n">
-        <f aca="false">Inputs!$B$51</f>
+      <c r="C56" s="6"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="23" t="n">
+        <f aca="false">Inputs!$B$54</f>
         <v>45</v>
       </c>
-      <c r="C53" s="6"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="B54" s="33" t="str">
-        <f aca="false">IF($B$52&lt;=$B$53,"OK","Over capacity")</f>
+      <c r="C57" s="6"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="33" t="str">
+        <f aca="false">IF($B$56&lt;=$B$57,"OK","Over capacity")</f>
         <v>OK</v>
       </c>
-      <c r="C54" s="6"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B55" s="24" t="n">
+      <c r="C58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B59" s="24" t="n">
         <f aca="false">$B$8*(Inputs!$B$31/60*Inputs!$B$32+Inputs!$B$9*15/60)</f>
         <v>236.5</v>
       </c>
-      <c r="C55" s="6"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B56" s="24" t="n">
+      <c r="C59" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" s="24" t="n">
         <f aca="false">Inputs!$B$42*Inputs!$B$29*Inputs!$B$30*Inputs!$B$44</f>
         <v>819</v>
       </c>
-      <c r="C56" s="6"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B57" s="33" t="str">
-        <f aca="false">IF($B$55&lt;=$B$56,"OK","Need more stations")</f>
+      <c r="C60" s="6"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" s="33" t="str">
+        <f aca="false">IF($B$59&lt;=$B$60,"OK","Need more stations")</f>
         <v>OK</v>
       </c>
-      <c r="C57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B58" s="24" t="n">
-        <f aca="false">IF(Inputs!$B$31*Inputs!$B$32+Inputs!$B$9*15=0,0,ROUNDDOWN($B$56/(Inputs!$B$31/60*Inputs!$B$32+Inputs!$B$9*15/60),0))</f>
-        <v>1638</v>
-      </c>
-      <c r="C58" s="6"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B59" s="24" t="n">
-        <f aca="false">ROUNDUP($B$55/Inputs!$B$40/Inputs!$B$41,0)</f>
-        <v>4</v>
-      </c>
-      <c r="C59" s="6"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>134</v>
-      </c>
+      <c r="C61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B62" s="25" t="n">
-        <f aca="false">Inputs!$B$47*MAX(0,Inputs!$B$70-Inputs!$B$71)</f>
-        <v>72000</v>
+        <v>196</v>
+      </c>
+      <c r="B62" s="24" t="n">
+        <f aca="false">IF(Inputs!$B$31*Inputs!$B$32+Inputs!$B$9*15=0,0,ROUNDDOWN($B$60/(Inputs!$B$31/60*Inputs!$B$32+Inputs!$B$9*15/60),0))</f>
+        <v>1638</v>
       </c>
       <c r="C62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B63" s="34" t="n">
-        <f aca="false">Inputs!$B$72</f>
+        <v>197</v>
+      </c>
+      <c r="B63" s="24" t="n">
+        <f aca="false">ROUNDUP($B$59/Inputs!$B$40/Inputs!$B$41,0)</f>
+        <v>4</v>
+      </c>
+      <c r="C63" s="6"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="25" t="n">
+        <f aca="false">Inputs!$B$47*MAX(0,Inputs!$B$75-Inputs!$B$76)</f>
+        <v>72000</v>
+      </c>
+      <c r="C66" s="6"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" s="34" t="n">
+        <f aca="false">Inputs!$B$77</f>
         <v>90000</v>
       </c>
-      <c r="C63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B64" s="34" t="n">
-        <f aca="false">Inputs!$B$73</f>
+      <c r="C67" s="6"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B68" s="34" t="n">
+        <f aca="false">Inputs!$B$78</f>
         <v>70000</v>
       </c>
-      <c r="C64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="B65" s="27" t="n">
-        <f aca="false">SUM($B$62:$B$64)</f>
+      <c r="C68" s="6"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" s="27" t="n">
+        <f aca="false">SUM($B$66:$B$68)</f>
         <v>232000</v>
       </c>
-      <c r="C65" s="6"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B66" s="35" t="n">
-        <f aca="false">IF($B$36&lt;=0,"Never",$B$65/$B$36)</f>
-        <v>1.07926734866439</v>
-      </c>
-      <c r="C66" s="6"/>
+      <c r="C69" s="6"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B70" s="35" t="n">
+        <f aca="false">IF($B$36&lt;=0,"Never",$B$69/$B$36)</f>
+        <v>0.90905300813477</v>
+      </c>
+      <c r="C70" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3343,7 +3504,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3385,7 +3546,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3467,7 +3628,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>0</v>
@@ -3583,7 +3744,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>0</v>
@@ -3593,912 +3754,912 @@
         <v>150</v>
       </c>
       <c r="D5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,C5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,C5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>185.5</v>
       </c>
       <c r="E5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,D5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,D5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>219.935</v>
       </c>
       <c r="F5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,E5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,E5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>253.33695</v>
       </c>
       <c r="G5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,F5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,F5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>285.7368415</v>
       </c>
       <c r="H5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,G5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,G5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>317.164736255</v>
       </c>
       <c r="I5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,H5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,H5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>347.64979416735</v>
       </c>
       <c r="J5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,I5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,I5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>377.220300342329</v>
       </c>
       <c r="K5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,J5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,J5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>405.90369133206</v>
       </c>
       <c r="L5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,K5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,K5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>433.726580592098</v>
       </c>
       <c r="M5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,L5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,L5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>460.714783174335</v>
       </c>
       <c r="N5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,M5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,M5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>486.893339679105</v>
       </c>
       <c r="O5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,N5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,N5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>512.286539488732</v>
       </c>
       <c r="P5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,O5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,O5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>536.91794330407</v>
       </c>
       <c r="Q5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,P5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,P5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="R5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,Q5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,Q5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="S5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,R5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,R5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="T5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,S5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,S5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="U5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,T5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,T5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="V5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,U5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,U5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="W5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,V5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,V5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="X5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,W5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,W5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="Y5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,X5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,X5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="Z5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,Y5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,Y5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AA5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,Z5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,Z5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AB5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AA5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AA5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AC5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AB5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AB5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AD5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AC5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AC5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AE5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AD5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AD5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AF5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AE5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AE5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AG5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AF5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AF5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AH5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AG5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AG5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AI5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AH5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AH5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AJ5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AI5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AI5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AK5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AJ5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AJ5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
       <c r="AL5" s="24" t="n">
-        <f aca="false">MIN(Inputs!$B$13,AK5*(1-'Unit Economics'!$B$46)+Inputs!$B$15)</f>
+        <f aca="false">MIN(Inputs!$B$13,AK5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B6" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="25" t="n">
-        <f aca="false">C5*'Unit Economics'!$B$44</f>
+        <f aca="false">C5*'Unit Economics'!$B$47</f>
         <v>24867</v>
       </c>
       <c r="D6" s="25" t="n">
-        <f aca="false">D5*'Unit Economics'!$B$44</f>
+        <f aca="false">D5*'Unit Economics'!$B$47</f>
         <v>30752.19</v>
       </c>
       <c r="E6" s="25" t="n">
-        <f aca="false">E5*'Unit Economics'!$B$44</f>
+        <f aca="false">E5*'Unit Economics'!$B$47</f>
         <v>36460.8243</v>
       </c>
       <c r="F6" s="25" t="n">
-        <f aca="false">F5*'Unit Economics'!$B$44</f>
+        <f aca="false">F5*'Unit Economics'!$B$47</f>
         <v>41998.199571</v>
       </c>
       <c r="G6" s="25" t="n">
-        <f aca="false">G5*'Unit Economics'!$B$44</f>
+        <f aca="false">G5*'Unit Economics'!$B$47</f>
         <v>47369.45358387</v>
       </c>
       <c r="H6" s="25" t="n">
-        <f aca="false">H5*'Unit Economics'!$B$44</f>
+        <f aca="false">H5*'Unit Economics'!$B$47</f>
         <v>52579.5699763539</v>
       </c>
       <c r="I6" s="25" t="n">
-        <f aca="false">I5*'Unit Economics'!$B$44</f>
+        <f aca="false">I5*'Unit Economics'!$B$47</f>
         <v>57633.3828770633</v>
       </c>
       <c r="J6" s="25" t="n">
-        <f aca="false">J5*'Unit Economics'!$B$44</f>
+        <f aca="false">J5*'Unit Economics'!$B$47</f>
         <v>62535.5813907514</v>
       </c>
       <c r="K6" s="25" t="n">
-        <f aca="false">K5*'Unit Economics'!$B$44</f>
+        <f aca="false">K5*'Unit Economics'!$B$47</f>
         <v>67290.7139490288</v>
       </c>
       <c r="L6" s="25" t="n">
-        <f aca="false">L5*'Unit Economics'!$B$44</f>
+        <f aca="false">L5*'Unit Economics'!$B$47</f>
         <v>71903.192530558</v>
       </c>
       <c r="M6" s="25" t="n">
-        <f aca="false">M5*'Unit Economics'!$B$44</f>
+        <f aca="false">M5*'Unit Economics'!$B$47</f>
         <v>76377.2967546412</v>
       </c>
       <c r="N6" s="25" t="n">
-        <f aca="false">N5*'Unit Economics'!$B$44</f>
+        <f aca="false">N5*'Unit Economics'!$B$47</f>
         <v>80717.177852002</v>
       </c>
       <c r="O6" s="25" t="n">
-        <f aca="false">O5*'Unit Economics'!$B$44</f>
+        <f aca="false">O5*'Unit Economics'!$B$47</f>
         <v>84926.8625164419</v>
       </c>
       <c r="P6" s="25" t="n">
-        <f aca="false">P5*'Unit Economics'!$B$44</f>
+        <f aca="false">P5*'Unit Economics'!$B$47</f>
         <v>89010.2566409487</v>
       </c>
       <c r="Q6" s="25" t="n">
-        <f aca="false">Q5*'Unit Economics'!$B$44</f>
+        <f aca="false">Q5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="R6" s="25" t="n">
-        <f aca="false">R5*'Unit Economics'!$B$44</f>
+        <f aca="false">R5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="S6" s="25" t="n">
-        <f aca="false">S5*'Unit Economics'!$B$44</f>
+        <f aca="false">S5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="T6" s="25" t="n">
-        <f aca="false">T5*'Unit Economics'!$B$44</f>
+        <f aca="false">T5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="U6" s="25" t="n">
-        <f aca="false">U5*'Unit Economics'!$B$44</f>
+        <f aca="false">U5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="V6" s="25" t="n">
-        <f aca="false">V5*'Unit Economics'!$B$44</f>
+        <f aca="false">V5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="W6" s="25" t="n">
-        <f aca="false">W5*'Unit Economics'!$B$44</f>
+        <f aca="false">W5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="X6" s="25" t="n">
-        <f aca="false">X5*'Unit Economics'!$B$44</f>
+        <f aca="false">X5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="Y6" s="25" t="n">
-        <f aca="false">Y5*'Unit Economics'!$B$44</f>
+        <f aca="false">Y5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="Z6" s="25" t="n">
-        <f aca="false">Z5*'Unit Economics'!$B$44</f>
+        <f aca="false">Z5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AA6" s="25" t="n">
-        <f aca="false">AA5*'Unit Economics'!$B$44</f>
+        <f aca="false">AA5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AB6" s="25" t="n">
-        <f aca="false">AB5*'Unit Economics'!$B$44</f>
+        <f aca="false">AB5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AC6" s="25" t="n">
-        <f aca="false">AC5*'Unit Economics'!$B$44</f>
+        <f aca="false">AC5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AD6" s="25" t="n">
-        <f aca="false">AD5*'Unit Economics'!$B$44</f>
+        <f aca="false">AD5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AE6" s="25" t="n">
-        <f aca="false">AE5*'Unit Economics'!$B$44</f>
+        <f aca="false">AE5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AF6" s="25" t="n">
-        <f aca="false">AF5*'Unit Economics'!$B$44</f>
+        <f aca="false">AF5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AG6" s="25" t="n">
-        <f aca="false">AG5*'Unit Economics'!$B$44</f>
+        <f aca="false">AG5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AH6" s="25" t="n">
-        <f aca="false">AH5*'Unit Economics'!$B$44</f>
+        <f aca="false">AH5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AI6" s="25" t="n">
-        <f aca="false">AI5*'Unit Economics'!$B$44</f>
+        <f aca="false">AI5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AJ6" s="25" t="n">
-        <f aca="false">AJ5*'Unit Economics'!$B$44</f>
+        <f aca="false">AJ5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AK6" s="25" t="n">
-        <f aca="false">AK5*'Unit Economics'!$B$44</f>
+        <f aca="false">AK5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
       <c r="AL6" s="25" t="n">
-        <f aca="false">AL5*'Unit Economics'!$B$44</f>
+        <f aca="false">AL5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B7" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="25" t="n">
-        <f aca="false">C5*'Unit Economics'!$B$45</f>
+        <f aca="false">C5*'Unit Economics'!$B$48</f>
         <v>6694.39</v>
       </c>
       <c r="D7" s="25" t="n">
-        <f aca="false">D5*'Unit Economics'!$B$45</f>
+        <f aca="false">D5*'Unit Economics'!$B$48</f>
         <v>8278.72896666667</v>
       </c>
       <c r="E7" s="25" t="n">
-        <f aca="false">E5*'Unit Economics'!$B$45</f>
+        <f aca="false">E5*'Unit Economics'!$B$48</f>
         <v>9815.53776433333</v>
       </c>
       <c r="F7" s="25" t="n">
-        <f aca="false">F5*'Unit Economics'!$B$45</f>
+        <f aca="false">F5*'Unit Economics'!$B$48</f>
         <v>11306.24229807</v>
       </c>
       <c r="G7" s="25" t="n">
-        <f aca="false">G5*'Unit Economics'!$B$45</f>
+        <f aca="false">G5*'Unit Economics'!$B$48</f>
         <v>12752.2256957946</v>
       </c>
       <c r="H7" s="25" t="n">
-        <f aca="false">H5*'Unit Economics'!$B$45</f>
+        <f aca="false">H5*'Unit Economics'!$B$48</f>
         <v>14154.8295915874</v>
       </c>
       <c r="I7" s="25" t="n">
-        <f aca="false">I5*'Unit Economics'!$B$45</f>
+        <f aca="false">I5*'Unit Economics'!$B$48</f>
         <v>15515.3553705064</v>
       </c>
       <c r="J7" s="25" t="n">
-        <f aca="false">J5*'Unit Economics'!$B$45</f>
+        <f aca="false">J5*'Unit Economics'!$B$48</f>
         <v>16835.0653760579</v>
       </c>
       <c r="K7" s="25" t="n">
-        <f aca="false">K5*'Unit Economics'!$B$45</f>
+        <f aca="false">K5*'Unit Economics'!$B$48</f>
         <v>18115.1840814428</v>
       </c>
       <c r="L7" s="25" t="n">
-        <f aca="false">L5*'Unit Economics'!$B$45</f>
+        <f aca="false">L5*'Unit Economics'!$B$48</f>
         <v>19356.8992256662</v>
       </c>
       <c r="M7" s="25" t="n">
-        <f aca="false">M5*'Unit Economics'!$B$45</f>
+        <f aca="false">M5*'Unit Economics'!$B$48</f>
         <v>20561.3629155629</v>
       </c>
       <c r="N7" s="25" t="n">
-        <f aca="false">N5*'Unit Economics'!$B$45</f>
+        <f aca="false">N5*'Unit Economics'!$B$48</f>
         <v>21729.6926947627</v>
       </c>
       <c r="O7" s="25" t="n">
-        <f aca="false">O5*'Unit Economics'!$B$45</f>
+        <f aca="false">O5*'Unit Economics'!$B$48</f>
         <v>22862.9725805865</v>
       </c>
       <c r="P7" s="25" t="n">
-        <f aca="false">P5*'Unit Economics'!$B$45</f>
+        <f aca="false">P5*'Unit Economics'!$B$48</f>
         <v>23962.2540698355</v>
       </c>
       <c r="Q7" s="25" t="n">
-        <f aca="false">Q5*'Unit Economics'!$B$45</f>
+        <f aca="false">Q5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="R7" s="25" t="n">
-        <f aca="false">R5*'Unit Economics'!$B$45</f>
+        <f aca="false">R5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="S7" s="25" t="n">
-        <f aca="false">S5*'Unit Economics'!$B$45</f>
+        <f aca="false">S5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="T7" s="25" t="n">
-        <f aca="false">T5*'Unit Economics'!$B$45</f>
+        <f aca="false">T5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="U7" s="25" t="n">
-        <f aca="false">U5*'Unit Economics'!$B$45</f>
+        <f aca="false">U5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="V7" s="25" t="n">
-        <f aca="false">V5*'Unit Economics'!$B$45</f>
+        <f aca="false">V5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="W7" s="25" t="n">
-        <f aca="false">W5*'Unit Economics'!$B$45</f>
+        <f aca="false">W5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="X7" s="25" t="n">
-        <f aca="false">X5*'Unit Economics'!$B$45</f>
+        <f aca="false">X5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="Y7" s="25" t="n">
-        <f aca="false">Y5*'Unit Economics'!$B$45</f>
+        <f aca="false">Y5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="Z7" s="25" t="n">
-        <f aca="false">Z5*'Unit Economics'!$B$45</f>
+        <f aca="false">Z5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AA7" s="25" t="n">
-        <f aca="false">AA5*'Unit Economics'!$B$45</f>
+        <f aca="false">AA5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AB7" s="25" t="n">
-        <f aca="false">AB5*'Unit Economics'!$B$45</f>
+        <f aca="false">AB5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AC7" s="25" t="n">
-        <f aca="false">AC5*'Unit Economics'!$B$45</f>
+        <f aca="false">AC5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AD7" s="25" t="n">
-        <f aca="false">AD5*'Unit Economics'!$B$45</f>
+        <f aca="false">AD5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AE7" s="25" t="n">
-        <f aca="false">AE5*'Unit Economics'!$B$45</f>
+        <f aca="false">AE5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AF7" s="25" t="n">
-        <f aca="false">AF5*'Unit Economics'!$B$45</f>
+        <f aca="false">AF5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AG7" s="25" t="n">
-        <f aca="false">AG5*'Unit Economics'!$B$45</f>
+        <f aca="false">AG5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AH7" s="25" t="n">
-        <f aca="false">AH5*'Unit Economics'!$B$45</f>
+        <f aca="false">AH5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AI7" s="25" t="n">
-        <f aca="false">AI5*'Unit Economics'!$B$45</f>
+        <f aca="false">AI5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AJ7" s="25" t="n">
-        <f aca="false">AJ5*'Unit Economics'!$B$45</f>
+        <f aca="false">AJ5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AK7" s="25" t="n">
-        <f aca="false">AK5*'Unit Economics'!$B$45</f>
+        <f aca="false">AK5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
       <c r="AL7" s="25" t="n">
-        <f aca="false">AL5*'Unit Economics'!$B$45</f>
+        <f aca="false">AL5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="B8" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,C6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
-        <v>3730.05</v>
+        <f aca="false">IF(C4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,C6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
+        <v>3000</v>
       </c>
       <c r="D8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,D6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
-        <v>4612.8285</v>
+        <f aca="false">IF(D4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,D6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
+        <v>3000</v>
       </c>
       <c r="E8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,E6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
-        <v>5469.123645</v>
+        <f aca="false">IF(E4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,E6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
+        <v>3000</v>
       </c>
       <c r="F8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,F6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
-        <v>6299.72993565</v>
+        <f aca="false">IF(F4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,F6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
+        <v>3000</v>
       </c>
       <c r="G8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,G6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
-        <v>7105.4180375805</v>
+        <f aca="false">IF(G4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,G6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
+        <v>3000</v>
       </c>
       <c r="H8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,H6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
-        <v>7886.93549645308</v>
+        <f aca="false">IF(H4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,H6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
+        <v>3000</v>
       </c>
       <c r="I8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,I6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(I4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,I6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>8645.00743155949</v>
       </c>
       <c r="J8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,J6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(J4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,J6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>9380.33720861271</v>
       </c>
       <c r="K8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,K6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(K4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,K6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>10093.6070923543</v>
       </c>
       <c r="L8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,L6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(L4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,L6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>10785.4788795837</v>
       </c>
       <c r="M8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,M6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(M4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,M6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>11456.5945131962</v>
       </c>
       <c r="N8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,N6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(N4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,N6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>12107.5766778003</v>
       </c>
       <c r="O8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,O6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(O4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,O6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>12739.0293774663</v>
       </c>
       <c r="P8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,P6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(P4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,P6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13351.5384961423</v>
       </c>
       <c r="Q8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,Q6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(Q4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,Q6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="R8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,R6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(R4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,R6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="S8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,S6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(S4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,S6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="T8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,T6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(T4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,T6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="U8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,U6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(U4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,U6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="V8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,V6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(V4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,V6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="W8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,W6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(W4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,W6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="X8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,X6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(X4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,X6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="Y8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,Y6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(Y4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,Y6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="Z8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,Z6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(Z4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,Z6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AA8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AA6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AA4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AA6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AB8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AB6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AB4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AB6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AC8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AC6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AC4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AC6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AD8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AD6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AD4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AD6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AE8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AE6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AE4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AE6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AF8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AF6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AF4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AF6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AG8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AG6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AG4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AG6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AH8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AH6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AH4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AH6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AI8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AI6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AI4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AI6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AJ8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AJ6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AJ4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AJ6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AK8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AK6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AK4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AK6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
       <c r="AL8" s="25" t="n">
-        <f aca="false">IF(Inputs!$B$49=2,AL6*Inputs!$B$50,Inputs!$B$47*Inputs!$B$48/12)</f>
+        <f aca="false">IF(AL4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AL6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="D9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="E9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="F9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="H9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="I9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="J9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="K9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="L9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="M9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="N9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="O9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="P9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="Q9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="S9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="T9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="U9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="V9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="W9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="X9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="Y9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="Z9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AA9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AB9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AC9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AD9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AE9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AF9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AG9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AH9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AI9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AJ9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AK9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
       <c r="AL9" s="25" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
-        <v>35042.6666666667</v>
+        <v>31688.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="B10" s="27" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="27" t="n">
         <f aca="false">C6-C7-C8-C9</f>
-        <v>-20600.1066666667</v>
+        <v>-16515.89</v>
       </c>
       <c r="D10" s="27" t="n">
         <f aca="false">D6-D7-D8-D9</f>
-        <v>-17182.0341333333</v>
+        <v>-12215.0389666667</v>
       </c>
       <c r="E10" s="27" t="n">
         <f aca="false">E6-E7-E8-E9</f>
-        <v>-13866.503776</v>
+        <v>-8043.21346433333</v>
       </c>
       <c r="F10" s="27" t="n">
         <f aca="false">F6-F7-F8-F9</f>
-        <v>-10650.4393293867</v>
+        <v>-3996.54272707</v>
       </c>
       <c r="G10" s="27" t="n">
         <f aca="false">G6-G7-G8-G9</f>
-        <v>-7530.85681617174</v>
+        <v>-71.2721119245689</v>
       </c>
       <c r="H10" s="27" t="n">
         <f aca="false">H6-H7-H8-H9</f>
-        <v>-4504.86177835326</v>
+        <v>3736.2403847665</v>
       </c>
       <c r="I10" s="27" t="n">
         <f aca="false">I6-I7-I8-I9</f>
-        <v>-1569.64659166933</v>
+        <v>1784.52007499734</v>
       </c>
       <c r="J10" s="27" t="n">
         <f aca="false">J6-J7-J8-J9</f>
-        <v>1277.51213941409</v>
+        <v>4631.67880608076</v>
       </c>
       <c r="K10" s="27" t="n">
         <f aca="false">K6-K7-K8-K9</f>
-        <v>4039.256108565</v>
+        <v>7393.42277523167</v>
       </c>
       <c r="L10" s="27" t="n">
         <f aca="false">L6-L7-L8-L9</f>
-        <v>6718.14775864138</v>
+        <v>10072.314425308</v>
       </c>
       <c r="M10" s="27" t="n">
         <f aca="false">M6-M7-M8-M9</f>
-        <v>9316.67265921547</v>
+        <v>12670.8393258821</v>
       </c>
       <c r="N10" s="27" t="n">
         <f aca="false">N6-N7-N8-N9</f>
-        <v>11837.2418127723</v>
+        <v>15191.408479439</v>
       </c>
       <c r="O10" s="27" t="n">
         <f aca="false">O6-O7-O8-O9</f>
-        <v>14282.1938917225</v>
+        <v>17636.3605583892</v>
       </c>
       <c r="P10" s="27" t="n">
         <f aca="false">P6-P7-P8-P9</f>
-        <v>16653.7974083042</v>
+        <v>20007.9640749708</v>
       </c>
       <c r="Q10" s="27" t="n">
         <f aca="false">Q6-Q7-Q8-Q9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="R10" s="27" t="n">
         <f aca="false">R6-R7-R8-R9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="S10" s="27" t="n">
         <f aca="false">S6-S7-S8-S9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="T10" s="27" t="n">
         <f aca="false">T6-T7-T8-T9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="U10" s="27" t="n">
         <f aca="false">U6-U7-U8-U9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="V10" s="27" t="n">
         <f aca="false">V6-V7-V8-V9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="W10" s="27" t="n">
         <f aca="false">W6-W7-W8-W9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="X10" s="27" t="n">
         <f aca="false">X6-X7-X8-X9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="Y10" s="27" t="n">
         <f aca="false">Y6-Y7-Y8-Y9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="Z10" s="27" t="n">
         <f aca="false">Z6-Z7-Z8-Z9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AA10" s="27" t="n">
         <f aca="false">AA6-AA7-AA8-AA9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AB10" s="27" t="n">
         <f aca="false">AB6-AB7-AB8-AB9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AC10" s="27" t="n">
         <f aca="false">AC6-AC7-AC8-AC9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AD10" s="27" t="n">
         <f aca="false">AD6-AD7-AD8-AD9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AE10" s="27" t="n">
         <f aca="false">AE6-AE7-AE8-AE9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AF10" s="27" t="n">
         <f aca="false">AF6-AF7-AF8-AF9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AG10" s="27" t="n">
         <f aca="false">AG6-AG7-AG8-AG9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AH10" s="27" t="n">
         <f aca="false">AH6-AH7-AH8-AH9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AI10" s="27" t="n">
         <f aca="false">AI6-AI7-AI8-AI9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AJ10" s="27" t="n">
         <f aca="false">AJ6-AJ7-AJ8-AJ9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AK10" s="27" t="n">
         <f aca="false">AK6-AK7-AK8-AK9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
       <c r="AL10" s="27" t="n">
         <f aca="false">AL6-AL7-AL8-AL9</f>
-        <v>17913.3866666667</v>
+        <v>21267.5533333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B11" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$65</f>
+        <f aca="false">'Unit Economics'!$B$69</f>
         <v>232000</v>
       </c>
       <c r="C11" s="25" t="n">
@@ -4612,313 +4773,313 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B12" s="25" t="n">
-        <f aca="false">B10-B11</f>
-        <v>-232000</v>
+        <f aca="false">B10-B11-B15</f>
+        <v>-278000</v>
       </c>
       <c r="C12" s="25" t="n">
-        <f aca="false">C10-C11</f>
-        <v>-20600.1066666667</v>
+        <f aca="false">C10-C11-C15</f>
+        <v>-28015.89</v>
       </c>
       <c r="D12" s="25" t="n">
-        <f aca="false">D10-D11</f>
-        <v>-17182.0341333333</v>
+        <f aca="false">D10-D11-D15</f>
+        <v>-23715.0389666667</v>
       </c>
       <c r="E12" s="25" t="n">
-        <f aca="false">E10-E11</f>
-        <v>-13866.503776</v>
+        <f aca="false">E10-E11-E15</f>
+        <v>-19543.2134643333</v>
       </c>
       <c r="F12" s="25" t="n">
-        <f aca="false">F10-F11</f>
-        <v>-10650.4393293867</v>
+        <f aca="false">F10-F11-F15</f>
+        <v>-15496.54272707</v>
       </c>
       <c r="G12" s="25" t="n">
-        <f aca="false">G10-G11</f>
-        <v>-7530.85681617174</v>
+        <f aca="false">G10-G11-G15</f>
+        <v>-11571.2721119246</v>
       </c>
       <c r="H12" s="25" t="n">
-        <f aca="false">H10-H11</f>
-        <v>-4504.86177835326</v>
+        <f aca="false">H10-H11-H15</f>
+        <v>-7763.7596152335</v>
       </c>
       <c r="I12" s="25" t="n">
-        <f aca="false">I10-I11</f>
-        <v>-1569.64659166933</v>
+        <f aca="false">I10-I11-I15</f>
+        <v>-9715.47992500266</v>
       </c>
       <c r="J12" s="25" t="n">
-        <f aca="false">J10-J11</f>
-        <v>1277.51213941409</v>
+        <f aca="false">J10-J11-J15</f>
+        <v>-6868.32119391924</v>
       </c>
       <c r="K12" s="25" t="n">
-        <f aca="false">K10-K11</f>
-        <v>4039.256108565</v>
+        <f aca="false">K10-K11-K15</f>
+        <v>-4106.57722476833</v>
       </c>
       <c r="L12" s="25" t="n">
-        <f aca="false">L10-L11</f>
-        <v>6718.14775864138</v>
+        <f aca="false">L10-L11-L15</f>
+        <v>-1427.68557469195</v>
       </c>
       <c r="M12" s="25" t="n">
-        <f aca="false">M10-M11</f>
-        <v>9316.67265921547</v>
+        <f aca="false">M10-M11-M15</f>
+        <v>1170.83932588214</v>
       </c>
       <c r="N12" s="25" t="n">
-        <f aca="false">N10-N11</f>
-        <v>11837.2418127723</v>
+        <f aca="false">N10-N11-N15</f>
+        <v>3691.40847943901</v>
       </c>
       <c r="O12" s="25" t="n">
-        <f aca="false">O10-O11</f>
-        <v>14282.1938917225</v>
+        <f aca="false">O10-O11-O15</f>
+        <v>6136.36055838917</v>
       </c>
       <c r="P12" s="25" t="n">
-        <f aca="false">P10-P11</f>
-        <v>16653.7974083042</v>
+        <f aca="false">P10-P11-P15</f>
+        <v>8507.96407497083</v>
       </c>
       <c r="Q12" s="25" t="n">
-        <f aca="false">Q10-Q11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">Q10-Q11-Q15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="R12" s="25" t="n">
-        <f aca="false">R10-R11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">R10-R11-R15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="S12" s="25" t="n">
-        <f aca="false">S10-S11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">S10-S11-S15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="T12" s="25" t="n">
-        <f aca="false">T10-T11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">T10-T11-T15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="U12" s="25" t="n">
-        <f aca="false">U10-U11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">U10-U11-U15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="V12" s="25" t="n">
-        <f aca="false">V10-V11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">V10-V11-V15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="W12" s="25" t="n">
-        <f aca="false">W10-W11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">W10-W11-W15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="X12" s="25" t="n">
-        <f aca="false">X10-X11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">X10-X11-X15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="Y12" s="25" t="n">
-        <f aca="false">Y10-Y11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">Y10-Y11-Y15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="Z12" s="25" t="n">
-        <f aca="false">Z10-Z11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">Z10-Z11-Z15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AA12" s="25" t="n">
-        <f aca="false">AA10-AA11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AA10-AA11-AA15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AB12" s="25" t="n">
-        <f aca="false">AB10-AB11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AB10-AB11-AB15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AC12" s="25" t="n">
-        <f aca="false">AC10-AC11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AC10-AC11-AC15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AD12" s="25" t="n">
-        <f aca="false">AD10-AD11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AD10-AD11-AD15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AE12" s="25" t="n">
-        <f aca="false">AE10-AE11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AE10-AE11-AE15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AF12" s="25" t="n">
-        <f aca="false">AF10-AF11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AF10-AF11-AF15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AG12" s="25" t="n">
-        <f aca="false">AG10-AG11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AG10-AG11-AG15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AH12" s="25" t="n">
-        <f aca="false">AH10-AH11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AH10-AH11-AH15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AI12" s="25" t="n">
-        <f aca="false">AI10-AI11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AI10-AI11-AI15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AJ12" s="25" t="n">
-        <f aca="false">AJ10-AJ11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AJ10-AJ11-AJ15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AK12" s="25" t="n">
-        <f aca="false">AK10-AK11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AK10-AK11-AK15</f>
+        <v>9767.55333333334</v>
       </c>
       <c r="AL12" s="25" t="n">
-        <f aca="false">AL10-AL11</f>
-        <v>17913.3866666667</v>
+        <f aca="false">AL10-AL11-AL15</f>
+        <v>9767.55333333334</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B13" s="27" t="n">
         <f aca="false">B12</f>
-        <v>-232000</v>
+        <v>-278000</v>
       </c>
       <c r="C13" s="27" t="n">
         <f aca="false">B13+C12</f>
-        <v>-252600.106666667</v>
+        <v>-306015.89</v>
       </c>
       <c r="D13" s="27" t="n">
         <f aca="false">C13+D12</f>
-        <v>-269782.1408</v>
+        <v>-329730.928966667</v>
       </c>
       <c r="E13" s="27" t="n">
         <f aca="false">D13+E12</f>
-        <v>-283648.644576</v>
+        <v>-349274.142431</v>
       </c>
       <c r="F13" s="27" t="n">
         <f aca="false">E13+F12</f>
-        <v>-294299.083905387</v>
+        <v>-364770.68515807</v>
       </c>
       <c r="G13" s="27" t="n">
         <f aca="false">F13+G12</f>
-        <v>-301829.940721558</v>
+        <v>-376341.957269995</v>
       </c>
       <c r="H13" s="27" t="n">
         <f aca="false">G13+H12</f>
-        <v>-306334.802499912</v>
+        <v>-384105.716885228</v>
       </c>
       <c r="I13" s="27" t="n">
         <f aca="false">H13+I12</f>
-        <v>-307904.449091581</v>
+        <v>-393821.196810231</v>
       </c>
       <c r="J13" s="27" t="n">
         <f aca="false">I13+J12</f>
-        <v>-306626.936952167</v>
+        <v>-400689.51800415</v>
       </c>
       <c r="K13" s="27" t="n">
         <f aca="false">J13+K12</f>
-        <v>-302587.680843602</v>
+        <v>-404796.095228918</v>
       </c>
       <c r="L13" s="27" t="n">
         <f aca="false">K13+L12</f>
-        <v>-295869.533084961</v>
+        <v>-406223.78080361</v>
       </c>
       <c r="M13" s="27" t="n">
         <f aca="false">L13+M12</f>
-        <v>-286552.860425745</v>
+        <v>-405052.941477728</v>
       </c>
       <c r="N13" s="27" t="n">
         <f aca="false">M13+N12</f>
-        <v>-274715.618612973</v>
+        <v>-401361.532998289</v>
       </c>
       <c r="O13" s="27" t="n">
         <f aca="false">N13+O12</f>
-        <v>-260433.42472125</v>
+        <v>-395225.1724399</v>
       </c>
       <c r="P13" s="27" t="n">
         <f aca="false">O13+P12</f>
-        <v>-243779.627312946</v>
+        <v>-386717.208364929</v>
       </c>
       <c r="Q13" s="27" t="n">
         <f aca="false">P13+Q12</f>
-        <v>-225866.240646279</v>
+        <v>-376949.655031596</v>
       </c>
       <c r="R13" s="27" t="n">
         <f aca="false">Q13+R12</f>
-        <v>-207952.853979613</v>
+        <v>-367182.101698262</v>
       </c>
       <c r="S13" s="27" t="n">
         <f aca="false">R13+S12</f>
-        <v>-190039.467312946</v>
+        <v>-357414.548364929</v>
       </c>
       <c r="T13" s="27" t="n">
         <f aca="false">S13+T12</f>
-        <v>-172126.080646279</v>
+        <v>-347646.995031596</v>
       </c>
       <c r="U13" s="27" t="n">
         <f aca="false">T13+U12</f>
-        <v>-154212.693979613</v>
+        <v>-337879.441698262</v>
       </c>
       <c r="V13" s="27" t="n">
         <f aca="false">U13+V12</f>
-        <v>-136299.307312946</v>
+        <v>-328111.888364929</v>
       </c>
       <c r="W13" s="27" t="n">
         <f aca="false">V13+W12</f>
-        <v>-118385.920646279</v>
+        <v>-318344.335031596</v>
       </c>
       <c r="X13" s="27" t="n">
         <f aca="false">W13+X12</f>
-        <v>-100472.533979613</v>
+        <v>-308576.781698262</v>
       </c>
       <c r="Y13" s="27" t="n">
         <f aca="false">X13+Y12</f>
-        <v>-82559.1473129462</v>
+        <v>-298809.228364929</v>
       </c>
       <c r="Z13" s="27" t="n">
         <f aca="false">Y13+Z12</f>
-        <v>-64645.7606462795</v>
+        <v>-289041.675031596</v>
       </c>
       <c r="AA13" s="27" t="n">
         <f aca="false">Z13+AA12</f>
-        <v>-46732.3739796128</v>
+        <v>-279274.121698262</v>
       </c>
       <c r="AB13" s="27" t="n">
         <f aca="false">AA13+AB12</f>
-        <v>-28818.9873129462</v>
+        <v>-269506.568364929</v>
       </c>
       <c r="AC13" s="27" t="n">
         <f aca="false">AB13+AC12</f>
-        <v>-10905.6006462795</v>
+        <v>-259739.015031596</v>
       </c>
       <c r="AD13" s="27" t="n">
         <f aca="false">AC13+AD12</f>
-        <v>7007.78602038718</v>
+        <v>-249971.461698262</v>
       </c>
       <c r="AE13" s="27" t="n">
         <f aca="false">AD13+AE12</f>
-        <v>24921.1726870538</v>
+        <v>-240203.908364929</v>
       </c>
       <c r="AF13" s="27" t="n">
         <f aca="false">AE13+AF12</f>
-        <v>42834.5593537205</v>
+        <v>-230436.355031596</v>
       </c>
       <c r="AG13" s="27" t="n">
         <f aca="false">AF13+AG12</f>
-        <v>60747.9460203872</v>
+        <v>-220668.801698262</v>
       </c>
       <c r="AH13" s="27" t="n">
         <f aca="false">AG13+AH12</f>
-        <v>78661.3326870538</v>
+        <v>-210901.248364929</v>
       </c>
       <c r="AI13" s="27" t="n">
         <f aca="false">AH13+AI12</f>
-        <v>96574.7193537205</v>
+        <v>-201133.695031596</v>
       </c>
       <c r="AJ13" s="27" t="n">
         <f aca="false">AI13+AJ12</f>
-        <v>114488.106020387</v>
+        <v>-191366.141698262</v>
       </c>
       <c r="AK13" s="27" t="n">
         <f aca="false">AJ13+AK12</f>
-        <v>132401.492687054</v>
+        <v>-181598.588364929</v>
       </c>
       <c r="AL13" s="27" t="n">
         <f aca="false">AK13+AL12</f>
-        <v>150314.87935372</v>
+        <v>-171831.035031596</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="36" t="str">
@@ -5029,9 +5190,9 @@
         <f aca="false">IF(AND(AC13&gt;=0,AB13&lt;0),AC4,"")</f>
         <v/>
       </c>
-      <c r="AD14" s="36" t="n">
+      <c r="AD14" s="36" t="str">
         <f aca="false">IF(AND(AD13&gt;=0,AC13&lt;0),AD4,"")</f>
-        <v>28</v>
+        <v/>
       </c>
       <c r="AE14" s="36" t="str">
         <f aca="false">IF(AND(AE13&gt;=0,AD13&lt;0),AE4,"")</f>
@@ -5067,52 +5228,165 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="6"/>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="6"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="6"/>
-      <c r="AL15" s="6"/>
+      <c r="A15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <f aca="false">Inputs!$B$59*'Unit Economics'!$B$37</f>
+        <v>46000</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="N15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="O15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="P15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="Q15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="R15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="S15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="T15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="U15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="V15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="W15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="X15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="Y15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="Z15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AA15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AB15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AC15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AD15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AE15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AF15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AG15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AH15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AI15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AJ15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AK15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
+      <c r="AL15" s="25" t="n">
+        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>11500</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="B16" s="3" t="str">
         <f aca="false">IF(COUNT(C14:AL14)=0,"Beyond 36 months",MIN(C14:AL14))</f>
-        <v>28</v>
+        <v>Beyond 36 months</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -5153,11 +5427,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B17" s="27" t="n">
         <f aca="false">MIN(B13:AL13)</f>
-        <v>-307904.449091581</v>
+        <v>-406223.78080361</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -5198,11 +5472,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B18" s="27" t="n">
         <f aca="false">AL13</f>
-        <v>150314.87935372</v>
+        <v>-171831.035031596</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -5266,7 +5540,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -5276,7 +5550,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5294,7 +5568,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -5304,7 +5578,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B5" s="37" t="n">
         <v>130</v>
@@ -5327,24 +5601,24 @@
         <v>250</v>
       </c>
       <c r="B6" s="25" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-18664.9833333333</v>
+        <f aca="false">$A6*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-15310.8166666667</v>
       </c>
       <c r="C6" s="25" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-15754.9833333333</v>
+        <f aca="false">$A6*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-12400.8166666667</v>
       </c>
       <c r="D6" s="25" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-12117.4833333333</v>
+        <f aca="false">$A6*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-8763.31666666667</v>
       </c>
       <c r="E6" s="25" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-9207.48333333333</v>
+        <f aca="false">$A6*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-5853.31666666666</v>
       </c>
       <c r="F6" s="25" t="n">
-        <f aca="false">$A6*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-4842.48333333334</v>
+        <f aca="false">$A6*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-1488.31666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5352,24 +5626,24 @@
         <v>300</v>
       </c>
       <c r="B7" s="25" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-13189.4466666667</v>
+        <f aca="false">$A7*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-9835.28</v>
       </c>
       <c r="C7" s="25" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-9697.44666666667</v>
+        <f aca="false">$A7*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-6343.28</v>
       </c>
       <c r="D7" s="25" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-5332.44666666668</v>
+        <f aca="false">$A7*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-1978.28000000001</v>
       </c>
       <c r="E7" s="25" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-1840.44666666666</v>
+        <f aca="false">$A7*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>1513.72000000001</v>
       </c>
       <c r="F7" s="25" t="n">
-        <f aca="false">$A7*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>3397.55333333333</v>
+        <f aca="false">$A7*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>6751.72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5377,24 +5651,24 @@
         <v>350</v>
       </c>
       <c r="B8" s="25" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-7713.91</v>
+        <f aca="false">$A8*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-4359.74333333333</v>
       </c>
       <c r="C8" s="25" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-3639.91</v>
+        <f aca="false">$A8*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>-285.743333333332</v>
       </c>
       <c r="D8" s="25" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>1452.58999999999</v>
+        <f aca="false">$A8*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>4806.75666666666</v>
       </c>
       <c r="E8" s="25" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>5526.59</v>
+        <f aca="false">$A8*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>8880.75666666668</v>
       </c>
       <c r="F8" s="25" t="n">
-        <f aca="false">$A8*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>11637.59</v>
+        <f aca="false">$A8*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>14991.7566666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5402,24 +5676,24 @@
         <v>400</v>
       </c>
       <c r="B9" s="25" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>-2238.37333333333</v>
+        <f aca="false">$A9*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>1115.79333333334</v>
       </c>
       <c r="C9" s="25" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>2417.62666666666</v>
+        <f aca="false">$A9*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>5771.79333333334</v>
       </c>
       <c r="D9" s="25" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>8237.62666666666</v>
+        <f aca="false">$A9*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>11591.7933333333</v>
       </c>
       <c r="E9" s="25" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>12893.6266666667</v>
+        <f aca="false">$A9*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>16247.7933333333</v>
       </c>
       <c r="F9" s="25" t="n">
-        <f aca="false">$A9*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>19877.6266666667</v>
+        <f aca="false">$A9*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>23231.7933333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5427,24 +5701,24 @@
         <v>450</v>
       </c>
       <c r="B10" s="25" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>3237.16333333334</v>
+        <f aca="false">$A10*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>6591.33000000001</v>
       </c>
       <c r="C10" s="25" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>8475.16333333333</v>
+        <f aca="false">$A10*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>11829.33</v>
       </c>
       <c r="D10" s="25" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>15022.6633333333</v>
+        <f aca="false">$A10*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>18376.83</v>
       </c>
       <c r="E10" s="25" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>20260.6633333333</v>
+        <f aca="false">$A10*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>23614.83</v>
       </c>
       <c r="F10" s="25" t="n">
-        <f aca="false">$A10*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>28117.6633333333</v>
+        <f aca="false">$A10*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>31471.83</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5452,24 +5726,24 @@
         <v>500</v>
       </c>
       <c r="B11" s="25" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>8712.7</v>
+        <f aca="false">$A11*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>12066.8666666667</v>
       </c>
       <c r="C11" s="25" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>14532.7</v>
+        <f aca="false">$A11*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>17886.8666666667</v>
       </c>
       <c r="D11" s="25" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>21807.7</v>
+        <f aca="false">$A11*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>25161.8666666667</v>
       </c>
       <c r="E11" s="25" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>27627.7</v>
+        <f aca="false">$A11*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>30981.8666666667</v>
       </c>
       <c r="F11" s="25" t="n">
-        <f aca="false">$A11*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>36357.7</v>
+        <f aca="false">$A11*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>39711.8666666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5477,24 +5751,24 @@
         <v>550</v>
       </c>
       <c r="B12" s="25" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>14188.2366666667</v>
+        <f aca="false">$A12*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>17542.4033333333</v>
       </c>
       <c r="C12" s="25" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>20590.2366666667</v>
+        <f aca="false">$A12*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>23944.4033333333</v>
       </c>
       <c r="D12" s="25" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>28592.7366666667</v>
+        <f aca="false">$A12*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>31946.9033333333</v>
       </c>
       <c r="E12" s="25" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>34994.7366666667</v>
+        <f aca="false">$A12*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>38348.9033333334</v>
       </c>
       <c r="F12" s="25" t="n">
-        <f aca="false">$A12*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>44597.7366666667</v>
+        <f aca="false">$A12*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>47951.9033333333</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5502,24 +5776,24 @@
         <v>600</v>
       </c>
       <c r="B13" s="25" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>19663.7733333333</v>
+        <f aca="false">$A13*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>23017.94</v>
       </c>
       <c r="C13" s="25" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>26647.7733333333</v>
+        <f aca="false">$A13*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>30001.94</v>
       </c>
       <c r="D13" s="25" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>35377.7733333333</v>
+        <f aca="false">$A13*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>38731.94</v>
       </c>
       <c r="E13" s="25" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>42361.7733333333</v>
+        <f aca="false">$A13*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>45715.94</v>
       </c>
       <c r="F13" s="25" t="n">
-        <f aca="false">$A13*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>52837.7733333333</v>
+        <f aca="false">$A13*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>56191.94</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5527,24 +5801,24 @@
         <v>700</v>
       </c>
       <c r="B14" s="25" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>30614.8466666667</v>
+        <f aca="false">$A14*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>33969.0133333334</v>
       </c>
       <c r="C14" s="25" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>38762.8466666667</v>
+        <f aca="false">$A14*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>42117.0133333333</v>
       </c>
       <c r="D14" s="25" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>48947.8466666667</v>
+        <f aca="false">$A14*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>52302.0133333333</v>
       </c>
       <c r="E14" s="25" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>57095.8466666667</v>
+        <f aca="false">$A14*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>60450.0133333334</v>
       </c>
       <c r="F14" s="25" t="n">
-        <f aca="false">$A14*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$42)-'Unit Economics'!$B$47</f>
-        <v>69317.8466666667</v>
+        <f aca="false">$A14*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
+        <v>72672.0133333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5565,7 +5839,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -5575,7 +5849,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B18" s="37" t="n">
         <v>130</v>
@@ -5598,24 +5872,24 @@
         <v>0</v>
       </c>
       <c r="B19" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>24523.2866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>27877.4533333333</v>
       </c>
       <c r="C19" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>30925.2866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>34279.4533333333</v>
       </c>
       <c r="D19" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>38927.7866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>42281.9533333333</v>
       </c>
       <c r="E19" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>45329.7866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>48683.9533333333</v>
       </c>
       <c r="F19" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>54932.7866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>58286.9533333333</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5623,24 +5897,24 @@
         <v>30</v>
       </c>
       <c r="B20" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>14188.2366666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>17542.4033333333</v>
       </c>
       <c r="C20" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>20590.2366666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>23944.4033333333</v>
       </c>
       <c r="D20" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>28592.7366666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>31946.9033333333</v>
       </c>
       <c r="E20" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>34994.7366666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>38348.9033333334</v>
       </c>
       <c r="F20" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>44597.7366666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>47951.9033333333</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5648,24 +5922,24 @@
         <v>45</v>
       </c>
       <c r="B21" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>9020.71166666666</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>12374.8783333333</v>
       </c>
       <c r="C21" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>15422.7116666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>18776.8783333333</v>
       </c>
       <c r="D21" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>23425.2116666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>26779.3783333333</v>
       </c>
       <c r="E21" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>29827.2116666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>33181.3783333333</v>
       </c>
       <c r="F21" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>39430.2116666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>42784.3783333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5673,24 +5947,24 @@
         <v>60</v>
       </c>
       <c r="B22" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>3853.18666666666</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>7207.35333333333</v>
       </c>
       <c r="C22" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>10255.1866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>13609.3533333333</v>
       </c>
       <c r="D22" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>18257.6866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>21611.8533333333</v>
       </c>
       <c r="E22" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>24659.6866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>28013.8533333333</v>
       </c>
       <c r="F22" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>34262.6866666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>37616.8533333333</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5698,24 +5972,24 @@
         <v>90</v>
       </c>
       <c r="B23" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>-6481.86333333334</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>-3127.69666666666</v>
       </c>
       <c r="C23" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>-79.8633333333346</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>3274.30333333334</v>
       </c>
       <c r="D23" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>7922.63666666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>11276.8033333333</v>
       </c>
       <c r="E23" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>14324.6366666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>17678.8033333334</v>
       </c>
       <c r="F23" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$40+Inputs!$B$43))))-'Unit Economics'!$B$47</f>
-        <v>23927.6366666667</v>
+        <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
+        <v>27281.8033333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5736,7 +6010,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -5746,7 +6020,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="B27" s="37" t="n">
         <v>100</v>
@@ -5769,24 +6043,24 @@
         <v>0</v>
       </c>
       <c r="B28" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>23398.5</v>
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>26752.6666666667</v>
       </c>
       <c r="C28" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>23398.5</v>
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>26752.6666666667</v>
       </c>
       <c r="D28" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>23398.5</v>
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>26752.6666666667</v>
       </c>
       <c r="E28" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>23398.5</v>
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>26752.6666666667</v>
       </c>
       <c r="F28" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$41+$A28*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>23398.5</v>
+        <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>26752.6666666667</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5794,24 +6068,24 @@
         <v>0.2</v>
       </c>
       <c r="B29" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>18034.3683333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>21388.535</v>
       </c>
       <c r="C29" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>19519.3683333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>22873.535</v>
       </c>
       <c r="D29" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>20509.3683333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>23863.535</v>
       </c>
       <c r="E29" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>21994.3683333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>25348.535</v>
       </c>
       <c r="F29" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$41+$A29*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>22984.3683333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>26338.535</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5819,24 +6093,24 @@
         <v>0.4</v>
       </c>
       <c r="B30" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>12670.2366666667</v>
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>16024.4033333333</v>
       </c>
       <c r="C30" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>15640.2366666667</v>
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>18994.4033333333</v>
       </c>
       <c r="D30" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>17620.2366666667</v>
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>20974.4033333333</v>
       </c>
       <c r="E30" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>20590.2366666667</v>
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>23944.4033333333</v>
       </c>
       <c r="F30" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$41+$A30*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>22570.2366666667</v>
+        <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>25924.4033333333</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5844,24 +6118,24 @@
         <v>0.6</v>
       </c>
       <c r="B31" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>7306.105</v>
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>10660.2716666667</v>
       </c>
       <c r="C31" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>11761.105</v>
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>15115.2716666667</v>
       </c>
       <c r="D31" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>14731.105</v>
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>18085.2716666667</v>
       </c>
       <c r="E31" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>19186.105</v>
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>22540.2716666667</v>
       </c>
       <c r="F31" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$41+$A31*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>22156.105</v>
+        <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>25510.2716666667</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5869,24 +6143,24 @@
         <v>0.8</v>
       </c>
       <c r="B32" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>1941.97333333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>5296.14</v>
       </c>
       <c r="C32" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>7881.97333333334</v>
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>11236.14</v>
       </c>
       <c r="D32" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>11841.9733333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>15196.14</v>
       </c>
       <c r="E32" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>17781.9733333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>21136.14</v>
       </c>
       <c r="F32" s="25" t="n">
-        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$41+$A32*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$39-'Unit Economics'!$B$40)))-'Unit Economics'!$B$47</f>
-        <v>21741.9733333333</v>
+        <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
+        <v>25096.14</v>
       </c>
     </row>
   </sheetData>
@@ -5938,7 +6212,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -5948,7 +6222,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -5967,49 +6241,49 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B5" s="23" t="n">
-        <f aca="false">Inputs!B77</f>
+        <f aca="false">Inputs!B82</f>
         <v>1</v>
       </c>
       <c r="C5" s="23" t="n">
-        <f aca="false">Inputs!C77</f>
+        <f aca="false">Inputs!C82</f>
         <v>1</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">Inputs!D77</f>
+        <f aca="false">Inputs!D82</f>
         <v>2</v>
       </c>
       <c r="E5" s="23" t="n">
-        <f aca="false">Inputs!E77</f>
+        <f aca="false">Inputs!E82</f>
         <v>4</v>
       </c>
       <c r="F5" s="23" t="n">
-        <f aca="false">Inputs!F77</f>
+        <f aca="false">Inputs!F82</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">0</f>
@@ -6034,7 +6308,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B7" s="24" t="n">
         <f aca="false">0</f>
@@ -6059,7 +6333,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">B5+B6+B7</f>
@@ -6084,7 +6358,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C6:N6)+B6*SUM('36-Month Ramp'!O6:Z6)+B7*SUM('36-Month Ramp'!AA6:AL6)</f>
@@ -6109,152 +6383,152 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C10:N10)+B6*SUM('36-Month Ramp'!O10:Z10)+B7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>-42715.6186129727</v>
+        <v>14638.4670017109</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C10:N10)+C6*SUM('36-Month Ramp'!O10:Z10)+C7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>167354.239353721</v>
+        <v>264958.324968404</v>
       </c>
       <c r="D10" s="25" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C10:N10)+D6*SUM('36-Month Ramp'!O10:Z10)+D7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>339599.260740748</v>
+        <v>534807.431970115</v>
       </c>
       <c r="E10" s="25" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C10:N10)+E6*SUM('36-Month Ramp'!O10:Z10)+E7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>679198.521481496</v>
+        <v>1069614.86394023</v>
       </c>
       <c r="F10" s="25" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C10:N10)+F6*SUM('36-Month Ramp'!O10:Z10)+F7*SUM('36-Month Ramp'!AA10:AL10)</f>
-        <v>1443828.28018894</v>
+        <v>2109952.79387704</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B11" s="25" t="n">
-        <f aca="false">-Inputs!B78</f>
+        <f aca="false">-Inputs!B83</f>
         <v>-150000</v>
       </c>
       <c r="C11" s="25" t="n">
-        <f aca="false">-Inputs!C78</f>
+        <f aca="false">-Inputs!C83</f>
         <v>-400000</v>
       </c>
       <c r="D11" s="25" t="n">
-        <f aca="false">-Inputs!D78</f>
+        <f aca="false">-Inputs!D83</f>
         <v>-800000</v>
       </c>
       <c r="E11" s="25" t="n">
-        <f aca="false">-Inputs!E78</f>
+        <f aca="false">-Inputs!E83</f>
         <v>-1400000</v>
       </c>
       <c r="F11" s="25" t="n">
-        <f aca="false">-Inputs!F78</f>
+        <f aca="false">-Inputs!F83</f>
         <v>-2200000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B12" s="27" t="n">
         <f aca="false">B10+B11</f>
-        <v>-192715.618612973</v>
+        <v>-135361.532998289</v>
       </c>
       <c r="C12" s="27" t="n">
         <f aca="false">C10+C11</f>
-        <v>-232645.760646279</v>
+        <v>-135041.675031596</v>
       </c>
       <c r="D12" s="27" t="n">
         <f aca="false">D10+D11</f>
-        <v>-460400.739259252</v>
+        <v>-265192.568029885</v>
       </c>
       <c r="E12" s="27" t="n">
         <f aca="false">E10+E11</f>
-        <v>-720801.478518504</v>
+        <v>-330385.13605977</v>
       </c>
       <c r="F12" s="27" t="n">
         <f aca="false">F10+F11</f>
-        <v>-756171.719811063</v>
+        <v>-90047.2061229609</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B13" s="25" t="n">
-        <f aca="false">-B5*'Unit Economics'!$B$65</f>
+        <f aca="false">-B5*'Unit Economics'!$B$69</f>
         <v>-232000</v>
       </c>
       <c r="C13" s="25" t="n">
-        <f aca="false">-C5*'Unit Economics'!$B$65</f>
+        <f aca="false">-C5*'Unit Economics'!$B$69</f>
         <v>-232000</v>
       </c>
       <c r="D13" s="25" t="n">
-        <f aca="false">-D5*'Unit Economics'!$B$65</f>
+        <f aca="false">-D5*'Unit Economics'!$B$69</f>
         <v>-464000</v>
       </c>
       <c r="E13" s="25" t="n">
-        <f aca="false">-E5*'Unit Economics'!$B$65</f>
+        <f aca="false">-E5*'Unit Economics'!$B$69</f>
         <v>-928000</v>
       </c>
       <c r="F13" s="25" t="n">
-        <f aca="false">-F5*'Unit Economics'!$B$65</f>
+        <f aca="false">-F5*'Unit Economics'!$B$69</f>
         <v>-1392000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">B12+B13</f>
-        <v>-424715.618612973</v>
+        <v>-367361.532998289</v>
       </c>
       <c r="C14" s="25" t="n">
         <f aca="false">C12+C13</f>
-        <v>-464645.760646279</v>
+        <v>-367041.675031596</v>
       </c>
       <c r="D14" s="25" t="n">
         <f aca="false">D12+D13</f>
-        <v>-924400.739259252</v>
+        <v>-729192.568029885</v>
       </c>
       <c r="E14" s="25" t="n">
         <f aca="false">E12+E13</f>
-        <v>-1648801.4785185</v>
+        <v>-1258385.13605977</v>
       </c>
       <c r="F14" s="25" t="n">
         <f aca="false">F12+F13</f>
-        <v>-2148171.71981106</v>
+        <v>-1482047.20612296</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B15" s="27" t="n">
         <f aca="false">B14</f>
-        <v>-424715.618612973</v>
+        <v>-367361.532998289</v>
       </c>
       <c r="C15" s="27" t="n">
         <f aca="false">B15+C14</f>
-        <v>-889361.379259252</v>
+        <v>-734403.208029885</v>
       </c>
       <c r="D15" s="27" t="n">
         <f aca="false">C15+D14</f>
-        <v>-1813762.1185185</v>
+        <v>-1463595.77605977</v>
       </c>
       <c r="E15" s="27" t="n">
         <f aca="false">D15+E14</f>
-        <v>-3462563.59703701</v>
+        <v>-2721980.91211954</v>
       </c>
       <c r="F15" s="27" t="n">
         <f aca="false">E15+F14</f>
-        <v>-5610735.31684807</v>
+        <v>-4204028.1182425</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6267,11 +6541,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B17" s="41" t="n">
         <f aca="false">-MIN(0,MIN(B15:F15))</f>
-        <v>5610735.31684807</v>
+        <v>4204028.1182425</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -6280,7 +6554,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -6314,14 +6588,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -6333,81 +6607,81 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="B5" s="34" t="n">
-        <f aca="false">'Unit Economics'!$B$62</f>
+        <f aca="false">'Unit Economics'!$B$66</f>
         <v>72000</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B6" s="34" t="n">
-        <f aca="false">'Unit Economics'!$B$63</f>
+        <f aca="false">'Unit Economics'!$B$67</f>
         <v>90000</v>
       </c>
       <c r="C6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="B7" s="34" t="n">
-        <f aca="false">'Unit Economics'!$B$64</f>
+        <f aca="false">'Unit Economics'!$B$68</f>
         <v>70000</v>
       </c>
       <c r="C7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="B8" s="25" t="n">
-        <f aca="false">MAX(0,-'36-Month Ramp'!$B$17-'Unit Economics'!$B$65)</f>
-        <v>75904.4490915811</v>
+        <f aca="false">MAX(0,-'36-Month Ramp'!$B$17-'Unit Economics'!$B$69)</f>
+        <v>174223.78080361</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>0.2</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="B10" s="25" t="n">
         <f aca="false">SUM($B$5:$B$8)*$B$9</f>
-        <v>61580.8898183162</v>
+        <v>81244.7561607221</v>
       </c>
       <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B11" s="27" t="n">
         <f aca="false">SUM($B$5:$B$8)+$B$10</f>
-        <v>369485.338909897</v>
+        <v>487468.536964332</v>
       </c>
       <c r="C11" s="6"/>
     </row>
@@ -6418,70 +6692,70 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>50000</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">$B$15*$B$16*Inputs!$B$6</f>
         <v>0</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>10</v>
@@ -6492,18 +6766,18 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B21" s="25" t="n">
         <f aca="false">$B$18*$B$19*$B$20*Inputs!$B$20</f>
@@ -6513,34 +6787,34 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="B22" s="10" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="B23" s="27" t="n">
         <f aca="false">MAX(0,$B$11-$B$14-$B$17-$B$21-$B$22)</f>
-        <v>69485.3389098973</v>
+        <v>437468.536964332</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B24" s="27" t="n">
         <f aca="false">$B$14+$B$17+$B$21+$B$22+$B$23</f>
-        <v>369485.338909897</v>
+        <v>487468.536964332</v>
       </c>
       <c r="C24" s="6"/>
     </row>
@@ -6551,26 +6825,26 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="B26" s="42"/>
       <c r="C26" s="42"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B27" s="30" t="n">
         <f aca="false">IF($B$11=0,0,($B$14+$B$23)/$B$11)</f>
-        <v>0.323383166602545</v>
+        <v>1</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B28" s="33" t="str">
         <f aca="false">IF($B$27&gt;=0.1,"Yes","No")</f>
@@ -6580,18 +6854,18 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="B29" s="17" t="n">
         <v>0.105</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>10</v>
@@ -6602,24 +6876,24 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B31" s="25" t="n">
         <f aca="false">IF($B$22=0,0,-PMT($B$29,$B$30,$B$22))</f>
-        <v>41564.3301565634</v>
+        <v>0</v>
       </c>
       <c r="C31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B32" s="43" t="n">
+        <v>276</v>
+      </c>
+      <c r="B32" s="43" t="str">
         <f aca="false">IF($B$31=0,"No loan",'Unit Economics'!$B$36/$B$31)</f>
-        <v>5.171757590951</v>
+        <v>No loan</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -6646,7 +6920,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6654,57 +6928,57 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6712,7 +6986,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/off-hours/Off_Hours_Unit_Economics.xlsx
+++ b/off-hours/Off_Hours_Unit_Economics.xlsx
@@ -14,8 +14,9 @@
     <sheet name="36-Month Ramp" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Sensitivity" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Rollout" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Funding Plan" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Sources &amp; Notes" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pop-Ups" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Funding Plan" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sources &amp; Notes" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="346">
   <si>
     <t xml:space="preserve">Off Hours: Unit Economics Model</t>
   </si>
@@ -53,6 +54,9 @@
     <t xml:space="preserve">4. Sensitivity shows monthly profit across price, member count, and included massage minutes.</t>
   </si>
   <si>
+    <t xml:space="preserve">7. Pop-Ups models weekly pop-ups before opening: cost, waitlist sign-ups, and companies likely to sign.</t>
+  </si>
+  <si>
     <t xml:space="preserve">6. Funding Plan shows how much cash Location 1 needs and one way to stack your $50K, prepayments, an SBA loan and investors.</t>
   </si>
   <si>
@@ -359,6 +363,18 @@
     <t xml:space="preserve">Assumption: lease signing to opening day</t>
   </si>
   <si>
+    <t xml:space="preserve">Reduced salary (per year, before taxes) while ramping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From you: about $6K/month after taxes. ~$86K gross is an estimate for a single filer in MA; check with an accountant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months after opening at the reduced salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: full $120K salary from month 7. Pre-opening months are also at the reduced salary</t>
+  </si>
+  <si>
     <t xml:space="preserve">Host / front desk hourly pay</t>
   </si>
   <si>
@@ -746,6 +762,150 @@
     <t xml:space="preserve">Add a 20-30% buffer on top of this when deciding how much to raise.</t>
   </si>
   <si>
+    <t xml:space="preserve">Pop-up program before opening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly pop-ups to prove demand and grow the waitlist before signing a lease. Blue cells are inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weeks of pop-ups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: about 3 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public pop-ups per week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From you: weekly pop-ups. Hosted at a cafe, coworking space or hotel lobby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company-hosted pop-ups per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: at your target tech and healthcare employers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massage chairs / therapists per pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours per pop-up (plus 0.5 hr setup paid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public pop-up (people buy a ticket)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tickets sold per public pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption. Capacity is chairs x hours x 4 slots = 48 massages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket price (15-min chair massage + tea + lounge time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venue fee per public pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: some partners host free for the foot traffic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplies per guest (tea, cups, sanitizing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue per public pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per public pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapists + venue + supplies + card fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit per public pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company-hosted pop-up (employer pays a flat fee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee per company pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: a wellness afternoon for staff; the company hosts in its office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employees served per company pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption: 3 chairs x 3 hours x 4 slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per company pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Therapists for one hour less than a public pop-up + supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit per company pop-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-time equipment (portable massage chairs, tea setup, signage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption. The chairs move into the location later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event insurance per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public pop-ups held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company pop-ups held</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program profit (cost if negative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it proves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of public guests who join the waitlist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of company pop-up employees who join the waitlist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company pop-ups that turn into seat contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waitlist sign-ups from pop-ups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your goal: 250+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companies likely to sign for seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your goal: 10 interested (5 tech, 5 healthcare)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">People who have actually tried Off Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The strongest proof for landlords and angels</t>
+  </si>
+  <si>
     <t xml:space="preserve">Funding plan for Location 1 (sources and uses)</t>
   </si>
   <si>
@@ -759,6 +919,12 @@
   </si>
   <si>
     <t xml:space="preserve">Lowest cumulative cash on the 36-Month Ramp, minus opening costs. Includes your salary before and after opening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pop-up program cost (if it loses money)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the Pop-Ups tab</t>
   </si>
   <si>
     <t xml:space="preserve">Contingency (% of the above)</t>
@@ -1067,7 +1233,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1088,7 +1254,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1512,7 +1682,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="130"/>
@@ -1572,20 +1742,20 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1595,20 +1765,20 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="A19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1620,6 +1790,11 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1638,7 +1813,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1649,1095 +1824,1123 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+        <v>20</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="C3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="C6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="C7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B8" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="C8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="C9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="B10" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="C10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B11" s="16" t="n">
         <f aca="false">Inputs!$B$10+Inputs!$B$9*Inputs!$B$7*(1-Inputs!$B$8)</f>
         <v>23</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="C11" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B12" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="C12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="B13" s="17" t="n">
         <v>550</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="C13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="B14" s="17" t="n">
         <v>150</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="C14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="B15" s="17" t="n">
         <v>40</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="C15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="B16" s="18" t="n">
         <v>0.04</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="C16" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="A18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="B19" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="C19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="B20" s="11" t="n">
         <v>140</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="C20" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="B21" s="18" t="n">
         <v>0.65</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="C21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="B22" s="14" t="n">
         <v>0.015</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="C22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="B23" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="C23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="18" t="n">
+        <v>58</v>
+      </c>
+      <c r="B26" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="C26" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="B27" s="19" t="n">
         <v>1.5</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="C27" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="18" t="n">
+        <v>61</v>
+      </c>
+      <c r="B28" s="19" t="n">
         <v>2.5</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="C28" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="19" t="n">
+        <v>63</v>
+      </c>
+      <c r="B29" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="C29" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="B30" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="C30" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="B31" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
+      <c r="C31" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="B32" s="18" t="n">
         <v>0.75</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
+      <c r="C32" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="18" t="n">
+        <v>71</v>
+      </c>
+      <c r="B33" s="19" t="n">
         <v>1.2</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="C33" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="B34" s="21" t="n">
         <v>1.1</v>
       </c>
-      <c r="C34" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
+      <c r="C34" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="B35" s="21" t="n">
         <v>0.75</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
+      <c r="C35" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
+      <c r="A37" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="B38" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
+      <c r="C38" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="B39" s="14" t="n">
         <v>0.15</v>
       </c>
-      <c r="C39" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
+      <c r="C39" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="B40" s="18" t="n">
         <v>0.75</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
+      <c r="C40" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="B41" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
+      <c r="C41" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="19" t="n">
+        <v>83</v>
+      </c>
+      <c r="B42" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
+      <c r="C42" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="B43" s="16" t="n">
         <f aca="false">Inputs!$B$9*15/60/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)</f>
         <v>7.28333333333333</v>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
+      <c r="C43" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="B44" s="14" t="n">
         <v>0.65</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
+      <c r="C44" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
+      <c r="A46" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="B47" s="17" t="n">
         <v>2400</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
+      <c r="C47" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B48" s="21" t="n">
+        <v>91</v>
+      </c>
+      <c r="B48" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="C48" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+      <c r="C48" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B49" s="22" t="n">
+        <v>93</v>
+      </c>
+      <c r="B49" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
+      <c r="C49" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="B50" s="18" t="n">
         <v>0.15</v>
       </c>
-      <c r="C50" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
+      <c r="C50" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="B51" s="11" t="n">
         <v>6000</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
+      <c r="C51" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B52" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="B52" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
+      <c r="C52" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B53" s="11" t="n">
         <v>3000</v>
       </c>
-      <c r="C53" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
+      <c r="C53" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B54" s="19" t="n">
+        <v>103</v>
+      </c>
+      <c r="B54" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="C54" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
+      <c r="C54" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
+      <c r="A56" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B57" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B57" s="11" t="n">
         <v>45000</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
+      <c r="C57" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B58" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B58" s="11" t="n">
         <v>120000</v>
       </c>
-      <c r="C58" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
+      <c r="C58" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B59" s="16" t="n">
+        <v>109</v>
+      </c>
+      <c r="B59" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
+      <c r="C59" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>86000</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
+        <v>113</v>
+      </c>
+      <c r="B61" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B62" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
+        <v>115</v>
+      </c>
+      <c r="B62" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B63" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="B63" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B64" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" s="13" t="n">
         <v>125</v>
       </c>
-      <c r="C63" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
+      <c r="C65" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B66" s="12" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B67" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
+      <c r="A67" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B68" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="B68" s="13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B69" s="12" t="n">
-        <v>800</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
+        <v>122</v>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B70" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="B70" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B71" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="B71" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B72" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="B72" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B74" s="13" t="n">
         <v>700</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
+      <c r="C74" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B75" s="10" t="n">
-        <v>120</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
+      <c r="A76" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B77" s="12" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C77" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
+      <c r="B77" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B78" s="12" t="n">
+        <v>131</v>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B80" s="13" t="n">
         <v>70000</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
+      <c r="C80" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="B82" s="10"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="s">
+      <c r="B83" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B82" s="19" t="n">
+      <c r="C83" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B84" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C82" s="19" t="n">
+      <c r="C84" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D82" s="19" t="n">
+      <c r="D84" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E82" s="19" t="n">
+      <c r="E84" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F82" s="19" t="n">
+      <c r="F84" s="20" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B83" s="12" t="n">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B85" s="13" t="n">
         <v>150000</v>
       </c>
-      <c r="C83" s="12" t="n">
+      <c r="C85" s="13" t="n">
         <v>400000</v>
       </c>
-      <c r="D83" s="12" t="n">
+      <c r="D85" s="13" t="n">
         <v>800000</v>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="E85" s="13" t="n">
         <v>1400000</v>
       </c>
-      <c r="F83" s="12" t="n">
+      <c r="F85" s="13" t="n">
         <v>2200000</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2765,719 +2968,719 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+        <v>146</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="A2" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>145</v>
+      <c r="A4" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="23" t="n">
+        <v>151</v>
+      </c>
+      <c r="B5" s="24" t="n">
         <f aca="false">Inputs!$B$13</f>
         <v>550</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="24" t="n">
+        <v>152</v>
+      </c>
+      <c r="B6" s="25" t="n">
         <f aca="false">$B$5*(1-Inputs!$B$19)</f>
         <v>330</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B7" s="24" t="n">
+        <v>153</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <f aca="false">$B$5*Inputs!$B$19</f>
         <v>220</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="24" t="n">
+        <v>154</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <f aca="false">$B$6+$B$7*Inputs!$B$21</f>
         <v>473</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" s="25" t="n">
+        <v>156</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <f aca="false">$B$6*Inputs!$B$6</f>
         <v>49500</v>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B11/$B$5)</f>
         <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12" s="25" t="n">
+        <v>157</v>
+      </c>
+      <c r="B12" s="26" t="n">
         <f aca="false">$B$7*Inputs!$B$20</f>
         <v>30800</v>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B12/$B$5)</f>
         <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="25" t="n">
+        <v>158</v>
+      </c>
+      <c r="B13" s="26" t="n">
         <f aca="false">$B$8*Inputs!$B$11</f>
         <v>10879</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B13/$B$5)</f>
         <v>19.78</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B14" s="27" t="n">
+        <v>159</v>
+      </c>
+      <c r="B14" s="28" t="n">
         <f aca="false">$B$11+$B$12+$B$13</f>
         <v>91179</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B14/$B$5)</f>
         <v>165.78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>145</v>
+      <c r="A16" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" s="25" t="n">
+        <v>161</v>
+      </c>
+      <c r="B17" s="26" t="n">
         <f aca="false">($B$11+$B$13)*Inputs!$B$12</f>
         <v>1811.37</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B17/$B$5)</f>
         <v>3.2934</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B18" s="25" t="n">
+        <v>162</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <f aca="false">$B$12*Inputs!$B$23</f>
         <v>3080</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B18/$B$5)</f>
         <v>5.6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B19" s="25" t="n">
+        <v>163</v>
+      </c>
+      <c r="B19" s="26" t="n">
         <f aca="false">$B$8*(Inputs!$B$31/60*Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)+Inputs!$B$43)</f>
         <v>13780.0666666667</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B19/$B$5)</f>
         <v>25.0546666666667</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B20" s="25" t="n">
+        <v>164</v>
+      </c>
+      <c r="B20" s="26" t="n">
         <f aca="false">$B$8*Inputs!$B$26*Inputs!$B$33*Inputs!$B$34</f>
         <v>3746.16</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B20/$B$5)</f>
         <v>6.8112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B21" s="25" t="n">
+        <v>165</v>
+      </c>
+      <c r="B21" s="26" t="n">
         <f aca="false">$B$8*Inputs!$B$26*Inputs!$B$35</f>
         <v>2128.5</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B21/$B$5)</f>
         <v>3.87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" s="27" t="n">
+        <v>166</v>
+      </c>
+      <c r="B22" s="28" t="n">
         <f aca="false">SUM($B$17:$B$21)</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B22/$B$5)</f>
         <v>44.6292666666667</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="27" t="n">
+        <v>167</v>
+      </c>
+      <c r="B23" s="28" t="n">
         <f aca="false">$B$14-$B$22</f>
         <v>66632.9033333333</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B23/$B$5)</f>
         <v>121.150733333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>145</v>
+      <c r="A25" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B26" s="25" t="n">
+        <v>169</v>
+      </c>
+      <c r="B26" s="26" t="n">
         <f aca="false">IF(Inputs!$B$49=2,MAX(Inputs!$B$51,$B$14*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12)</f>
         <v>13676.85</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B26/$B$5)</f>
         <v>24.867</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B27" s="25" t="n">
+        <v>170</v>
+      </c>
+      <c r="B27" s="26" t="n">
         <f aca="false">Inputs!$B$57*(1+Inputs!$B$39)/12</f>
         <v>4312.5</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B27/$B$5)</f>
         <v>7.84090909090909</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B28" s="25" t="n">
-        <f aca="false">Inputs!$B$29*Inputs!$B$30*Inputs!$B$61*Inputs!$B$60*(1+Inputs!$B$39)</f>
+        <v>171</v>
+      </c>
+      <c r="B28" s="26" t="n">
+        <f aca="false">Inputs!$B$29*Inputs!$B$30*Inputs!$B$63*Inputs!$B$62*(1+Inputs!$B$39)</f>
         <v>10626</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B28/$B$5)</f>
         <v>19.32</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B29" s="25" t="n">
-        <f aca="false">Inputs!$B$62*Inputs!$B$63</f>
+        <v>172</v>
+      </c>
+      <c r="B29" s="26" t="n">
+        <f aca="false">Inputs!$B$64*Inputs!$B$65</f>
         <v>3750</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B29/$B$5)</f>
         <v>6.81818181818182</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B30" s="25" t="n">
-        <f aca="false">Inputs!$B$66+Inputs!$B$67+Inputs!$B$68+Inputs!$B$69+Inputs!$B$70+Inputs!$B$71+Inputs!$B$72</f>
+        <v>173</v>
+      </c>
+      <c r="B30" s="26" t="n">
+        <f aca="false">Inputs!$B$68+Inputs!$B$69+Inputs!$B$70+Inputs!$B$71+Inputs!$B$72+Inputs!$B$73+Inputs!$B$74</f>
         <v>13000</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B30/$B$5)</f>
         <v>23.6363636363636</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B31" s="27" t="n">
+        <v>174</v>
+      </c>
+      <c r="B31" s="28" t="n">
         <f aca="false">SUM($B$26:$B$30)</f>
         <v>45365.35</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B31/$B$5)</f>
         <v>82.4824545454545</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>145</v>
+      <c r="A33" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B34" s="27" t="n">
+        <v>176</v>
+      </c>
+      <c r="B34" s="28" t="n">
         <f aca="false">$B$23-$B$31</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <f aca="false">IF($B$5=0,0,B34/$B$5)</f>
         <v>38.6682787878788</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B35" s="28" t="n">
+        <v>177</v>
+      </c>
+      <c r="B35" s="29" t="n">
         <f aca="false">IF($B$14=0,0,$B$34/$B$14)</f>
         <v>0.233250565736994</v>
       </c>
-      <c r="C35" s="6"/>
+      <c r="C35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B36" s="27" t="n">
+        <v>178</v>
+      </c>
+      <c r="B36" s="28" t="n">
         <f aca="false">$B$34*12</f>
         <v>255210.64</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B37" s="25" t="n">
+        <v>179</v>
+      </c>
+      <c r="B37" s="26" t="n">
         <f aca="false">Inputs!$B$58*(1+Inputs!$B$39)/12</f>
         <v>11500</v>
       </c>
-      <c r="C37" s="6"/>
+      <c r="C37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B38" s="27" t="n">
+        <v>180</v>
+      </c>
+      <c r="B38" s="28" t="n">
         <f aca="false">$B$34-$B$37</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B39" s="27" t="n">
+        <v>181</v>
+      </c>
+      <c r="B39" s="28" t="n">
         <f aca="false">$B$38*12</f>
         <v>117210.64</v>
       </c>
-      <c r="C39" s="6"/>
+      <c r="C39" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>145</v>
+      <c r="A41" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B42" s="15" t="n">
+        <v>183</v>
+      </c>
+      <c r="B42" s="16" t="n">
         <f aca="false">Inputs!$B$31/60*Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)+Inputs!$B$43</f>
         <v>29.1333333333333</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B43" s="15" t="n">
+        <v>184</v>
+      </c>
+      <c r="B43" s="16" t="n">
         <f aca="false">Inputs!$B$26*(Inputs!$B$33*Inputs!$B$34+Inputs!$B$35)</f>
         <v>12.42</v>
       </c>
-      <c r="C43" s="6"/>
+      <c r="C43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B44" s="15" t="n">
+        <v>185</v>
+      </c>
+      <c r="B44" s="16" t="n">
         <f aca="false">(Inputs!$B$6+Inputs!$B$11)*(1-Inputs!$B$12)-$B$42-$B$43</f>
         <v>126.256666666667</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="7"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B45" s="15" t="n">
+        <v>186</v>
+      </c>
+      <c r="B45" s="16" t="n">
         <f aca="false">Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$B$42-$B$43)</f>
         <v>113.491833333333</v>
       </c>
-      <c r="C45" s="6"/>
+      <c r="C45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B46" s="29" t="n">
+        <v>187</v>
+      </c>
+      <c r="B46" s="30" t="n">
         <f aca="false">(1-Inputs!$B$19)*$B$44+Inputs!$B$19*$B$45</f>
         <v>121.150733333333</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="7"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B47" s="15" t="n">
+        <v>188</v>
+      </c>
+      <c r="B47" s="16" t="n">
         <f aca="false">(1-Inputs!$B$19)*(Inputs!$B$6+Inputs!$B$11)+Inputs!$B$19*(Inputs!$B$20+Inputs!$B$21*Inputs!$B$11)</f>
         <v>165.78</v>
       </c>
-      <c r="C47" s="6"/>
+      <c r="C47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B48" s="15" t="n">
+        <v>189</v>
+      </c>
+      <c r="B48" s="16" t="n">
         <f aca="false">$B$47-$B$46</f>
         <v>44.6292666666667</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="7"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B49" s="30" t="n">
+        <v>190</v>
+      </c>
+      <c r="B49" s="31" t="n">
         <f aca="false">(1-Inputs!$B$19)*Inputs!$B$16+Inputs!$B$19*Inputs!$B$22</f>
         <v>0.03</v>
       </c>
-      <c r="C49" s="6"/>
+      <c r="C49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B50" s="25" t="n">
+        <v>191</v>
+      </c>
+      <c r="B50" s="26" t="n">
         <f aca="false">$B$31-$B$26+Inputs!$B$47*Inputs!$B$48/12</f>
         <v>42688.5</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B51" s="31" t="n">
+        <v>192</v>
+      </c>
+      <c r="B51" s="32" t="n">
         <f aca="false">IF($B$46&lt;=0,"Never",ROUNDUP($B$50/$B$46,0))</f>
         <v>353</v>
       </c>
-      <c r="C51" s="6"/>
+      <c r="C51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B52" s="31" t="n">
+        <v>193</v>
+      </c>
+      <c r="B52" s="32" t="n">
         <f aca="false">IF($B$46-$B$47*Inputs!$B$50&lt;=0,"Never",ROUNDUP(($B$50-Inputs!$B$47*Inputs!$B$48/12+$B$37)/($B$46-$B$47*Inputs!$B$50),0))</f>
         <v>449</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B53" s="31" t="n">
+        <v>194</v>
+      </c>
+      <c r="B53" s="32" t="n">
         <f aca="false">IF($B$46-$B$47*Inputs!$B$50&lt;=0,"Never",ROUNDUP(($B$50-Inputs!$B$47*Inputs!$B$48/12)/($B$46-$B$47*Inputs!$B$50),0))</f>
         <v>330</v>
       </c>
-      <c r="C53" s="6"/>
+      <c r="C53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>145</v>
+      <c r="A55" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B56" s="32" t="n">
+        <v>196</v>
+      </c>
+      <c r="B56" s="33" t="n">
         <f aca="false">$B$8*Inputs!$B$26/Inputs!$B$30*Inputs!$B$27/Inputs!$B$29*Inputs!$B$28</f>
         <v>25.3392857142857</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B57" s="23" t="n">
+        <v>103</v>
+      </c>
+      <c r="B57" s="24" t="n">
         <f aca="false">Inputs!$B$54</f>
         <v>45</v>
       </c>
-      <c r="C57" s="6"/>
+      <c r="C57" s="7"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B58" s="33" t="str">
+        <v>197</v>
+      </c>
+      <c r="B58" s="34" t="str">
         <f aca="false">IF($B$56&lt;=$B$57,"OK","Over capacity")</f>
         <v>OK</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B59" s="24" t="n">
+        <v>198</v>
+      </c>
+      <c r="B59" s="25" t="n">
         <f aca="false">$B$8*(Inputs!$B$31/60*Inputs!$B$32+Inputs!$B$9*15/60)</f>
         <v>236.5</v>
       </c>
-      <c r="C59" s="6"/>
+      <c r="C59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B60" s="24" t="n">
+        <v>199</v>
+      </c>
+      <c r="B60" s="25" t="n">
         <f aca="false">Inputs!$B$42*Inputs!$B$29*Inputs!$B$30*Inputs!$B$44</f>
         <v>819</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B61" s="33" t="str">
+        <v>200</v>
+      </c>
+      <c r="B61" s="34" t="str">
         <f aca="false">IF($B$59&lt;=$B$60,"OK","Need more stations")</f>
         <v>OK</v>
       </c>
-      <c r="C61" s="6"/>
+      <c r="C61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B62" s="24" t="n">
+        <v>201</v>
+      </c>
+      <c r="B62" s="25" t="n">
         <f aca="false">IF(Inputs!$B$31*Inputs!$B$32+Inputs!$B$9*15=0,0,ROUNDDOWN($B$60/(Inputs!$B$31/60*Inputs!$B$32+Inputs!$B$9*15/60),0))</f>
         <v>1638</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B63" s="24" t="n">
+        <v>202</v>
+      </c>
+      <c r="B63" s="25" t="n">
         <f aca="false">ROUNDUP($B$59/Inputs!$B$40/Inputs!$B$41,0)</f>
         <v>4</v>
       </c>
-      <c r="C63" s="6"/>
+      <c r="C63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>145</v>
+      <c r="A65" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B66" s="25" t="n">
-        <f aca="false">Inputs!$B$47*MAX(0,Inputs!$B$75-Inputs!$B$76)</f>
+        <v>204</v>
+      </c>
+      <c r="B66" s="26" t="n">
+        <f aca="false">Inputs!$B$47*MAX(0,Inputs!$B$77-Inputs!$B$78)</f>
         <v>72000</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B67" s="34" t="n">
-        <f aca="false">Inputs!$B$77</f>
+        <v>133</v>
+      </c>
+      <c r="B67" s="35" t="n">
+        <f aca="false">Inputs!$B$79</f>
         <v>90000</v>
       </c>
-      <c r="C67" s="6"/>
+      <c r="C67" s="7"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B68" s="34" t="n">
-        <f aca="false">Inputs!$B$78</f>
+        <v>205</v>
+      </c>
+      <c r="B68" s="35" t="n">
+        <f aca="false">Inputs!$B$80</f>
         <v>70000</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="7"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B69" s="27" t="n">
+        <v>206</v>
+      </c>
+      <c r="B69" s="28" t="n">
         <f aca="false">SUM($B$66:$B$68)</f>
         <v>232000</v>
       </c>
-      <c r="C69" s="6"/>
+      <c r="C69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B70" s="35" t="n">
+        <v>207</v>
+      </c>
+      <c r="B70" s="36" t="n">
         <f aca="false">IF($B$36&lt;=0,"Never",$B$69/$B$36)</f>
         <v>0.90905300813477</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3504,2016 +3707,2016 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
+        <v>208</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+      <c r="AH1" s="7"/>
+      <c r="AI1" s="7"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6"/>
-      <c r="AL2" s="6"/>
+      <c r="A2" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="7"/>
+      <c r="AL2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6"/>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="7"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="J4" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="8" t="n">
+      <c r="K4" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" s="8" t="n">
+      <c r="O4" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="P4" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" s="8" t="n">
+      <c r="Q4" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="T4" s="8" t="n">
+      <c r="T4" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="V4" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="W4" s="8" t="n">
+      <c r="W4" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="Y4" s="8" t="n">
+      <c r="Y4" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="Z4" s="8" t="n">
+      <c r="Z4" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="AA4" s="8" t="n">
+      <c r="AA4" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="AB4" s="8" t="n">
+      <c r="AB4" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="AC4" s="8" t="n">
+      <c r="AC4" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="AD4" s="8" t="n">
+      <c r="AD4" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="AE4" s="8" t="n">
+      <c r="AE4" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="AF4" s="8" t="n">
+      <c r="AF4" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="AG4" s="8" t="n">
+      <c r="AG4" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="AH4" s="8" t="n">
+      <c r="AH4" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="AI4" s="8" t="n">
+      <c r="AI4" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="AJ4" s="8" t="n">
+      <c r="AJ4" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="AK4" s="8" t="n">
+      <c r="AK4" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="AL4" s="8" t="n">
+      <c r="AL4" s="9" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="24" t="n">
+        <v>148</v>
+      </c>
+      <c r="B5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="25" t="n">
         <f aca="false">Inputs!$B$14</f>
         <v>150</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,C5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>185.5</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,D5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>219.935</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,E5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>253.33695</v>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,F5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>285.7368415</v>
       </c>
-      <c r="H5" s="24" t="n">
+      <c r="H5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,G5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>317.164736255</v>
       </c>
-      <c r="I5" s="24" t="n">
+      <c r="I5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,H5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>347.64979416735</v>
       </c>
-      <c r="J5" s="24" t="n">
+      <c r="J5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,I5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>377.220300342329</v>
       </c>
-      <c r="K5" s="24" t="n">
+      <c r="K5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,J5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>405.90369133206</v>
       </c>
-      <c r="L5" s="24" t="n">
+      <c r="L5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,K5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>433.726580592098</v>
       </c>
-      <c r="M5" s="24" t="n">
+      <c r="M5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,L5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>460.714783174335</v>
       </c>
-      <c r="N5" s="24" t="n">
+      <c r="N5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,M5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>486.893339679105</v>
       </c>
-      <c r="O5" s="24" t="n">
+      <c r="O5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,N5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>512.286539488732</v>
       </c>
-      <c r="P5" s="24" t="n">
+      <c r="P5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,O5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>536.91794330407</v>
       </c>
-      <c r="Q5" s="24" t="n">
+      <c r="Q5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,P5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="R5" s="24" t="n">
+      <c r="R5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,Q5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="S5" s="24" t="n">
+      <c r="S5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,R5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="T5" s="24" t="n">
+      <c r="T5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,S5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="U5" s="24" t="n">
+      <c r="U5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,T5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="V5" s="24" t="n">
+      <c r="V5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,U5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="W5" s="24" t="n">
+      <c r="W5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,V5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="X5" s="24" t="n">
+      <c r="X5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,W5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="Y5" s="24" t="n">
+      <c r="Y5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,X5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="Z5" s="24" t="n">
+      <c r="Z5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,Y5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AA5" s="24" t="n">
+      <c r="AA5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,Z5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AB5" s="24" t="n">
+      <c r="AB5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AA5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AC5" s="24" t="n">
+      <c r="AC5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AB5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AD5" s="24" t="n">
+      <c r="AD5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AC5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AE5" s="24" t="n">
+      <c r="AE5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AD5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AF5" s="24" t="n">
+      <c r="AF5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AE5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AG5" s="24" t="n">
+      <c r="AG5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AF5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AH5" s="24" t="n">
+      <c r="AH5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AG5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AI5" s="24" t="n">
+      <c r="AI5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AH5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AJ5" s="24" t="n">
+      <c r="AJ5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AI5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AK5" s="24" t="n">
+      <c r="AK5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AJ5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
-      <c r="AL5" s="24" t="n">
+      <c r="AL5" s="25" t="n">
         <f aca="false">MIN(Inputs!$B$13,AK5*(1-'Unit Economics'!$B$49)+Inputs!$B$15)</f>
         <v>550</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="25" t="n">
+        <v>155</v>
+      </c>
+      <c r="B6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <f aca="false">C5*'Unit Economics'!$B$47</f>
         <v>24867</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">D5*'Unit Economics'!$B$47</f>
         <v>30752.19</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">E5*'Unit Economics'!$B$47</f>
         <v>36460.8243</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">F5*'Unit Economics'!$B$47</f>
         <v>41998.199571</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">G5*'Unit Economics'!$B$47</f>
         <v>47369.45358387</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="26" t="n">
         <f aca="false">H5*'Unit Economics'!$B$47</f>
         <v>52579.5699763539</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="26" t="n">
         <f aca="false">I5*'Unit Economics'!$B$47</f>
         <v>57633.3828770633</v>
       </c>
-      <c r="J6" s="25" t="n">
+      <c r="J6" s="26" t="n">
         <f aca="false">J5*'Unit Economics'!$B$47</f>
         <v>62535.5813907514</v>
       </c>
-      <c r="K6" s="25" t="n">
+      <c r="K6" s="26" t="n">
         <f aca="false">K5*'Unit Economics'!$B$47</f>
         <v>67290.7139490288</v>
       </c>
-      <c r="L6" s="25" t="n">
+      <c r="L6" s="26" t="n">
         <f aca="false">L5*'Unit Economics'!$B$47</f>
         <v>71903.192530558</v>
       </c>
-      <c r="M6" s="25" t="n">
+      <c r="M6" s="26" t="n">
         <f aca="false">M5*'Unit Economics'!$B$47</f>
         <v>76377.2967546412</v>
       </c>
-      <c r="N6" s="25" t="n">
+      <c r="N6" s="26" t="n">
         <f aca="false">N5*'Unit Economics'!$B$47</f>
         <v>80717.177852002</v>
       </c>
-      <c r="O6" s="25" t="n">
+      <c r="O6" s="26" t="n">
         <f aca="false">O5*'Unit Economics'!$B$47</f>
         <v>84926.8625164419</v>
       </c>
-      <c r="P6" s="25" t="n">
+      <c r="P6" s="26" t="n">
         <f aca="false">P5*'Unit Economics'!$B$47</f>
         <v>89010.2566409487</v>
       </c>
-      <c r="Q6" s="25" t="n">
+      <c r="Q6" s="26" t="n">
         <f aca="false">Q5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="R6" s="25" t="n">
+      <c r="R6" s="26" t="n">
         <f aca="false">R5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="S6" s="25" t="n">
+      <c r="S6" s="26" t="n">
         <f aca="false">S5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="T6" s="25" t="n">
+      <c r="T6" s="26" t="n">
         <f aca="false">T5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="U6" s="25" t="n">
+      <c r="U6" s="26" t="n">
         <f aca="false">U5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="V6" s="25" t="n">
+      <c r="V6" s="26" t="n">
         <f aca="false">V5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="W6" s="25" t="n">
+      <c r="W6" s="26" t="n">
         <f aca="false">W5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="X6" s="25" t="n">
+      <c r="X6" s="26" t="n">
         <f aca="false">X5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="Y6" s="25" t="n">
+      <c r="Y6" s="26" t="n">
         <f aca="false">Y5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="Z6" s="25" t="n">
+      <c r="Z6" s="26" t="n">
         <f aca="false">Z5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AA6" s="25" t="n">
+      <c r="AA6" s="26" t="n">
         <f aca="false">AA5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AB6" s="25" t="n">
+      <c r="AB6" s="26" t="n">
         <f aca="false">AB5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AC6" s="25" t="n">
+      <c r="AC6" s="26" t="n">
         <f aca="false">AC5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AD6" s="25" t="n">
+      <c r="AD6" s="26" t="n">
         <f aca="false">AD5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AE6" s="25" t="n">
+      <c r="AE6" s="26" t="n">
         <f aca="false">AE5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AF6" s="25" t="n">
+      <c r="AF6" s="26" t="n">
         <f aca="false">AF5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AG6" s="25" t="n">
+      <c r="AG6" s="26" t="n">
         <f aca="false">AG5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AH6" s="25" t="n">
+      <c r="AH6" s="26" t="n">
         <f aca="false">AH5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AI6" s="25" t="n">
+      <c r="AI6" s="26" t="n">
         <f aca="false">AI5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AJ6" s="25" t="n">
+      <c r="AJ6" s="26" t="n">
         <f aca="false">AJ5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AK6" s="25" t="n">
+      <c r="AK6" s="26" t="n">
         <f aca="false">AK5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
-      <c r="AL6" s="25" t="n">
+      <c r="AL6" s="26" t="n">
         <f aca="false">AL5*'Unit Economics'!$B$47</f>
         <v>91179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7" s="25" t="n">
+        <v>211</v>
+      </c>
+      <c r="B7" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">C5*'Unit Economics'!$B$48</f>
         <v>6694.39</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">D5*'Unit Economics'!$B$48</f>
         <v>8278.72896666667</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">E5*'Unit Economics'!$B$48</f>
         <v>9815.53776433333</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <f aca="false">F5*'Unit Economics'!$B$48</f>
         <v>11306.24229807</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <f aca="false">G5*'Unit Economics'!$B$48</f>
         <v>12752.2256957946</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="26" t="n">
         <f aca="false">H5*'Unit Economics'!$B$48</f>
         <v>14154.8295915874</v>
       </c>
-      <c r="I7" s="25" t="n">
+      <c r="I7" s="26" t="n">
         <f aca="false">I5*'Unit Economics'!$B$48</f>
         <v>15515.3553705064</v>
       </c>
-      <c r="J7" s="25" t="n">
+      <c r="J7" s="26" t="n">
         <f aca="false">J5*'Unit Economics'!$B$48</f>
         <v>16835.0653760579</v>
       </c>
-      <c r="K7" s="25" t="n">
+      <c r="K7" s="26" t="n">
         <f aca="false">K5*'Unit Economics'!$B$48</f>
         <v>18115.1840814428</v>
       </c>
-      <c r="L7" s="25" t="n">
+      <c r="L7" s="26" t="n">
         <f aca="false">L5*'Unit Economics'!$B$48</f>
         <v>19356.8992256662</v>
       </c>
-      <c r="M7" s="25" t="n">
+      <c r="M7" s="26" t="n">
         <f aca="false">M5*'Unit Economics'!$B$48</f>
         <v>20561.3629155629</v>
       </c>
-      <c r="N7" s="25" t="n">
+      <c r="N7" s="26" t="n">
         <f aca="false">N5*'Unit Economics'!$B$48</f>
         <v>21729.6926947627</v>
       </c>
-      <c r="O7" s="25" t="n">
+      <c r="O7" s="26" t="n">
         <f aca="false">O5*'Unit Economics'!$B$48</f>
         <v>22862.9725805865</v>
       </c>
-      <c r="P7" s="25" t="n">
+      <c r="P7" s="26" t="n">
         <f aca="false">P5*'Unit Economics'!$B$48</f>
         <v>23962.2540698355</v>
       </c>
-      <c r="Q7" s="25" t="n">
+      <c r="Q7" s="26" t="n">
         <f aca="false">Q5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="R7" s="25" t="n">
+      <c r="R7" s="26" t="n">
         <f aca="false">R5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="S7" s="25" t="n">
+      <c r="S7" s="26" t="n">
         <f aca="false">S5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="T7" s="25" t="n">
+      <c r="T7" s="26" t="n">
         <f aca="false">T5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="U7" s="25" t="n">
+      <c r="U7" s="26" t="n">
         <f aca="false">U5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="V7" s="25" t="n">
+      <c r="V7" s="26" t="n">
         <f aca="false">V5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="W7" s="25" t="n">
+      <c r="W7" s="26" t="n">
         <f aca="false">W5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="X7" s="25" t="n">
+      <c r="X7" s="26" t="n">
         <f aca="false">X5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="Y7" s="25" t="n">
+      <c r="Y7" s="26" t="n">
         <f aca="false">Y5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="Z7" s="25" t="n">
+      <c r="Z7" s="26" t="n">
         <f aca="false">Z5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AA7" s="25" t="n">
+      <c r="AA7" s="26" t="n">
         <f aca="false">AA5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AB7" s="25" t="n">
+      <c r="AB7" s="26" t="n">
         <f aca="false">AB5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AC7" s="25" t="n">
+      <c r="AC7" s="26" t="n">
         <f aca="false">AC5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AD7" s="25" t="n">
+      <c r="AD7" s="26" t="n">
         <f aca="false">AD5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AE7" s="25" t="n">
+      <c r="AE7" s="26" t="n">
         <f aca="false">AE5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AF7" s="25" t="n">
+      <c r="AF7" s="26" t="n">
         <f aca="false">AF5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AG7" s="25" t="n">
+      <c r="AG7" s="26" t="n">
         <f aca="false">AG5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AH7" s="25" t="n">
+      <c r="AH7" s="26" t="n">
         <f aca="false">AH5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AI7" s="25" t="n">
+      <c r="AI7" s="26" t="n">
         <f aca="false">AI5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AJ7" s="25" t="n">
+      <c r="AJ7" s="26" t="n">
         <f aca="false">AJ5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AK7" s="25" t="n">
+      <c r="AK7" s="26" t="n">
         <f aca="false">AK5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
-      <c r="AL7" s="25" t="n">
+      <c r="AL7" s="26" t="n">
         <f aca="false">AL5*'Unit Economics'!$B$48</f>
         <v>24546.0966666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="25" t="n">
+        <v>212</v>
+      </c>
+      <c r="B8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">IF(C4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,C6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>3000</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">IF(D4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,D6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>3000</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">IF(E4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,E6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>3000</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <f aca="false">IF(F4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,F6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>3000</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="26" t="n">
         <f aca="false">IF(G4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,G6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>3000</v>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="26" t="n">
         <f aca="false">IF(H4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,H6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>3000</v>
       </c>
-      <c r="I8" s="25" t="n">
+      <c r="I8" s="26" t="n">
         <f aca="false">IF(I4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,I6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>8645.00743155949</v>
       </c>
-      <c r="J8" s="25" t="n">
+      <c r="J8" s="26" t="n">
         <f aca="false">IF(J4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,J6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>9380.33720861271</v>
       </c>
-      <c r="K8" s="25" t="n">
+      <c r="K8" s="26" t="n">
         <f aca="false">IF(K4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,K6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>10093.6070923543</v>
       </c>
-      <c r="L8" s="25" t="n">
+      <c r="L8" s="26" t="n">
         <f aca="false">IF(L4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,L6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>10785.4788795837</v>
       </c>
-      <c r="M8" s="25" t="n">
+      <c r="M8" s="26" t="n">
         <f aca="false">IF(M4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,M6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>11456.5945131962</v>
       </c>
-      <c r="N8" s="25" t="n">
+      <c r="N8" s="26" t="n">
         <f aca="false">IF(N4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,N6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>12107.5766778003</v>
       </c>
-      <c r="O8" s="25" t="n">
+      <c r="O8" s="26" t="n">
         <f aca="false">IF(O4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,O6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>12739.0293774663</v>
       </c>
-      <c r="P8" s="25" t="n">
+      <c r="P8" s="26" t="n">
         <f aca="false">IF(P4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,P6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13351.5384961423</v>
       </c>
-      <c r="Q8" s="25" t="n">
+      <c r="Q8" s="26" t="n">
         <f aca="false">IF(Q4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,Q6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="R8" s="25" t="n">
+      <c r="R8" s="26" t="n">
         <f aca="false">IF(R4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,R6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="S8" s="25" t="n">
+      <c r="S8" s="26" t="n">
         <f aca="false">IF(S4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,S6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="T8" s="25" t="n">
+      <c r="T8" s="26" t="n">
         <f aca="false">IF(T4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,T6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="U8" s="25" t="n">
+      <c r="U8" s="26" t="n">
         <f aca="false">IF(U4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,U6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="V8" s="25" t="n">
+      <c r="V8" s="26" t="n">
         <f aca="false">IF(V4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,V6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="W8" s="25" t="n">
+      <c r="W8" s="26" t="n">
         <f aca="false">IF(W4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,W6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="X8" s="25" t="n">
+      <c r="X8" s="26" t="n">
         <f aca="false">IF(X4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,X6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="Y8" s="25" t="n">
+      <c r="Y8" s="26" t="n">
         <f aca="false">IF(Y4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,Y6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="Z8" s="25" t="n">
+      <c r="Z8" s="26" t="n">
         <f aca="false">IF(Z4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,Z6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AA8" s="25" t="n">
+      <c r="AA8" s="26" t="n">
         <f aca="false">IF(AA4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AA6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AB8" s="25" t="n">
+      <c r="AB8" s="26" t="n">
         <f aca="false">IF(AB4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AB6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AC8" s="25" t="n">
+      <c r="AC8" s="26" t="n">
         <f aca="false">IF(AC4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AC6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AD8" s="25" t="n">
+      <c r="AD8" s="26" t="n">
         <f aca="false">IF(AD4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AD6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AE8" s="25" t="n">
+      <c r="AE8" s="26" t="n">
         <f aca="false">IF(AE4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AE6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AF8" s="25" t="n">
+      <c r="AF8" s="26" t="n">
         <f aca="false">IF(AF4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AF6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AG8" s="25" t="n">
+      <c r="AG8" s="26" t="n">
         <f aca="false">IF(AG4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AG6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AH8" s="25" t="n">
+      <c r="AH8" s="26" t="n">
         <f aca="false">IF(AH4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AH6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AI8" s="25" t="n">
+      <c r="AI8" s="26" t="n">
         <f aca="false">IF(AI4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AI6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AJ8" s="25" t="n">
+      <c r="AJ8" s="26" t="n">
         <f aca="false">IF(AJ4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AJ6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AK8" s="25" t="n">
+      <c r="AK8" s="26" t="n">
         <f aca="false">IF(AK4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AK6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
-      <c r="AL8" s="25" t="n">
+      <c r="AL8" s="26" t="n">
         <f aca="false">IF(AL4&lt;=Inputs!$B$52,Inputs!$B$53,IF(Inputs!$B$49=2,MAX(Inputs!$B$51,AL6*Inputs!$B$50),Inputs!$B$47*Inputs!$B$48/12))</f>
         <v>13676.85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B9" s="25" t="n">
+        <v>213</v>
+      </c>
+      <c r="B9" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="I9" s="25" t="n">
+      <c r="I9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="J9" s="25" t="n">
+      <c r="J9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="K9" s="25" t="n">
+      <c r="K9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="L9" s="25" t="n">
+      <c r="L9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="M9" s="25" t="n">
+      <c r="M9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="N9" s="25" t="n">
+      <c r="N9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="O9" s="25" t="n">
+      <c r="O9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="P9" s="25" t="n">
+      <c r="P9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="Q9" s="25" t="n">
+      <c r="Q9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="R9" s="25" t="n">
+      <c r="R9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="S9" s="25" t="n">
+      <c r="S9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="T9" s="25" t="n">
+      <c r="T9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="U9" s="25" t="n">
+      <c r="U9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="V9" s="25" t="n">
+      <c r="V9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="W9" s="25" t="n">
+      <c r="W9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="X9" s="25" t="n">
+      <c r="X9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="Y9" s="25" t="n">
+      <c r="Y9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="Z9" s="25" t="n">
+      <c r="Z9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AA9" s="25" t="n">
+      <c r="AA9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AB9" s="25" t="n">
+      <c r="AB9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AC9" s="25" t="n">
+      <c r="AC9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AD9" s="25" t="n">
+      <c r="AD9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AE9" s="25" t="n">
+      <c r="AE9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AF9" s="25" t="n">
+      <c r="AF9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AG9" s="25" t="n">
+      <c r="AG9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AH9" s="25" t="n">
+      <c r="AH9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AI9" s="25" t="n">
+      <c r="AI9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AJ9" s="25" t="n">
+      <c r="AJ9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AK9" s="25" t="n">
+      <c r="AK9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
-      <c r="AL9" s="25" t="n">
+      <c r="AL9" s="26" t="n">
         <f aca="false">('Unit Economics'!$B$31-'Unit Economics'!$B$26)</f>
         <v>31688.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="27" t="n">
+        <v>214</v>
+      </c>
+      <c r="B10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <f aca="false">C6-C7-C8-C9</f>
         <v>-16515.89</v>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="28" t="n">
         <f aca="false">D6-D7-D8-D9</f>
         <v>-12215.0389666667</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="28" t="n">
         <f aca="false">E6-E7-E8-E9</f>
         <v>-8043.21346433333</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="28" t="n">
         <f aca="false">F6-F7-F8-F9</f>
         <v>-3996.54272707</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="28" t="n">
         <f aca="false">G6-G7-G8-G9</f>
         <v>-71.2721119245689</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="28" t="n">
         <f aca="false">H6-H7-H8-H9</f>
         <v>3736.2403847665</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="28" t="n">
         <f aca="false">I6-I7-I8-I9</f>
         <v>1784.52007499734</v>
       </c>
-      <c r="J10" s="27" t="n">
+      <c r="J10" s="28" t="n">
         <f aca="false">J6-J7-J8-J9</f>
         <v>4631.67880608076</v>
       </c>
-      <c r="K10" s="27" t="n">
+      <c r="K10" s="28" t="n">
         <f aca="false">K6-K7-K8-K9</f>
         <v>7393.42277523167</v>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="L10" s="28" t="n">
         <f aca="false">L6-L7-L8-L9</f>
         <v>10072.314425308</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="28" t="n">
         <f aca="false">M6-M7-M8-M9</f>
         <v>12670.8393258821</v>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="N10" s="28" t="n">
         <f aca="false">N6-N7-N8-N9</f>
         <v>15191.408479439</v>
       </c>
-      <c r="O10" s="27" t="n">
+      <c r="O10" s="28" t="n">
         <f aca="false">O6-O7-O8-O9</f>
         <v>17636.3605583892</v>
       </c>
-      <c r="P10" s="27" t="n">
+      <c r="P10" s="28" t="n">
         <f aca="false">P6-P7-P8-P9</f>
         <v>20007.9640749708</v>
       </c>
-      <c r="Q10" s="27" t="n">
+      <c r="Q10" s="28" t="n">
         <f aca="false">Q6-Q7-Q8-Q9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="R10" s="27" t="n">
+      <c r="R10" s="28" t="n">
         <f aca="false">R6-R7-R8-R9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="S10" s="27" t="n">
+      <c r="S10" s="28" t="n">
         <f aca="false">S6-S7-S8-S9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="T10" s="27" t="n">
+      <c r="T10" s="28" t="n">
         <f aca="false">T6-T7-T8-T9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="U10" s="27" t="n">
+      <c r="U10" s="28" t="n">
         <f aca="false">U6-U7-U8-U9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="V10" s="27" t="n">
+      <c r="V10" s="28" t="n">
         <f aca="false">V6-V7-V8-V9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="W10" s="27" t="n">
+      <c r="W10" s="28" t="n">
         <f aca="false">W6-W7-W8-W9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="X10" s="27" t="n">
+      <c r="X10" s="28" t="n">
         <f aca="false">X6-X7-X8-X9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="Y10" s="27" t="n">
+      <c r="Y10" s="28" t="n">
         <f aca="false">Y6-Y7-Y8-Y9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="Z10" s="27" t="n">
+      <c r="Z10" s="28" t="n">
         <f aca="false">Z6-Z7-Z8-Z9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AA10" s="27" t="n">
+      <c r="AA10" s="28" t="n">
         <f aca="false">AA6-AA7-AA8-AA9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AB10" s="27" t="n">
+      <c r="AB10" s="28" t="n">
         <f aca="false">AB6-AB7-AB8-AB9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AC10" s="27" t="n">
+      <c r="AC10" s="28" t="n">
         <f aca="false">AC6-AC7-AC8-AC9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AD10" s="27" t="n">
+      <c r="AD10" s="28" t="n">
         <f aca="false">AD6-AD7-AD8-AD9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AE10" s="27" t="n">
+      <c r="AE10" s="28" t="n">
         <f aca="false">AE6-AE7-AE8-AE9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AF10" s="27" t="n">
+      <c r="AF10" s="28" t="n">
         <f aca="false">AF6-AF7-AF8-AF9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AG10" s="27" t="n">
+      <c r="AG10" s="28" t="n">
         <f aca="false">AG6-AG7-AG8-AG9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AH10" s="27" t="n">
+      <c r="AH10" s="28" t="n">
         <f aca="false">AH6-AH7-AH8-AH9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AI10" s="27" t="n">
+      <c r="AI10" s="28" t="n">
         <f aca="false">AI6-AI7-AI8-AI9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AJ10" s="27" t="n">
+      <c r="AJ10" s="28" t="n">
         <f aca="false">AJ6-AJ7-AJ8-AJ9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AK10" s="27" t="n">
+      <c r="AK10" s="28" t="n">
         <f aca="false">AK6-AK7-AK8-AK9</f>
         <v>21267.5533333333</v>
       </c>
-      <c r="AL10" s="27" t="n">
+      <c r="AL10" s="28" t="n">
         <f aca="false">AL6-AL7-AL8-AL9</f>
         <v>21267.5533333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="25" t="n">
+        <v>215</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <f aca="false">'Unit Economics'!$B$69</f>
         <v>232000</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="25" t="n">
+      <c r="I11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="25" t="n">
+      <c r="J11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="25" t="n">
+      <c r="K11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="25" t="n">
+      <c r="L11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="25" t="n">
+      <c r="M11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="25" t="n">
+      <c r="N11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="25" t="n">
+      <c r="O11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="25" t="n">
+      <c r="P11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="25" t="n">
+      <c r="Q11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="25" t="n">
+      <c r="R11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="25" t="n">
+      <c r="S11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="25" t="n">
+      <c r="T11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="25" t="n">
+      <c r="U11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="25" t="n">
+      <c r="V11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="25" t="n">
+      <c r="W11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="25" t="n">
+      <c r="X11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" s="25" t="n">
+      <c r="Y11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="25" t="n">
+      <c r="Z11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AA11" s="25" t="n">
+      <c r="AA11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AB11" s="25" t="n">
+      <c r="AB11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="25" t="n">
+      <c r="AC11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" s="25" t="n">
+      <c r="AD11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" s="25" t="n">
+      <c r="AE11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" s="25" t="n">
+      <c r="AF11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AG11" s="25" t="n">
+      <c r="AG11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" s="25" t="n">
+      <c r="AH11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="25" t="n">
+      <c r="AI11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" s="25" t="n">
+      <c r="AJ11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AK11" s="25" t="n">
+      <c r="AK11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="AL11" s="25" t="n">
+      <c r="AL11" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B12" s="25" t="n">
+        <v>216</v>
+      </c>
+      <c r="B12" s="26" t="n">
         <f aca="false">B10-B11-B15</f>
-        <v>-278000</v>
-      </c>
-      <c r="C12" s="25" t="n">
+        <v>-264966.666666667</v>
+      </c>
+      <c r="C12" s="26" t="n">
         <f aca="false">C10-C11-C15</f>
-        <v>-28015.89</v>
-      </c>
-      <c r="D12" s="25" t="n">
+        <v>-24757.5566666667</v>
+      </c>
+      <c r="D12" s="26" t="n">
         <f aca="false">D10-D11-D15</f>
-        <v>-23715.0389666667</v>
-      </c>
-      <c r="E12" s="25" t="n">
+        <v>-20456.7056333333</v>
+      </c>
+      <c r="E12" s="26" t="n">
         <f aca="false">E10-E11-E15</f>
-        <v>-19543.2134643333</v>
-      </c>
-      <c r="F12" s="25" t="n">
+        <v>-16284.880131</v>
+      </c>
+      <c r="F12" s="26" t="n">
         <f aca="false">F10-F11-F15</f>
-        <v>-15496.54272707</v>
-      </c>
-      <c r="G12" s="25" t="n">
+        <v>-12238.2093937367</v>
+      </c>
+      <c r="G12" s="26" t="n">
         <f aca="false">G10-G11-G15</f>
-        <v>-11571.2721119246</v>
-      </c>
-      <c r="H12" s="25" t="n">
+        <v>-8312.93877859124</v>
+      </c>
+      <c r="H12" s="26" t="n">
         <f aca="false">H10-H11-H15</f>
-        <v>-7763.7596152335</v>
-      </c>
-      <c r="I12" s="25" t="n">
+        <v>-4505.42628190017</v>
+      </c>
+      <c r="I12" s="26" t="n">
         <f aca="false">I10-I11-I15</f>
         <v>-9715.47992500266</v>
       </c>
-      <c r="J12" s="25" t="n">
+      <c r="J12" s="26" t="n">
         <f aca="false">J10-J11-J15</f>
         <v>-6868.32119391924</v>
       </c>
-      <c r="K12" s="25" t="n">
+      <c r="K12" s="26" t="n">
         <f aca="false">K10-K11-K15</f>
         <v>-4106.57722476833</v>
       </c>
-      <c r="L12" s="25" t="n">
+      <c r="L12" s="26" t="n">
         <f aca="false">L10-L11-L15</f>
         <v>-1427.68557469195</v>
       </c>
-      <c r="M12" s="25" t="n">
+      <c r="M12" s="26" t="n">
         <f aca="false">M10-M11-M15</f>
         <v>1170.83932588214</v>
       </c>
-      <c r="N12" s="25" t="n">
+      <c r="N12" s="26" t="n">
         <f aca="false">N10-N11-N15</f>
         <v>3691.40847943901</v>
       </c>
-      <c r="O12" s="25" t="n">
+      <c r="O12" s="26" t="n">
         <f aca="false">O10-O11-O15</f>
         <v>6136.36055838917</v>
       </c>
-      <c r="P12" s="25" t="n">
+      <c r="P12" s="26" t="n">
         <f aca="false">P10-P11-P15</f>
         <v>8507.96407497083</v>
       </c>
-      <c r="Q12" s="25" t="n">
+      <c r="Q12" s="26" t="n">
         <f aca="false">Q10-Q11-Q15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="R12" s="25" t="n">
+      <c r="R12" s="26" t="n">
         <f aca="false">R10-R11-R15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="S12" s="25" t="n">
+      <c r="S12" s="26" t="n">
         <f aca="false">S10-S11-S15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="T12" s="25" t="n">
+      <c r="T12" s="26" t="n">
         <f aca="false">T10-T11-T15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="U12" s="25" t="n">
+      <c r="U12" s="26" t="n">
         <f aca="false">U10-U11-U15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="V12" s="25" t="n">
+      <c r="V12" s="26" t="n">
         <f aca="false">V10-V11-V15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="W12" s="25" t="n">
+      <c r="W12" s="26" t="n">
         <f aca="false">W10-W11-W15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="X12" s="25" t="n">
+      <c r="X12" s="26" t="n">
         <f aca="false">X10-X11-X15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="Y12" s="25" t="n">
+      <c r="Y12" s="26" t="n">
         <f aca="false">Y10-Y11-Y15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="Z12" s="25" t="n">
+      <c r="Z12" s="26" t="n">
         <f aca="false">Z10-Z11-Z15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AA12" s="25" t="n">
+      <c r="AA12" s="26" t="n">
         <f aca="false">AA10-AA11-AA15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AB12" s="25" t="n">
+      <c r="AB12" s="26" t="n">
         <f aca="false">AB10-AB11-AB15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AC12" s="25" t="n">
+      <c r="AC12" s="26" t="n">
         <f aca="false">AC10-AC11-AC15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AD12" s="25" t="n">
+      <c r="AD12" s="26" t="n">
         <f aca="false">AD10-AD11-AD15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AE12" s="25" t="n">
+      <c r="AE12" s="26" t="n">
         <f aca="false">AE10-AE11-AE15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AF12" s="25" t="n">
+      <c r="AF12" s="26" t="n">
         <f aca="false">AF10-AF11-AF15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AG12" s="25" t="n">
+      <c r="AG12" s="26" t="n">
         <f aca="false">AG10-AG11-AG15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AH12" s="25" t="n">
+      <c r="AH12" s="26" t="n">
         <f aca="false">AH10-AH11-AH15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AI12" s="25" t="n">
+      <c r="AI12" s="26" t="n">
         <f aca="false">AI10-AI11-AI15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AJ12" s="25" t="n">
+      <c r="AJ12" s="26" t="n">
         <f aca="false">AJ10-AJ11-AJ15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AK12" s="25" t="n">
+      <c r="AK12" s="26" t="n">
         <f aca="false">AK10-AK11-AK15</f>
         <v>9767.55333333334</v>
       </c>
-      <c r="AL12" s="25" t="n">
+      <c r="AL12" s="26" t="n">
         <f aca="false">AL10-AL11-AL15</f>
         <v>9767.55333333334</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B13" s="27" t="n">
+        <v>217</v>
+      </c>
+      <c r="B13" s="28" t="n">
         <f aca="false">B12</f>
-        <v>-278000</v>
-      </c>
-      <c r="C13" s="27" t="n">
+        <v>-264966.666666667</v>
+      </c>
+      <c r="C13" s="28" t="n">
         <f aca="false">B13+C12</f>
-        <v>-306015.89</v>
-      </c>
-      <c r="D13" s="27" t="n">
+        <v>-289724.223333333</v>
+      </c>
+      <c r="D13" s="28" t="n">
         <f aca="false">C13+D12</f>
-        <v>-329730.928966667</v>
-      </c>
-      <c r="E13" s="27" t="n">
+        <v>-310180.928966667</v>
+      </c>
+      <c r="E13" s="28" t="n">
         <f aca="false">D13+E12</f>
-        <v>-349274.142431</v>
-      </c>
-      <c r="F13" s="27" t="n">
+        <v>-326465.809097667</v>
+      </c>
+      <c r="F13" s="28" t="n">
         <f aca="false">E13+F12</f>
-        <v>-364770.68515807</v>
-      </c>
-      <c r="G13" s="27" t="n">
+        <v>-338704.018491403</v>
+      </c>
+      <c r="G13" s="28" t="n">
         <f aca="false">F13+G12</f>
-        <v>-376341.957269995</v>
-      </c>
-      <c r="H13" s="27" t="n">
+        <v>-347016.957269995</v>
+      </c>
+      <c r="H13" s="28" t="n">
         <f aca="false">G13+H12</f>
-        <v>-384105.716885228</v>
-      </c>
-      <c r="I13" s="27" t="n">
+        <v>-351522.383551895</v>
+      </c>
+      <c r="I13" s="28" t="n">
         <f aca="false">H13+I12</f>
-        <v>-393821.196810231</v>
-      </c>
-      <c r="J13" s="27" t="n">
+        <v>-361237.863476897</v>
+      </c>
+      <c r="J13" s="28" t="n">
         <f aca="false">I13+J12</f>
-        <v>-400689.51800415</v>
-      </c>
-      <c r="K13" s="27" t="n">
+        <v>-368106.184670817</v>
+      </c>
+      <c r="K13" s="28" t="n">
         <f aca="false">J13+K12</f>
-        <v>-404796.095228918</v>
-      </c>
-      <c r="L13" s="27" t="n">
+        <v>-372212.761895585</v>
+      </c>
+      <c r="L13" s="28" t="n">
         <f aca="false">K13+L12</f>
-        <v>-406223.78080361</v>
-      </c>
-      <c r="M13" s="27" t="n">
+        <v>-373640.447470277</v>
+      </c>
+      <c r="M13" s="28" t="n">
         <f aca="false">L13+M12</f>
-        <v>-405052.941477728</v>
-      </c>
-      <c r="N13" s="27" t="n">
+        <v>-372469.608144395</v>
+      </c>
+      <c r="N13" s="28" t="n">
         <f aca="false">M13+N12</f>
-        <v>-401361.532998289</v>
-      </c>
-      <c r="O13" s="27" t="n">
+        <v>-368778.199664956</v>
+      </c>
+      <c r="O13" s="28" t="n">
         <f aca="false">N13+O12</f>
-        <v>-395225.1724399</v>
-      </c>
-      <c r="P13" s="27" t="n">
+        <v>-362641.839106567</v>
+      </c>
+      <c r="P13" s="28" t="n">
         <f aca="false">O13+P12</f>
-        <v>-386717.208364929</v>
-      </c>
-      <c r="Q13" s="27" t="n">
+        <v>-354133.875031596</v>
+      </c>
+      <c r="Q13" s="28" t="n">
         <f aca="false">P13+Q12</f>
-        <v>-376949.655031596</v>
-      </c>
-      <c r="R13" s="27" t="n">
+        <v>-344366.321698263</v>
+      </c>
+      <c r="R13" s="28" t="n">
         <f aca="false">Q13+R12</f>
-        <v>-367182.101698262</v>
-      </c>
-      <c r="S13" s="27" t="n">
+        <v>-334598.768364929</v>
+      </c>
+      <c r="S13" s="28" t="n">
         <f aca="false">R13+S12</f>
-        <v>-357414.548364929</v>
-      </c>
-      <c r="T13" s="27" t="n">
+        <v>-324831.215031596</v>
+      </c>
+      <c r="T13" s="28" t="n">
         <f aca="false">S13+T12</f>
-        <v>-347646.995031596</v>
-      </c>
-      <c r="U13" s="27" t="n">
+        <v>-315063.661698262</v>
+      </c>
+      <c r="U13" s="28" t="n">
         <f aca="false">T13+U12</f>
-        <v>-337879.441698262</v>
-      </c>
-      <c r="V13" s="27" t="n">
+        <v>-305296.108364929</v>
+      </c>
+      <c r="V13" s="28" t="n">
         <f aca="false">U13+V12</f>
-        <v>-328111.888364929</v>
-      </c>
-      <c r="W13" s="27" t="n">
+        <v>-295528.555031596</v>
+      </c>
+      <c r="W13" s="28" t="n">
         <f aca="false">V13+W12</f>
-        <v>-318344.335031596</v>
-      </c>
-      <c r="X13" s="27" t="n">
+        <v>-285761.001698262</v>
+      </c>
+      <c r="X13" s="28" t="n">
         <f aca="false">W13+X12</f>
-        <v>-308576.781698262</v>
-      </c>
-      <c r="Y13" s="27" t="n">
+        <v>-275993.448364929</v>
+      </c>
+      <c r="Y13" s="28" t="n">
         <f aca="false">X13+Y12</f>
-        <v>-298809.228364929</v>
-      </c>
-      <c r="Z13" s="27" t="n">
+        <v>-266225.895031596</v>
+      </c>
+      <c r="Z13" s="28" t="n">
         <f aca="false">Y13+Z12</f>
-        <v>-289041.675031596</v>
-      </c>
-      <c r="AA13" s="27" t="n">
+        <v>-256458.341698262</v>
+      </c>
+      <c r="AA13" s="28" t="n">
         <f aca="false">Z13+AA12</f>
-        <v>-279274.121698262</v>
-      </c>
-      <c r="AB13" s="27" t="n">
+        <v>-246690.788364929</v>
+      </c>
+      <c r="AB13" s="28" t="n">
         <f aca="false">AA13+AB12</f>
-        <v>-269506.568364929</v>
-      </c>
-      <c r="AC13" s="27" t="n">
+        <v>-236923.235031596</v>
+      </c>
+      <c r="AC13" s="28" t="n">
         <f aca="false">AB13+AC12</f>
-        <v>-259739.015031596</v>
-      </c>
-      <c r="AD13" s="27" t="n">
+        <v>-227155.681698262</v>
+      </c>
+      <c r="AD13" s="28" t="n">
         <f aca="false">AC13+AD12</f>
-        <v>-249971.461698262</v>
-      </c>
-      <c r="AE13" s="27" t="n">
+        <v>-217388.128364929</v>
+      </c>
+      <c r="AE13" s="28" t="n">
         <f aca="false">AD13+AE12</f>
-        <v>-240203.908364929</v>
-      </c>
-      <c r="AF13" s="27" t="n">
+        <v>-207620.575031596</v>
+      </c>
+      <c r="AF13" s="28" t="n">
         <f aca="false">AE13+AF12</f>
-        <v>-230436.355031596</v>
-      </c>
-      <c r="AG13" s="27" t="n">
+        <v>-197853.021698262</v>
+      </c>
+      <c r="AG13" s="28" t="n">
         <f aca="false">AF13+AG12</f>
-        <v>-220668.801698262</v>
-      </c>
-      <c r="AH13" s="27" t="n">
+        <v>-188085.468364929</v>
+      </c>
+      <c r="AH13" s="28" t="n">
         <f aca="false">AG13+AH12</f>
-        <v>-210901.248364929</v>
-      </c>
-      <c r="AI13" s="27" t="n">
+        <v>-178317.915031596</v>
+      </c>
+      <c r="AI13" s="28" t="n">
         <f aca="false">AH13+AI12</f>
-        <v>-201133.695031596</v>
-      </c>
-      <c r="AJ13" s="27" t="n">
+        <v>-168550.361698262</v>
+      </c>
+      <c r="AJ13" s="28" t="n">
         <f aca="false">AI13+AJ12</f>
-        <v>-191366.141698262</v>
-      </c>
-      <c r="AK13" s="27" t="n">
+        <v>-158782.808364929</v>
+      </c>
+      <c r="AK13" s="28" t="n">
         <f aca="false">AJ13+AK12</f>
-        <v>-181598.588364929</v>
-      </c>
-      <c r="AL13" s="27" t="n">
+        <v>-149015.255031596</v>
+      </c>
+      <c r="AL13" s="28" t="n">
         <f aca="false">AK13+AL12</f>
-        <v>-171831.035031596</v>
+        <v>-139247.701698262</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36" t="str">
+        <v>218</v>
+      </c>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37" t="str">
         <f aca="false">IF(AND(C13&gt;=0,B13&lt;0),C4,"")</f>
         <v/>
       </c>
-      <c r="D14" s="36" t="str">
+      <c r="D14" s="37" t="str">
         <f aca="false">IF(AND(D13&gt;=0,C13&lt;0),D4,"")</f>
         <v/>
       </c>
-      <c r="E14" s="36" t="str">
+      <c r="E14" s="37" t="str">
         <f aca="false">IF(AND(E13&gt;=0,D13&lt;0),E4,"")</f>
         <v/>
       </c>
-      <c r="F14" s="36" t="str">
+      <c r="F14" s="37" t="str">
         <f aca="false">IF(AND(F13&gt;=0,E13&lt;0),F4,"")</f>
         <v/>
       </c>
-      <c r="G14" s="36" t="str">
+      <c r="G14" s="37" t="str">
         <f aca="false">IF(AND(G13&gt;=0,F13&lt;0),G4,"")</f>
         <v/>
       </c>
-      <c r="H14" s="36" t="str">
+      <c r="H14" s="37" t="str">
         <f aca="false">IF(AND(H13&gt;=0,G13&lt;0),H4,"")</f>
         <v/>
       </c>
-      <c r="I14" s="36" t="str">
+      <c r="I14" s="37" t="str">
         <f aca="false">IF(AND(I13&gt;=0,H13&lt;0),I4,"")</f>
         <v/>
       </c>
-      <c r="J14" s="36" t="str">
+      <c r="J14" s="37" t="str">
         <f aca="false">IF(AND(J13&gt;=0,I13&lt;0),J4,"")</f>
         <v/>
       </c>
-      <c r="K14" s="36" t="str">
+      <c r="K14" s="37" t="str">
         <f aca="false">IF(AND(K13&gt;=0,J13&lt;0),K4,"")</f>
         <v/>
       </c>
-      <c r="L14" s="36" t="str">
+      <c r="L14" s="37" t="str">
         <f aca="false">IF(AND(L13&gt;=0,K13&lt;0),L4,"")</f>
         <v/>
       </c>
-      <c r="M14" s="36" t="str">
+      <c r="M14" s="37" t="str">
         <f aca="false">IF(AND(M13&gt;=0,L13&lt;0),M4,"")</f>
         <v/>
       </c>
-      <c r="N14" s="36" t="str">
+      <c r="N14" s="37" t="str">
         <f aca="false">IF(AND(N13&gt;=0,M13&lt;0),N4,"")</f>
         <v/>
       </c>
-      <c r="O14" s="36" t="str">
+      <c r="O14" s="37" t="str">
         <f aca="false">IF(AND(O13&gt;=0,N13&lt;0),O4,"")</f>
         <v/>
       </c>
-      <c r="P14" s="36" t="str">
+      <c r="P14" s="37" t="str">
         <f aca="false">IF(AND(P13&gt;=0,O13&lt;0),P4,"")</f>
         <v/>
       </c>
-      <c r="Q14" s="36" t="str">
+      <c r="Q14" s="37" t="str">
         <f aca="false">IF(AND(Q13&gt;=0,P13&lt;0),Q4,"")</f>
         <v/>
       </c>
-      <c r="R14" s="36" t="str">
+      <c r="R14" s="37" t="str">
         <f aca="false">IF(AND(R13&gt;=0,Q13&lt;0),R4,"")</f>
         <v/>
       </c>
-      <c r="S14" s="36" t="str">
+      <c r="S14" s="37" t="str">
         <f aca="false">IF(AND(S13&gt;=0,R13&lt;0),S4,"")</f>
         <v/>
       </c>
-      <c r="T14" s="36" t="str">
+      <c r="T14" s="37" t="str">
         <f aca="false">IF(AND(T13&gt;=0,S13&lt;0),T4,"")</f>
         <v/>
       </c>
-      <c r="U14" s="36" t="str">
+      <c r="U14" s="37" t="str">
         <f aca="false">IF(AND(U13&gt;=0,T13&lt;0),U4,"")</f>
         <v/>
       </c>
-      <c r="V14" s="36" t="str">
+      <c r="V14" s="37" t="str">
         <f aca="false">IF(AND(V13&gt;=0,U13&lt;0),V4,"")</f>
         <v/>
       </c>
-      <c r="W14" s="36" t="str">
+      <c r="W14" s="37" t="str">
         <f aca="false">IF(AND(W13&gt;=0,V13&lt;0),W4,"")</f>
         <v/>
       </c>
-      <c r="X14" s="36" t="str">
+      <c r="X14" s="37" t="str">
         <f aca="false">IF(AND(X13&gt;=0,W13&lt;0),X4,"")</f>
         <v/>
       </c>
-      <c r="Y14" s="36" t="str">
+      <c r="Y14" s="37" t="str">
         <f aca="false">IF(AND(Y13&gt;=0,X13&lt;0),Y4,"")</f>
         <v/>
       </c>
-      <c r="Z14" s="36" t="str">
+      <c r="Z14" s="37" t="str">
         <f aca="false">IF(AND(Z13&gt;=0,Y13&lt;0),Z4,"")</f>
         <v/>
       </c>
-      <c r="AA14" s="36" t="str">
+      <c r="AA14" s="37" t="str">
         <f aca="false">IF(AND(AA13&gt;=0,Z13&lt;0),AA4,"")</f>
         <v/>
       </c>
-      <c r="AB14" s="36" t="str">
+      <c r="AB14" s="37" t="str">
         <f aca="false">IF(AND(AB13&gt;=0,AA13&lt;0),AB4,"")</f>
         <v/>
       </c>
-      <c r="AC14" s="36" t="str">
+      <c r="AC14" s="37" t="str">
         <f aca="false">IF(AND(AC13&gt;=0,AB13&lt;0),AC4,"")</f>
         <v/>
       </c>
-      <c r="AD14" s="36" t="str">
+      <c r="AD14" s="37" t="str">
         <f aca="false">IF(AND(AD13&gt;=0,AC13&lt;0),AD4,"")</f>
         <v/>
       </c>
-      <c r="AE14" s="36" t="str">
+      <c r="AE14" s="37" t="str">
         <f aca="false">IF(AND(AE13&gt;=0,AD13&lt;0),AE4,"")</f>
         <v/>
       </c>
-      <c r="AF14" s="36" t="str">
+      <c r="AF14" s="37" t="str">
         <f aca="false">IF(AND(AF13&gt;=0,AE13&lt;0),AF4,"")</f>
         <v/>
       </c>
-      <c r="AG14" s="36" t="str">
+      <c r="AG14" s="37" t="str">
         <f aca="false">IF(AND(AG13&gt;=0,AF13&lt;0),AG4,"")</f>
         <v/>
       </c>
-      <c r="AH14" s="36" t="str">
+      <c r="AH14" s="37" t="str">
         <f aca="false">IF(AND(AH13&gt;=0,AG13&lt;0),AH4,"")</f>
         <v/>
       </c>
-      <c r="AI14" s="36" t="str">
+      <c r="AI14" s="37" t="str">
         <f aca="false">IF(AND(AI13&gt;=0,AH13&lt;0),AI4,"")</f>
         <v/>
       </c>
-      <c r="AJ14" s="36" t="str">
+      <c r="AJ14" s="37" t="str">
         <f aca="false">IF(AND(AJ13&gt;=0,AI13&lt;0),AJ4,"")</f>
         <v/>
       </c>
-      <c r="AK14" s="36" t="str">
+      <c r="AK14" s="37" t="str">
         <f aca="false">IF(AND(AK13&gt;=0,AJ13&lt;0),AK4,"")</f>
         <v/>
       </c>
-      <c r="AL14" s="36" t="str">
+      <c r="AL14" s="37" t="str">
         <f aca="false">IF(AND(AL13&gt;=0,AK13&lt;0),AL4,"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="25" t="n">
-        <f aca="false">Inputs!$B$59*'Unit Economics'!$B$37</f>
-        <v>46000</v>
-      </c>
-      <c r="C15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+        <v>219</v>
+      </c>
+      <c r="B15" s="26" t="n">
+        <f aca="false">Inputs!$B$59*Inputs!$B$60*(1+Inputs!$B$39)/12</f>
+        <v>32966.6666666667</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <f aca="false">IF(C4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
+        <v>8241.66666666667</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <f aca="false">IF(D4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
+        <v>8241.66666666667</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <f aca="false">IF(E4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
+        <v>8241.66666666667</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <f aca="false">IF(F4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
+        <v>8241.66666666667</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <f aca="false">IF(G4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
+        <v>8241.66666666667</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <f aca="false">IF(H4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
+        <v>8241.66666666667</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <f aca="false">IF(I4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="D15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="J15" s="26" t="n">
+        <f aca="false">IF(J4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="E15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="K15" s="26" t="n">
+        <f aca="false">IF(K4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="F15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="L15" s="26" t="n">
+        <f aca="false">IF(L4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="G15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="M15" s="26" t="n">
+        <f aca="false">IF(M4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="H15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="N15" s="26" t="n">
+        <f aca="false">IF(N4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="I15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="O15" s="26" t="n">
+        <f aca="false">IF(O4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="J15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="P15" s="26" t="n">
+        <f aca="false">IF(P4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="K15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="Q15" s="26" t="n">
+        <f aca="false">IF(Q4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="L15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="R15" s="26" t="n">
+        <f aca="false">IF(R4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="M15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="S15" s="26" t="n">
+        <f aca="false">IF(S4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="N15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="T15" s="26" t="n">
+        <f aca="false">IF(T4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="O15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="U15" s="26" t="n">
+        <f aca="false">IF(U4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="P15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="V15" s="26" t="n">
+        <f aca="false">IF(V4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="Q15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="W15" s="26" t="n">
+        <f aca="false">IF(W4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="R15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="X15" s="26" t="n">
+        <f aca="false">IF(X4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="S15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="Y15" s="26" t="n">
+        <f aca="false">IF(Y4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="T15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="Z15" s="26" t="n">
+        <f aca="false">IF(Z4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="U15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AA15" s="26" t="n">
+        <f aca="false">IF(AA4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="V15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AB15" s="26" t="n">
+        <f aca="false">IF(AB4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="W15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AC15" s="26" t="n">
+        <f aca="false">IF(AC4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="X15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AD15" s="26" t="n">
+        <f aca="false">IF(AD4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="Y15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AE15" s="26" t="n">
+        <f aca="false">IF(AE4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="Z15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AF15" s="26" t="n">
+        <f aca="false">IF(AF4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="AA15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AG15" s="26" t="n">
+        <f aca="false">IF(AG4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="AB15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AH15" s="26" t="n">
+        <f aca="false">IF(AH4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="AC15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AI15" s="26" t="n">
+        <f aca="false">IF(AI4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="AD15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AJ15" s="26" t="n">
+        <f aca="false">IF(AJ4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="AE15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AK15" s="26" t="n">
+        <f aca="false">IF(AK4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
-      <c r="AF15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
-        <v>11500</v>
-      </c>
-      <c r="AG15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
-        <v>11500</v>
-      </c>
-      <c r="AH15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
-        <v>11500</v>
-      </c>
-      <c r="AI15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
-        <v>11500</v>
-      </c>
-      <c r="AJ15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
-        <v>11500</v>
-      </c>
-      <c r="AK15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
-        <v>11500</v>
-      </c>
-      <c r="AL15" s="25" t="n">
-        <f aca="false">'Unit Economics'!$B$37</f>
+      <c r="AL15" s="26" t="n">
+        <f aca="false">IF(AL4&lt;=Inputs!$B$61,Inputs!$B$60*(1+Inputs!$B$39)/12,'Unit Economics'!$B$37)</f>
         <v>11500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B16" s="3" t="str">
         <f aca="false">IF(COUNT(C14:AL14)=0,"Beyond 36 months",MIN(C14:AL14))</f>
         <v>Beyond 36 months</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="6"/>
-      <c r="AB16" s="6"/>
-      <c r="AC16" s="6"/>
-      <c r="AD16" s="6"/>
-      <c r="AE16" s="6"/>
-      <c r="AF16" s="6"/>
-      <c r="AG16" s="6"/>
-      <c r="AH16" s="6"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="6"/>
-      <c r="AK16" s="6"/>
-      <c r="AL16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="27" t="n">
+        <v>221</v>
+      </c>
+      <c r="B17" s="28" t="n">
         <f aca="false">MIN(B13:AL13)</f>
-        <v>-406223.78080361</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="6"/>
-      <c r="AA17" s="6"/>
-      <c r="AB17" s="6"/>
-      <c r="AC17" s="6"/>
-      <c r="AD17" s="6"/>
-      <c r="AE17" s="6"/>
-      <c r="AF17" s="6"/>
-      <c r="AG17" s="6"/>
-      <c r="AH17" s="6"/>
-      <c r="AI17" s="6"/>
-      <c r="AJ17" s="6"/>
-      <c r="AK17" s="6"/>
-      <c r="AL17" s="6"/>
+        <v>-373640.447470277</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="7"/>
+      <c r="AG17" s="7"/>
+      <c r="AH17" s="7"/>
+      <c r="AI17" s="7"/>
+      <c r="AJ17" s="7"/>
+      <c r="AK17" s="7"/>
+      <c r="AL17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B18" s="27" t="n">
+        <v>222</v>
+      </c>
+      <c r="B18" s="28" t="n">
         <f aca="false">AL13</f>
-        <v>-171831.035031596</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="6"/>
-      <c r="AE18" s="6"/>
-      <c r="AF18" s="6"/>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="6"/>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="6"/>
-      <c r="AK18" s="6"/>
-      <c r="AL18" s="6"/>
+        <v>-139247.701698262</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="7"/>
+      <c r="AI18" s="7"/>
+      <c r="AJ18" s="7"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5540,625 +5743,625 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+        <v>223</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="A2" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+        <v>225</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="37" t="n">
+      <c r="A5" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B5" s="38" t="n">
         <v>130</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="38" t="n">
         <v>150</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="38" t="n">
         <v>175</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="38" t="n">
         <v>195</v>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="38" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="38" t="n">
+      <c r="A6" s="39" t="n">
         <v>250</v>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="26" t="n">
         <f aca="false">$A6*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-15310.8166666667</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <f aca="false">$A6*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-12400.8166666667</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">$A6*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-8763.31666666667</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">$A6*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-5853.31666666666</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">$A6*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-1488.31666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="38" t="n">
+      <c r="A7" s="39" t="n">
         <v>300</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <f aca="false">$A7*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-9835.28</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">$A7*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-6343.28</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">$A7*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-1978.28000000001</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">$A7*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>1513.72000000001</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <f aca="false">$A7*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>6751.72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="n">
+      <c r="A8" s="39" t="n">
         <v>350</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <f aca="false">$A8*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-4359.74333333333</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">$A8*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>-285.743333333332</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">$A8*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>4806.75666666666</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">$A8*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>8880.75666666668</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <f aca="false">$A8*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>14991.7566666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="n">
+      <c r="A9" s="39" t="n">
         <v>400</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">$A9*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>1115.79333333334</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">$A9*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>5771.79333333334</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">$A9*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>11591.7933333333</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">$A9*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>16247.7933333333</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">$A9*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>23231.7933333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="n">
+      <c r="A10" s="39" t="n">
         <v>450</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <f aca="false">$A10*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>6591.33000000001</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <f aca="false">$A10*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>11829.33</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <f aca="false">$A10*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>18376.83</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <f aca="false">$A10*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>23614.83</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <f aca="false">$A10*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>31471.83</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="39" t="n">
         <v>500</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="26" t="n">
         <f aca="false">$A11*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>12066.8666666667</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <f aca="false">$A11*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>17886.8666666667</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">$A11*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>25161.8666666667</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">$A11*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>30981.8666666667</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">$A11*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>39711.8666666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="38" t="n">
+      <c r="A12" s="39" t="n">
         <v>550</v>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="26" t="n">
         <f aca="false">$A12*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>17542.4033333333</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="26" t="n">
         <f aca="false">$A12*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>23944.4033333333</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="26" t="n">
         <f aca="false">$A12*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>31946.9033333333</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <f aca="false">$A12*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>38348.9033333334</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="26" t="n">
         <f aca="false">$A12*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>47951.9033333333</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="n">
+      <c r="A13" s="39" t="n">
         <v>600</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <f aca="false">$A13*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>23017.94</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <f aca="false">$A13*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>30001.94</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">$A13*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>38731.94</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">$A13*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>45715.94</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <f aca="false">$A13*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>56191.94</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="39" t="n">
         <v>700</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <f aca="false">$A14*((1-Inputs!$B$19)*((B$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>33969.0133333334</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="26" t="n">
         <f aca="false">$A14*((1-Inputs!$B$19)*((C$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>42117.0133333333</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="26" t="n">
         <f aca="false">$A14*((1-Inputs!$B$19)*((D$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>52302.0133333333</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <f aca="false">$A14*((1-Inputs!$B$19)*((E$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>60450.0133333334</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="26" t="n">
         <f aca="false">$A14*((1-Inputs!$B$19)*((F$5+Inputs!$B$11)*(1-Inputs!$B$12)-Inputs!$B$31*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*'Unit Economics'!$B$45)-'Unit Economics'!$B$50</f>
         <v>72672.0133333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+        <v>227</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="37" t="n">
+      <c r="A18" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="38" t="n">
         <v>130</v>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="38" t="n">
         <v>150</v>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="38" t="n">
         <v>175</v>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="38" t="n">
         <v>195</v>
       </c>
-      <c r="F18" s="37" t="n">
+      <c r="F18" s="38" t="n">
         <v>225</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="n">
+      <c r="A19" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>27877.4533333333</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>34279.4533333333</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>42281.9533333333</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>48683.9533333333</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A19*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>58286.9533333333</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="39" t="n">
+      <c r="A20" s="40" t="n">
         <v>30</v>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>17542.4033333333</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>23944.4033333333</v>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>31946.9033333333</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>38348.9033333334</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A20*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>47951.9033333333</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39" t="n">
+      <c r="A21" s="40" t="n">
         <v>45</v>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>12374.8783333333</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>18776.8783333333</v>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>26779.3783333333</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>33181.3783333333</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A21*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>42784.3783333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="39" t="n">
+      <c r="A22" s="40" t="n">
         <v>60</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>7207.35333333333</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>13609.3533333333</v>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>21611.8533333333</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>28013.8533333333</v>
       </c>
-      <c r="F22" s="25" t="n">
+      <c r="F22" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A22*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>37616.8533333333</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="39" t="n">
+      <c r="A23" s="40" t="n">
         <v>90</v>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((B$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>-3127.69666666666</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((C$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>3274.30333333334</v>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D23" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((D$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>11276.8033333333</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((E$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>17678.8033333334</v>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="F23" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-Inputs!$B$19)*((F$18+Inputs!$B$11)*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))+Inputs!$B$19*(Inputs!$B$20*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-$A23*(Inputs!$B$32/Inputs!$B$40*Inputs!$B$38*(1+Inputs!$B$39)/60)-('Unit Economics'!$B$43+Inputs!$B$43))))-'Unit Economics'!$B$50</f>
         <v>27281.8033333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+        <v>229</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B27" s="37" t="n">
+      <c r="A27" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B27" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="38" t="n">
         <v>115</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="38" t="n">
         <v>125</v>
       </c>
-      <c r="E27" s="37" t="n">
+      <c r="E27" s="38" t="n">
         <v>140</v>
       </c>
-      <c r="F27" s="37" t="n">
+      <c r="F27" s="38" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40" t="n">
+      <c r="A28" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>26752.6666666667</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>26752.6666666667</v>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>26752.6666666667</v>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>26752.6666666667</v>
       </c>
-      <c r="F28" s="25" t="n">
+      <c r="F28" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A28)*'Unit Economics'!$B$44+$A28*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>26752.6666666667</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40" t="n">
+      <c r="A29" s="41" t="n">
         <v>0.2</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>21388.535</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>22873.535</v>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>23863.535</v>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>25348.535</v>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A29)*'Unit Economics'!$B$44+$A29*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>26338.535</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40" t="n">
+      <c r="A30" s="41" t="n">
         <v>0.4</v>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>16024.4033333333</v>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>18994.4033333333</v>
       </c>
-      <c r="D30" s="25" t="n">
+      <c r="D30" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>20974.4033333333</v>
       </c>
-      <c r="E30" s="25" t="n">
+      <c r="E30" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>23944.4033333333</v>
       </c>
-      <c r="F30" s="25" t="n">
+      <c r="F30" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A30)*'Unit Economics'!$B$44+$A30*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>25924.4033333333</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="40" t="n">
+      <c r="A31" s="41" t="n">
         <v>0.6</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>10660.2716666667</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>15115.2716666667</v>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>18085.2716666667</v>
       </c>
-      <c r="E31" s="25" t="n">
+      <c r="E31" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>22540.2716666667</v>
       </c>
-      <c r="F31" s="25" t="n">
+      <c r="F31" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A31)*'Unit Economics'!$B$44+$A31*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>25510.2716666667</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="40" t="n">
+      <c r="A32" s="41" t="n">
         <v>0.8</v>
       </c>
-      <c r="B32" s="25" t="n">
+      <c r="B32" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(B$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>5296.14</v>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(C$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>11236.14</v>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D32" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(D$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>15196.14</v>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E32" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(E$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>21136.14</v>
       </c>
-      <c r="F32" s="25" t="n">
+      <c r="F32" s="26" t="n">
         <f aca="false">Inputs!$B$13*((1-$A32)*'Unit Economics'!$B$44+$A32*(F$27*(1-Inputs!$B$23)+Inputs!$B$21*(Inputs!$B$11*(1-Inputs!$B$12)-'Unit Economics'!$B$42-'Unit Economics'!$B$43)))-'Unit Economics'!$B$50</f>
         <v>25096.14</v>
       </c>
@@ -6212,355 +6415,355 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+        <v>231</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="A2" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>137</v>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="23" t="n">
-        <f aca="false">Inputs!B82</f>
+        <v>233</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <f aca="false">Inputs!B84</f>
         <v>1</v>
       </c>
-      <c r="C5" s="23" t="n">
-        <f aca="false">Inputs!C82</f>
+      <c r="C5" s="24" t="n">
+        <f aca="false">Inputs!C84</f>
         <v>1</v>
       </c>
-      <c r="D5" s="23" t="n">
-        <f aca="false">Inputs!D82</f>
+      <c r="D5" s="24" t="n">
+        <f aca="false">Inputs!D84</f>
         <v>2</v>
       </c>
-      <c r="E5" s="23" t="n">
-        <f aca="false">Inputs!E82</f>
+      <c r="E5" s="24" t="n">
+        <f aca="false">Inputs!E84</f>
         <v>4</v>
       </c>
-      <c r="F5" s="23" t="n">
-        <f aca="false">Inputs!F82</f>
+      <c r="F5" s="24" t="n">
+        <f aca="false">Inputs!F84</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="24" t="n">
+        <v>234</v>
+      </c>
+      <c r="B6" s="25" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">B5</f>
         <v>1</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="25" t="n">
         <f aca="false">C5</f>
         <v>1</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="25" t="n">
         <f aca="false">D5</f>
         <v>2</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="25" t="n">
         <f aca="false">E5</f>
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="24" t="n">
+        <v>235</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <f aca="false">B7+B6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="25" t="n">
         <f aca="false">C7+C6</f>
         <v>1</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">D7+D6</f>
         <v>2</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="25" t="n">
         <f aca="false">E7+E6</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="24" t="n">
+        <v>236</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <f aca="false">B5+B6+B7</f>
         <v>1</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <f aca="false">C5+C6+C7</f>
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="25" t="n">
         <f aca="false">D5+D6+D7</f>
         <v>4</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="25" t="n">
         <f aca="false">E5+E6+E7</f>
         <v>8</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="25" t="n">
         <f aca="false">F5+F6+F7</f>
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="25" t="n">
+        <v>155</v>
+      </c>
+      <c r="B9" s="26" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C6:N6)+B6*SUM('36-Month Ramp'!O6:Z6)+B7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>650484.582785269</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C6:N6)+C6*SUM('36-Month Ramp'!O6:Z6)+C7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>1736211.70194266</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C6:N6)+D6*SUM('36-Month Ramp'!O6:Z6)+D7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>3480844.28472793</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C6:N6)+E6*SUM('36-Month Ramp'!O6:Z6)+E7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>6961688.56945586</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C6:N6)+F6*SUM('36-Month Ramp'!O6:Z6)+F7*SUM('36-Month Ramp'!AA6:AL6)</f>
         <v>12622407.9733412</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="25" t="n">
+        <v>237</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <f aca="false">B5*SUM('36-Month Ramp'!C10:N10)+B6*SUM('36-Month Ramp'!O10:Z10)+B7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>14638.4670017109</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <f aca="false">C5*SUM('36-Month Ramp'!C10:N10)+C6*SUM('36-Month Ramp'!O10:Z10)+C7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>264958.324968404</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <f aca="false">D5*SUM('36-Month Ramp'!C10:N10)+D6*SUM('36-Month Ramp'!O10:Z10)+D7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>534807.431970115</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <f aca="false">E5*SUM('36-Month Ramp'!C10:N10)+E6*SUM('36-Month Ramp'!O10:Z10)+E7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>1069614.86394023</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <f aca="false">F5*SUM('36-Month Ramp'!C10:N10)+F6*SUM('36-Month Ramp'!O10:Z10)+F7*SUM('36-Month Ramp'!AA10:AL10)</f>
         <v>2109952.79387704</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B11" s="25" t="n">
-        <f aca="false">-Inputs!B83</f>
+        <v>238</v>
+      </c>
+      <c r="B11" s="26" t="n">
+        <f aca="false">-Inputs!B85</f>
         <v>-150000</v>
       </c>
-      <c r="C11" s="25" t="n">
-        <f aca="false">-Inputs!C83</f>
+      <c r="C11" s="26" t="n">
+        <f aca="false">-Inputs!C85</f>
         <v>-400000</v>
       </c>
-      <c r="D11" s="25" t="n">
-        <f aca="false">-Inputs!D83</f>
+      <c r="D11" s="26" t="n">
+        <f aca="false">-Inputs!D85</f>
         <v>-800000</v>
       </c>
-      <c r="E11" s="25" t="n">
-        <f aca="false">-Inputs!E83</f>
+      <c r="E11" s="26" t="n">
+        <f aca="false">-Inputs!E85</f>
         <v>-1400000</v>
       </c>
-      <c r="F11" s="25" t="n">
-        <f aca="false">-Inputs!F83</f>
+      <c r="F11" s="26" t="n">
+        <f aca="false">-Inputs!F85</f>
         <v>-2200000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B12" s="27" t="n">
+        <v>239</v>
+      </c>
+      <c r="B12" s="28" t="n">
         <f aca="false">B10+B11</f>
         <v>-135361.532998289</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="28" t="n">
         <f aca="false">C10+C11</f>
         <v>-135041.675031596</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="28" t="n">
         <f aca="false">D10+D11</f>
         <v>-265192.568029885</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="28" t="n">
         <f aca="false">E10+E11</f>
         <v>-330385.13605977</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="28" t="n">
         <f aca="false">F10+F11</f>
         <v>-90047.2061229609</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B13" s="25" t="n">
+        <v>240</v>
+      </c>
+      <c r="B13" s="26" t="n">
         <f aca="false">-B5*'Unit Economics'!$B$69</f>
         <v>-232000</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <f aca="false">-C5*'Unit Economics'!$B$69</f>
         <v>-232000</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">-D5*'Unit Economics'!$B$69</f>
         <v>-464000</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">-E5*'Unit Economics'!$B$69</f>
         <v>-928000</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <f aca="false">-F5*'Unit Economics'!$B$69</f>
         <v>-1392000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="25" t="n">
+        <v>241</v>
+      </c>
+      <c r="B14" s="26" t="n">
         <f aca="false">B12+B13</f>
         <v>-367361.532998289</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="26" t="n">
         <f aca="false">C12+C13</f>
         <v>-367041.675031596</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="26" t="n">
         <f aca="false">D12+D13</f>
         <v>-729192.568029885</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <f aca="false">E12+E13</f>
         <v>-1258385.13605977</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="26" t="n">
         <f aca="false">F12+F13</f>
         <v>-1482047.20612296</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="27" t="n">
+        <v>217</v>
+      </c>
+      <c r="B15" s="28" t="n">
         <f aca="false">B14</f>
         <v>-367361.532998289</v>
       </c>
-      <c r="C15" s="27" t="n">
+      <c r="C15" s="28" t="n">
         <f aca="false">B15+C14</f>
         <v>-734403.208029885</v>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="28" t="n">
         <f aca="false">C15+D14</f>
         <v>-1463595.77605977</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="28" t="n">
         <f aca="false">D15+E14</f>
         <v>-2721980.91211954</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="28" t="n">
         <f aca="false">E15+F14</f>
         <v>-4204028.1182425</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B17" s="41" t="n">
+        <v>242</v>
+      </c>
+      <c r="B17" s="42" t="n">
         <f aca="false">-MIN(0,MIN(B15:F15))</f>
         <v>4204028.1182425</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="A18" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6578,322 +6781,403 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
+        <v>244</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="A2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
+      <c r="A4" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="34" t="n">
-        <f aca="false">'Unit Economics'!$B$66</f>
-        <v>72000</v>
-      </c>
-      <c r="C5" s="6"/>
+        <v>247</v>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="34" t="n">
-        <f aca="false">'Unit Economics'!$B$67</f>
-        <v>90000</v>
-      </c>
-      <c r="C6" s="6"/>
+        <v>249</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="34" t="n">
-        <f aca="false">'Unit Economics'!$B$68</f>
-        <v>70000</v>
-      </c>
-      <c r="C7" s="6"/>
+        <v>251</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" s="25" t="n">
-        <f aca="false">MAX(0,-'36-Month Ramp'!$B$17-'Unit Economics'!$B$69)</f>
-        <v>174223.78080361</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>243</v>
+        <v>253</v>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" s="17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>245</v>
+        <v>254</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="25" t="n">
-        <f aca="false">SUM($B$5:$B$8)*$B$9</f>
-        <v>81244.7561607221</v>
-      </c>
-      <c r="C10" s="6"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="27" t="n">
-        <f aca="false">SUM($B$5:$B$8)+$B$10</f>
-        <v>487468.536964332</v>
-      </c>
-      <c r="C11" s="6"/>
+      <c r="A11" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
+      <c r="A12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
+      <c r="A13" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>250</v>
+        <v>259</v>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>252</v>
+        <v>261</v>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>254</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="B16" s="26" t="n">
+        <f aca="false">$B$12*$B$13</f>
+        <v>900</v>
+      </c>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B17" s="25" t="n">
-        <f aca="false">$B$15*$B$16*Inputs!$B$6</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>256</v>
+        <v>263</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <f aca="false">$B$8*($B$9+0.5)*Inputs!$B$38*(1+Inputs!$B$39)+$B$14+$B$12*$B$15+$B$16*Inputs!$B$12</f>
+        <v>976.95</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>258</v>
-      </c>
+      <c r="A18" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B18" s="28" t="n">
+        <f aca="false">$B$16-$B$17</f>
+        <v>-76.9499999999999</v>
+      </c>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>33</v>
-      </c>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>261</v>
-      </c>
+      <c r="A20" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B21" s="25" t="n">
-        <f aca="false">$B$18*$B$19*$B$20*Inputs!$B$20</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="6"/>
+        <v>267</v>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>264</v>
+        <v>269</v>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B23" s="27" t="n">
-        <f aca="false">MAX(0,$B$11-$B$14-$B$17-$B$21-$B$22)</f>
-        <v>437468.536964332</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>266</v>
+      <c r="A23" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" s="26" t="n">
+        <f aca="false">$B$8*($B$9-1+0.5)*Inputs!$B$38*(1+Inputs!$B$39)+$B$22*$B$15</f>
+        <v>530.85</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B24" s="27" t="n">
-        <f aca="false">$B$14+$B$17+$B$21+$B$22+$B$23</f>
-        <v>487468.536964332</v>
-      </c>
-      <c r="C24" s="6"/>
+        <v>273</v>
+      </c>
+      <c r="B24" s="28" t="n">
+        <f aca="false">$B$21-$B$23</f>
+        <v>469.15</v>
+      </c>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
+      <c r="A26" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B27" s="30" t="n">
-        <f aca="false">IF($B$11=0,0,($B$14+$B$23)/$B$11)</f>
-        <v>1</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>270</v>
+        <v>275</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B28" s="33" t="str">
-        <f aca="false">IF($B$27&gt;=0.1,"Yes","No")</f>
-        <v>Yes</v>
-      </c>
-      <c r="C28" s="6"/>
+      <c r="A28" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B29" s="17" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>273</v>
+        <v>278</v>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>33</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="B30" s="25" t="n">
+        <f aca="false">$B$5*$B$6</f>
+        <v>12</v>
+      </c>
+      <c r="C30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B31" s="25" t="n">
-        <f aca="false">IF($B$22=0,0,-PMT($B$29,$B$30,$B$22))</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="6"/>
+        <f aca="false">ROUND($B$5/52*12*$B$7,0)</f>
+        <v>6</v>
+      </c>
+      <c r="C31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B32" s="43" t="str">
-        <f aca="false">IF($B$31=0,"No loan",'Unit Economics'!$B$36/$B$31)</f>
-        <v>No loan</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>277</v>
+      <c r="A32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="26" t="n">
+        <f aca="false">$B$30*$B$16+$B$31*$B$21</f>
+        <v>16800</v>
+      </c>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" s="28" t="n">
+        <f aca="false">$B$30*$B$18+$B$31*$B$24-$B$27-($B$28+$B$29)*$B$5/52*12</f>
+        <v>-3046.96153846154</v>
+      </c>
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B39" s="32" t="n">
+        <f aca="false">ROUND($B$30*$B$12*$B$36+$B$31*$B$22*$B$37,0)</f>
+        <v>234</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B40" s="32" t="n">
+        <f aca="false">ROUND($B$31*$B$38,0)</f>
+        <v>2</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B41" s="32" t="n">
+        <f aca="false">$B$30*$B$12+$B$31*$B$22</f>
+        <v>576</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -6912,6 +7196,352 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="35" t="n">
+        <f aca="false">'Unit Economics'!$B$66</f>
+        <v>72000</v>
+      </c>
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="35" t="n">
+        <f aca="false">'Unit Economics'!$B$67</f>
+        <v>90000</v>
+      </c>
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="35" t="n">
+        <f aca="false">'Unit Economics'!$B$68</f>
+        <v>70000</v>
+      </c>
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" s="26" t="n">
+        <f aca="false">MAX(0,-'36-Month Ramp'!$B$17-'Unit Economics'!$B$69)</f>
+        <v>141640.447470277</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B9" s="35" t="n">
+        <f aca="false">MAX(0,-'Pop-Ups'!$B$33)</f>
+        <v>3046.96153846154</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B11" s="26" t="n">
+        <f aca="false">SUM($B$5:$B$9)*$B$10</f>
+        <v>75337.4818017477</v>
+      </c>
+      <c r="C11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="28" t="n">
+        <f aca="false">SUM($B$5:$B$9)+$B$11</f>
+        <v>452024.890810486</v>
+      </c>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="26" t="n">
+        <f aca="false">$B$16*$B$17*Inputs!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B22" s="26" t="n">
+        <f aca="false">$B$19*$B$20*$B$21*Inputs!$B$20</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B24" s="28" t="n">
+        <f aca="false">MAX(0,$B$12-$B$15-$B$18-$B$22-$B$23)</f>
+        <v>402024.890810486</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B25" s="28" t="n">
+        <f aca="false">$B$15+$B$18+$B$22+$B$23+$B$24</f>
+        <v>452024.890810486</v>
+      </c>
+      <c r="C25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" s="31" t="n">
+        <f aca="false">IF($B$12=0,0,($B$15+$B$24)/$B$12)</f>
+        <v>1</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B29" s="34" t="str">
+        <f aca="false">IF($B$28&gt;=0.1,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B32" s="26" t="n">
+        <f aca="false">IF($B$23=0,0,-PMT($B$30,$B$31,$B$23))</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B33" s="44" t="str">
+        <f aca="false">IF($B$32=0,"No loan",'Unit Economics'!$B$36/$B$32)</f>
+        <v>No loan</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6920,7 +7550,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6928,57 +7558,57 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>280</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>281</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>283</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>285</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>287</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>288</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>289</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6986,7 +7616,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>290</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
